--- a/files/data.xlsx
+++ b/files/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/totoferro21/Desktop/salvatore non toccare/monitoraggio/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AC354F2-E231-F147-9207-95D738D22D89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC40B8FF-3A9D-D943-A657-2755AC186025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1600" yWindow="500" windowWidth="10000" windowHeight="16320" xr2:uid="{F1546C66-1100-0F4C-AEC5-783BC2578DB8}"/>
+    <workbookView xWindow="1600" yWindow="500" windowWidth="10000" windowHeight="16320" activeTab="1" xr2:uid="{F1546C66-1100-0F4C-AEC5-783BC2578DB8}"/>
   </bookViews>
   <sheets>
     <sheet name="vix" sheetId="2" r:id="rId1"/>
@@ -5050,29 +5050,59 @@
       </c>
     </row>
     <row r="416" spans="1:3" ht="24" x14ac:dyDescent="0.2">
-      <c r="A416" s="4"/>
-      <c r="B416" s="5"/>
-      <c r="C416" s="6"/>
+      <c r="A416" s="4">
+        <v>46076</v>
+      </c>
+      <c r="B416" s="5">
+        <v>60.832857565733235</v>
+      </c>
+      <c r="C416" s="6">
+        <v>21.01</v>
+      </c>
     </row>
     <row r="417" spans="1:3" ht="24" x14ac:dyDescent="0.2">
-      <c r="A417" s="4"/>
-      <c r="B417" s="5"/>
-      <c r="C417" s="6"/>
+      <c r="A417" s="4">
+        <v>46077</v>
+      </c>
+      <c r="B417" s="5">
+        <v>60.046295097449452</v>
+      </c>
+      <c r="C417" s="6">
+        <v>19.55</v>
+      </c>
     </row>
     <row r="418" spans="1:3" ht="24" x14ac:dyDescent="0.2">
-      <c r="A418" s="4"/>
-      <c r="B418" s="5"/>
-      <c r="C418" s="6"/>
+      <c r="A418" s="4">
+        <v>46078</v>
+      </c>
+      <c r="B418" s="5">
+        <v>59.226899670105595</v>
+      </c>
+      <c r="C418" s="6">
+        <v>18.02</v>
+      </c>
     </row>
     <row r="419" spans="1:3" ht="24" x14ac:dyDescent="0.2">
-      <c r="A419" s="4"/>
-      <c r="B419" s="5"/>
-      <c r="C419" s="6"/>
+      <c r="A419" s="4">
+        <v>46079</v>
+      </c>
+      <c r="B419" s="5">
+        <v>59.003082189650947</v>
+      </c>
+      <c r="C419" s="6">
+        <v>18.63</v>
+      </c>
     </row>
     <row r="420" spans="1:3" ht="24" x14ac:dyDescent="0.2">
-      <c r="A420" s="4"/>
-      <c r="B420" s="5"/>
-      <c r="C420" s="6"/>
+      <c r="A420" s="4">
+        <v>46080</v>
+      </c>
+      <c r="B420" s="5">
+        <v>59.636759066130473</v>
+      </c>
+      <c r="C420" s="6">
+        <v>19.86</v>
+      </c>
     </row>
     <row r="421" spans="1:3" ht="24" x14ac:dyDescent="0.2">
       <c r="A421" s="4"/>
@@ -9797,29 +9827,59 @@
       </c>
     </row>
     <row r="416" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A416" s="4"/>
-      <c r="B416" s="5"/>
-      <c r="C416" s="5"/>
+      <c r="A416" s="4">
+        <v>46076</v>
+      </c>
+      <c r="B416" s="5">
+        <v>60.832857565733235</v>
+      </c>
+      <c r="C416" s="5">
+        <v>41.065992498526946</v>
+      </c>
     </row>
     <row r="417" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A417" s="4"/>
-      <c r="B417" s="5"/>
-      <c r="C417" s="5"/>
+      <c r="A417" s="4">
+        <v>46077</v>
+      </c>
+      <c r="B417" s="5">
+        <v>60.046295097449452</v>
+      </c>
+      <c r="C417" s="5">
+        <v>41.825706081441119</v>
+      </c>
     </row>
     <row r="418" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A418" s="4"/>
-      <c r="B418" s="5"/>
-      <c r="C418" s="5"/>
+      <c r="A418" s="4">
+        <v>46078</v>
+      </c>
+      <c r="B418" s="5">
+        <v>59.226899670105595</v>
+      </c>
+      <c r="C418" s="5">
+        <v>42.633587274212715</v>
+      </c>
     </row>
     <row r="419" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A419" s="4"/>
-      <c r="B419" s="5"/>
-      <c r="C419" s="5"/>
+      <c r="A419" s="4">
+        <v>46079</v>
+      </c>
+      <c r="B419" s="5">
+        <v>59.003082189650947</v>
+      </c>
+      <c r="C419" s="5">
+        <v>42.060808821072911</v>
+      </c>
     </row>
     <row r="420" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A420" s="4"/>
-      <c r="B420" s="5"/>
-      <c r="C420" s="5"/>
+      <c r="A420" s="4">
+        <v>46080</v>
+      </c>
+      <c r="B420" s="5">
+        <v>59.636759066130473</v>
+      </c>
+      <c r="C420" s="5">
+        <v>41.611825519220965</v>
+      </c>
     </row>
     <row r="421" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A421" s="4"/>

--- a/files/data.xlsx
+++ b/files/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11008"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/totoferro21/Desktop/salvatore non toccare/monitoraggio/files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ferrara/Desktop/salvatore non toccare/monitoraggio/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC40B8FF-3A9D-D943-A657-2755AC186025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F8BE0E8-D187-B646-A211-3D442B74995E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1600" yWindow="500" windowWidth="10000" windowHeight="16320" activeTab="1" xr2:uid="{F1546C66-1100-0F4C-AEC5-783BC2578DB8}"/>
+    <workbookView xWindow="1600" yWindow="600" windowWidth="10000" windowHeight="16320" xr2:uid="{F1546C66-1100-0F4C-AEC5-783BC2578DB8}"/>
   </bookViews>
   <sheets>
     <sheet name="vix" sheetId="2" r:id="rId1"/>
@@ -54,7 +54,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -143,7 +143,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -476,7 +476,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2D1AE83-71FF-D646-9DA6-2F2BACDC27FF}">
   <dimension ref="A1:C448"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="15.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.5" style="1" bestFit="1" customWidth="1"/>
@@ -484,7 +484,7 @@
     <col min="4" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="40" customHeight="1">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -495,7 +495,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="40" customHeight="1">
       <c r="A2" s="4">
         <v>45138</v>
       </c>
@@ -506,7 +506,7 @@
         <v>14.45</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" ht="40" customHeight="1">
       <c r="A3" s="4">
         <v>45140</v>
       </c>
@@ -517,7 +517,7 @@
         <v>17.13</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" ht="40" customHeight="1">
       <c r="A4" s="4">
         <v>45146</v>
       </c>
@@ -528,7 +528,7 @@
         <v>18.329999999999998</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" ht="40" customHeight="1">
       <c r="A5" s="4">
         <v>45154</v>
       </c>
@@ -539,7 +539,7 @@
         <v>17.829999999999998</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" ht="40" customHeight="1">
       <c r="A6" s="4">
         <v>45162</v>
       </c>
@@ -550,7 +550,7 @@
         <v>17.73</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" ht="40" customHeight="1">
       <c r="A7" s="4">
         <v>45166</v>
       </c>
@@ -561,7 +561,7 @@
         <v>16.829999999999998</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" ht="40" customHeight="1">
       <c r="A8" s="4">
         <v>45167</v>
       </c>
@@ -572,7 +572,7 @@
         <v>16.38</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" ht="40" customHeight="1">
       <c r="A9" s="4">
         <v>45168</v>
       </c>
@@ -583,7 +583,7 @@
         <v>15.88</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" ht="40" customHeight="1">
       <c r="A10" s="4">
         <v>45176</v>
       </c>
@@ -594,7 +594,7 @@
         <v>15.73</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" ht="40" customHeight="1">
       <c r="A11" s="4">
         <v>45183</v>
       </c>
@@ -605,7 +605,7 @@
         <v>13.58</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" ht="40" customHeight="1">
       <c r="A12" s="4">
         <v>45184</v>
       </c>
@@ -616,7 +616,7 @@
         <v>13.83</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" ht="40" customHeight="1">
       <c r="A13" s="4">
         <v>45188</v>
       </c>
@@ -627,7 +627,7 @@
         <v>15.93</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" ht="40" customHeight="1">
       <c r="A14" s="4">
         <v>45190</v>
       </c>
@@ -638,7 +638,7 @@
         <v>17.13</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" ht="40" customHeight="1">
       <c r="A15" s="4">
         <v>45191</v>
       </c>
@@ -649,7 +649,7 @@
         <v>16.829999999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" ht="40" customHeight="1">
       <c r="A16" s="4">
         <v>45195</v>
       </c>
@@ -660,7 +660,7 @@
         <v>17.93</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" ht="40" customHeight="1">
       <c r="A17" s="4">
         <v>45196</v>
       </c>
@@ -671,7 +671,7 @@
         <v>19.03</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" ht="40" customHeight="1">
       <c r="A18" s="4">
         <v>45197</v>
       </c>
@@ -682,7 +682,7 @@
         <v>17.43</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" ht="40" customHeight="1">
       <c r="A19" s="4">
         <v>45201</v>
       </c>
@@ -693,7 +693,7 @@
         <v>17.73</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" ht="40" customHeight="1">
       <c r="A20" s="4">
         <v>45202</v>
       </c>
@@ -704,7 +704,7 @@
         <v>19.23</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" ht="40" customHeight="1">
       <c r="A21" s="4">
         <v>45205</v>
       </c>
@@ -715,7 +715,7 @@
         <v>17.78</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" ht="40" customHeight="1">
       <c r="A22" s="4">
         <v>45209</v>
       </c>
@@ -726,7 +726,7 @@
         <v>16.88</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" ht="40" customHeight="1">
       <c r="A23" s="4">
         <v>45212</v>
       </c>
@@ -737,7 +737,7 @@
         <v>18.43</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" ht="40" customHeight="1">
       <c r="A24" s="4">
         <v>45216</v>
       </c>
@@ -748,7 +748,7 @@
         <v>17.829999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" ht="40" customHeight="1">
       <c r="A25" s="4">
         <v>45217</v>
       </c>
@@ -759,7 +759,7 @@
         <v>19.329999999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" ht="40" customHeight="1">
       <c r="A26" s="4">
         <v>45219</v>
       </c>
@@ -770,7 +770,7 @@
         <v>20.88</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" ht="40" customHeight="1">
       <c r="A27" s="4">
         <v>45225</v>
       </c>
@@ -781,7 +781,7 @@
         <v>20.66</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" ht="40" customHeight="1">
       <c r="A28" s="4">
         <v>45231</v>
       </c>
@@ -792,7 +792,7 @@
         <v>17.93</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" ht="40" customHeight="1">
       <c r="A29" s="4">
         <v>45232</v>
       </c>
@@ -803,7 +803,7 @@
         <v>17.03</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" ht="40" customHeight="1">
       <c r="A30" s="4">
         <v>45233</v>
       </c>
@@ -814,7 +814,7 @@
         <v>16.079999999999998</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" ht="40" customHeight="1">
       <c r="A31" s="4">
         <v>45237</v>
       </c>
@@ -825,7 +825,7 @@
         <v>15.63</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" ht="40" customHeight="1">
       <c r="A32" s="4">
         <v>45243</v>
       </c>
@@ -836,7 +836,7 @@
         <v>15.88</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" ht="40" customHeight="1">
       <c r="A33" s="4">
         <v>45244</v>
       </c>
@@ -847,7 +847,7 @@
         <v>15.55</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" ht="40" customHeight="1">
       <c r="A34" s="4">
         <v>45246</v>
       </c>
@@ -858,7 +858,7 @@
         <v>15.33</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" ht="40" customHeight="1">
       <c r="A35" s="4">
         <v>45252</v>
       </c>
@@ -869,7 +869,7 @@
         <v>14.43</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" ht="40" customHeight="1">
       <c r="A36" s="4">
         <v>45260</v>
       </c>
@@ -880,7 +880,7 @@
         <v>14.03</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" ht="40" customHeight="1">
       <c r="A37" s="4">
         <v>45271</v>
       </c>
@@ -891,7 +891,7 @@
         <v>13.04</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" ht="40" customHeight="1">
       <c r="A38" s="4">
         <v>45274</v>
       </c>
@@ -902,7 +902,7 @@
         <v>12.23</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" ht="40" customHeight="1">
       <c r="A39" s="4">
         <v>45279</v>
       </c>
@@ -913,7 +913,7 @@
         <v>14.73</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:3" ht="40" customHeight="1">
       <c r="A40" s="4">
         <v>45281</v>
       </c>
@@ -924,7 +924,7 @@
         <v>15.88</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:3" ht="40" customHeight="1">
       <c r="A41" s="4">
         <v>45282</v>
       </c>
@@ -935,7 +935,7 @@
         <v>15.33</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:3" ht="40" customHeight="1">
       <c r="A42" s="4">
         <v>45294</v>
       </c>
@@ -946,7 +946,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:3" ht="40" customHeight="1">
       <c r="A43" s="4">
         <v>45301</v>
       </c>
@@ -957,7 +957,7 @@
         <v>13.43</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:3" ht="40" customHeight="1">
       <c r="A44" s="4">
         <v>45308</v>
       </c>
@@ -968,7 +968,7 @@
         <v>15.43</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:3" ht="40" customHeight="1">
       <c r="A45" s="4">
         <v>45309</v>
       </c>
@@ -979,7 +979,7 @@
         <v>15.04</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:3" ht="40" customHeight="1">
       <c r="A46" s="4">
         <v>45310</v>
       </c>
@@ -990,7 +990,7 @@
         <v>14.63</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:3" ht="40" customHeight="1">
       <c r="A47" s="4">
         <v>45313</v>
       </c>
@@ -1001,7 +1001,7 @@
         <v>14.48</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:3" ht="40" customHeight="1">
       <c r="A48" s="4">
         <v>45314</v>
       </c>
@@ -1012,7 +1012,7 @@
         <v>13.83</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:3" ht="40" customHeight="1">
       <c r="A49" s="4">
         <v>45315</v>
       </c>
@@ -1023,7 +1023,7 @@
         <v>13.63</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:3" ht="40" customHeight="1">
       <c r="A50" s="4">
         <v>45321</v>
       </c>
@@ -1034,7 +1034,7 @@
         <v>14.13</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:3" ht="40" customHeight="1">
       <c r="A51" s="4">
         <v>45322</v>
       </c>
@@ -1045,7 +1045,7 @@
         <v>14.63</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:3" ht="40" customHeight="1">
       <c r="A52" s="4">
         <v>45324</v>
       </c>
@@ -1056,7 +1056,7 @@
         <v>14.42</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:3" ht="40" customHeight="1">
       <c r="A53" s="4">
         <v>45330</v>
       </c>
@@ -1067,7 +1067,7 @@
         <v>13.43</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:3" ht="40" customHeight="1">
       <c r="A54" s="4">
         <v>45334</v>
       </c>
@@ -1078,7 +1078,7 @@
         <v>14.74</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:3" ht="40" customHeight="1">
       <c r="A55" s="4">
         <v>45335</v>
       </c>
@@ -1089,7 +1089,7 @@
         <v>15.38</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:3" ht="40" customHeight="1">
       <c r="A56" s="4">
         <v>45337</v>
       </c>
@@ -1100,7 +1100,7 @@
         <v>15.13</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:3" ht="40" customHeight="1">
       <c r="A57" s="4">
         <v>45342</v>
       </c>
@@ -1111,7 +1111,7 @@
         <v>15.58</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:3" ht="40" customHeight="1">
       <c r="A58" s="4">
         <v>45344</v>
       </c>
@@ -1122,7 +1122,7 @@
         <v>14.67</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:3" ht="40" customHeight="1">
       <c r="A59" s="4">
         <v>45345</v>
       </c>
@@ -1133,7 +1133,7 @@
         <v>14.73</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:3" ht="40" customHeight="1">
       <c r="A60" s="4">
         <v>45355</v>
       </c>
@@ -1144,7 +1144,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:3" ht="40" customHeight="1">
       <c r="A61" s="4">
         <v>45356</v>
       </c>
@@ -1155,7 +1155,7 @@
         <v>14.73</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:3" ht="40" customHeight="1">
       <c r="A62" s="4">
         <v>45357</v>
       </c>
@@ -1166,7 +1166,7 @@
         <v>14.68</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:3" ht="40" customHeight="1">
       <c r="A63" s="4">
         <v>45359</v>
       </c>
@@ -1177,7 +1177,7 @@
         <v>14.37</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:3" ht="40" customHeight="1">
       <c r="A64" s="4">
         <v>45362</v>
       </c>
@@ -1188,7 +1188,7 @@
         <v>15.18</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:3" ht="40" customHeight="1">
       <c r="A65" s="4">
         <v>45363</v>
       </c>
@@ -1199,7 +1199,7 @@
         <v>14.08</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:3" ht="40" customHeight="1">
       <c r="A66" s="4">
         <v>45366</v>
       </c>
@@ -1210,7 +1210,7 @@
         <v>14.78</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:3" ht="40" customHeight="1">
       <c r="A67" s="4">
         <v>45370</v>
       </c>
@@ -1221,7 +1221,7 @@
         <v>14.98</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:3" ht="40" customHeight="1">
       <c r="A68" s="4">
         <v>45372</v>
       </c>
@@ -1232,7 +1232,7 @@
         <v>14.53</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:3" ht="40" customHeight="1">
       <c r="A69" s="4">
         <v>45384</v>
       </c>
@@ -1243,7 +1243,7 @@
         <v>15.43</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:3" ht="40" customHeight="1">
       <c r="A70" s="4">
         <v>45386</v>
       </c>
@@ -1254,7 +1254,7 @@
         <v>14.58</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:3" ht="40" customHeight="1">
       <c r="A71" s="4">
         <v>45387</v>
       </c>
@@ -1265,7 +1265,7 @@
         <v>15.78</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:3" ht="40" customHeight="1">
       <c r="A72" s="4">
         <v>45393</v>
       </c>
@@ -1276,7 +1276,7 @@
         <v>15.97</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:3" ht="40" customHeight="1">
       <c r="A73" s="4">
         <v>45394</v>
       </c>
@@ -1287,7 +1287,7 @@
         <v>17.23</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:3" ht="40" customHeight="1">
       <c r="A74" s="4">
         <v>45398</v>
       </c>
@@ -1298,7 +1298,7 @@
         <v>18.329999999999998</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:3" ht="40" customHeight="1">
       <c r="A75" s="4">
         <v>45404</v>
       </c>
@@ -1309,7 +1309,7 @@
         <v>16.940000000000001</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:3" ht="40" customHeight="1">
       <c r="A76" s="4">
         <v>45405</v>
       </c>
@@ -1320,7 +1320,7 @@
         <v>15.98</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:3" ht="40" customHeight="1">
       <c r="A77" s="4">
         <v>45407</v>
       </c>
@@ -1331,7 +1331,7 @@
         <v>16.63</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:3" ht="40" customHeight="1">
       <c r="A78" s="4">
         <v>45408</v>
       </c>
@@ -1342,7 +1342,7 @@
         <v>15.54</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:3" ht="40" customHeight="1">
       <c r="A79" s="4">
         <v>45413</v>
       </c>
@@ -1353,7 +1353,7 @@
         <v>15.35</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:3" ht="40" customHeight="1">
       <c r="A80" s="4">
         <v>45415</v>
       </c>
@@ -1364,7 +1364,7 @@
         <v>14.73</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:3" ht="40" customHeight="1">
       <c r="A81" s="4">
         <v>45418</v>
       </c>
@@ -1375,7 +1375,7 @@
         <v>14.33</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:3" ht="40" customHeight="1">
       <c r="A82" s="4">
         <v>45419</v>
       </c>
@@ -1386,7 +1386,7 @@
         <v>14.18</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:3" ht="40" customHeight="1">
       <c r="A83" s="4">
         <v>45422</v>
       </c>
@@ -1397,7 +1397,7 @@
         <v>13.83</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:3" ht="40" customHeight="1">
       <c r="A84" s="4">
         <v>45427</v>
       </c>
@@ -1408,7 +1408,7 @@
         <v>13.18</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:3" ht="40" customHeight="1">
       <c r="A85" s="4">
         <v>45428</v>
       </c>
@@ -1419,7 +1419,7 @@
         <v>12.88</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:3" ht="40" customHeight="1">
       <c r="A86" s="4">
         <v>45443</v>
       </c>
@@ -1430,7 +1430,7 @@
         <v>14.23</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:3" ht="40" customHeight="1">
       <c r="A87" s="4">
         <v>45446</v>
       </c>
@@ -1441,7 +1441,7 @@
         <v>13.88</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:3" ht="40" customHeight="1">
       <c r="A88" s="4">
         <v>45448</v>
       </c>
@@ -1452,7 +1452,7 @@
         <v>13.47</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:3" ht="40" customHeight="1">
       <c r="A89" s="4">
         <v>45449</v>
       </c>
@@ -1463,7 +1463,7 @@
         <v>13.28</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:3" ht="40" customHeight="1">
       <c r="A90" s="4">
         <v>45455</v>
       </c>
@@ -1474,7 +1474,7 @@
         <v>12.64</v>
       </c>
     </row>
-    <row r="91" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:3" ht="40" customHeight="1">
       <c r="A91" s="4">
         <v>45463</v>
       </c>
@@ -1485,7 +1485,7 @@
         <v>14.48</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:3" ht="40" customHeight="1">
       <c r="A92" s="4">
         <v>45471</v>
       </c>
@@ -1496,7 +1496,7 @@
         <v>14.48</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:3" ht="40" customHeight="1">
       <c r="A93" s="4">
         <v>45474</v>
       </c>
@@ -1507,7 +1507,7 @@
         <v>13.87</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:3" ht="40" customHeight="1">
       <c r="A94" s="4">
         <v>45476</v>
       </c>
@@ -1518,7 +1518,7 @@
         <v>13.18</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:3" ht="40" customHeight="1">
       <c r="A95" s="4">
         <v>45481</v>
       </c>
@@ -1529,7 +1529,7 @@
         <v>13.03</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:3" ht="40" customHeight="1">
       <c r="A96" s="4">
         <v>45484</v>
       </c>
@@ -1540,7 +1540,7 @@
         <v>12.98</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:3" ht="40" customHeight="1">
       <c r="A97" s="4">
         <v>45491</v>
       </c>
@@ -1551,7 +1551,7 @@
         <v>15.28</v>
       </c>
     </row>
-    <row r="98" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:3" ht="40" customHeight="1">
       <c r="A98" s="4">
         <v>45497</v>
       </c>
@@ -1562,7 +1562,7 @@
         <v>16.079999999999998</v>
       </c>
     </row>
-    <row r="99" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:3" ht="40" customHeight="1">
       <c r="A99" s="4">
         <v>45503</v>
       </c>
@@ -1573,7 +1573,7 @@
         <v>16.63</v>
       </c>
     </row>
-    <row r="100" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:3" ht="40" customHeight="1">
       <c r="A100" s="4">
         <v>45504</v>
       </c>
@@ -1584,7 +1584,7 @@
         <v>15.73</v>
       </c>
     </row>
-    <row r="101" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:3" ht="40" customHeight="1">
       <c r="A101" s="4">
         <v>45505</v>
       </c>
@@ -1595,7 +1595,7 @@
         <v>16.98</v>
       </c>
     </row>
-    <row r="102" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:3" ht="40" customHeight="1">
       <c r="A102" s="4">
         <v>45506</v>
       </c>
@@ -1606,7 +1606,7 @@
         <v>19.329999999999998</v>
       </c>
     </row>
-    <row r="103" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:3" ht="40" customHeight="1">
       <c r="A103" s="4">
         <v>45509</v>
       </c>
@@ -1617,7 +1617,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="104" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:3" ht="40" customHeight="1">
       <c r="A104" s="4">
         <v>45510</v>
       </c>
@@ -1628,7 +1628,7 @@
         <v>25.03</v>
       </c>
     </row>
-    <row r="105" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:3" ht="40" customHeight="1">
       <c r="A105" s="4">
         <v>45517</v>
       </c>
@@ -1639,7 +1639,7 @@
         <v>18.48</v>
       </c>
     </row>
-    <row r="106" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:3" ht="40" customHeight="1">
       <c r="A106" s="4">
         <v>45518</v>
       </c>
@@ -1650,7 +1650,7 @@
         <v>16.68</v>
       </c>
     </row>
-    <row r="107" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:3" ht="40" customHeight="1">
       <c r="A107" s="4">
         <v>45519</v>
       </c>
@@ -1661,7 +1661,7 @@
         <v>15.13</v>
       </c>
     </row>
-    <row r="108" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:3" ht="40" customHeight="1">
       <c r="A108" s="4">
         <v>45523</v>
       </c>
@@ -1672,7 +1672,7 @@
         <v>15.33</v>
       </c>
     </row>
-    <row r="109" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:3" ht="40" customHeight="1">
       <c r="A109" s="4">
         <v>45525</v>
       </c>
@@ -1683,7 +1683,7 @@
         <v>16.34</v>
       </c>
     </row>
-    <row r="110" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:3" ht="40" customHeight="1">
       <c r="A110" s="4">
         <v>45533</v>
       </c>
@@ -1694,7 +1694,7 @@
         <v>15.78</v>
       </c>
     </row>
-    <row r="111" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:3" ht="40" customHeight="1">
       <c r="A111" s="4">
         <v>45538</v>
       </c>
@@ -1705,7 +1705,7 @@
         <v>17.25</v>
       </c>
     </row>
-    <row r="112" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:3" ht="40" customHeight="1">
       <c r="A112" s="4">
         <v>45539</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>18.760000000000002</v>
       </c>
     </row>
-    <row r="113" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:3" ht="40" customHeight="1">
       <c r="A113" s="4">
         <v>45540</v>
       </c>
@@ -1727,7 +1727,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="114" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:3" ht="40" customHeight="1">
       <c r="A114" s="4">
         <v>45541</v>
       </c>
@@ -1738,7 +1738,7 @@
         <v>20.89</v>
       </c>
     </row>
-    <row r="115" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:3" ht="40" customHeight="1">
       <c r="A115" s="4">
         <v>45544</v>
       </c>
@@ -1749,7 +1749,7 @@
         <v>18.899999999999999</v>
       </c>
     </row>
-    <row r="116" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:3" ht="40" customHeight="1">
       <c r="A116" s="4">
         <v>45546</v>
       </c>
@@ -1760,7 +1760,7 @@
         <v>19.62</v>
       </c>
     </row>
-    <row r="117" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:3" ht="40" customHeight="1">
       <c r="A117" s="4">
         <v>45547</v>
       </c>
@@ -1771,7 +1771,7 @@
         <v>17.45</v>
       </c>
     </row>
-    <row r="118" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:3" ht="40" customHeight="1">
       <c r="A118" s="4">
         <v>45548</v>
       </c>
@@ -1782,7 +1782,7 @@
         <v>16.399999999999999</v>
       </c>
     </row>
-    <row r="119" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:3" ht="40" customHeight="1">
       <c r="A119" s="4">
         <v>45554</v>
       </c>
@@ -1793,7 +1793,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="120" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:3" ht="40" customHeight="1">
       <c r="A120" s="4">
         <v>45562</v>
       </c>
@@ -1804,7 +1804,7 @@
         <v>18.45</v>
       </c>
     </row>
-    <row r="121" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:3" ht="40" customHeight="1">
       <c r="A121" s="4">
         <v>45566</v>
       </c>
@@ -1815,7 +1815,7 @@
         <v>20.3</v>
       </c>
     </row>
-    <row r="122" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:3" ht="40" customHeight="1">
       <c r="A122" s="4">
         <v>45573</v>
       </c>
@@ -1826,7 +1826,7 @@
         <v>21.35</v>
       </c>
     </row>
-    <row r="123" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:3" ht="40" customHeight="1">
       <c r="A123" s="4">
         <v>45574</v>
       </c>
@@ -1837,7 +1837,7 @@
         <v>20.85</v>
       </c>
     </row>
-    <row r="124" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:3" ht="40" customHeight="1">
       <c r="A124" s="4">
         <v>45576</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>21.07</v>
       </c>
     </row>
-    <row r="125" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:3" ht="40" customHeight="1">
       <c r="A125" s="4">
         <v>45579</v>
       </c>
@@ -1859,7 +1859,7 @@
         <v>20.149999999999999</v>
       </c>
     </row>
-    <row r="126" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:3" ht="40" customHeight="1">
       <c r="A126" s="4">
         <v>45589</v>
       </c>
@@ -1870,7 +1870,7 @@
         <v>19.440000000000001</v>
       </c>
     </row>
-    <row r="127" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:3" ht="40" customHeight="1">
       <c r="A127" s="4">
         <v>45590</v>
       </c>
@@ -1881,7 +1881,7 @@
         <v>18.510000000000002</v>
       </c>
     </row>
-    <row r="128" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:3" ht="40" customHeight="1">
       <c r="A128" s="4">
         <v>45596</v>
       </c>
@@ -1892,7 +1892,7 @@
         <v>20.78</v>
       </c>
     </row>
-    <row r="129" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:3" ht="40" customHeight="1">
       <c r="A129" s="4">
         <v>45601</v>
       </c>
@@ -1903,7 +1903,7 @@
         <v>18.53</v>
       </c>
     </row>
-    <row r="130" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:3" ht="40" customHeight="1">
       <c r="A130" s="4">
         <v>45602</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>16.43</v>
       </c>
     </row>
-    <row r="131" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:3" ht="40" customHeight="1">
       <c r="A131" s="4">
         <v>45603</v>
       </c>
@@ -1925,7 +1925,7 @@
         <v>15.73</v>
       </c>
     </row>
-    <row r="132" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:3" ht="40" customHeight="1">
       <c r="A132" s="4">
         <v>45611</v>
       </c>
@@ -1936,7 +1936,7 @@
         <v>16.399999999999999</v>
       </c>
     </row>
-    <row r="133" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:3" ht="40" customHeight="1">
       <c r="A133" s="4">
         <v>45615</v>
       </c>
@@ -1947,7 +1947,7 @@
         <v>16.18</v>
       </c>
     </row>
-    <row r="134" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:3" ht="40" customHeight="1">
       <c r="A134" s="4">
         <v>45617</v>
       </c>
@@ -1958,7 +1958,7 @@
         <v>16.8</v>
       </c>
     </row>
-    <row r="135" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:3" ht="40" customHeight="1">
       <c r="A135" s="4">
         <v>45622</v>
       </c>
@@ -1969,7 +1969,7 @@
         <v>15.22</v>
       </c>
     </row>
-    <row r="136" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:3" ht="40" customHeight="1">
       <c r="A136" s="4">
         <v>45625</v>
       </c>
@@ -1980,7 +1980,7 @@
         <v>14.88</v>
       </c>
     </row>
-    <row r="137" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:3" ht="40" customHeight="1">
       <c r="A137" s="4">
         <v>45630</v>
       </c>
@@ -1991,7 +1991,7 @@
         <v>14.42</v>
       </c>
     </row>
-    <row r="138" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:3" ht="40" customHeight="1">
       <c r="A138" s="4">
         <v>45645</v>
       </c>
@@ -2002,7 +2002,7 @@
         <v>19.329999999999998</v>
       </c>
     </row>
-    <row r="139" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:3" ht="40" customHeight="1">
       <c r="A139" s="4">
         <v>45646</v>
       </c>
@@ -2013,7 +2013,7 @@
         <v>21.87</v>
       </c>
     </row>
-    <row r="140" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:3" ht="40" customHeight="1">
       <c r="A140" s="4">
         <v>45663</v>
       </c>
@@ -2024,7 +2024,7 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="141" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:3" ht="40" customHeight="1">
       <c r="A141" s="4">
         <v>45664</v>
       </c>
@@ -2035,7 +2035,7 @@
         <v>18.010000000000002</v>
       </c>
     </row>
-    <row r="142" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:3" ht="40" customHeight="1">
       <c r="A142" s="4">
         <v>45667</v>
       </c>
@@ -2046,7 +2046,7 @@
         <v>18.8</v>
       </c>
     </row>
-    <row r="143" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:3" ht="40" customHeight="1">
       <c r="A143" s="4">
         <v>45670</v>
       </c>
@@ -2057,7 +2057,7 @@
         <v>19.25</v>
       </c>
     </row>
-    <row r="144" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:3" ht="40" customHeight="1">
       <c r="A144" s="4">
         <v>45672</v>
       </c>
@@ -2068,7 +2068,7 @@
         <v>16.55</v>
       </c>
     </row>
-    <row r="145" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:3" ht="40" customHeight="1">
       <c r="A145" s="4">
         <v>45674</v>
       </c>
@@ -2079,7 +2079,7 @@
         <v>15.88</v>
       </c>
     </row>
-    <row r="146" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:3" ht="40" customHeight="1">
       <c r="A146" s="4">
         <v>45679</v>
       </c>
@@ -2090,7 +2090,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="147" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:3" ht="40" customHeight="1">
       <c r="A147" s="4">
         <v>45684</v>
       </c>
@@ -2101,7 +2101,7 @@
         <v>17.829999999999998</v>
       </c>
     </row>
-    <row r="148" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:3" ht="40" customHeight="1">
       <c r="A148" s="4">
         <v>45685</v>
       </c>
@@ -2112,7 +2112,7 @@
         <v>17.100000000000001</v>
       </c>
     </row>
-    <row r="149" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:3" ht="40" customHeight="1">
       <c r="A149" s="4">
         <v>45688</v>
       </c>
@@ -2123,7 +2123,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="150" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:3" ht="40" customHeight="1">
       <c r="A150" s="4">
         <v>45691</v>
       </c>
@@ -2134,7 +2134,7 @@
         <v>18.940000000000001</v>
       </c>
     </row>
-    <row r="151" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:3" ht="40" customHeight="1">
       <c r="A151" s="4">
         <v>45692</v>
       </c>
@@ -2145,7 +2145,7 @@
         <v>17.350000000000001</v>
       </c>
     </row>
-    <row r="152" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:3" ht="40" customHeight="1">
       <c r="A152" s="4">
         <v>45694</v>
       </c>
@@ -2156,7 +2156,7 @@
         <v>16.68</v>
       </c>
     </row>
-    <row r="153" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:3" ht="24">
       <c r="A153" s="4">
         <v>45695</v>
       </c>
@@ -2167,7 +2167,7 @@
         <v>17.350000000000001</v>
       </c>
     </row>
-    <row r="154" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:3" ht="24">
       <c r="A154" s="4">
         <v>45698</v>
       </c>
@@ -2178,7 +2178,7 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="155" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:3" ht="24">
       <c r="A155" s="4">
         <v>45699</v>
       </c>
@@ -2189,7 +2189,7 @@
         <v>16.77</v>
       </c>
     </row>
-    <row r="156" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:3" ht="24">
       <c r="A156" s="4">
         <v>45700</v>
       </c>
@@ -2200,7 +2200,7 @@
         <v>16.8</v>
       </c>
     </row>
-    <row r="157" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:3" ht="24">
       <c r="A157" s="4">
         <v>45701</v>
       </c>
@@ -2211,7 +2211,7 @@
         <v>16.13</v>
       </c>
     </row>
-    <row r="158" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:3" ht="24">
       <c r="A158" s="4">
         <v>45702</v>
       </c>
@@ -2222,7 +2222,7 @@
         <v>16.010000000000002</v>
       </c>
     </row>
-    <row r="159" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:3" ht="24">
       <c r="A159" s="4">
         <v>45705</v>
       </c>
@@ -2233,7 +2233,7 @@
         <v>16.010000000000002</v>
       </c>
     </row>
-    <row r="160" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:3" ht="24">
       <c r="A160" s="4">
         <v>45706</v>
       </c>
@@ -2244,7 +2244,7 @@
         <v>15.66</v>
       </c>
     </row>
-    <row r="161" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:3" ht="24">
       <c r="A161" s="4">
         <v>45707</v>
       </c>
@@ -2255,7 +2255,7 @@
         <v>15.94</v>
       </c>
     </row>
-    <row r="162" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:3" ht="24">
       <c r="A162" s="4">
         <v>45708</v>
       </c>
@@ -2266,7 +2266,7 @@
         <v>17.03</v>
       </c>
     </row>
-    <row r="163" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:3" ht="24">
       <c r="A163" s="4">
         <v>45709</v>
       </c>
@@ -2277,7 +2277,7 @@
         <v>18.3</v>
       </c>
     </row>
-    <row r="164" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:3" ht="24">
       <c r="A164" s="4">
         <v>45712</v>
       </c>
@@ -2288,7 +2288,7 @@
         <v>18.43</v>
       </c>
     </row>
-    <row r="165" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:3" ht="24">
       <c r="A165" s="4">
         <v>45713</v>
       </c>
@@ -2299,7 +2299,7 @@
         <v>18.48</v>
       </c>
     </row>
-    <row r="166" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:3" ht="24">
       <c r="A166" s="4">
         <v>45714</v>
       </c>
@@ -2310,7 +2310,7 @@
         <v>18.13</v>
       </c>
     </row>
-    <row r="167" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:3" ht="24">
       <c r="A167" s="4">
         <v>45715</v>
       </c>
@@ -2321,7 +2321,7 @@
         <v>19.309999999999999</v>
       </c>
     </row>
-    <row r="168" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:3" ht="24">
       <c r="A168" s="4">
         <v>45716</v>
       </c>
@@ -2332,7 +2332,7 @@
         <v>18.829999999999998</v>
       </c>
     </row>
-    <row r="169" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:3" ht="24">
       <c r="A169" s="4">
         <v>45719</v>
       </c>
@@ -2343,7 +2343,7 @@
         <v>20.66</v>
       </c>
     </row>
-    <row r="170" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:3" ht="24">
       <c r="A170" s="4">
         <v>45720</v>
       </c>
@@ -2354,7 +2354,7 @@
         <v>21.24</v>
       </c>
     </row>
-    <row r="171" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:3" ht="24">
       <c r="A171" s="4">
         <v>45721</v>
       </c>
@@ -2365,7 +2365,7 @@
         <v>20.13</v>
       </c>
     </row>
-    <row r="172" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:3" ht="24">
       <c r="A172" s="4">
         <v>45722</v>
       </c>
@@ -2376,7 +2376,7 @@
         <v>22.83</v>
       </c>
     </row>
-    <row r="173" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:3" ht="24">
       <c r="A173" s="4">
         <v>45723</v>
       </c>
@@ -2387,7 +2387,7 @@
         <v>21.63</v>
       </c>
     </row>
-    <row r="174" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:3" ht="24">
       <c r="A174" s="4">
         <v>45726</v>
       </c>
@@ -2398,7 +2398,7 @@
         <v>25.33</v>
       </c>
     </row>
-    <row r="175" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:3" ht="24">
       <c r="A175" s="4">
         <v>45727</v>
       </c>
@@ -2409,7 +2409,7 @@
         <v>24.61</v>
       </c>
     </row>
-    <row r="176" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:3" ht="24">
       <c r="A176" s="4">
         <v>45728</v>
       </c>
@@ -2420,7 +2420,7 @@
         <v>22.98</v>
       </c>
     </row>
-    <row r="177" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:3" ht="24">
       <c r="A177" s="4">
         <v>45729</v>
       </c>
@@ -2431,7 +2431,7 @@
         <v>24.41</v>
       </c>
     </row>
-    <row r="178" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:3" ht="24">
       <c r="A178" s="4">
         <v>45730</v>
       </c>
@@ -2442,7 +2442,7 @@
         <v>21.52</v>
       </c>
     </row>
-    <row r="179" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:3" ht="24">
       <c r="A179" s="4">
         <v>45733</v>
       </c>
@@ -2453,7 +2453,7 @@
         <v>19.920000000000002</v>
       </c>
     </row>
-    <row r="180" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:3" ht="24">
       <c r="A180" s="4">
         <v>45734</v>
       </c>
@@ -2464,7 +2464,7 @@
         <v>20.48</v>
       </c>
     </row>
-    <row r="181" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:3" ht="24">
       <c r="A181" s="4">
         <v>45735</v>
       </c>
@@ -2475,7 +2475,7 @@
         <v>19.75</v>
       </c>
     </row>
-    <row r="182" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:3" ht="24">
       <c r="A182" s="4">
         <v>45736</v>
       </c>
@@ -2486,7 +2486,7 @@
         <v>19.47</v>
       </c>
     </row>
-    <row r="183" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:3" ht="24">
       <c r="A183" s="4">
         <v>45737</v>
       </c>
@@ -2497,7 +2497,7 @@
         <v>19.47</v>
       </c>
     </row>
-    <row r="184" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:3" ht="24">
       <c r="A184" s="4">
         <v>45740</v>
       </c>
@@ -2508,7 +2508,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="185" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:3" ht="24">
       <c r="A185" s="4">
         <v>45741</v>
       </c>
@@ -2519,7 +2519,7 @@
         <v>18.66</v>
       </c>
     </row>
-    <row r="186" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:3" ht="24">
       <c r="A186" s="4">
         <v>45742</v>
       </c>
@@ -2530,7 +2530,7 @@
         <v>19.149999999999999</v>
       </c>
     </row>
-    <row r="187" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:3" ht="24">
       <c r="A187" s="4">
         <v>45743</v>
       </c>
@@ -2541,7 +2541,7 @@
         <v>19.16</v>
       </c>
     </row>
-    <row r="188" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:3" ht="24">
       <c r="A188" s="4">
         <v>45744</v>
       </c>
@@ -2552,7 +2552,7 @@
         <v>20.55</v>
       </c>
     </row>
-    <row r="189" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:3" ht="24">
       <c r="A189" s="4">
         <v>45747</v>
       </c>
@@ -2563,7 +2563,7 @@
         <v>20.49</v>
       </c>
     </row>
-    <row r="190" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:3" ht="24">
       <c r="A190" s="4">
         <v>45748</v>
       </c>
@@ -2574,7 +2574,7 @@
         <v>20.51</v>
       </c>
     </row>
-    <row r="191" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:3" ht="24">
       <c r="A191" s="4">
         <v>45749</v>
       </c>
@@ -2585,7 +2585,7 @@
         <v>20.02</v>
       </c>
     </row>
-    <row r="192" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:3" ht="24">
       <c r="A192" s="4">
         <v>45750</v>
       </c>
@@ -2596,7 +2596,7 @@
         <v>24.19</v>
       </c>
     </row>
-    <row r="193" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:3" ht="24">
       <c r="A193" s="4">
         <v>45751</v>
       </c>
@@ -2607,7 +2607,7 @@
         <v>28.52</v>
       </c>
     </row>
-    <row r="194" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:3" ht="24">
       <c r="A194" s="4">
         <v>45754</v>
       </c>
@@ -2618,7 +2618,7 @@
         <v>26.07</v>
       </c>
     </row>
-    <row r="195" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:3" ht="24">
       <c r="A195" s="4">
         <v>45755</v>
       </c>
@@ -2629,7 +2629,7 @@
         <v>27.91</v>
       </c>
     </row>
-    <row r="196" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:3" ht="24">
       <c r="A196" s="4">
         <v>45756</v>
       </c>
@@ -2640,7 +2640,7 @@
         <v>23.83</v>
       </c>
     </row>
-    <row r="197" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:3" ht="24">
       <c r="A197" s="4">
         <v>45757</v>
       </c>
@@ -2651,7 +2651,7 @@
         <v>27.57</v>
       </c>
     </row>
-    <row r="198" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:3" ht="24">
       <c r="A198" s="4">
         <v>45758</v>
       </c>
@@ -2662,7 +2662,7 @@
         <v>27.14</v>
       </c>
     </row>
-    <row r="199" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:3" ht="24">
       <c r="A199" s="4">
         <v>45761</v>
       </c>
@@ -2673,7 +2673,7 @@
         <v>29.86</v>
       </c>
     </row>
-    <row r="200" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:3" ht="24">
       <c r="A200" s="4">
         <v>45762</v>
       </c>
@@ -2684,7 +2684,7 @@
         <v>29.9</v>
       </c>
     </row>
-    <row r="201" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:3" ht="24">
       <c r="A201" s="4">
         <v>45763</v>
       </c>
@@ -2695,7 +2695,7 @@
         <v>31.91</v>
       </c>
     </row>
-    <row r="202" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:3" ht="24">
       <c r="A202" s="4">
         <v>45764</v>
       </c>
@@ -2706,7 +2706,7 @@
         <v>26.73</v>
       </c>
     </row>
-    <row r="203" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:3" ht="24">
       <c r="A203" s="4">
         <v>45769</v>
       </c>
@@ -2717,7 +2717,7 @@
         <v>26.54</v>
       </c>
     </row>
-    <row r="204" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:3" ht="24">
       <c r="A204" s="4">
         <v>45770</v>
       </c>
@@ -2728,7 +2728,7 @@
         <v>25.44</v>
       </c>
     </row>
-    <row r="205" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:3" ht="24">
       <c r="A205" s="4">
         <v>45771</v>
       </c>
@@ -2739,7 +2739,7 @@
         <v>24.57</v>
       </c>
     </row>
-    <row r="206" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:3" ht="24">
       <c r="A206" s="4">
         <v>45772</v>
       </c>
@@ -2750,7 +2750,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="207" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:3" ht="24">
       <c r="A207" s="4">
         <v>45775</v>
       </c>
@@ -2761,7 +2761,7 @@
         <v>23.68</v>
       </c>
     </row>
-    <row r="208" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:3" ht="24">
       <c r="A208" s="4">
         <v>45776</v>
       </c>
@@ -2772,7 +2772,7 @@
         <v>23.38</v>
       </c>
     </row>
-    <row r="209" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:3" ht="24">
       <c r="A209" s="4">
         <v>45777</v>
       </c>
@@ -2783,7 +2783,7 @@
         <v>24.01</v>
       </c>
     </row>
-    <row r="210" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:3" ht="24">
       <c r="A210" s="4">
         <v>45779</v>
       </c>
@@ -2794,7 +2794,7 @@
         <v>22.48</v>
       </c>
     </row>
-    <row r="211" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:3" ht="24">
       <c r="A211" s="4">
         <v>45782</v>
       </c>
@@ -2805,7 +2805,7 @@
         <v>23.18</v>
       </c>
     </row>
-    <row r="212" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:3" ht="24">
       <c r="A212" s="4">
         <v>45783</v>
       </c>
@@ -2816,7 +2816,7 @@
         <v>24.11</v>
       </c>
     </row>
-    <row r="213" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:3" ht="24">
       <c r="A213" s="4">
         <v>45784</v>
       </c>
@@ -2827,7 +2827,7 @@
         <v>23.32</v>
       </c>
     </row>
-    <row r="214" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:3" ht="24">
       <c r="A214" s="4">
         <v>45785</v>
       </c>
@@ -2838,7 +2838,7 @@
         <v>22.29</v>
       </c>
     </row>
-    <row r="215" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:3" ht="24">
       <c r="A215" s="4">
         <v>45786</v>
       </c>
@@ -2849,7 +2849,7 @@
         <v>22.01</v>
       </c>
     </row>
-    <row r="216" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:3" ht="24">
       <c r="A216" s="4">
         <v>45789</v>
       </c>
@@ -2860,7 +2860,7 @@
         <v>18.57</v>
       </c>
     </row>
-    <row r="217" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:3" ht="24">
       <c r="A217" s="4">
         <v>45790</v>
       </c>
@@ -2871,7 +2871,7 @@
         <v>18.440000000000001</v>
       </c>
     </row>
-    <row r="218" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:3" ht="24">
       <c r="A218" s="4">
         <v>45791</v>
       </c>
@@ -2882,7 +2882,7 @@
         <v>18.78</v>
       </c>
     </row>
-    <row r="219" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:3" ht="24">
       <c r="A219" s="4">
         <v>45792</v>
       </c>
@@ -2893,7 +2893,7 @@
         <v>18.23</v>
       </c>
     </row>
-    <row r="220" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:3" ht="24">
       <c r="A220" s="4">
         <v>45793</v>
       </c>
@@ -2904,7 +2904,7 @@
         <v>17.93</v>
       </c>
     </row>
-    <row r="221" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:3" ht="24">
       <c r="A221" s="4">
         <v>45796</v>
       </c>
@@ -2915,7 +2915,7 @@
         <v>19.649999999999999</v>
       </c>
     </row>
-    <row r="222" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:3" ht="24">
       <c r="A222" s="4">
         <v>45797</v>
       </c>
@@ -2926,7 +2926,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="223" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:3" ht="24">
       <c r="A223" s="4">
         <v>45798</v>
       </c>
@@ -2937,7 +2937,7 @@
         <v>20.79</v>
       </c>
     </row>
-    <row r="224" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:3" ht="24">
       <c r="A224" s="4">
         <v>45799</v>
       </c>
@@ -2948,7 +2948,7 @@
         <v>21.24</v>
       </c>
     </row>
-    <row r="225" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:3" ht="24">
       <c r="A225" s="4">
         <v>45800</v>
       </c>
@@ -2959,7 +2959,7 @@
         <v>22.28</v>
       </c>
     </row>
-    <row r="226" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:3" ht="24">
       <c r="A226" s="4">
         <v>45803</v>
       </c>
@@ -2970,7 +2970,7 @@
         <v>20.93</v>
       </c>
     </row>
-    <row r="227" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:3" ht="24">
       <c r="A227" s="4">
         <v>45804</v>
       </c>
@@ -2981,7 +2981,7 @@
         <v>20.52</v>
       </c>
     </row>
-    <row r="228" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:3" ht="24">
       <c r="A228" s="4">
         <v>45805</v>
       </c>
@@ -2992,7 +2992,7 @@
         <v>20.79</v>
       </c>
     </row>
-    <row r="229" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:3" ht="24">
       <c r="A229" s="4">
         <v>45807</v>
       </c>
@@ -3003,7 +3003,7 @@
         <v>21.04</v>
       </c>
     </row>
-    <row r="230" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:3" ht="24">
       <c r="A230" s="4">
         <v>45810</v>
       </c>
@@ -3014,7 +3014,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="231" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:3" ht="24">
       <c r="A231" s="4">
         <v>45811</v>
       </c>
@@ -3025,7 +3025,7 @@
         <v>20.57</v>
       </c>
     </row>
-    <row r="232" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:3" ht="24">
       <c r="A232" s="4">
         <v>45812</v>
       </c>
@@ -3036,7 +3036,7 @@
         <v>20.57</v>
       </c>
     </row>
-    <row r="233" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:3" ht="24">
       <c r="A233" s="4">
         <v>45813</v>
       </c>
@@ -3047,7 +3047,7 @@
         <v>20.89</v>
       </c>
     </row>
-    <row r="234" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:3" ht="24">
       <c r="A234" s="4">
         <v>45814</v>
       </c>
@@ -3058,7 +3058,7 @@
         <v>20.149999999999999</v>
       </c>
     </row>
-    <row r="235" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:3" ht="24">
       <c r="A235" s="4">
         <v>45818</v>
       </c>
@@ -3069,7 +3069,7 @@
         <v>19.97</v>
       </c>
     </row>
-    <row r="236" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:3" ht="24">
       <c r="A236" s="4">
         <v>45819</v>
       </c>
@@ -3080,7 +3080,7 @@
         <v>20.09</v>
       </c>
     </row>
-    <row r="237" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:3" ht="24">
       <c r="A237" s="4">
         <v>45820</v>
       </c>
@@ -3091,7 +3091,7 @@
         <v>20.3</v>
       </c>
     </row>
-    <row r="238" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:3" ht="24">
       <c r="A238" s="4">
         <v>45821</v>
       </c>
@@ -3102,7 +3102,7 @@
         <v>21.82</v>
       </c>
     </row>
-    <row r="239" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:3" ht="24">
       <c r="A239" s="4">
         <v>45824</v>
       </c>
@@ -3113,7 +3113,7 @@
         <v>20.28</v>
       </c>
     </row>
-    <row r="240" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:3" ht="24">
       <c r="A240" s="4">
         <v>45825</v>
       </c>
@@ -3124,7 +3124,7 @@
         <v>21.41</v>
       </c>
     </row>
-    <row r="241" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:3" ht="24">
       <c r="A241" s="4">
         <v>45826</v>
       </c>
@@ -3135,7 +3135,7 @@
         <v>20.81</v>
       </c>
     </row>
-    <row r="242" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:3" ht="24">
       <c r="A242" s="4">
         <v>45827</v>
       </c>
@@ -3146,7 +3146,7 @@
         <v>21.13</v>
       </c>
     </row>
-    <row r="243" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:3" ht="24">
       <c r="A243" s="4">
         <v>45828</v>
       </c>
@@ -3157,7 +3157,7 @@
         <v>21.65</v>
       </c>
     </row>
-    <row r="244" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:3" ht="24">
       <c r="A244" s="4">
         <v>45831</v>
       </c>
@@ -3168,7 +3168,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="245" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:3" ht="24">
       <c r="A245" s="4">
         <v>45832</v>
       </c>
@@ -3179,7 +3179,7 @@
         <v>19.25</v>
       </c>
     </row>
-    <row r="246" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:3" ht="24">
       <c r="A246" s="4">
         <v>45833</v>
       </c>
@@ -3190,7 +3190,7 @@
         <v>19.02</v>
       </c>
     </row>
-    <row r="247" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:3" ht="24">
       <c r="A247" s="4">
         <v>45834</v>
       </c>
@@ -3201,7 +3201,7 @@
         <v>18.91</v>
       </c>
     </row>
-    <row r="248" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:3" ht="24">
       <c r="A248" s="4">
         <v>45835</v>
       </c>
@@ -3212,7 +3212,7 @@
         <v>18.850000000000001</v>
       </c>
     </row>
-    <row r="249" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:3" ht="24">
       <c r="A249" s="4">
         <v>45838</v>
       </c>
@@ -3223,7 +3223,7 @@
         <v>18.71</v>
       </c>
     </row>
-    <row r="250" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:3" ht="24">
       <c r="A250" s="4">
         <v>45839</v>
       </c>
@@ -3234,7 +3234,7 @@
         <v>18.649999999999999</v>
       </c>
     </row>
-    <row r="251" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:3" ht="24">
       <c r="A251" s="4">
         <v>45840</v>
       </c>
@@ -3245,7 +3245,7 @@
         <v>18.559999999999999</v>
       </c>
     </row>
-    <row r="252" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:3" ht="24">
       <c r="A252" s="4">
         <v>45841</v>
       </c>
@@ -3256,7 +3256,7 @@
         <v>18.32</v>
       </c>
     </row>
-    <row r="253" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:3" ht="24">
       <c r="A253" s="4">
         <v>45842</v>
       </c>
@@ -3267,7 +3267,7 @@
         <v>18.75</v>
       </c>
     </row>
-    <row r="254" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:3" ht="24">
       <c r="A254" s="4">
         <v>45845</v>
       </c>
@@ -3278,7 +3278,7 @@
         <v>18.239999999999998</v>
       </c>
     </row>
-    <row r="255" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:3" ht="24">
       <c r="A255" s="4">
         <v>45846</v>
       </c>
@@ -3289,7 +3289,7 @@
         <v>17.82</v>
       </c>
     </row>
-    <row r="256" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:3" ht="24">
       <c r="A256" s="4">
         <v>45847</v>
       </c>
@@ -3300,7 +3300,7 @@
         <v>17.260000000000002</v>
       </c>
     </row>
-    <row r="257" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:3" ht="24">
       <c r="A257" s="4">
         <v>45848</v>
       </c>
@@ -3311,7 +3311,7 @@
         <v>17.11</v>
       </c>
     </row>
-    <row r="258" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:3" ht="24">
       <c r="A258" s="4">
         <v>45849</v>
       </c>
@@ -3322,7 +3322,7 @@
         <v>16.399999999999999</v>
       </c>
     </row>
-    <row r="259" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:3" ht="24">
       <c r="A259" s="4">
         <v>45852</v>
       </c>
@@ -3333,7 +3333,7 @@
         <v>17.2</v>
       </c>
     </row>
-    <row r="260" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:3" ht="24">
       <c r="A260" s="4">
         <v>45853</v>
       </c>
@@ -3344,7 +3344,7 @@
         <v>17.38</v>
       </c>
     </row>
-    <row r="261" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:3" ht="24">
       <c r="A261" s="4">
         <v>45854</v>
       </c>
@@ -3355,7 +3355,7 @@
         <v>17.16</v>
       </c>
     </row>
-    <row r="262" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:3" ht="24">
       <c r="A262" s="4">
         <v>45855</v>
       </c>
@@ -3366,7 +3366,7 @@
         <v>16.52</v>
       </c>
     </row>
-    <row r="263" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:3" ht="24">
       <c r="A263" s="4">
         <v>45856</v>
       </c>
@@ -3377,7 +3377,7 @@
         <v>16.41</v>
       </c>
     </row>
-    <row r="264" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:3" ht="24">
       <c r="A264" s="4">
         <v>45859</v>
       </c>
@@ -3388,7 +3388,7 @@
         <v>16.649999999999999</v>
       </c>
     </row>
-    <row r="265" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:3" ht="24">
       <c r="A265" s="4">
         <v>45860</v>
       </c>
@@ -3399,7 +3399,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="266" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:3" ht="24">
       <c r="A266" s="4">
         <v>45861</v>
       </c>
@@ -3410,7 +3410,7 @@
         <v>15.37</v>
       </c>
     </row>
-    <row r="267" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:3" ht="24">
       <c r="A267" s="4">
         <v>45862</v>
       </c>
@@ -3421,7 +3421,7 @@
         <v>15.39</v>
       </c>
     </row>
-    <row r="268" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:3" ht="24">
       <c r="A268" s="4">
         <v>45863</v>
       </c>
@@ -3432,7 +3432,7 @@
         <v>14.93</v>
       </c>
     </row>
-    <row r="269" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:3" ht="24">
       <c r="A269" s="4">
         <v>45866</v>
       </c>
@@ -3443,7 +3443,7 @@
         <v>15.03</v>
       </c>
     </row>
-    <row r="270" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:3" ht="24">
       <c r="A270" s="4">
         <v>45867</v>
       </c>
@@ -3454,7 +3454,7 @@
         <v>15.98</v>
       </c>
     </row>
-    <row r="271" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:3" ht="24">
       <c r="A271" s="4">
         <v>45868</v>
       </c>
@@ -3465,7 +3465,7 @@
         <v>15.48</v>
       </c>
     </row>
-    <row r="272" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:3" ht="24">
       <c r="A272" s="4">
         <v>45869</v>
       </c>
@@ -3476,7 +3476,7 @@
         <v>16.72</v>
       </c>
     </row>
-    <row r="273" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:3" ht="24">
       <c r="A273" s="4">
         <v>45873</v>
       </c>
@@ -3487,7 +3487,7 @@
         <v>17.52</v>
       </c>
     </row>
-    <row r="274" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:3" ht="24">
       <c r="A274" s="4">
         <v>45874</v>
       </c>
@@ -3498,7 +3498,7 @@
         <v>17.850000000000001</v>
       </c>
     </row>
-    <row r="275" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:3" ht="24">
       <c r="A275" s="4">
         <v>45875</v>
       </c>
@@ -3509,7 +3509,7 @@
         <v>16.77</v>
       </c>
     </row>
-    <row r="276" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:3" ht="24">
       <c r="A276" s="4">
         <v>45876</v>
       </c>
@@ -3520,7 +3520,7 @@
         <v>16.57</v>
       </c>
     </row>
-    <row r="277" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:3" ht="24">
       <c r="A277" s="4">
         <v>45877</v>
       </c>
@@ -3531,7 +3531,7 @@
         <v>15.15</v>
       </c>
     </row>
-    <row r="278" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:3" ht="24">
       <c r="A278" s="4">
         <v>45880</v>
       </c>
@@ -3542,7 +3542,7 @@
         <v>16.25</v>
       </c>
     </row>
-    <row r="279" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:3" ht="24">
       <c r="A279" s="4">
         <v>45881</v>
       </c>
@@ -3553,7 +3553,7 @@
         <v>14.73</v>
       </c>
     </row>
-    <row r="280" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:3" ht="24">
       <c r="A280" s="4">
         <v>45882</v>
       </c>
@@ -3564,7 +3564,7 @@
         <v>14.49</v>
       </c>
     </row>
-    <row r="281" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:3" ht="24">
       <c r="A281" s="4">
         <v>45883</v>
       </c>
@@ -3575,7 +3575,7 @@
         <v>14.83</v>
       </c>
     </row>
-    <row r="282" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:3" ht="24">
       <c r="A282" s="4">
         <v>45884</v>
       </c>
@@ -3586,7 +3586,7 @@
         <v>15.09</v>
       </c>
     </row>
-    <row r="283" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:3" ht="24">
       <c r="A283" s="4">
         <v>45887</v>
       </c>
@@ -3597,7 +3597,7 @@
         <v>14.99</v>
       </c>
     </row>
-    <row r="284" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:3" ht="24">
       <c r="A284" s="4">
         <v>45888</v>
       </c>
@@ -3608,7 +3608,7 @@
         <v>15.57</v>
       </c>
     </row>
-    <row r="285" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:3" ht="24">
       <c r="A285" s="4">
         <v>45889</v>
       </c>
@@ -3619,7 +3619,7 @@
         <v>15.69</v>
       </c>
     </row>
-    <row r="286" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:3" ht="24">
       <c r="A286" s="4">
         <v>45890</v>
       </c>
@@ -3630,7 +3630,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="287" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:3" ht="24">
       <c r="A287" s="4">
         <v>45891</v>
       </c>
@@ -3641,7 +3641,7 @@
         <v>14.22</v>
       </c>
     </row>
-    <row r="288" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:3" ht="24">
       <c r="A288" s="4">
         <v>45894</v>
       </c>
@@ -3652,7 +3652,7 @@
         <v>14.79</v>
       </c>
     </row>
-    <row r="289" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:3" ht="24">
       <c r="A289" s="4">
         <v>45895</v>
       </c>
@@ -3663,7 +3663,7 @@
         <v>14.62</v>
       </c>
     </row>
-    <row r="290" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:3" ht="24">
       <c r="A290" s="4">
         <v>45896</v>
       </c>
@@ -3674,7 +3674,7 @@
         <v>14.85</v>
       </c>
     </row>
-    <row r="291" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:3" ht="24">
       <c r="A291" s="4">
         <v>45897</v>
       </c>
@@ -3685,7 +3685,7 @@
         <v>14.43</v>
       </c>
     </row>
-    <row r="292" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:3" ht="24">
       <c r="A292" s="4">
         <v>45898</v>
       </c>
@@ -3696,7 +3696,7 @@
         <v>15.36</v>
       </c>
     </row>
-    <row r="293" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:3" ht="24">
       <c r="A293" s="4">
         <v>45901</v>
       </c>
@@ -3707,7 +3707,7 @@
         <v>16.12</v>
       </c>
     </row>
-    <row r="294" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:3" ht="24">
       <c r="A294" s="4">
         <v>45902</v>
       </c>
@@ -3718,7 +3718,7 @@
         <v>17.170000000000002</v>
       </c>
     </row>
-    <row r="295" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:3" ht="24">
       <c r="A295" s="4">
         <v>45903</v>
       </c>
@@ -3729,7 +3729,7 @@
         <v>16.350000000000001</v>
       </c>
     </row>
-    <row r="296" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:3" ht="24">
       <c r="A296" s="4">
         <v>45904</v>
       </c>
@@ -3740,7 +3740,7 @@
         <v>15.3</v>
       </c>
     </row>
-    <row r="297" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:3" ht="24">
       <c r="A297" s="4">
         <v>45905</v>
       </c>
@@ -3751,7 +3751,7 @@
         <v>15.18</v>
       </c>
     </row>
-    <row r="298" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:3" ht="24">
       <c r="A298" s="4">
         <v>45908</v>
       </c>
@@ -3762,7 +3762,7 @@
         <v>15.11</v>
       </c>
     </row>
-    <row r="299" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:3" ht="24">
       <c r="A299" s="4">
         <v>45909</v>
       </c>
@@ -3773,7 +3773,7 @@
         <v>15.04</v>
       </c>
     </row>
-    <row r="300" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:3" ht="24">
       <c r="A300" s="4">
         <v>45910</v>
       </c>
@@ -3784,7 +3784,7 @@
         <v>15.35</v>
       </c>
     </row>
-    <row r="301" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:3" ht="24">
       <c r="A301" s="4">
         <v>45911</v>
       </c>
@@ -3795,7 +3795,7 @@
         <v>14.71</v>
       </c>
     </row>
-    <row r="302" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:3" ht="24">
       <c r="A302" s="4">
         <v>45912</v>
       </c>
@@ -3806,7 +3806,7 @@
         <v>14.76</v>
       </c>
     </row>
-    <row r="303" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:3" ht="24">
       <c r="A303" s="4">
         <v>45915</v>
       </c>
@@ -3817,7 +3817,7 @@
         <v>15.69</v>
       </c>
     </row>
-    <row r="304" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:3" ht="24">
       <c r="A304" s="4">
         <v>45916</v>
       </c>
@@ -3828,7 +3828,7 @@
         <v>16.36</v>
       </c>
     </row>
-    <row r="305" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:3" ht="24">
       <c r="A305" s="4">
         <v>45917</v>
       </c>
@@ -3839,7 +3839,7 @@
         <v>15.72</v>
       </c>
     </row>
-    <row r="306" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:3" ht="24">
       <c r="A306" s="4">
         <v>45918</v>
       </c>
@@ -3850,7 +3850,7 @@
         <v>15.7</v>
       </c>
     </row>
-    <row r="307" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:3" ht="24">
       <c r="A307" s="4">
         <v>45919</v>
       </c>
@@ -3861,7 +3861,7 @@
         <v>15.45</v>
       </c>
     </row>
-    <row r="308" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:3" ht="24">
       <c r="A308" s="4">
         <v>45922</v>
       </c>
@@ -3872,7 +3872,7 @@
         <v>16.100000000000001</v>
       </c>
     </row>
-    <row r="309" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:3" ht="24">
       <c r="A309" s="4">
         <v>45923</v>
       </c>
@@ -3883,7 +3883,7 @@
         <v>16.64</v>
       </c>
     </row>
-    <row r="310" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:3" ht="24">
       <c r="A310" s="4">
         <v>45924</v>
       </c>
@@ -3894,7 +3894,7 @@
         <v>16.18</v>
       </c>
     </row>
-    <row r="311" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:3" ht="24">
       <c r="A311" s="4">
         <v>45925</v>
       </c>
@@ -3905,7 +3905,7 @@
         <v>16.739999999999998</v>
       </c>
     </row>
-    <row r="312" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:3" ht="24">
       <c r="A312" s="4">
         <v>45926</v>
       </c>
@@ -3916,7 +3916,7 @@
         <v>15.29</v>
       </c>
     </row>
-    <row r="313" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:3" ht="24">
       <c r="A313" s="4">
         <v>45929</v>
       </c>
@@ -3927,7 +3927,7 @@
         <v>16.12</v>
       </c>
     </row>
-    <row r="314" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:3" ht="24">
       <c r="A314" s="4">
         <v>45930</v>
       </c>
@@ -3938,7 +3938,7 @@
         <v>16.28</v>
       </c>
     </row>
-    <row r="315" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:3" ht="24">
       <c r="A315" s="4">
         <v>45931</v>
       </c>
@@ -3949,7 +3949,7 @@
         <v>16.29</v>
       </c>
     </row>
-    <row r="316" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:3" ht="24">
       <c r="A316" s="4">
         <v>45932</v>
       </c>
@@ -3960,7 +3960,7 @@
         <v>16.63</v>
       </c>
     </row>
-    <row r="317" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:3" ht="24">
       <c r="A317" s="4">
         <v>45933</v>
       </c>
@@ -3971,7 +3971,7 @@
         <v>16.649999999999999</v>
       </c>
     </row>
-    <row r="318" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:3" ht="24">
       <c r="A318" s="4">
         <v>45936</v>
       </c>
@@ -3982,7 +3982,7 @@
         <v>16.37</v>
       </c>
     </row>
-    <row r="319" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:3" ht="24">
       <c r="A319" s="4">
         <v>45937</v>
       </c>
@@ -3993,7 +3993,7 @@
         <v>17.239999999999998</v>
       </c>
     </row>
-    <row r="320" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:3" ht="24">
       <c r="A320" s="4">
         <v>45938</v>
       </c>
@@ -4004,7 +4004,7 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="321" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:3" ht="24">
       <c r="A321" s="4">
         <v>45939</v>
       </c>
@@ -4015,7 +4015,7 @@
         <v>16.43</v>
       </c>
     </row>
-    <row r="322" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:3" ht="24">
       <c r="A322" s="4">
         <v>45940</v>
       </c>
@@ -4026,7 +4026,7 @@
         <v>21.66</v>
       </c>
     </row>
-    <row r="323" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:3" ht="24">
       <c r="A323" s="4">
         <v>45943</v>
       </c>
@@ -4037,7 +4037,7 @@
         <v>19.03</v>
       </c>
     </row>
-    <row r="324" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:3" ht="24">
       <c r="A324" s="4">
         <v>45944</v>
       </c>
@@ -4048,7 +4048,7 @@
         <v>20.81</v>
       </c>
     </row>
-    <row r="325" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:3" ht="24">
       <c r="A325" s="4">
         <v>45945</v>
       </c>
@@ -4059,7 +4059,7 @@
         <v>20.64</v>
       </c>
     </row>
-    <row r="326" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:3" ht="24">
       <c r="A326" s="4">
         <v>45946</v>
       </c>
@@ -4070,7 +4070,7 @@
         <v>25.31</v>
       </c>
     </row>
-    <row r="327" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:3" ht="24">
       <c r="A327" s="4">
         <v>45947</v>
       </c>
@@ -4081,7 +4081,7 @@
         <v>20.78</v>
       </c>
     </row>
-    <row r="328" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:3" ht="24">
       <c r="A328" s="4">
         <v>45950</v>
       </c>
@@ -4092,7 +4092,7 @@
         <v>18.23</v>
       </c>
     </row>
-    <row r="329" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:3" ht="24">
       <c r="A329" s="4">
         <v>45951</v>
       </c>
@@ -4103,7 +4103,7 @@
         <v>17.87</v>
       </c>
     </row>
-    <row r="330" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:3" ht="24">
       <c r="A330" s="4">
         <v>45952</v>
       </c>
@@ -4114,7 +4114,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="331" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:3" ht="24">
       <c r="A331" s="4">
         <v>45953</v>
       </c>
@@ -4125,7 +4125,7 @@
         <v>17.3</v>
       </c>
     </row>
-    <row r="332" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:3" ht="24">
       <c r="A332" s="4">
         <v>45954</v>
       </c>
@@ -4136,7 +4136,7 @@
         <v>16.37</v>
       </c>
     </row>
-    <row r="333" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:3" ht="24">
       <c r="A333" s="4">
         <v>45957</v>
       </c>
@@ -4147,7 +4147,7 @@
         <v>15.79</v>
       </c>
     </row>
-    <row r="334" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:3" ht="24">
       <c r="A334" s="4">
         <v>45958</v>
       </c>
@@ -4158,7 +4158,7 @@
         <v>16.420000000000002</v>
       </c>
     </row>
-    <row r="335" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:3" ht="24">
       <c r="A335" s="4">
         <v>45959</v>
       </c>
@@ -4169,7 +4169,7 @@
         <v>16.920000000000002</v>
       </c>
     </row>
-    <row r="336" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:3" ht="24">
       <c r="A336" s="4">
         <v>45960</v>
       </c>
@@ -4180,7 +4180,7 @@
         <v>16.91</v>
       </c>
     </row>
-    <row r="337" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:3" ht="24">
       <c r="A337" s="4">
         <v>45961</v>
       </c>
@@ -4191,7 +4191,7 @@
         <v>17.440000000000001</v>
       </c>
     </row>
-    <row r="338" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:3" ht="24">
       <c r="A338" s="4">
         <v>45964</v>
       </c>
@@ -4202,7 +4202,7 @@
         <v>17.170000000000002</v>
       </c>
     </row>
-    <row r="339" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:3" ht="24">
       <c r="A339" s="4">
         <v>45965</v>
       </c>
@@ -4213,7 +4213,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="340" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:3" ht="24">
       <c r="A340" s="4">
         <v>45966</v>
       </c>
@@ -4224,7 +4224,7 @@
         <v>18.010000000000002</v>
       </c>
     </row>
-    <row r="341" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:3" ht="24">
       <c r="A341" s="4">
         <v>45967</v>
       </c>
@@ -4235,7 +4235,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="342" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:3" ht="24">
       <c r="A342" s="4">
         <v>45968</v>
       </c>
@@ -4246,7 +4246,7 @@
         <v>19.079999999999998</v>
       </c>
     </row>
-    <row r="343" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:3" ht="24">
       <c r="A343" s="4">
         <v>45971</v>
       </c>
@@ -4257,7 +4257,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="344" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:3" ht="24">
       <c r="A344" s="4">
         <v>45972</v>
       </c>
@@ -4268,7 +4268,7 @@
         <v>17.28</v>
       </c>
     </row>
-    <row r="345" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:3" ht="24">
       <c r="A345" s="4">
         <v>45973</v>
       </c>
@@ -4279,7 +4279,7 @@
         <v>17.510000000000002</v>
       </c>
     </row>
-    <row r="346" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:3" ht="24">
       <c r="A346" s="4">
         <v>45974</v>
       </c>
@@ -4290,7 +4290,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="347" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:3" ht="24">
       <c r="A347" s="4">
         <v>45975</v>
       </c>
@@ -4301,7 +4301,7 @@
         <v>19.829999999999998</v>
       </c>
     </row>
-    <row r="348" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:3" ht="24">
       <c r="A348" s="4">
         <v>45978</v>
       </c>
@@ -4312,7 +4312,7 @@
         <v>22.38</v>
       </c>
     </row>
-    <row r="349" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:3" ht="24">
       <c r="A349" s="4">
         <v>45979</v>
       </c>
@@ -4323,7 +4323,7 @@
         <v>24.69</v>
       </c>
     </row>
-    <row r="350" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:3" ht="24">
       <c r="A350" s="4">
         <v>45980</v>
       </c>
@@ -4334,7 +4334,7 @@
         <v>23.66</v>
       </c>
     </row>
-    <row r="351" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:3" ht="24">
       <c r="A351" s="4">
         <v>45981</v>
       </c>
@@ -4345,7 +4345,7 @@
         <v>26.42</v>
       </c>
     </row>
-    <row r="352" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:3" ht="24">
       <c r="A352" s="4">
         <v>45982</v>
       </c>
@@ -4356,7 +4356,7 @@
         <v>23.43</v>
       </c>
     </row>
-    <row r="353" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:3" ht="24">
       <c r="A353" s="4">
         <v>45985</v>
       </c>
@@ -4367,7 +4367,7 @@
         <v>20.52</v>
       </c>
     </row>
-    <row r="354" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:3" ht="24">
       <c r="A354" s="4">
         <v>45986</v>
       </c>
@@ -4378,7 +4378,7 @@
         <v>18.559999999999999</v>
       </c>
     </row>
-    <row r="355" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:3" ht="24">
       <c r="A355" s="4">
         <v>45987</v>
       </c>
@@ -4389,7 +4389,7 @@
         <v>17.190000000000001</v>
       </c>
     </row>
-    <row r="356" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:3" ht="24">
       <c r="A356" s="4">
         <v>45988</v>
       </c>
@@ -4400,7 +4400,7 @@
         <v>17.21</v>
       </c>
     </row>
-    <row r="357" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:3" ht="24">
       <c r="A357" s="4">
         <v>45989</v>
       </c>
@@ -4411,7 +4411,7 @@
         <v>16.350000000000001</v>
       </c>
     </row>
-    <row r="358" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:3" ht="24">
       <c r="A358" s="4">
         <v>45992</v>
       </c>
@@ -4422,7 +4422,7 @@
         <v>17.239999999999998</v>
       </c>
     </row>
-    <row r="359" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:3" ht="24">
       <c r="A359" s="4">
         <v>45993</v>
       </c>
@@ -4433,7 +4433,7 @@
         <v>16.59</v>
       </c>
     </row>
-    <row r="360" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:3" ht="24">
       <c r="A360" s="4">
         <v>45994</v>
       </c>
@@ -4444,7 +4444,7 @@
         <v>16.079999999999998</v>
       </c>
     </row>
-    <row r="361" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:3" ht="24">
       <c r="A361" s="4">
         <v>45995</v>
       </c>
@@ -4455,7 +4455,7 @@
         <v>15.78</v>
       </c>
     </row>
-    <row r="362" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:3" ht="24">
       <c r="A362" s="4">
         <v>45996</v>
       </c>
@@ -4466,7 +4466,7 @@
         <v>15.41</v>
       </c>
     </row>
-    <row r="363" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:3" ht="24">
       <c r="A363" s="4">
         <v>45999</v>
       </c>
@@ -4477,7 +4477,7 @@
         <v>16.66</v>
       </c>
     </row>
-    <row r="364" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:3" ht="24">
       <c r="A364" s="4">
         <v>46000</v>
       </c>
@@ -4488,7 +4488,7 @@
         <v>16.93</v>
       </c>
     </row>
-    <row r="365" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:3" ht="24">
       <c r="A365" s="4">
         <v>46001</v>
       </c>
@@ -4499,7 +4499,7 @@
         <v>15.77</v>
       </c>
     </row>
-    <row r="366" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:3" ht="24">
       <c r="A366" s="4">
         <v>46002</v>
       </c>
@@ -4510,7 +4510,7 @@
         <v>14.85</v>
       </c>
     </row>
-    <row r="367" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:3" ht="24">
       <c r="A367" s="4">
         <v>46003</v>
       </c>
@@ -4521,7 +4521,7 @@
         <v>15.74</v>
       </c>
     </row>
-    <row r="368" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:3" ht="24">
       <c r="A368" s="4">
         <v>46006</v>
       </c>
@@ -4532,7 +4532,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="369" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:3" ht="24">
       <c r="A369" s="4">
         <v>46007</v>
       </c>
@@ -4543,7 +4543,7 @@
         <v>16.48</v>
       </c>
     </row>
-    <row r="370" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:3" ht="24">
       <c r="A370" s="4">
         <v>46008</v>
       </c>
@@ -4554,7 +4554,7 @@
         <v>17.62</v>
       </c>
     </row>
-    <row r="371" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:3" ht="24">
       <c r="A371" s="4">
         <v>46009</v>
       </c>
@@ -4565,7 +4565,7 @@
         <v>16.87</v>
       </c>
     </row>
-    <row r="372" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:3" ht="24">
       <c r="A372" s="4">
         <v>46010</v>
       </c>
@@ -4576,7 +4576,7 @@
         <v>14.91</v>
       </c>
     </row>
-    <row r="373" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:3" ht="24">
       <c r="A373" s="4">
         <v>46013</v>
       </c>
@@ -4587,7 +4587,7 @@
         <v>14.08</v>
       </c>
     </row>
-    <row r="374" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:3" ht="24">
       <c r="A374" s="4">
         <v>46014</v>
       </c>
@@ -4598,7 +4598,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="375" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:3" ht="24">
       <c r="A375" s="4">
         <v>46015</v>
       </c>
@@ -4609,7 +4609,7 @@
         <v>13.47</v>
       </c>
     </row>
-    <row r="376" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:3" ht="24">
       <c r="A376" s="4">
         <v>46017</v>
       </c>
@@ -4620,7 +4620,7 @@
         <v>13.6</v>
       </c>
     </row>
-    <row r="377" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:3" ht="24">
       <c r="A377" s="4">
         <v>46020</v>
       </c>
@@ -4631,7 +4631,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="378" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:3" ht="24">
       <c r="A378" s="4">
         <v>46021</v>
       </c>
@@ -4642,7 +4642,7 @@
         <v>14.33</v>
       </c>
     </row>
-    <row r="379" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:3" ht="24">
       <c r="A379" s="4">
         <v>46022</v>
       </c>
@@ -4653,7 +4653,7 @@
         <v>14.95</v>
       </c>
     </row>
-    <row r="380" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:3" ht="24">
       <c r="A380" s="4">
         <v>46024</v>
       </c>
@@ -4664,7 +4664,7 @@
         <v>14.51</v>
       </c>
     </row>
-    <row r="381" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:3" ht="24">
       <c r="A381" s="4">
         <v>46027</v>
       </c>
@@ -4675,7 +4675,7 @@
         <v>14.9</v>
       </c>
     </row>
-    <row r="382" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:3" ht="24">
       <c r="A382" s="4">
         <v>46028</v>
       </c>
@@ -4686,7 +4686,7 @@
         <v>14.75</v>
       </c>
     </row>
-    <row r="383" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:3" ht="24">
       <c r="A383" s="4">
         <v>46029</v>
       </c>
@@ -4697,7 +4697,7 @@
         <v>15.38</v>
       </c>
     </row>
-    <row r="384" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:3" ht="24">
       <c r="A384" s="4">
         <v>46030</v>
       </c>
@@ -4708,7 +4708,7 @@
         <v>15.45</v>
       </c>
     </row>
-    <row r="385" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:3" ht="24">
       <c r="A385" s="4">
         <v>46031</v>
       </c>
@@ -4719,7 +4719,7 @@
         <v>14.49</v>
       </c>
     </row>
-    <row r="386" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:3" ht="24">
       <c r="A386" s="4">
         <v>46034</v>
       </c>
@@ -4730,7 +4730,7 @@
         <v>15.12</v>
       </c>
     </row>
-    <row r="387" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:3" ht="24">
       <c r="A387" s="4">
         <v>46035</v>
       </c>
@@ -4741,7 +4741,7 @@
         <v>15.98</v>
       </c>
     </row>
-    <row r="388" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:3" ht="24">
       <c r="A388" s="4">
         <v>46036</v>
       </c>
@@ -4752,7 +4752,7 @@
         <v>16.75</v>
       </c>
     </row>
-    <row r="389" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:3" ht="24">
       <c r="A389" s="4">
         <v>46037</v>
       </c>
@@ -4763,7 +4763,7 @@
         <v>15.84</v>
       </c>
     </row>
-    <row r="390" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:3" ht="24">
       <c r="A390" s="4">
         <v>46038</v>
       </c>
@@ -4774,7 +4774,7 @@
         <v>15.86</v>
       </c>
     </row>
-    <row r="391" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:3" ht="24">
       <c r="A391" s="4">
         <v>46041</v>
       </c>
@@ -4785,7 +4785,7 @@
         <v>18.84</v>
       </c>
     </row>
-    <row r="392" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:3" ht="24">
       <c r="A392" s="4">
         <v>46042</v>
       </c>
@@ -4796,7 +4796,7 @@
         <v>20.09</v>
       </c>
     </row>
-    <row r="393" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:3" ht="24">
       <c r="A393" s="4">
         <v>46043</v>
       </c>
@@ -4807,7 +4807,7 @@
         <v>16.899999999999999</v>
       </c>
     </row>
-    <row r="394" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:3" ht="24">
       <c r="A394" s="4">
         <v>46044</v>
       </c>
@@ -4818,7 +4818,7 @@
         <v>15.64</v>
       </c>
     </row>
-    <row r="395" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:3" ht="24">
       <c r="A395" s="4">
         <v>46045</v>
       </c>
@@ -4829,7 +4829,7 @@
         <v>16.09</v>
       </c>
     </row>
-    <row r="396" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:3" ht="24">
       <c r="A396" s="4">
         <v>46048</v>
       </c>
@@ -4840,7 +4840,7 @@
         <v>16.149999999999999</v>
       </c>
     </row>
-    <row r="397" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:3" ht="24">
       <c r="A397" s="4">
         <v>46049</v>
       </c>
@@ -4851,7 +4851,7 @@
         <v>16.350000000000001</v>
       </c>
     </row>
-    <row r="398" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:3" ht="24">
       <c r="A398" s="4">
         <v>46050</v>
       </c>
@@ -4862,7 +4862,7 @@
         <v>16.350000000000001</v>
       </c>
     </row>
-    <row r="399" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:3" ht="24">
       <c r="A399" s="4">
         <v>46051</v>
       </c>
@@ -4873,7 +4873,7 @@
         <v>16.88</v>
       </c>
     </row>
-    <row r="400" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:3" ht="24">
       <c r="A400" s="4">
         <v>46052</v>
       </c>
@@ -4884,7 +4884,7 @@
         <v>17.440000000000001</v>
       </c>
     </row>
-    <row r="401" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:3" ht="24">
       <c r="A401" s="4">
         <v>46055</v>
       </c>
@@ -4895,7 +4895,7 @@
         <v>16.34</v>
       </c>
     </row>
-    <row r="402" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:3" ht="24">
       <c r="A402" s="4">
         <v>46056</v>
       </c>
@@ -4906,7 +4906,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="403" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:3" ht="24">
       <c r="A403" s="4">
         <v>46057</v>
       </c>
@@ -4917,7 +4917,7 @@
         <v>18.64</v>
       </c>
     </row>
-    <row r="404" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:3" ht="24">
       <c r="A404" s="4">
         <v>46058</v>
       </c>
@@ -4928,7 +4928,7 @@
         <v>21.77</v>
       </c>
     </row>
-    <row r="405" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:3" ht="24">
       <c r="A405" s="4">
         <v>46059</v>
       </c>
@@ -4939,7 +4939,7 @@
         <v>17.66</v>
       </c>
     </row>
-    <row r="406" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:3" ht="24">
       <c r="A406" s="4">
         <v>46062</v>
       </c>
@@ -4950,7 +4950,7 @@
         <v>17.36</v>
       </c>
     </row>
-    <row r="407" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:3" ht="24">
       <c r="A407" s="4">
         <v>46063</v>
       </c>
@@ -4961,7 +4961,7 @@
         <v>17.79</v>
       </c>
     </row>
-    <row r="408" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:3" ht="24">
       <c r="A408" s="4">
         <v>46064</v>
       </c>
@@ -4972,7 +4972,7 @@
         <v>17.649999999999999</v>
       </c>
     </row>
-    <row r="409" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:3" ht="24">
       <c r="A409" s="4">
         <v>46065</v>
       </c>
@@ -4983,7 +4983,7 @@
         <v>20.82</v>
       </c>
     </row>
-    <row r="410" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:3" ht="24">
       <c r="A410" s="4">
         <v>46066</v>
       </c>
@@ -4994,7 +4994,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="411" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:3" ht="24">
       <c r="A411" s="4">
         <v>46069</v>
       </c>
@@ -5005,7 +5005,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="412" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:3" ht="24">
       <c r="A412" s="4">
         <v>46070</v>
       </c>
@@ -5016,7 +5016,7 @@
         <v>20.29</v>
       </c>
     </row>
-    <row r="413" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:3" ht="24">
       <c r="A413" s="4">
         <v>46071</v>
       </c>
@@ -5027,7 +5027,7 @@
         <v>19.62</v>
       </c>
     </row>
-    <row r="414" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:3" ht="24">
       <c r="A414" s="4">
         <v>46072</v>
       </c>
@@ -5038,7 +5038,7 @@
         <v>20.23</v>
       </c>
     </row>
-    <row r="415" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:3" ht="24">
       <c r="A415" s="4">
         <v>46073</v>
       </c>
@@ -5049,7 +5049,7 @@
         <v>19.09</v>
       </c>
     </row>
-    <row r="416" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:3" ht="24">
       <c r="A416" s="4">
         <v>46076</v>
       </c>
@@ -5060,7 +5060,7 @@
         <v>21.01</v>
       </c>
     </row>
-    <row r="417" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:3" ht="24">
       <c r="A417" s="4">
         <v>46077</v>
       </c>
@@ -5071,7 +5071,7 @@
         <v>19.55</v>
       </c>
     </row>
-    <row r="418" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:3" ht="24">
       <c r="A418" s="4">
         <v>46078</v>
       </c>
@@ -5082,7 +5082,7 @@
         <v>18.02</v>
       </c>
     </row>
-    <row r="419" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:3" ht="24">
       <c r="A419" s="4">
         <v>46079</v>
       </c>
@@ -5093,7 +5093,7 @@
         <v>18.63</v>
       </c>
     </row>
-    <row r="420" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:3" ht="24">
       <c r="A420" s="4">
         <v>46080</v>
       </c>
@@ -5104,142 +5104,172 @@
         <v>19.86</v>
       </c>
     </row>
-    <row r="421" spans="1:3" ht="24" x14ac:dyDescent="0.2">
-      <c r="A421" s="4"/>
-      <c r="B421" s="5"/>
-      <c r="C421" s="6"/>
-    </row>
-    <row r="422" spans="1:3" ht="24" x14ac:dyDescent="0.2">
-      <c r="A422" s="4"/>
-      <c r="B422" s="5"/>
-      <c r="C422" s="6"/>
-    </row>
-    <row r="423" spans="1:3" ht="24" x14ac:dyDescent="0.2">
-      <c r="A423" s="4"/>
-      <c r="B423" s="5"/>
-      <c r="C423" s="6"/>
-    </row>
-    <row r="424" spans="1:3" ht="24" x14ac:dyDescent="0.2">
-      <c r="A424" s="4"/>
-      <c r="B424" s="5"/>
-      <c r="C424" s="6"/>
-    </row>
-    <row r="425" spans="1:3" ht="24" x14ac:dyDescent="0.2">
-      <c r="A425" s="4"/>
-      <c r="B425" s="5"/>
-      <c r="C425" s="6"/>
-    </row>
-    <row r="426" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:3" ht="23">
+      <c r="A421" s="4">
+        <v>46083</v>
+      </c>
+      <c r="B421" s="5">
+        <v>60.822172522730369</v>
+      </c>
+      <c r="C421" s="6">
+        <v>21.44</v>
+      </c>
+    </row>
+    <row r="422" spans="1:3" ht="23">
+      <c r="A422" s="4">
+        <v>46084</v>
+      </c>
+      <c r="B422" s="5">
+        <v>61.705385387182574</v>
+      </c>
+      <c r="C422" s="6">
+        <v>23.57</v>
+      </c>
+    </row>
+    <row r="423" spans="1:3" ht="23">
+      <c r="A423" s="4">
+        <v>46085</v>
+      </c>
+      <c r="B423" s="5">
+        <v>58.266471003626428</v>
+      </c>
+      <c r="C423" s="6">
+        <v>21.15</v>
+      </c>
+    </row>
+    <row r="424" spans="1:3" ht="23">
+      <c r="A424" s="4">
+        <v>46086</v>
+      </c>
+      <c r="B424" s="5">
+        <v>59.186971398995546</v>
+      </c>
+      <c r="C424" s="6">
+        <v>23.75</v>
+      </c>
+    </row>
+    <row r="425" spans="1:3" ht="23">
+      <c r="A425" s="4">
+        <v>46087</v>
+      </c>
+      <c r="B425" s="5">
+        <v>62.484811680261231</v>
+      </c>
+      <c r="C425" s="6">
+        <v>29.49</v>
+      </c>
+    </row>
+    <row r="426" spans="1:3" ht="24">
       <c r="A426" s="4"/>
       <c r="B426" s="5"/>
       <c r="C426" s="6"/>
     </row>
-    <row r="427" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:3" ht="24">
       <c r="A427" s="4"/>
       <c r="B427" s="5"/>
       <c r="C427" s="6"/>
     </row>
-    <row r="428" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:3" ht="24">
       <c r="A428" s="4"/>
       <c r="B428" s="5"/>
       <c r="C428" s="6"/>
     </row>
-    <row r="429" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:3" ht="24">
       <c r="A429" s="4"/>
       <c r="B429" s="5"/>
       <c r="C429" s="6"/>
     </row>
-    <row r="430" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:3" ht="24">
       <c r="A430" s="4"/>
       <c r="B430" s="5"/>
       <c r="C430" s="6"/>
     </row>
-    <row r="431" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:3" ht="24">
       <c r="A431" s="4"/>
       <c r="B431" s="5"/>
       <c r="C431" s="6"/>
     </row>
-    <row r="432" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:3" ht="24">
       <c r="A432" s="4"/>
       <c r="B432" s="5"/>
       <c r="C432" s="6"/>
     </row>
-    <row r="433" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:3" ht="24">
       <c r="A433" s="4"/>
       <c r="B433" s="5"/>
       <c r="C433" s="6"/>
     </row>
-    <row r="434" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:3" ht="24">
       <c r="A434" s="4"/>
       <c r="B434" s="5"/>
       <c r="C434" s="6"/>
     </row>
-    <row r="435" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:3" ht="23">
       <c r="A435" s="4"/>
       <c r="B435" s="5"/>
       <c r="C435" s="6"/>
     </row>
-    <row r="436" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:3" ht="23">
       <c r="A436" s="4"/>
       <c r="B436" s="5"/>
       <c r="C436" s="6"/>
     </row>
-    <row r="437" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:3" ht="23">
       <c r="A437" s="4"/>
       <c r="B437" s="5"/>
       <c r="C437" s="6"/>
     </row>
-    <row r="438" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:3" ht="23">
       <c r="A438" s="4"/>
       <c r="B438" s="5"/>
       <c r="C438" s="6"/>
     </row>
-    <row r="439" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:3" ht="23">
       <c r="A439" s="4"/>
       <c r="B439" s="5"/>
       <c r="C439" s="6"/>
     </row>
-    <row r="440" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:3" ht="23">
       <c r="A440" s="4"/>
       <c r="B440" s="5"/>
       <c r="C440" s="6"/>
     </row>
-    <row r="441" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:3" ht="23">
       <c r="A441" s="4"/>
       <c r="B441" s="5"/>
       <c r="C441" s="6"/>
     </row>
-    <row r="442" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:3" ht="23">
       <c r="A442" s="4"/>
       <c r="B442" s="5"/>
       <c r="C442" s="6"/>
     </row>
-    <row r="443" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:3" ht="23">
       <c r="A443" s="4"/>
       <c r="B443" s="5"/>
       <c r="C443" s="6"/>
     </row>
-    <row r="444" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:3" ht="23">
       <c r="A444" s="4"/>
       <c r="B444" s="5"/>
       <c r="C444" s="6"/>
     </row>
-    <row r="445" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:3" ht="23">
       <c r="A445" s="4"/>
       <c r="B445" s="5"/>
       <c r="C445" s="6"/>
     </row>
-    <row r="446" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:3" ht="23">
       <c r="A446" s="4"/>
       <c r="B446" s="5"/>
       <c r="C446" s="6"/>
     </row>
-    <row r="447" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:3" ht="23">
       <c r="A447" s="4"/>
       <c r="B447" s="5"/>
       <c r="C447" s="6"/>
     </row>
-    <row r="448" spans="1:3" ht="24" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:3" ht="23">
       <c r="A448" s="4"/>
       <c r="B448" s="5"/>
       <c r="C448" s="6"/>
@@ -5252,7 +5282,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7E960FF-368A-3E44-924C-861BEDCA6476}">
   <dimension ref="A1:D448"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="40" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="40" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="15.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.5" style="1" bestFit="1" customWidth="1"/>
@@ -5260,7 +5290,7 @@
     <col min="4" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="40" customHeight="1">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -5271,7 +5301,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" ht="40" customHeight="1">
       <c r="A2" s="4">
         <v>45138</v>
       </c>
@@ -5283,7 +5313,7 @@
       </c>
       <c r="D2" s="2"/>
     </row>
-    <row r="3" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" ht="40" customHeight="1">
       <c r="A3" s="4">
         <v>45140</v>
       </c>
@@ -5294,7 +5324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" ht="40" customHeight="1">
       <c r="A4" s="4">
         <v>45146</v>
       </c>
@@ -5305,7 +5335,7 @@
         <v>-1.2456</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" ht="40" customHeight="1">
       <c r="A5" s="4">
         <v>45154</v>
       </c>
@@ -5316,7 +5346,7 @@
         <v>-2.0286</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" ht="40" customHeight="1">
       <c r="A6" s="4">
         <v>45162</v>
       </c>
@@ -5327,7 +5357,7 @@
         <v>-3.0272999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" ht="40" customHeight="1">
       <c r="A7" s="4">
         <v>45166</v>
       </c>
@@ -5338,7 +5368,7 @@
         <v>-2.5295000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" ht="40" customHeight="1">
       <c r="A8" s="4">
         <v>45167</v>
       </c>
@@ -5349,7 +5379,7 @@
         <v>-1.5078</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" ht="40" customHeight="1">
       <c r="A9" s="4">
         <v>45168</v>
       </c>
@@ -5360,7 +5390,7 @@
         <v>-0.45219999999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" ht="40" customHeight="1">
       <c r="A10" s="4">
         <v>45176</v>
       </c>
@@ -5371,7 +5401,7 @@
         <v>-2.1015999999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" ht="40" customHeight="1">
       <c r="A11" s="4">
         <v>45183</v>
       </c>
@@ -5382,7 +5412,7 @@
         <v>9.35E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" ht="40" customHeight="1">
       <c r="A12" s="4">
         <v>45184</v>
       </c>
@@ -5393,7 +5423,7 @@
         <v>-0.7621</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" ht="40" customHeight="1">
       <c r="A13" s="4">
         <v>45188</v>
       </c>
@@ -5404,7 +5434,7 @@
         <v>-1.6418999999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" ht="40" customHeight="1">
       <c r="A14" s="4">
         <v>45190</v>
       </c>
@@ -5415,7 +5445,7 @@
         <v>-3.2090000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" ht="40" customHeight="1">
       <c r="A15" s="4">
         <v>45191</v>
       </c>
@@ -5426,7 +5456,7 @@
         <v>-3.4251</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" ht="40" customHeight="1">
       <c r="A16" s="4">
         <v>45195</v>
       </c>
@@ -5437,7 +5467,7 @@
         <v>-4.5069999999999997</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" ht="40" customHeight="1">
       <c r="A17" s="4">
         <v>45196</v>
       </c>
@@ -5448,7 +5478,7 @@
         <v>-5.3798000000000004</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" ht="40" customHeight="1">
       <c r="A18" s="4">
         <v>45197</v>
       </c>
@@ -5459,7 +5489,7 @@
         <v>-4.4207000000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" ht="40" customHeight="1">
       <c r="A19" s="4">
         <v>45201</v>
       </c>
@@ -5470,7 +5500,7 @@
         <v>-5.1189</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" ht="40" customHeight="1">
       <c r="A20" s="4">
         <v>45202</v>
       </c>
@@ -5481,7 +5511,7 @@
         <v>-6.3071999999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" ht="40" customHeight="1">
       <c r="A21" s="4">
         <v>45205</v>
       </c>
@@ -5492,7 +5522,7 @@
         <v>-4.9684999999999997</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" ht="40" customHeight="1">
       <c r="A22" s="4">
         <v>45209</v>
       </c>
@@ -5503,7 +5533,7 @@
         <v>-3.2317</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" ht="40" customHeight="1">
       <c r="A23" s="4">
         <v>45212</v>
       </c>
@@ -5514,7 +5544,7 @@
         <v>-3.9274</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" ht="40" customHeight="1">
       <c r="A24" s="4">
         <v>45216</v>
       </c>
@@ -5525,7 +5555,7 @@
         <v>-2.8403999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" ht="40" customHeight="1">
       <c r="A25" s="4">
         <v>45217</v>
       </c>
@@ -5536,7 +5566,7 @@
         <v>-3.8610000000000002</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" ht="40" customHeight="1">
       <c r="A26" s="4">
         <v>45219</v>
       </c>
@@ -5547,7 +5577,7 @@
         <v>-6.3483000000000001</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" ht="40" customHeight="1">
       <c r="A27" s="4">
         <v>45225</v>
       </c>
@@ -5558,7 +5588,7 @@
         <v>-8.4063999999999997</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" ht="40" customHeight="1">
       <c r="A28" s="4">
         <v>45231</v>
       </c>
@@ -5569,7 +5599,7 @@
         <v>-7.3262</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" ht="40" customHeight="1">
       <c r="A29" s="4">
         <v>45232</v>
       </c>
@@ -5580,7 +5610,7 @@
         <v>-5.1478999999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" ht="40" customHeight="1">
       <c r="A30" s="4">
         <v>45233</v>
       </c>
@@ -5591,7 +5621,7 @@
         <v>-3.6587999999999998</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" ht="40" customHeight="1">
       <c r="A31" s="4">
         <v>45237</v>
       </c>
@@ -5602,7 +5632,7 @@
         <v>-3.3113000000000001</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" ht="40" customHeight="1">
       <c r="A32" s="4">
         <v>45243</v>
       </c>
@@ -5613,7 +5643,7 @@
         <v>-2.7271999999999998</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" ht="40" customHeight="1">
       <c r="A33" s="4">
         <v>45244</v>
       </c>
@@ -5624,7 +5654,7 @@
         <v>-0.56830000000000003</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" ht="40" customHeight="1">
       <c r="A34" s="4">
         <v>45246</v>
       </c>
@@ -5635,7 +5665,7 @@
         <v>-0.81030000000000002</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" ht="40" customHeight="1">
       <c r="A35" s="4">
         <v>45252</v>
       </c>
@@ -5646,7 +5676,7 @@
         <v>0.60340000000000005</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" ht="40" customHeight="1">
       <c r="A36" s="4">
         <v>45260</v>
       </c>
@@ -5657,7 +5687,7 @@
         <v>0.5706</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" ht="40" customHeight="1">
       <c r="A37" s="4">
         <v>45271</v>
       </c>
@@ -5668,7 +5698,7 @@
         <v>1.4257</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" ht="40" customHeight="1">
       <c r="A38" s="4">
         <v>45274</v>
       </c>
@@ -5679,7 +5709,7 @@
         <v>5.0162000000000004</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" ht="40" customHeight="1">
       <c r="A39" s="4">
         <v>45279</v>
       </c>
@@ -5690,7 +5720,7 @@
         <v>5.7617000000000003</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:3" ht="40" customHeight="1">
       <c r="A40" s="4">
         <v>45281</v>
       </c>
@@ -5701,7 +5731,7 @@
         <v>4.7279999999999998</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:3" ht="40" customHeight="1">
       <c r="A41" s="4">
         <v>45282</v>
       </c>
@@ -5712,7 +5742,7 @@
         <v>5.6628999999999996</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:3" ht="40" customHeight="1">
       <c r="A42" s="4">
         <v>45294</v>
       </c>
@@ -5723,7 +5753,7 @@
         <v>4.5598999999999998</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:3" ht="40" customHeight="1">
       <c r="A43" s="4">
         <v>45301</v>
       </c>
@@ -5734,7 +5764,7 @@
         <v>5.4307999999999996</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:3" ht="40" customHeight="1">
       <c r="A44" s="4">
         <v>45308</v>
       </c>
@@ -5745,7 +5775,7 @@
         <v>4.9009999999999998</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:3" ht="40" customHeight="1">
       <c r="A45" s="4">
         <v>45309</v>
       </c>
@@ -5756,7 +5786,7 @@
         <v>5.3244999999999996</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:3" ht="40" customHeight="1">
       <c r="A46" s="4">
         <v>45310</v>
       </c>
@@ -5767,7 +5797,7 @@
         <v>6.1246</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:3" ht="40" customHeight="1">
       <c r="A47" s="4">
         <v>45313</v>
       </c>
@@ -5778,7 +5808,7 @@
         <v>7.1440000000000001</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:3" ht="40" customHeight="1">
       <c r="A48" s="4">
         <v>45314</v>
       </c>
@@ -5789,7 +5819,7 @@
         <v>7.0568999999999997</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:3" ht="40" customHeight="1">
       <c r="A49" s="4">
         <v>45315</v>
       </c>
@@ -5800,7 +5830,7 @@
         <v>8.0669000000000004</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:3" ht="40" customHeight="1">
       <c r="A50" s="4">
         <v>45321</v>
       </c>
@@ -5811,7 +5841,7 @@
         <v>8.5023999999999997</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:3" ht="40" customHeight="1">
       <c r="A51" s="4">
         <v>45322</v>
       </c>
@@ -5822,7 +5852,7 @@
         <v>7.6855000000000002</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:3" ht="40" customHeight="1">
       <c r="A52" s="4">
         <v>45324</v>
       </c>
@@ -5833,7 +5863,7 @@
         <v>8.7094000000000005</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:3" ht="40" customHeight="1">
       <c r="A53" s="4">
         <v>45330</v>
       </c>
@@ -5844,7 +5874,7 @@
         <v>9.8277000000000001</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:3" ht="40" customHeight="1">
       <c r="A54" s="4">
         <v>45334</v>
       </c>
@@ -5855,7 +5885,7 @@
         <v>10.5977</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:3" ht="40" customHeight="1">
       <c r="A55" s="4">
         <v>45335</v>
       </c>
@@ -5866,7 +5896,7 @@
         <v>9.1773000000000007</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:3" ht="40" customHeight="1">
       <c r="A56" s="4">
         <v>45337</v>
       </c>
@@ -5877,7 +5907,7 @@
         <v>10.046900000000001</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:3" ht="40" customHeight="1">
       <c r="A57" s="4">
         <v>45342</v>
       </c>
@@ -5888,7 +5918,7 @@
         <v>9.1170000000000009</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:3" ht="40" customHeight="1">
       <c r="A58" s="4">
         <v>45344</v>
       </c>
@@ -5899,7 +5929,7 @@
         <v>10.9582</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:3" ht="40" customHeight="1">
       <c r="A59" s="4">
         <v>45345</v>
       </c>
@@ -5910,7 +5940,7 @@
         <v>12.8368</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:3" ht="40" customHeight="1">
       <c r="A60" s="4">
         <v>45355</v>
       </c>
@@ -5921,7 +5951,7 @@
         <v>13.5024</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:3" ht="40" customHeight="1">
       <c r="A61" s="4">
         <v>45356</v>
       </c>
@@ -5932,7 +5962,7 @@
         <v>12.6159</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:3" ht="40" customHeight="1">
       <c r="A62" s="4">
         <v>45357</v>
       </c>
@@ -5943,7 +5973,7 @@
         <v>13.2926</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:3" ht="40" customHeight="1">
       <c r="A63" s="4">
         <v>45359</v>
       </c>
@@ -5954,7 +5984,7 @@
         <v>14.451599999999999</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:3" ht="40" customHeight="1">
       <c r="A64" s="4">
         <v>45362</v>
       </c>
@@ -5965,7 +5995,7 @@
         <v>13.0746</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:3" ht="40" customHeight="1">
       <c r="A65" s="4">
         <v>45363</v>
       </c>
@@ -5976,7 +6006,7 @@
         <v>14.0412</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:3" ht="40" customHeight="1">
       <c r="A66" s="4">
         <v>45366</v>
       </c>
@@ -5987,7 +6017,7 @@
         <v>13.119</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:3" ht="40" customHeight="1">
       <c r="A67" s="4">
         <v>45370</v>
       </c>
@@ -5998,7 +6028,7 @@
         <v>13.926399999999999</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:3" ht="40" customHeight="1">
       <c r="A68" s="4">
         <v>45372</v>
       </c>
@@ -6009,7 +6039,7 @@
         <v>15.7384</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:3" ht="40" customHeight="1">
       <c r="A69" s="4">
         <v>45384</v>
       </c>
@@ -6020,7 +6050,7 @@
         <v>14.2514</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:3" ht="40" customHeight="1">
       <c r="A70" s="4">
         <v>45386</v>
       </c>
@@ -6031,7 +6061,7 @@
         <v>15.3805</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:3" ht="40" customHeight="1">
       <c r="A71" s="4">
         <v>45387</v>
       </c>
@@ -6042,7 +6072,7 @@
         <v>14.3849</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:3" ht="40" customHeight="1">
       <c r="A72" s="4">
         <v>45393</v>
       </c>
@@ -6053,7 +6083,7 @@
         <v>13.36</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:3" ht="40" customHeight="1">
       <c r="A73" s="4">
         <v>45394</v>
       </c>
@@ -6064,7 +6094,7 @@
         <v>13.2926</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:3" ht="40" customHeight="1">
       <c r="A74" s="4">
         <v>45398</v>
       </c>
@@ -6075,7 +6105,7 @@
         <v>11.327400000000001</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:3" ht="40" customHeight="1">
       <c r="A75" s="4">
         <v>45404</v>
       </c>
@@ -6086,7 +6116,7 @@
         <v>9.8026999999999997</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:3" ht="40" customHeight="1">
       <c r="A76" s="4">
         <v>45405</v>
       </c>
@@ -6097,7 +6127,7 @@
         <v>11.631500000000001</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:3" ht="40" customHeight="1">
       <c r="A77" s="4">
         <v>45407</v>
       </c>
@@ -6108,7 +6138,7 @@
         <v>10.3102</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:3" ht="40" customHeight="1">
       <c r="A78" s="4">
         <v>45408</v>
       </c>
@@ -6119,7 +6149,7 @@
         <v>12.246700000000001</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:3" ht="40" customHeight="1">
       <c r="A79" s="4">
         <v>45413</v>
       </c>
@@ -6130,7 +6160,7 @@
         <v>10.7065</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:3" ht="40" customHeight="1">
       <c r="A80" s="4">
         <v>45415</v>
       </c>
@@ -6141,7 +6171,7 @@
         <v>12.2126</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:3" ht="40" customHeight="1">
       <c r="A81" s="4">
         <v>45418</v>
       </c>
@@ -6152,7 +6182,7 @@
         <v>13.181800000000001</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:3" ht="40" customHeight="1">
       <c r="A82" s="4">
         <v>45419</v>
       </c>
@@ -6163,7 +6193,7 @@
         <v>13.912100000000001</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:3" ht="40" customHeight="1">
       <c r="A83" s="4">
         <v>45422</v>
       </c>
@@ -6174,7 +6204,7 @@
         <v>14.513400000000001</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:3" ht="40" customHeight="1">
       <c r="A84" s="4">
         <v>45427</v>
       </c>
@@ -6185,7 +6215,7 @@
         <v>15.517200000000001</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:3" ht="40" customHeight="1">
       <c r="A85" s="4">
         <v>45428</v>
       </c>
@@ -6196,7 +6226,7 @@
         <v>16.2821</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:3" ht="40" customHeight="1">
       <c r="A86" s="4">
         <v>45443</v>
       </c>
@@ -6207,7 +6237,7 @@
         <v>14.079499999999999</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:3" ht="40" customHeight="1">
       <c r="A87" s="4">
         <v>45446</v>
       </c>
@@ -6218,7 +6248,7 @@
         <v>15.035500000000001</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:3" ht="40" customHeight="1">
       <c r="A88" s="4">
         <v>45448</v>
       </c>
@@ -6229,7 +6259,7 @@
         <v>15.945</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:3" ht="40" customHeight="1">
       <c r="A89" s="4">
         <v>45449</v>
       </c>
@@ -6240,7 +6270,7 @@
         <v>16.5809</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:3" ht="40" customHeight="1">
       <c r="A90" s="4">
         <v>45455</v>
       </c>
@@ -6251,7 +6281,7 @@
         <v>18.098199999999999</v>
       </c>
     </row>
-    <row r="91" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:3" ht="40" customHeight="1">
       <c r="A91" s="4">
         <v>45463</v>
       </c>
@@ -6262,7 +6292,7 @@
         <v>20.316400000000002</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:3" ht="40" customHeight="1">
       <c r="A92" s="4">
         <v>45471</v>
       </c>
@@ -6273,7 +6303,7 @@
         <v>20.1206</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:3" ht="40" customHeight="1">
       <c r="A93" s="4">
         <v>45474</v>
       </c>
@@ -6284,7 +6314,7 @@
         <v>19.330100000000002</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:3" ht="40" customHeight="1">
       <c r="A94" s="4">
         <v>45476</v>
       </c>
@@ -6295,7 +6325,7 @@
         <v>20.4709</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:3" ht="40" customHeight="1">
       <c r="A95" s="4">
         <v>45481</v>
       </c>
@@ -6306,7 +6336,7 @@
         <v>21.372399999999999</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:3" ht="40" customHeight="1">
       <c r="A96" s="4">
         <v>45484</v>
       </c>
@@ -6317,7 +6347,7 @@
         <v>21.913</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:3" ht="40" customHeight="1">
       <c r="A97" s="4">
         <v>45491</v>
       </c>
@@ -6328,7 +6358,7 @@
         <v>20.962800000000001</v>
       </c>
     </row>
-    <row r="98" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:3" ht="40" customHeight="1">
       <c r="A98" s="4">
         <v>45497</v>
       </c>
@@ -6339,7 +6369,7 @@
         <v>19.348299999999998</v>
       </c>
     </row>
-    <row r="99" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:3" ht="40" customHeight="1">
       <c r="A99" s="4">
         <v>45503</v>
       </c>
@@ -6350,7 +6380,7 @@
         <v>18.364100000000001</v>
       </c>
     </row>
-    <row r="100" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:3" ht="40" customHeight="1">
       <c r="A100" s="4">
         <v>45504</v>
       </c>
@@ -6361,7 +6391,7 @@
         <v>20.178999999999998</v>
       </c>
     </row>
-    <row r="101" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:3" ht="40" customHeight="1">
       <c r="A101" s="4">
         <v>45505</v>
       </c>
@@ -6372,7 +6402,7 @@
         <v>19.343699999999998</v>
       </c>
     </row>
-    <row r="102" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:3" ht="40" customHeight="1">
       <c r="A102" s="4">
         <v>45506</v>
       </c>
@@ -6383,7 +6413,7 @@
         <v>17.222100000000001</v>
       </c>
     </row>
-    <row r="103" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:3" ht="40" customHeight="1">
       <c r="A103" s="4">
         <v>45509</v>
       </c>
@@ -6394,7 +6424,7 @@
         <v>13.5562</v>
       </c>
     </row>
-    <row r="104" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:3" ht="40" customHeight="1">
       <c r="A104" s="4">
         <v>45510</v>
       </c>
@@ -6405,7 +6435,7 @@
         <v>15.361599999999999</v>
       </c>
     </row>
-    <row r="105" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:3" ht="40" customHeight="1">
       <c r="A105" s="4">
         <v>45517</v>
       </c>
@@ -6416,7 +6446,7 @@
         <v>17.434899999999999</v>
       </c>
     </row>
-    <row r="106" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:3" ht="40" customHeight="1">
       <c r="A106" s="4">
         <v>45518</v>
       </c>
@@ -6427,7 +6457,7 @@
         <v>18.364100000000001</v>
       </c>
     </row>
-    <row r="107" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:3" ht="40" customHeight="1">
       <c r="A107" s="4">
         <v>45519</v>
       </c>
@@ -6438,7 +6468,7 @@
         <v>20.053100000000001</v>
       </c>
     </row>
-    <row r="108" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:3" ht="40" customHeight="1">
       <c r="A108" s="4">
         <v>45523</v>
       </c>
@@ -6449,7 +6479,7 @@
         <v>20.949400000000001</v>
       </c>
     </row>
-    <row r="109" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:3" ht="40" customHeight="1">
       <c r="A109" s="4">
         <v>45525</v>
       </c>
@@ -6460,7 +6490,7 @@
         <v>21.479900000000001</v>
       </c>
     </row>
-    <row r="110" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:3" ht="40" customHeight="1">
       <c r="A110" s="4">
         <v>45533</v>
       </c>
@@ -6471,7 +6501,7 @@
         <v>21.815799999999999</v>
       </c>
     </row>
-    <row r="111" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:3" ht="40" customHeight="1">
       <c r="A111" s="4">
         <v>45538</v>
       </c>
@@ -6482,7 +6512,7 @@
         <v>20.439499999999999</v>
       </c>
     </row>
-    <row r="112" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:3" ht="40" customHeight="1">
       <c r="A112" s="4">
         <v>45539</v>
       </c>
@@ -6493,7 +6523,7 @@
         <v>19.8187</v>
       </c>
     </row>
-    <row r="113" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:3" ht="40" customHeight="1">
       <c r="A113" s="4">
         <v>45540</v>
       </c>
@@ -6504,7 +6534,7 @@
         <v>19.0304</v>
       </c>
     </row>
-    <row r="114" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:3" ht="40" customHeight="1">
       <c r="A114" s="4">
         <v>45541</v>
       </c>
@@ -6515,7 +6545,7 @@
         <v>17.813099999999999</v>
       </c>
     </row>
-    <row r="115" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:3" ht="40" customHeight="1">
       <c r="A115" s="4">
         <v>45544</v>
       </c>
@@ -6526,7 +6556,7 @@
         <v>18.766200000000001</v>
       </c>
     </row>
-    <row r="116" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:3" ht="40" customHeight="1">
       <c r="A116" s="4">
         <v>45546</v>
       </c>
@@ -6537,7 +6567,7 @@
         <v>17.886800000000001</v>
       </c>
     </row>
-    <row r="117" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:3" ht="40" customHeight="1">
       <c r="A117" s="4">
         <v>45547</v>
       </c>
@@ -6548,7 +6578,7 @@
         <v>21.3324</v>
       </c>
     </row>
-    <row r="118" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:3" ht="40" customHeight="1">
       <c r="A118" s="4">
         <v>45548</v>
       </c>
@@ -6559,7 +6589,7 @@
         <v>22.613199999999999</v>
       </c>
     </row>
-    <row r="119" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:3" ht="40" customHeight="1">
       <c r="A119" s="4">
         <v>45554</v>
       </c>
@@ -6570,7 +6600,7 @@
         <v>23.851800000000001</v>
       </c>
     </row>
-    <row r="120" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:3" ht="40" customHeight="1">
       <c r="A120" s="4">
         <v>45562</v>
       </c>
@@ -6581,7 +6611,7 @@
         <v>24.68</v>
       </c>
     </row>
-    <row r="121" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:3" ht="40" customHeight="1">
       <c r="A121" s="4">
         <v>45566</v>
       </c>
@@ -6592,7 +6622,7 @@
         <v>23.55</v>
       </c>
     </row>
-    <row r="122" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:3" ht="40" customHeight="1">
       <c r="A122" s="4">
         <v>45573</v>
       </c>
@@ -6603,7 +6633,7 @@
         <v>24.18</v>
       </c>
     </row>
-    <row r="123" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:3" ht="40" customHeight="1">
       <c r="A123" s="4">
         <v>45574</v>
       </c>
@@ -6614,7 +6644,7 @@
         <v>24.88</v>
       </c>
     </row>
-    <row r="124" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:3" ht="40" customHeight="1">
       <c r="A124" s="4">
         <v>45576</v>
       </c>
@@ -6625,7 +6655,7 @@
         <v>25.41</v>
       </c>
     </row>
-    <row r="125" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:3" ht="40" customHeight="1">
       <c r="A125" s="4">
         <v>45579</v>
       </c>
@@ -6636,7 +6666,7 @@
         <v>26.11</v>
       </c>
     </row>
-    <row r="126" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:3" ht="40" customHeight="1">
       <c r="A126" s="4">
         <v>45589</v>
       </c>
@@ -6647,7 +6677,7 @@
         <v>25.02</v>
       </c>
     </row>
-    <row r="127" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:3" ht="40" customHeight="1">
       <c r="A127" s="4">
         <v>45590</v>
       </c>
@@ -6658,7 +6688,7 @@
         <v>25.94</v>
       </c>
     </row>
-    <row r="128" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:3" ht="40" customHeight="1">
       <c r="A128" s="4">
         <v>45596</v>
       </c>
@@ -6669,7 +6699,7 @@
         <v>23.62</v>
       </c>
     </row>
-    <row r="129" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:3" ht="40" customHeight="1">
       <c r="A129" s="4">
         <v>45601</v>
       </c>
@@ -6680,7 +6710,7 @@
         <v>24.19</v>
       </c>
     </row>
-    <row r="130" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:3" ht="40" customHeight="1">
       <c r="A130" s="4">
         <v>45602</v>
       </c>
@@ -6691,7 +6721,7 @@
         <v>26.4</v>
       </c>
     </row>
-    <row r="131" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:3" ht="40" customHeight="1">
       <c r="A131" s="4">
         <v>45603</v>
       </c>
@@ -6702,7 +6732,7 @@
         <v>27.69</v>
       </c>
     </row>
-    <row r="132" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:3" ht="40" customHeight="1">
       <c r="A132" s="4">
         <v>45611</v>
       </c>
@@ -6713,7 +6743,7 @@
         <v>26.11</v>
       </c>
     </row>
-    <row r="133" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:3" ht="40" customHeight="1">
       <c r="A133" s="4">
         <v>45615</v>
       </c>
@@ -6724,7 +6754,7 @@
         <v>26.54</v>
       </c>
     </row>
-    <row r="134" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:3" ht="40" customHeight="1">
       <c r="A134" s="4">
         <v>45617</v>
       </c>
@@ -6735,7 +6765,7 @@
         <v>27.21</v>
       </c>
     </row>
-    <row r="135" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:3" ht="40" customHeight="1">
       <c r="A135" s="4">
         <v>45622</v>
       </c>
@@ -6746,7 +6776,7 @@
         <v>28.26</v>
       </c>
     </row>
-    <row r="136" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:3" ht="40" customHeight="1">
       <c r="A136" s="4">
         <v>45625</v>
       </c>
@@ -6757,7 +6787,7 @@
         <v>28.62</v>
       </c>
     </row>
-    <row r="137" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:3" ht="40" customHeight="1">
       <c r="A137" s="4">
         <v>45630</v>
       </c>
@@ -6768,7 +6798,7 @@
         <v>29.23</v>
       </c>
     </row>
-    <row r="138" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:3" ht="40" customHeight="1">
       <c r="A138" s="4">
         <v>45645</v>
       </c>
@@ -6779,7 +6809,7 @@
         <v>25.7</v>
       </c>
     </row>
-    <row r="139" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:3" ht="40" customHeight="1">
       <c r="A139" s="4">
         <v>45646</v>
       </c>
@@ -6790,7 +6820,7 @@
         <v>24.86</v>
       </c>
     </row>
-    <row r="140" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:3" ht="40" customHeight="1">
       <c r="A140" s="4">
         <v>45663</v>
       </c>
@@ -6801,7 +6831,7 @@
         <v>28.74</v>
       </c>
     </row>
-    <row r="141" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:3" ht="40" customHeight="1">
       <c r="A141" s="4">
         <v>45664</v>
       </c>
@@ -6812,7 +6842,7 @@
         <v>26.82</v>
       </c>
     </row>
-    <row r="142" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:3" ht="40" customHeight="1">
       <c r="A142" s="4">
         <v>45667</v>
       </c>
@@ -6823,7 +6853,7 @@
         <v>25.78</v>
       </c>
     </row>
-    <row r="143" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:3" ht="40" customHeight="1">
       <c r="A143" s="4">
         <v>45670</v>
       </c>
@@ -6834,7 +6864,7 @@
         <v>25.07</v>
       </c>
     </row>
-    <row r="144" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:3" ht="40" customHeight="1">
       <c r="A144" s="4">
         <v>45672</v>
       </c>
@@ -6845,7 +6875,7 @@
         <v>27.42</v>
       </c>
     </row>
-    <row r="145" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:3" ht="40" customHeight="1">
       <c r="A145" s="4">
         <v>45674</v>
       </c>
@@ -6856,7 +6886,7 @@
         <v>28.49</v>
       </c>
     </row>
-    <row r="146" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:3" ht="40" customHeight="1">
       <c r="A146" s="4">
         <v>45679</v>
       </c>
@@ -6867,7 +6897,7 @@
         <v>29.97</v>
       </c>
     </row>
-    <row r="147" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:3" ht="40" customHeight="1">
       <c r="A147" s="4">
         <v>45684</v>
       </c>
@@ -6878,7 +6908,7 @@
         <v>28.32</v>
       </c>
     </row>
-    <row r="148" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:3" ht="40" customHeight="1">
       <c r="A148" s="4">
         <v>45685</v>
       </c>
@@ -6889,7 +6919,7 @@
         <v>29.1</v>
       </c>
     </row>
-    <row r="149" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:3" ht="40" customHeight="1">
       <c r="A149" s="4">
         <v>45688</v>
       </c>
@@ -6900,7 +6930,7 @@
         <v>30.04</v>
       </c>
     </row>
-    <row r="150" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:3" ht="40" customHeight="1">
       <c r="A150" s="4">
         <v>45691</v>
       </c>
@@ -6911,7 +6941,7 @@
         <v>27.17</v>
       </c>
     </row>
-    <row r="151" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:3" ht="40" customHeight="1">
       <c r="A151" s="4">
         <v>45692</v>
       </c>
@@ -6922,7 +6952,7 @@
         <v>28.72</v>
       </c>
     </row>
-    <row r="152" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:3" ht="40" customHeight="1">
       <c r="A152" s="4">
         <v>45694</v>
       </c>
@@ -6933,7 +6963,7 @@
         <v>29.38</v>
       </c>
     </row>
-    <row r="153" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:3" ht="40" customHeight="1">
       <c r="A153" s="4">
         <v>45695</v>
       </c>
@@ -6944,7 +6974,7 @@
         <v>28.62</v>
       </c>
     </row>
-    <row r="154" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:3" ht="40" customHeight="1">
       <c r="A154" s="4">
         <v>45698</v>
       </c>
@@ -6955,7 +6985,7 @@
         <v>29.26</v>
       </c>
     </row>
-    <row r="155" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:3" ht="40" customHeight="1">
       <c r="A155" s="4">
         <v>45699</v>
       </c>
@@ -6966,7 +6996,7 @@
         <v>29.32</v>
       </c>
     </row>
-    <row r="156" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:3" ht="40" customHeight="1">
       <c r="A156" s="4">
         <v>45700</v>
       </c>
@@ -6977,7 +7007,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="157" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:3" ht="40" customHeight="1">
       <c r="A157" s="4">
         <v>45701</v>
       </c>
@@ -6988,7 +7018,7 @@
         <v>30.02</v>
       </c>
     </row>
-    <row r="158" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:3" ht="40" customHeight="1">
       <c r="A158" s="4">
         <v>45702</v>
       </c>
@@ -6999,7 +7029,7 @@
         <v>29.97</v>
       </c>
     </row>
-    <row r="159" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:3" ht="40" customHeight="1">
       <c r="A159" s="4">
         <v>45705</v>
       </c>
@@ -7010,7 +7040,7 @@
         <v>29.971327959071754</v>
       </c>
     </row>
-    <row r="160" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:3" ht="40" customHeight="1">
       <c r="A160" s="4">
         <v>45706</v>
       </c>
@@ -7021,7 +7051,7 @@
         <v>30.211580543331717</v>
       </c>
     </row>
-    <row r="161" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:3" ht="40" customHeight="1">
       <c r="A161" s="4">
         <v>45707</v>
       </c>
@@ -7032,7 +7062,7 @@
         <v>30.475599056125596</v>
       </c>
     </row>
-    <row r="162" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:3" ht="40" customHeight="1">
       <c r="A162" s="4">
         <v>45708</v>
       </c>
@@ -7043,7 +7073,7 @@
         <v>30.044686563657574</v>
       </c>
     </row>
-    <row r="163" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:3" ht="40" customHeight="1">
       <c r="A163" s="4">
         <v>45709</v>
       </c>
@@ -7054,7 +7084,7 @@
         <v>28.277347808841842</v>
       </c>
     </row>
-    <row r="164" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:3" ht="40" customHeight="1">
       <c r="A164" s="4">
         <v>45712</v>
       </c>
@@ -7065,7 +7095,7 @@
         <v>27.807677999735585</v>
       </c>
     </row>
-    <row r="165" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:3" ht="40" customHeight="1">
       <c r="A165" s="4">
         <v>45713</v>
       </c>
@@ -7076,7 +7106,7 @@
         <v>27.293924598566065</v>
       </c>
     </row>
-    <row r="166" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:3" ht="40" customHeight="1">
       <c r="A166" s="4">
         <v>45714</v>
       </c>
@@ -7087,7 +7117,7 @@
         <v>27.306486623581023</v>
       </c>
     </row>
-    <row r="167" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:3" ht="40" customHeight="1">
       <c r="A167" s="4">
         <v>45715</v>
       </c>
@@ -7098,7 +7128,7 @@
         <v>25.711112193735332</v>
       </c>
     </row>
-    <row r="168" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:3" ht="40" customHeight="1">
       <c r="A168" s="4">
         <v>45716</v>
       </c>
@@ -7109,7 +7139,7 @@
         <v>27.180795304871548</v>
       </c>
     </row>
-    <row r="169" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:3" ht="40" customHeight="1">
       <c r="A169" s="4">
         <v>45719</v>
       </c>
@@ -7120,7 +7150,7 @@
         <v>25.446990032864019</v>
       </c>
     </row>
-    <row r="170" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:3" ht="40" customHeight="1">
       <c r="A170" s="4">
         <v>45720</v>
       </c>
@@ -7131,7 +7161,7 @@
         <v>24.223825065134069</v>
       </c>
     </row>
-    <row r="171" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:3" ht="40" customHeight="1">
       <c r="A171" s="4">
         <v>45721</v>
       </c>
@@ -7142,7 +7172,7 @@
         <v>25.284763221329332</v>
       </c>
     </row>
-    <row r="172" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:3" ht="40" customHeight="1">
       <c r="A172" s="4">
         <v>45722</v>
       </c>
@@ -7153,7 +7183,7 @@
         <v>23.473978671945069</v>
       </c>
     </row>
-    <row r="173" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:3" ht="40" customHeight="1">
       <c r="A173" s="4">
         <v>45723</v>
       </c>
@@ -7164,7 +7194,7 @@
         <v>23.99037201716752</v>
       </c>
     </row>
-    <row r="174" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:3" ht="40" customHeight="1">
       <c r="A174" s="4">
         <v>45726</v>
       </c>
@@ -7175,7 +7205,7 @@
         <v>21.265742554012483</v>
       </c>
     </row>
-    <row r="175" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:3" ht="40" customHeight="1">
       <c r="A175" s="4">
         <v>45727</v>
       </c>
@@ -7186,7 +7216,7 @@
         <v>20.484331598856667</v>
       </c>
     </row>
-    <row r="176" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:3" ht="40" customHeight="1">
       <c r="A176" s="4">
         <v>45728</v>
       </c>
@@ -7197,7 +7227,7 @@
         <v>20.980677107752204</v>
       </c>
     </row>
-    <row r="177" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:3" ht="40" customHeight="1">
       <c r="A177" s="4">
         <v>45729</v>
       </c>
@@ -7208,7 +7238,7 @@
         <v>19.592795233061427</v>
       </c>
     </row>
-    <row r="178" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:3" ht="40" customHeight="1">
       <c r="A178" s="4">
         <v>45730</v>
       </c>
@@ -7219,7 +7249,7 @@
         <v>21.60763840911175</v>
       </c>
     </row>
-    <row r="179" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:3" ht="40" customHeight="1">
       <c r="A179" s="4">
         <v>45733</v>
       </c>
@@ -7230,7 +7260,7 @@
         <v>22.318756443012568</v>
       </c>
     </row>
-    <row r="180" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:3" ht="40" customHeight="1">
       <c r="A180" s="4">
         <v>45734</v>
       </c>
@@ -7241,7 +7271,7 @@
         <v>22.124915243940873</v>
       </c>
     </row>
-    <row r="181" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:3" ht="40" customHeight="1">
       <c r="A181" s="4">
         <v>45735</v>
       </c>
@@ -7252,7 +7282,7 @@
         <v>23.186421833852929</v>
       </c>
     </row>
-    <row r="182" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:3" ht="40" customHeight="1">
       <c r="A182" s="4">
         <v>45736</v>
       </c>
@@ -7263,7 +7293,7 @@
         <v>22.889283752002022</v>
       </c>
     </row>
-    <row r="183" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:3" ht="40" customHeight="1">
       <c r="A183" s="4">
         <v>45737</v>
       </c>
@@ -7274,7 +7304,7 @@
         <v>22.985513310648209</v>
       </c>
     </row>
-    <row r="184" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:3" ht="40" customHeight="1">
       <c r="A184" s="4">
         <v>45740</v>
       </c>
@@ -7285,7 +7315,7 @@
         <v>24.67</v>
       </c>
     </row>
-    <row r="185" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:3" ht="40" customHeight="1">
       <c r="A185" s="4">
         <v>45741</v>
       </c>
@@ -7296,7 +7326,7 @@
         <v>24.86</v>
       </c>
     </row>
-    <row r="186" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:3" ht="40" customHeight="1">
       <c r="A186" s="4">
         <v>45742</v>
       </c>
@@ -7307,7 +7337,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="187" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:3" ht="40" customHeight="1">
       <c r="A187" s="4">
         <v>45743</v>
       </c>
@@ -7318,7 +7348,7 @@
         <v>23.35</v>
       </c>
     </row>
-    <row r="188" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:3" ht="40" customHeight="1">
       <c r="A188" s="4">
         <v>45744</v>
       </c>
@@ -7329,7 +7359,7 @@
         <v>21.31</v>
       </c>
     </row>
-    <row r="189" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:3" ht="40" customHeight="1">
       <c r="A189" s="4">
         <v>45747</v>
       </c>
@@ -7340,7 +7370,7 @@
         <v>21.842291960211625</v>
       </c>
     </row>
-    <row r="190" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:3" ht="40" customHeight="1">
       <c r="A190" s="4">
         <v>45748</v>
       </c>
@@ -7351,7 +7381,7 @@
         <v>22.217477234020642</v>
       </c>
     </row>
-    <row r="191" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:3" ht="40" customHeight="1">
       <c r="A191" s="4">
         <v>45749</v>
       </c>
@@ -7362,7 +7392,7 @@
         <v>22.880531016766646</v>
       </c>
     </row>
-    <row r="192" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:3" ht="40" customHeight="1">
       <c r="A192" s="4">
         <v>45750</v>
       </c>
@@ -7373,7 +7403,7 @@
         <v>17.863776999885843</v>
       </c>
     </row>
-    <row r="193" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:3" ht="40" customHeight="1">
       <c r="A193" s="4">
         <v>45751</v>
       </c>
@@ -7384,7 +7414,7 @@
         <v>11.74406452790994</v>
       </c>
     </row>
-    <row r="194" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:3" ht="40" customHeight="1">
       <c r="A194" s="4">
         <v>45754</v>
       </c>
@@ -7395,7 +7425,7 @@
         <v>11.49</v>
       </c>
     </row>
-    <row r="195" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:3" ht="40" customHeight="1">
       <c r="A195" s="4">
         <v>45755</v>
       </c>
@@ -7406,7 +7436,7 @@
         <v>9.9700000000000006</v>
       </c>
     </row>
-    <row r="196" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:3" ht="40" customHeight="1">
       <c r="A196" s="4">
         <v>45756</v>
       </c>
@@ -7417,7 +7447,7 @@
         <v>18.93</v>
       </c>
     </row>
-    <row r="197" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:3" ht="40" customHeight="1">
       <c r="A197" s="4">
         <v>45757</v>
       </c>
@@ -7428,7 +7458,7 @@
         <v>15.43</v>
       </c>
     </row>
-    <row r="198" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:3" ht="40" customHeight="1">
       <c r="A198" s="4">
         <v>45758</v>
       </c>
@@ -7439,7 +7469,7 @@
         <v>17.100000000000001</v>
       </c>
     </row>
-    <row r="199" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:3" ht="40" customHeight="1">
       <c r="A199" s="4">
         <v>45761</v>
       </c>
@@ -7450,7 +7480,7 @@
         <v>18.010923759318938</v>
       </c>
     </row>
-    <row r="200" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:3" ht="40" customHeight="1">
       <c r="A200" s="4">
         <v>45762</v>
       </c>
@@ -7461,7 +7491,7 @@
         <v>17.780911697289426</v>
       </c>
     </row>
-    <row r="201" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:3" ht="40" customHeight="1">
       <c r="A201" s="4">
         <v>45763</v>
       </c>
@@ -7472,7 +7502,7 @@
         <v>15.498345671476349</v>
       </c>
     </row>
-    <row r="202" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:3" ht="40" customHeight="1">
       <c r="A202" s="4">
         <v>45764</v>
       </c>
@@ -7483,7 +7513,7 @@
         <v>15.630191054798287</v>
       </c>
     </row>
-    <row r="203" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:3" ht="40" customHeight="1">
       <c r="A203" s="4">
         <v>45769</v>
       </c>
@@ -7494,7 +7524,7 @@
         <v>15.667829258018443</v>
       </c>
     </row>
-    <row r="204" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:3" ht="40" customHeight="1">
       <c r="A204" s="4">
         <v>45770</v>
       </c>
@@ -7505,7 +7535,7 @@
         <v>17.291529372479239</v>
       </c>
     </row>
-    <row r="205" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:3" ht="40" customHeight="1">
       <c r="A205" s="4">
         <v>45771</v>
       </c>
@@ -7516,7 +7546,7 @@
         <v>19.298377627116025</v>
       </c>
     </row>
-    <row r="206" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:3" ht="40" customHeight="1">
       <c r="A206" s="4">
         <v>45772</v>
       </c>
@@ -7527,7 +7557,7 @@
         <v>19.994520027988962</v>
       </c>
     </row>
-    <row r="207" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:3" ht="40" customHeight="1">
       <c r="A207" s="4">
         <v>45775</v>
       </c>
@@ -7538,7 +7568,7 @@
         <v>20.053064084062015</v>
       </c>
     </row>
-    <row r="208" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:3" ht="40" customHeight="1">
       <c r="A208" s="4">
         <v>45776</v>
       </c>
@@ -7549,7 +7579,7 @@
         <v>20.605291226534135</v>
       </c>
     </row>
-    <row r="209" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:3" ht="40" customHeight="1">
       <c r="A209" s="4">
         <v>45777</v>
       </c>
@@ -7560,7 +7590,7 @@
         <v>20.663478905816177</v>
       </c>
     </row>
-    <row r="210" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:3" ht="40" customHeight="1">
       <c r="A210" s="4">
         <v>45779</v>
       </c>
@@ -7571,7 +7601,7 @@
         <v>22.823619556327209</v>
       </c>
     </row>
-    <row r="211" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:3" ht="40" customHeight="1">
       <c r="A211" s="4">
         <v>45782</v>
       </c>
@@ -7582,7 +7612,7 @@
         <v>22.169003067598293</v>
       </c>
     </row>
-    <row r="212" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:3" ht="40" customHeight="1">
       <c r="A212" s="4">
         <v>45783</v>
       </c>
@@ -7593,7 +7623,7 @@
         <v>21.354659111686829</v>
       </c>
     </row>
-    <row r="213" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:3" ht="40" customHeight="1">
       <c r="A213" s="4">
         <v>45784</v>
       </c>
@@ -7604,7 +7634,7 @@
         <v>21.820178340343087</v>
       </c>
     </row>
-    <row r="214" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:3" ht="40" customHeight="1">
       <c r="A214" s="4">
         <v>45785</v>
       </c>
@@ -7615,7 +7645,7 @@
         <v>22.393549116817407</v>
       </c>
     </row>
-    <row r="215" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:3" ht="40" customHeight="1">
       <c r="A215" s="4">
         <v>45786</v>
       </c>
@@ -7626,7 +7656,7 @@
         <v>22.279137663192934</v>
       </c>
     </row>
-    <row r="216" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:3" ht="40" customHeight="1">
       <c r="A216" s="4">
         <v>45789</v>
       </c>
@@ -7637,7 +7667,7 @@
         <v>25.519480068658879</v>
       </c>
     </row>
-    <row r="217" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:3" ht="40" customHeight="1">
       <c r="A217" s="4">
         <v>45790</v>
       </c>
@@ -7648,7 +7678,7 @@
         <v>26.190709064034923</v>
       </c>
     </row>
-    <row r="218" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:3" ht="40" customHeight="1">
       <c r="A218" s="4">
         <v>45791</v>
       </c>
@@ -7659,7 +7689,7 @@
         <v>26.258431067808324</v>
       </c>
     </row>
-    <row r="219" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:3" ht="40" customHeight="1">
       <c r="A219" s="4">
         <v>45792</v>
       </c>
@@ -7670,7 +7700,7 @@
         <v>26.676444216862848</v>
       </c>
     </row>
-    <row r="220" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:3" ht="40" customHeight="1">
       <c r="A220" s="4">
         <v>45793</v>
       </c>
@@ -7681,7 +7711,7 @@
         <v>27.386009490594859</v>
       </c>
     </row>
-    <row r="221" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:3" ht="40" customHeight="1">
       <c r="A221" s="4">
         <v>45796</v>
       </c>
@@ -7692,7 +7722,7 @@
         <v>27.503085938154136</v>
       </c>
     </row>
-    <row r="222" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:3" ht="40" customHeight="1">
       <c r="A222" s="4">
         <v>45797</v>
       </c>
@@ -7703,7 +7733,7 @@
         <v>27.122085246991258</v>
       </c>
     </row>
-    <row r="223" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:3" ht="40" customHeight="1">
       <c r="A223" s="4">
         <v>45798</v>
       </c>
@@ -7714,7 +7744,7 @@
         <v>25.4555210002809</v>
       </c>
     </row>
-    <row r="224" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:3" ht="40" customHeight="1">
       <c r="A224" s="4">
         <v>45799</v>
       </c>
@@ -7725,7 +7755,7 @@
         <v>25.378716080990703</v>
       </c>
     </row>
-    <row r="225" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:3" ht="40" customHeight="1">
       <c r="A225" s="4">
         <v>45800</v>
       </c>
@@ -7736,7 +7766,7 @@
         <v>24.697698350977436</v>
       </c>
     </row>
-    <row r="226" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:3" ht="40" customHeight="1">
       <c r="A226" s="4">
         <v>45803</v>
       </c>
@@ -7747,7 +7777,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="227" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:3" ht="40" customHeight="1">
       <c r="A227" s="4">
         <v>45804</v>
       </c>
@@ -7758,7 +7788,7 @@
         <v>26.69</v>
       </c>
     </row>
-    <row r="228" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:3" ht="40" customHeight="1">
       <c r="A228" s="4">
         <v>45805</v>
       </c>
@@ -7769,7 +7799,7 @@
         <v>26.16</v>
       </c>
     </row>
-    <row r="229" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:3" ht="40" customHeight="1">
       <c r="A229" s="4">
         <v>45807</v>
       </c>
@@ -7780,7 +7810,7 @@
         <v>26.39</v>
       </c>
     </row>
-    <row r="230" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:3" ht="40" customHeight="1">
       <c r="A230" s="4">
         <v>45810</v>
       </c>
@@ -7791,7 +7821,7 @@
         <v>26.912124642438844</v>
       </c>
     </row>
-    <row r="231" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:3" ht="40" customHeight="1">
       <c r="A231" s="4">
         <v>45811</v>
       </c>
@@ -7802,7 +7832,7 @@
         <v>27.486369120997161</v>
       </c>
     </row>
-    <row r="232" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:3" ht="40" customHeight="1">
       <c r="A232" s="4">
         <v>45812</v>
       </c>
@@ -7813,7 +7843,7 @@
         <v>27.478009664356971</v>
       </c>
     </row>
-    <row r="233" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:3" ht="40" customHeight="1">
       <c r="A233" s="4">
         <v>45813</v>
       </c>
@@ -7824,7 +7854,7 @@
         <v>26.891104315705576</v>
       </c>
     </row>
-    <row r="234" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:3" ht="40" customHeight="1">
       <c r="A234" s="4">
         <v>45814</v>
       </c>
@@ -7835,7 +7865,7 @@
         <v>27.907615547091403</v>
       </c>
     </row>
-    <row r="235" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:3" ht="40" customHeight="1">
       <c r="A235" s="4">
         <v>45818</v>
       </c>
@@ -7846,7 +7876,7 @@
         <v>28.54238026479058</v>
       </c>
     </row>
-    <row r="236" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:3" ht="40" customHeight="1">
       <c r="A236" s="4">
         <v>45819</v>
       </c>
@@ -7857,7 +7887,7 @@
         <v>28.277347808841835</v>
       </c>
     </row>
-    <row r="237" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:3" ht="40" customHeight="1">
       <c r="A237" s="4">
         <v>45820</v>
       </c>
@@ -7868,7 +7898,7 @@
         <v>28.616794258054533</v>
       </c>
     </row>
-    <row r="238" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:3" ht="40" customHeight="1">
       <c r="A238" s="4">
         <v>45821</v>
       </c>
@@ -7879,7 +7909,7 @@
         <v>28.318805460445123</v>
       </c>
     </row>
-    <row r="239" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:3" ht="40" customHeight="1">
       <c r="A239" s="4">
         <v>45824</v>
       </c>
@@ -7890,7 +7920,7 @@
         <v>29.279934855722427</v>
       </c>
     </row>
-    <row r="240" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:3" ht="40" customHeight="1">
       <c r="A240" s="4">
         <v>45825</v>
       </c>
@@ -7901,7 +7931,7 @@
         <v>28.43479553144428</v>
       </c>
     </row>
-    <row r="241" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:3" ht="40" customHeight="1">
       <c r="A241" s="4">
         <v>45826</v>
       </c>
@@ -7912,7 +7942,7 @@
         <v>28.364389034572181</v>
       </c>
     </row>
-    <row r="242" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:3" ht="40" customHeight="1">
       <c r="A242" s="4">
         <v>45827</v>
       </c>
@@ -7923,7 +7953,7 @@
         <v>28.364389034572181</v>
       </c>
     </row>
-    <row r="243" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:3" ht="40" customHeight="1">
       <c r="A243" s="4">
         <v>45828</v>
       </c>
@@ -7934,7 +7964,7 @@
         <v>28.094729678900332</v>
       </c>
     </row>
-    <row r="244" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:3" ht="40" customHeight="1">
       <c r="A244" s="4">
         <v>45831</v>
       </c>
@@ -7945,7 +7975,7 @@
         <v>29.070347173436801</v>
       </c>
     </row>
-    <row r="245" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:3" ht="40" customHeight="1">
       <c r="A245" s="4">
         <v>45832</v>
       </c>
@@ -7956,7 +7986,7 @@
         <v>30.203445832516202</v>
       </c>
     </row>
-    <row r="246" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:3" ht="40" customHeight="1">
       <c r="A246" s="4">
         <v>45833</v>
       </c>
@@ -7967,7 +7997,7 @@
         <v>30.215647650602236</v>
       </c>
     </row>
-    <row r="247" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:3" ht="40" customHeight="1">
       <c r="A247" s="4">
         <v>45834</v>
       </c>
@@ -7978,7 +8008,7 @@
         <v>30.993483366225572</v>
       </c>
     </row>
-    <row r="248" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:3" ht="40" customHeight="1">
       <c r="A248" s="4">
         <v>45835</v>
       </c>
@@ -7989,7 +8019,7 @@
         <v>31.456493755540549</v>
       </c>
     </row>
-    <row r="249" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:3" ht="40" customHeight="1">
       <c r="A249" s="4">
         <v>45838</v>
       </c>
@@ -8000,7 +8030,7 @@
         <v>31.937360240142787</v>
       </c>
     </row>
-    <row r="250" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:3" ht="40" customHeight="1">
       <c r="A250" s="4">
         <v>45839</v>
       </c>
@@ -8011,7 +8041,7 @@
         <v>31.857376232679325</v>
       </c>
     </row>
-    <row r="251" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:3" ht="40" customHeight="1">
       <c r="A251" s="4">
         <v>45840</v>
       </c>
@@ -8022,7 +8052,7 @@
         <v>32.276580359899768</v>
       </c>
     </row>
-    <row r="252" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:3" ht="40" customHeight="1">
       <c r="A252" s="4">
         <v>45841</v>
       </c>
@@ -8033,7 +8063,7 @@
         <v>33.058376908881797</v>
       </c>
     </row>
-    <row r="253" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:3" ht="40" customHeight="1">
       <c r="A253" s="4">
         <v>45842</v>
       </c>
@@ -8044,7 +8074,7 @@
         <v>33.058376908881797</v>
       </c>
     </row>
-    <row r="254" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:3" ht="40" customHeight="1">
       <c r="A254" s="4">
         <v>45845</v>
       </c>
@@ -8055,7 +8085,7 @@
         <v>32.292515345193621</v>
       </c>
     </row>
-    <row r="255" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:3" ht="40" customHeight="1">
       <c r="A255" s="4">
         <v>45846</v>
       </c>
@@ -8066,7 +8096,7 @@
         <v>32.228760162925681</v>
       </c>
     </row>
-    <row r="256" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:3" ht="40" customHeight="1">
       <c r="A256" s="4">
         <v>45847</v>
       </c>
@@ -8077,7 +8107,7 @@
         <v>32.789208397398802</v>
       </c>
     </row>
-    <row r="257" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:3" ht="40" customHeight="1">
       <c r="A257" s="4">
         <v>45848</v>
       </c>
@@ -8088,7 +8118,7 @@
         <v>33.058376908881797</v>
       </c>
     </row>
-    <row r="258" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:3" ht="40" customHeight="1">
       <c r="A258" s="4">
         <v>45849</v>
       </c>
@@ -8099,7 +8129,7 @@
         <v>32.674195197863703</v>
       </c>
     </row>
-    <row r="259" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:3" ht="40" customHeight="1">
       <c r="A259" s="4">
         <v>45852</v>
       </c>
@@ -8110,7 +8140,7 @@
         <v>32.848646118325256</v>
       </c>
     </row>
-    <row r="260" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:3" ht="40" customHeight="1">
       <c r="A260" s="4">
         <v>45853</v>
       </c>
@@ -8121,7 +8151,7 @@
         <v>32.4199038974525</v>
       </c>
     </row>
-    <row r="261" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:3" ht="40" customHeight="1">
       <c r="A261" s="4">
         <v>45854</v>
       </c>
@@ -8132,7 +8162,7 @@
         <v>32.725769197777041</v>
       </c>
     </row>
-    <row r="262" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:3" ht="40" customHeight="1">
       <c r="A262" s="4">
         <v>45855</v>
       </c>
@@ -8143,7 +8173,7 @@
         <v>33.314994827396724</v>
       </c>
     </row>
-    <row r="263" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:3" ht="40" customHeight="1">
       <c r="A263" s="4">
         <v>45856</v>
       </c>
@@ -8154,7 +8184,7 @@
         <v>33.22426682764241</v>
       </c>
     </row>
-    <row r="264" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:3" ht="40" customHeight="1">
       <c r="A264" s="4">
         <v>45859</v>
       </c>
@@ -8165,7 +8195,7 @@
         <v>33.382001786802618</v>
       </c>
     </row>
-    <row r="265" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:3" ht="40" customHeight="1">
       <c r="A265" s="4">
         <v>45860</v>
       </c>
@@ -8176,7 +8206,7 @@
         <v>33.413518944215923</v>
       </c>
     </row>
-    <row r="266" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:3" ht="40" customHeight="1">
       <c r="A266" s="4">
         <v>45861</v>
       </c>
@@ -8187,7 +8217,7 @@
         <v>34.190419971831439</v>
       </c>
     </row>
-    <row r="267" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:3" ht="40" customHeight="1">
       <c r="A267" s="4">
         <v>45862</v>
       </c>
@@ -8198,7 +8228,7 @@
         <v>34.272465648524658</v>
       </c>
     </row>
-    <row r="268" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:3" ht="40" customHeight="1">
       <c r="A268" s="4">
         <v>45863</v>
       </c>
@@ -8209,7 +8239,7 @@
         <v>34.638894936243346</v>
       </c>
     </row>
-    <row r="269" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:3" ht="40" customHeight="1">
       <c r="A269" s="4">
         <v>45866</v>
       </c>
@@ -8220,7 +8250,7 @@
         <v>34.603869347747271</v>
       </c>
     </row>
-    <row r="270" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:3" ht="40" customHeight="1">
       <c r="A270" s="4">
         <v>45867</v>
       </c>
@@ -8231,7 +8261,7 @@
         <v>34.342736976811644</v>
       </c>
     </row>
-    <row r="271" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:3" ht="40" customHeight="1">
       <c r="A271" s="4">
         <v>45868</v>
       </c>
@@ -8242,7 +8272,7 @@
         <v>34.190419971831453</v>
       </c>
     </row>
-    <row r="272" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:3" ht="40" customHeight="1">
       <c r="A272" s="4">
         <v>45869</v>
       </c>
@@ -8253,7 +8283,7 @@
         <v>33.845875564585825</v>
       </c>
     </row>
-    <row r="273" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:3" ht="40" customHeight="1">
       <c r="A273" s="4">
         <v>45873</v>
       </c>
@@ -8264,7 +8294,7 @@
         <v>33.559156725561955</v>
       </c>
     </row>
-    <row r="274" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:3" ht="40" customHeight="1">
       <c r="A274" s="4">
         <v>45874</v>
       </c>
@@ -8275,7 +8305,7 @@
         <v>33.074187810531399</v>
       </c>
     </row>
-    <row r="275" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:3" ht="40" customHeight="1">
       <c r="A275" s="4">
         <v>45875</v>
       </c>
@@ -8286,7 +8316,7 @@
         <v>33.794876171550129</v>
       </c>
     </row>
-    <row r="276" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:3" ht="40" customHeight="1">
       <c r="A276" s="4">
         <v>45876</v>
       </c>
@@ -8297,7 +8327,7 @@
         <v>33.724218661250333</v>
       </c>
     </row>
-    <row r="277" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:3" ht="40" customHeight="1">
       <c r="A277" s="4">
         <v>45877</v>
       </c>
@@ -8308,7 +8338,7 @@
         <v>34.459746233891856</v>
       </c>
     </row>
-    <row r="278" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:3" ht="40" customHeight="1">
       <c r="A278" s="4">
         <v>45880</v>
       </c>
@@ -8319,7 +8349,7 @@
         <v>34.245124568381712</v>
       </c>
     </row>
-    <row r="279" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:3" ht="40" customHeight="1">
       <c r="A279" s="4">
         <v>45881</v>
       </c>
@@ -8330,7 +8360,7 @@
         <v>35.313656095696984</v>
       </c>
     </row>
-    <row r="280" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:3" ht="40" customHeight="1">
       <c r="A280" s="4">
         <v>45882</v>
       </c>
@@ -8341,7 +8371,7 @@
         <v>35.626222674045195</v>
       </c>
     </row>
-    <row r="281" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:3" ht="40" customHeight="1">
       <c r="A281" s="4">
         <v>45883</v>
       </c>
@@ -8352,7 +8382,7 @@
         <v>35.653188793206233</v>
       </c>
     </row>
-    <row r="282" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:3" ht="40" customHeight="1">
       <c r="A282" s="4">
         <v>45884</v>
       </c>
@@ -8363,7 +8393,7 @@
         <v>35.360023948150605</v>
       </c>
     </row>
-    <row r="283" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:3" ht="40" customHeight="1">
       <c r="A283" s="4">
         <v>45887</v>
       </c>
@@ -8374,7 +8404,7 @@
         <v>35.325250074570278</v>
       </c>
     </row>
-    <row r="284" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:3" ht="40" customHeight="1">
       <c r="A284" s="4">
         <v>45888</v>
       </c>
@@ -8385,7 +8415,7 @@
         <v>34.75555837549124</v>
       </c>
     </row>
-    <row r="285" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:3" ht="40" customHeight="1">
       <c r="A285" s="4">
         <v>45889</v>
       </c>
@@ -8396,7 +8426,7 @@
         <v>34.451949874787609</v>
       </c>
     </row>
-    <row r="286" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:3" ht="40" customHeight="1">
       <c r="A286" s="4">
         <v>45890</v>
       </c>
@@ -8407,7 +8437,7 @@
         <v>34.061354893391616</v>
       </c>
     </row>
-    <row r="287" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:3" ht="40" customHeight="1">
       <c r="A287" s="4">
         <v>45891</v>
       </c>
@@ -8418,7 +8448,7 @@
         <v>35.54</v>
       </c>
     </row>
-    <row r="288" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:3" ht="40" customHeight="1">
       <c r="A288" s="4">
         <v>45894</v>
       </c>
@@ -8429,7 +8459,7 @@
         <v>35.112479921378643</v>
       </c>
     </row>
-    <row r="289" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:3" ht="40" customHeight="1">
       <c r="A289" s="4">
         <v>45895</v>
       </c>
@@ -8440,7 +8470,7 @@
         <v>35.529855701183251</v>
       </c>
     </row>
-    <row r="290" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:3" ht="40" customHeight="1">
       <c r="A290" s="4">
         <v>45896</v>
       </c>
@@ -8451,7 +8481,7 @@
         <v>35.737892144052694</v>
       </c>
     </row>
-    <row r="291" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:3" ht="40" customHeight="1">
       <c r="A291" s="4">
         <v>45897</v>
       </c>
@@ -8462,7 +8492,7 @@
         <v>36.060646593139346</v>
       </c>
     </row>
-    <row r="292" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:3" ht="40" customHeight="1">
       <c r="A292" s="4">
         <v>45898</v>
       </c>
@@ -8473,7 +8503,7 @@
         <v>35.379337543050035</v>
       </c>
     </row>
-    <row r="293" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:3" ht="40" customHeight="1">
       <c r="A293" s="4">
         <v>45901</v>
       </c>
@@ -8484,7 +8514,7 @@
         <v>35.379337543050035</v>
       </c>
     </row>
-    <row r="294" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:3" ht="40" customHeight="1">
       <c r="A294" s="4">
         <v>45902</v>
       </c>
@@ -8495,7 +8525,7 @@
         <v>34.64667673462089</v>
       </c>
     </row>
-    <row r="295" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:3" ht="40" customHeight="1">
       <c r="A295" s="4">
         <v>45903</v>
       </c>
@@ -8506,7 +8536,7 @@
         <v>35.139584914671538</v>
       </c>
     </row>
-    <row r="296" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:3" ht="40" customHeight="1">
       <c r="A296" s="4">
         <v>45904</v>
       </c>
@@ -8517,7 +8547,7 @@
         <v>35.964697553904017</v>
       </c>
     </row>
-    <row r="297" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:3" ht="40" customHeight="1">
       <c r="A297" s="4">
         <v>45905</v>
       </c>
@@ -8528,7 +8558,7 @@
         <v>35.641632775397106</v>
       </c>
     </row>
-    <row r="298" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:3" ht="40" customHeight="1">
       <c r="A298" s="4">
         <v>45908</v>
       </c>
@@ -8539,7 +8569,7 @@
         <v>35.891714663230992</v>
       </c>
     </row>
-    <row r="299" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:3" ht="40" customHeight="1">
       <c r="A299" s="4">
         <v>45909</v>
       </c>
@@ -8550,7 +8580,7 @@
         <v>36.133506341353403</v>
       </c>
     </row>
-    <row r="300" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:3" ht="40" customHeight="1">
       <c r="A300" s="4">
         <v>45910</v>
       </c>
@@ -8561,7 +8591,7 @@
         <v>36.409125701991975</v>
       </c>
     </row>
-    <row r="301" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:3" ht="40" customHeight="1">
       <c r="A301" s="4">
         <v>45911</v>
       </c>
@@ -8572,7 +8602,7 @@
         <v>37.21249578264549</v>
       </c>
     </row>
-    <row r="302" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:3" ht="40" customHeight="1">
       <c r="A302" s="4">
         <v>45912</v>
       </c>
@@ -8583,7 +8613,7 @@
         <v>37.148007796039458</v>
       </c>
     </row>
-    <row r="303" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:3" ht="40" customHeight="1">
       <c r="A303" s="4">
         <v>45915</v>
       </c>
@@ -8594,7 +8624,7 @@
         <v>37.651424896603217</v>
       </c>
     </row>
-    <row r="304" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:3" ht="40" customHeight="1">
       <c r="A304" s="4">
         <v>45916</v>
       </c>
@@ -8605,7 +8635,7 @@
         <v>37.488943045594787</v>
       </c>
     </row>
-    <row r="305" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:3" ht="40" customHeight="1">
       <c r="A305" s="4">
         <v>45917</v>
       </c>
@@ -8616,7 +8646,7 @@
         <v>38.212409783022203</v>
       </c>
     </row>
-    <row r="306" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:3" ht="40" customHeight="1">
       <c r="A306" s="4">
         <v>45918</v>
       </c>
@@ -8627,7 +8657,7 @@
         <v>38.732922482496548</v>
       </c>
     </row>
-    <row r="307" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:3" ht="40" customHeight="1">
       <c r="A307" s="4">
         <v>45919</v>
       </c>
@@ -8638,7 +8668,7 @@
         <v>39.157804788406416</v>
       </c>
     </row>
-    <row r="308" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:3" ht="40" customHeight="1">
       <c r="A308" s="4">
         <v>45922</v>
       </c>
@@ -8649,7 +8679,7 @@
         <v>39.610512526578376</v>
       </c>
     </row>
-    <row r="309" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:3" ht="40" customHeight="1">
       <c r="A309" s="4">
         <v>45923</v>
       </c>
@@ -8660,7 +8690,7 @@
         <v>39.053614855635104</v>
       </c>
     </row>
-    <row r="310" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:3" ht="40" customHeight="1">
       <c r="A310" s="4">
         <v>45924</v>
       </c>
@@ -8671,7 +8701,7 @@
         <v>38.714245904738355</v>
       </c>
     </row>
-    <row r="311" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:3" ht="40" customHeight="1">
       <c r="A311" s="4">
         <v>45925</v>
       </c>
@@ -8682,7 +8712,7 @@
         <v>38.227426489135937</v>
       </c>
     </row>
-    <row r="312" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:3" ht="40" customHeight="1">
       <c r="A312" s="4">
         <v>45926</v>
       </c>
@@ -8693,7 +8723,7 @@
         <v>38.770265176832439</v>
       </c>
     </row>
-    <row r="313" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:3" ht="40" customHeight="1">
       <c r="A313" s="4">
         <v>45929</v>
       </c>
@@ -8704,7 +8734,7 @@
         <v>39.031274311177597</v>
       </c>
     </row>
-    <row r="314" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:3" ht="40" customHeight="1">
       <c r="A314" s="4">
         <v>45930</v>
       </c>
@@ -8715,7 +8745,7 @@
         <v>39.406676636489166</v>
       </c>
     </row>
-    <row r="315" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:3" ht="40" customHeight="1">
       <c r="A315" s="4">
         <v>45931</v>
       </c>
@@ -8726,7 +8756,7 @@
         <v>39.743707751242766</v>
       </c>
     </row>
-    <row r="316" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:3" ht="40" customHeight="1">
       <c r="A316" s="4">
         <v>45932</v>
       </c>
@@ -8737,7 +8767,7 @@
         <v>39.821323115588591</v>
       </c>
     </row>
-    <row r="317" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:3" ht="40" customHeight="1">
       <c r="A317" s="4">
         <v>45933</v>
       </c>
@@ -8748,7 +8778,7 @@
         <v>39.780674961748417</v>
       </c>
     </row>
-    <row r="318" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:3" ht="40" customHeight="1">
       <c r="A318" s="4">
         <v>45936</v>
       </c>
@@ -8759,7 +8789,7 @@
         <v>40.145914894806836</v>
       </c>
     </row>
-    <row r="319" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:3" ht="40" customHeight="1">
       <c r="A319" s="4">
         <v>45937</v>
       </c>
@@ -8770,7 +8800,7 @@
         <v>39.743707751242773</v>
       </c>
     </row>
-    <row r="320" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:3" ht="40" customHeight="1">
       <c r="A320" s="4">
         <v>45938</v>
       </c>
@@ -8781,7 +8811,7 @@
         <v>40.329873739914831</v>
       </c>
     </row>
-    <row r="321" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:3" ht="40" customHeight="1">
       <c r="A321" s="4">
         <v>45939</v>
       </c>
@@ -8792,7 +8822,7 @@
         <v>40.005879494564326</v>
       </c>
     </row>
-    <row r="322" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:3" ht="40" customHeight="1">
       <c r="A322" s="4">
         <v>45940</v>
       </c>
@@ -8803,7 +8833,7 @@
         <v>37.254201153764299</v>
       </c>
     </row>
-    <row r="323" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:3" ht="40" customHeight="1">
       <c r="A323" s="4">
         <v>45943</v>
       </c>
@@ -8814,7 +8844,7 @@
         <v>38.751595572760522</v>
       </c>
     </row>
-    <row r="324" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:3" ht="40" customHeight="1">
       <c r="A324" s="4">
         <v>45944</v>
       </c>
@@ -8825,7 +8855,7 @@
         <v>38.628288691186455</v>
       </c>
     </row>
-    <row r="325" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:3" ht="40" customHeight="1">
       <c r="A325" s="4">
         <v>45945</v>
       </c>
@@ -8836,7 +8866,7 @@
         <v>39.053614855635125</v>
       </c>
     </row>
-    <row r="326" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:3" ht="40" customHeight="1">
       <c r="A326" s="4">
         <v>45946</v>
       </c>
@@ -8847,7 +8877,7 @@
         <v>38.362475464907682</v>
       </c>
     </row>
-    <row r="327" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:3" ht="40" customHeight="1">
       <c r="A327" s="4">
         <v>45947</v>
       </c>
@@ -8858,7 +8888,7 @@
         <v>38.867290970912777</v>
       </c>
     </row>
-    <row r="328" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:3" ht="40" customHeight="1">
       <c r="A328" s="4">
         <v>45950</v>
       </c>
@@ -8869,7 +8899,7 @@
         <v>39.924716647933742</v>
       </c>
     </row>
-    <row r="329" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:3" ht="40" customHeight="1">
       <c r="A329" s="4">
         <v>45951</v>
       </c>
@@ -8880,7 +8910,7 @@
         <v>39.917334939803126</v>
       </c>
     </row>
-    <row r="330" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:3" ht="40" customHeight="1">
       <c r="A330" s="4">
         <v>45952</v>
       </c>
@@ -8891,7 +8921,7 @@
         <v>39.380704055967328</v>
       </c>
     </row>
-    <row r="331" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:3" ht="40" customHeight="1">
       <c r="A331" s="4">
         <v>45953</v>
       </c>
@@ -8902,7 +8932,7 @@
         <v>39.943168534691495</v>
       </c>
     </row>
-    <row r="332" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:3" ht="40" customHeight="1">
       <c r="A332" s="4">
         <v>45954</v>
       </c>
@@ -8913,7 +8943,7 @@
         <v>40.707765701729357</v>
       </c>
     </row>
-    <row r="333" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:3" ht="40" customHeight="1">
       <c r="A333" s="4">
         <v>45957</v>
       </c>
@@ -8924,7 +8954,7 @@
         <v>41.890866813546793</v>
       </c>
     </row>
-    <row r="334" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:3" ht="40" customHeight="1">
       <c r="A334" s="4">
         <v>45958</v>
       </c>
@@ -8935,7 +8965,7 @@
         <v>42.143866803927651</v>
       </c>
     </row>
-    <row r="335" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:3" ht="40" customHeight="1">
       <c r="A335" s="4">
         <v>45959</v>
       </c>
@@ -8946,7 +8976,7 @@
         <v>42.100540811265212</v>
       </c>
     </row>
-    <row r="336" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:3" ht="40" customHeight="1">
       <c r="A336" s="4">
         <v>45960</v>
       </c>
@@ -8957,7 +8987,7 @@
         <v>41.117063159542802</v>
       </c>
     </row>
-    <row r="337" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:3" ht="40" customHeight="1">
       <c r="A337" s="4">
         <v>45961</v>
       </c>
@@ -8968,7 +8998,7 @@
         <v>41.393849700879244</v>
       </c>
     </row>
-    <row r="338" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:3" ht="40" customHeight="1">
       <c r="A338" s="4">
         <v>45964</v>
       </c>
@@ -8979,7 +9009,7 @@
         <v>41.521059996624551</v>
       </c>
     </row>
-    <row r="339" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:3" ht="40" customHeight="1">
       <c r="A339" s="4">
         <v>45965</v>
       </c>
@@ -8990,7 +9020,7 @@
         <v>40.337225059480012</v>
       </c>
     </row>
-    <row r="340" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:3" ht="40" customHeight="1">
       <c r="A340" s="4">
         <v>45966</v>
       </c>
@@ -9001,7 +9031,7 @@
         <v>40.682128901794052</v>
       </c>
     </row>
-    <row r="341" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:3" ht="40" customHeight="1">
       <c r="A341" s="4">
         <v>45967</v>
       </c>
@@ -9012,7 +9042,7 @@
         <v>39.53643844911732</v>
       </c>
     </row>
-    <row r="342" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:3" ht="40" customHeight="1">
       <c r="A342" s="4">
         <v>45968</v>
       </c>
@@ -9023,7 +9053,7 @@
         <v>39.629022475728902</v>
       </c>
     </row>
-    <row r="343" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:3" ht="40" customHeight="1">
       <c r="A343" s="4">
         <v>45971</v>
       </c>
@@ -9034,7 +9064,7 @@
         <v>41.142588712583141</v>
       </c>
     </row>
-    <row r="344" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:3" ht="40" customHeight="1">
       <c r="A344" s="4">
         <v>45972</v>
       </c>
@@ -9045,7 +9075,7 @@
         <v>41.357474159392012</v>
       </c>
     </row>
-    <row r="345" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:3" ht="40" customHeight="1">
       <c r="A345" s="4">
         <v>45973</v>
       </c>
@@ -9056,7 +9086,7 @@
         <v>41.419304709289598</v>
       </c>
     </row>
-    <row r="346" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:3" ht="40" customHeight="1">
       <c r="A346" s="4">
         <v>45974</v>
       </c>
@@ -9067,7 +9097,7 @@
         <v>39.721520863602336</v>
       </c>
     </row>
-    <row r="347" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:3" ht="40" customHeight="1">
       <c r="A347" s="4">
         <v>45975</v>
       </c>
@@ -9078,7 +9108,7 @@
         <v>39.65122989309755</v>
       </c>
     </row>
-    <row r="348" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:3" ht="40" customHeight="1">
       <c r="A348" s="4">
         <v>45978</v>
       </c>
@@ -9089,7 +9119,7 @@
         <v>38.710510170572825</v>
       </c>
     </row>
-    <row r="349" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:3" ht="40" customHeight="1">
       <c r="A349" s="4">
         <v>45979</v>
       </c>
@@ -9100,7 +9130,7 @@
         <v>37.926663075828188</v>
       </c>
     </row>
-    <row r="350" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:3" ht="40" customHeight="1">
       <c r="A350" s="4">
         <v>45980</v>
       </c>
@@ -9111,7 +9141,7 @@
         <v>38.253700299928035</v>
       </c>
     </row>
-    <row r="351" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:3" ht="40" customHeight="1">
       <c r="A351" s="4">
         <v>45981</v>
       </c>
@@ -9122,7 +9152,7 @@
         <v>36.680175134004237</v>
       </c>
     </row>
-    <row r="352" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:3" ht="40" customHeight="1">
       <c r="A352" s="4">
         <v>45982</v>
       </c>
@@ -9133,7 +9163,7 @@
         <v>37.632545216746557</v>
       </c>
     </row>
-    <row r="353" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:3" ht="40" customHeight="1">
       <c r="A353" s="4">
         <v>45985</v>
       </c>
@@ -9144,7 +9174,7 @@
         <v>39.146646772290147</v>
       </c>
     </row>
-    <row r="354" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:3" ht="40" customHeight="1">
       <c r="A354" s="4">
         <v>45986</v>
       </c>
@@ -9155,7 +9185,7 @@
         <v>40.039063500178315</v>
       </c>
     </row>
-    <row r="355" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:3" ht="40" customHeight="1">
       <c r="A355" s="4">
         <v>45987</v>
       </c>
@@ -9166,7 +9196,7 @@
         <v>40.722412351334484</v>
       </c>
     </row>
-    <row r="356" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:3" ht="40" customHeight="1">
       <c r="A356" s="4">
         <v>45988</v>
       </c>
@@ -9177,7 +9207,7 @@
         <v>40.722412351334484</v>
       </c>
     </row>
-    <row r="357" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:3" ht="40" customHeight="1">
       <c r="A357" s="4">
         <v>45989</v>
       </c>
@@ -9188,7 +9218,7 @@
         <v>41.175397709833504</v>
       </c>
     </row>
-    <row r="358" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:3" ht="40" customHeight="1">
       <c r="A358" s="4">
         <v>45992</v>
       </c>
@@ -9199,7 +9229,7 @@
         <v>40.704103704109293</v>
       </c>
     </row>
-    <row r="359" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:3" ht="40" customHeight="1">
       <c r="A359" s="4">
         <v>45993</v>
       </c>
@@ -9210,7 +9240,7 @@
         <v>40.90165992552879</v>
       </c>
     </row>
-    <row r="360" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:3" ht="40" customHeight="1">
       <c r="A360" s="4">
         <v>45994</v>
       </c>
@@ -9221,7 +9251,7 @@
         <v>41.219126301740872</v>
       </c>
     </row>
-    <row r="361" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:3" ht="40" customHeight="1">
       <c r="A361" s="4">
         <v>45995</v>
       </c>
@@ -9232,7 +9262,7 @@
         <v>41.288324155726677</v>
       </c>
     </row>
-    <row r="362" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:3" ht="40" customHeight="1">
       <c r="A362" s="4">
         <v>45996</v>
       </c>
@@ -9243,7 +9273,7 @@
         <v>41.455657770617691</v>
       </c>
     </row>
-    <row r="363" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:3" ht="40" customHeight="1">
       <c r="A363" s="4">
         <v>45999</v>
       </c>
@@ -9254,7 +9284,7 @@
         <v>41.12800348010515</v>
       </c>
     </row>
-    <row r="364" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:3" ht="40" customHeight="1">
       <c r="A364" s="4">
         <v>46000</v>
       </c>
@@ -9265,7 +9295,7 @@
         <v>41.018546376357286</v>
       </c>
     </row>
-    <row r="365" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:3" ht="40" customHeight="1">
       <c r="A365" s="4">
         <v>46001</v>
       </c>
@@ -9276,7 +9306,7 @@
         <v>41.651736264811781</v>
       </c>
     </row>
-    <row r="366" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:3" ht="40" customHeight="1">
       <c r="A366" s="4">
         <v>46002</v>
       </c>
@@ -9287,7 +9317,7 @@
         <v>41.876390319728351</v>
       </c>
     </row>
-    <row r="367" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:3" ht="40" customHeight="1">
       <c r="A367" s="4">
         <v>46003</v>
       </c>
@@ -9298,7 +9328,7 @@
         <v>40.762679579846015</v>
       </c>
     </row>
-    <row r="368" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:3" ht="40" customHeight="1">
       <c r="A368" s="4">
         <v>46006</v>
       </c>
@@ -9309,7 +9339,7 @@
         <v>40.649157641443736</v>
       </c>
     </row>
-    <row r="369" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:3" ht="40" customHeight="1">
       <c r="A369" s="4">
         <v>46007</v>
       </c>
@@ -9320,7 +9350,7 @@
         <v>40.326197877465248</v>
       </c>
     </row>
-    <row r="370" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:3" ht="40" customHeight="1">
       <c r="A370" s="4">
         <v>46008</v>
       </c>
@@ -9331,7 +9361,7 @@
         <v>39.224726752461137</v>
       </c>
     </row>
-    <row r="371" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:3" ht="40" customHeight="1">
       <c r="A371" s="4">
         <v>46009</v>
       </c>
@@ -9342,7 +9372,7 @@
         <v>39.991127512240006</v>
       </c>
     </row>
-    <row r="372" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:3" ht="40" customHeight="1">
       <c r="A372" s="4">
         <v>46010</v>
       </c>
@@ -9353,7 +9383,7 @@
         <v>41.586419476075505</v>
       </c>
     </row>
-    <row r="373" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:3" ht="40" customHeight="1">
       <c r="A373" s="4">
         <v>46013</v>
       </c>
@@ -9364,7 +9394,7 @@
         <v>42.208820616834927</v>
       </c>
     </row>
-    <row r="374" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:3" ht="40" customHeight="1">
       <c r="A374" s="4">
         <v>46014</v>
       </c>
@@ -9375,7 +9405,7 @@
         <v>42.651546076768035</v>
       </c>
     </row>
-    <row r="375" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:3" ht="40" customHeight="1">
       <c r="A375" s="4">
         <v>46015</v>
       </c>
@@ -9386,7 +9416,7 @@
         <v>42.959933741834583</v>
       </c>
     </row>
-    <row r="376" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:3" ht="40" customHeight="1">
       <c r="A376" s="4">
         <v>46017</v>
       </c>
@@ -9397,7 +9427,7 @@
         <v>42.913377972554919</v>
       </c>
     </row>
-    <row r="377" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:3" ht="40" customHeight="1">
       <c r="A377" s="4">
         <v>46020</v>
       </c>
@@ -9408,7 +9438,7 @@
         <v>42.565314395655719</v>
       </c>
     </row>
-    <row r="378" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:3" ht="40" customHeight="1">
       <c r="A378" s="4">
         <v>46021</v>
       </c>
@@ -9419,7 +9449,7 @@
         <v>42.408469675716674</v>
       </c>
     </row>
-    <row r="379" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:3" ht="40" customHeight="1">
       <c r="A379" s="4">
         <v>46022</v>
       </c>
@@ -9430,7 +9460,7 @@
         <v>41.662618249696578</v>
       </c>
     </row>
-    <row r="380" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:3" ht="40" customHeight="1">
       <c r="A380" s="4">
         <v>46024</v>
       </c>
@@ -9441,7 +9471,7 @@
         <v>41.778619132710872</v>
       </c>
     </row>
-    <row r="381" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:3" ht="40" customHeight="1">
       <c r="A381" s="4">
         <v>46027</v>
       </c>
@@ -9452,7 +9482,7 @@
         <v>42.403429298695414</v>
       </c>
     </row>
-    <row r="382" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:3" ht="40" customHeight="1">
       <c r="A382" s="4">
         <v>46028</v>
       </c>
@@ -9463,7 +9493,7 @@
         <v>43.035093459765804</v>
       </c>
     </row>
-    <row r="383" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:3" ht="40" customHeight="1">
       <c r="A383" s="4">
         <v>46029</v>
       </c>
@@ -9474,7 +9504,7 @@
         <v>42.683863796136542</v>
       </c>
     </row>
-    <row r="384" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:3" ht="40" customHeight="1">
       <c r="A384" s="4">
         <v>46030</v>
       </c>
@@ -9485,7 +9515,7 @@
         <v>42.665910797039821</v>
       </c>
     </row>
-    <row r="385" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:3" ht="40" customHeight="1">
       <c r="A385" s="4">
         <v>46031</v>
       </c>
@@ -9496,7 +9526,7 @@
         <v>43.281649837012139</v>
       </c>
     </row>
-    <row r="386" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:3" ht="40" customHeight="1">
       <c r="A386" s="4">
         <v>46034</v>
       </c>
@@ -9507,7 +9537,7 @@
         <v>43.445683679020448</v>
       </c>
     </row>
-    <row r="387" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:3" ht="40" customHeight="1">
       <c r="A387" s="4">
         <v>46035</v>
       </c>
@@ -9518,7 +9548,7 @@
         <v>43.235243639167173</v>
       </c>
     </row>
-    <row r="388" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:3" ht="40" customHeight="1">
       <c r="A388" s="4">
         <v>46036</v>
       </c>
@@ -9529,7 +9559,7 @@
         <v>42.726937848276023</v>
       </c>
     </row>
-    <row r="389" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:3" ht="40" customHeight="1">
       <c r="A389" s="4">
         <v>46037</v>
       </c>
@@ -9540,7 +9570,7 @@
         <v>42.949192026372295</v>
       </c>
     </row>
-    <row r="390" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:3" ht="40" customHeight="1">
       <c r="A390" s="4">
         <v>46038</v>
       </c>
@@ -9551,7 +9581,7 @@
         <v>42.877551087677581</v>
       </c>
     </row>
-    <row r="391" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:3" ht="40" customHeight="1">
       <c r="A391" s="4">
         <v>46041</v>
       </c>
@@ -9562,7 +9592,7 @@
         <v>42.877551087677581</v>
       </c>
     </row>
-    <row r="392" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:3" ht="40" customHeight="1">
       <c r="A392" s="4">
         <v>46042</v>
       </c>
@@ -9573,7 +9603,7 @@
         <v>40.744378304196047</v>
       </c>
     </row>
-    <row r="393" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:3" ht="40" customHeight="1">
       <c r="A393" s="4">
         <v>46043</v>
       </c>
@@ -9584,7 +9614,7 @@
         <v>41.916195636072956</v>
       </c>
     </row>
-    <row r="394" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:3" ht="40" customHeight="1">
       <c r="A394" s="4">
         <v>46044</v>
       </c>
@@ -9595,7 +9625,7 @@
         <v>42.4214294787458</v>
       </c>
     </row>
-    <row r="395" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:3" ht="40" customHeight="1">
       <c r="A395" s="4">
         <v>46045</v>
       </c>
@@ -9606,7 +9636,7 @@
         <v>42.432228031750199</v>
       </c>
     </row>
-    <row r="396" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:3" ht="40" customHeight="1">
       <c r="A396" s="4">
         <v>46048</v>
       </c>
@@ -9617,7 +9647,7 @@
         <v>42.942030241652468</v>
       </c>
     </row>
-    <row r="397" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:3" ht="40" customHeight="1">
       <c r="A397" s="4">
         <v>46049</v>
       </c>
@@ -9628,7 +9658,7 @@
         <v>43.331601670212635</v>
       </c>
     </row>
-    <row r="398" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:3" ht="40" customHeight="1">
       <c r="A398" s="4">
         <v>46050</v>
       </c>
@@ -9639,7 +9669,7 @@
         <v>43.313764594018863</v>
       </c>
     </row>
-    <row r="399" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:3" ht="40" customHeight="1">
       <c r="A399" s="4">
         <v>46051</v>
       </c>
@@ -9650,7 +9680,7 @@
         <v>43.106621662808294</v>
       </c>
     </row>
-    <row r="400" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:3" ht="40" customHeight="1">
       <c r="A400" s="4">
         <v>46052</v>
       </c>
@@ -9661,7 +9691,7 @@
         <v>42.719760127916906</v>
       </c>
     </row>
-    <row r="401" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:3" ht="40" customHeight="1">
       <c r="A401" s="4">
         <v>46055</v>
       </c>
@@ -9672,7 +9702,7 @@
         <v>43.245954673327745</v>
       </c>
     </row>
-    <row r="402" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:3" ht="40" customHeight="1">
       <c r="A402" s="4">
         <v>46056</v>
       </c>
@@ -9683,7 +9713,7 @@
         <v>42.374622269581131</v>
       </c>
     </row>
-    <row r="403" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:3" ht="40" customHeight="1">
       <c r="A403" s="4">
         <v>46057</v>
       </c>
@@ -9694,7 +9724,7 @@
         <v>41.861911729917722</v>
       </c>
     </row>
-    <row r="404" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:3" ht="40" customHeight="1">
       <c r="A404" s="4">
         <v>46058</v>
       </c>
@@ -9705,7 +9735,7 @@
         <v>40.616175506467712</v>
       </c>
     </row>
-    <row r="405" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:3" ht="40" customHeight="1">
       <c r="A405" s="4">
         <v>46059</v>
       </c>
@@ -9716,7 +9746,7 @@
         <v>42.532958334903562</v>
       </c>
     </row>
-    <row r="406" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:3" ht="40" customHeight="1">
       <c r="A406" s="4">
         <v>46062</v>
       </c>
@@ -9727,7 +9757,7 @@
         <v>42.970674303576281</v>
       </c>
     </row>
-    <row r="407" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:3" ht="40" customHeight="1">
       <c r="A407" s="4">
         <v>46063</v>
       </c>
@@ -9738,7 +9768,7 @@
         <v>42.651546076768049</v>
       </c>
     </row>
-    <row r="408" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:3" ht="40" customHeight="1">
       <c r="A408" s="4">
         <v>46064</v>
       </c>
@@ -9749,7 +9779,7 @@
         <v>42.6443629427636</v>
       </c>
     </row>
-    <row r="409" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:3" ht="40" customHeight="1">
       <c r="A409" s="4">
         <v>46065</v>
       </c>
@@ -9760,7 +9790,7 @@
         <v>41.058694560191306</v>
       </c>
     </row>
-    <row r="410" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:3" ht="40" customHeight="1">
       <c r="A410" s="4">
         <v>46066</v>
       </c>
@@ -9771,7 +9801,7 @@
         <v>41.051396089217732</v>
       </c>
     </row>
-    <row r="411" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:3" ht="40" customHeight="1">
       <c r="A411" s="4">
         <v>46069</v>
       </c>
@@ -9782,7 +9812,7 @@
         <v>41.051396089217732</v>
       </c>
     </row>
-    <row r="412" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:3" ht="40" customHeight="1">
       <c r="A412" s="4">
         <v>46070</v>
       </c>
@@ -9793,7 +9823,7 @@
         <v>41.197264396024394</v>
       </c>
     </row>
-    <row r="413" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:3" ht="40" customHeight="1">
       <c r="A413" s="4">
         <v>46071</v>
       </c>
@@ -9804,7 +9834,7 @@
         <v>41.688004943578719</v>
       </c>
     </row>
-    <row r="414" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:3" ht="40" customHeight="1">
       <c r="A414" s="4">
         <v>46072</v>
       </c>
@@ -9815,7 +9845,7 @@
         <v>41.437482891884997</v>
       </c>
     </row>
-    <row r="415" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:3" ht="40" customHeight="1">
       <c r="A415" s="4">
         <v>46073</v>
       </c>
@@ -9826,7 +9856,7 @@
         <v>42.107763113738443</v>
       </c>
     </row>
-    <row r="416" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:3" ht="40" customHeight="1">
       <c r="A416" s="4">
         <v>46076</v>
       </c>
@@ -9837,7 +9867,7 @@
         <v>41.065992498526946</v>
       </c>
     </row>
-    <row r="417" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:3" ht="40" customHeight="1">
       <c r="A417" s="4">
         <v>46077</v>
       </c>
@@ -9848,7 +9878,7 @@
         <v>41.825706081441119</v>
       </c>
     </row>
-    <row r="418" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:3" ht="40" customHeight="1">
       <c r="A418" s="4">
         <v>46078</v>
       </c>
@@ -9859,7 +9889,7 @@
         <v>42.633587274212715</v>
       </c>
     </row>
-    <row r="419" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:3" ht="40" customHeight="1">
       <c r="A419" s="4">
         <v>46079</v>
       </c>
@@ -9870,7 +9900,7 @@
         <v>42.060808821072911</v>
       </c>
     </row>
-    <row r="420" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:3" ht="40" customHeight="1">
       <c r="A420" s="4">
         <v>46080</v>
       </c>
@@ -9881,142 +9911,172 @@
         <v>41.611825519220965</v>
       </c>
     </row>
-    <row r="421" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A421" s="4"/>
-      <c r="B421" s="5"/>
-      <c r="C421" s="5"/>
-    </row>
-    <row r="422" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A422" s="4"/>
-      <c r="B422" s="5"/>
-      <c r="C422" s="5"/>
-    </row>
-    <row r="423" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A423" s="4"/>
-      <c r="B423" s="5"/>
-      <c r="C423" s="5"/>
-    </row>
-    <row r="424" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A424" s="4"/>
-      <c r="B424" s="5"/>
-      <c r="C424" s="5"/>
-    </row>
-    <row r="425" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A425" s="4"/>
-      <c r="B425" s="5"/>
-      <c r="C425" s="5"/>
-    </row>
-    <row r="426" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:3" ht="40" customHeight="1">
+      <c r="A421" s="4">
+        <v>46083</v>
+      </c>
+      <c r="B421" s="5">
+        <v>60.822172522730369</v>
+      </c>
+      <c r="C421" s="5">
+        <v>41.600938005373997</v>
+      </c>
+    </row>
+    <row r="422" spans="1:3" ht="40" customHeight="1">
+      <c r="A422" s="4">
+        <v>46084</v>
+      </c>
+      <c r="B422" s="5">
+        <v>61.705385387182574</v>
+      </c>
+      <c r="C422" s="5">
+        <v>40.674802894464804</v>
+      </c>
+    </row>
+    <row r="423" spans="1:3" ht="40" customHeight="1">
+      <c r="A423" s="4">
+        <v>46085</v>
+      </c>
+      <c r="B423" s="5">
+        <v>58.266471003626428</v>
+      </c>
+      <c r="C423" s="5">
+        <v>41.422940610175367</v>
+      </c>
+    </row>
+    <row r="424" spans="1:3" ht="40" customHeight="1">
+      <c r="A424" s="4">
+        <v>46086</v>
+      </c>
+      <c r="B424" s="5">
+        <v>59.186971398995546</v>
+      </c>
+      <c r="C424" s="5">
+        <v>40.82853645329314</v>
+      </c>
+    </row>
+    <row r="425" spans="1:3" ht="40" customHeight="1">
+      <c r="A425" s="4">
+        <v>46087</v>
+      </c>
+      <c r="B425" s="5">
+        <v>62.484811680261231</v>
+      </c>
+      <c r="C425" s="5">
+        <v>39.480846860545853</v>
+      </c>
+    </row>
+    <row r="426" spans="1:3" ht="40" customHeight="1">
       <c r="A426" s="4"/>
       <c r="B426" s="5"/>
       <c r="C426" s="5"/>
     </row>
-    <row r="427" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:3" ht="40" customHeight="1">
       <c r="A427" s="4"/>
       <c r="B427" s="5"/>
       <c r="C427" s="5"/>
     </row>
-    <row r="428" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:3" ht="40" customHeight="1">
       <c r="A428" s="4"/>
       <c r="B428" s="5"/>
       <c r="C428" s="5"/>
     </row>
-    <row r="429" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:3" ht="40" customHeight="1">
       <c r="A429" s="4"/>
       <c r="B429" s="5"/>
       <c r="C429" s="5"/>
     </row>
-    <row r="430" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:3" ht="40" customHeight="1">
       <c r="A430" s="4"/>
       <c r="B430" s="5"/>
       <c r="C430" s="5"/>
     </row>
-    <row r="431" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:3" ht="40" customHeight="1">
       <c r="A431" s="4"/>
       <c r="B431" s="5"/>
       <c r="C431" s="5"/>
     </row>
-    <row r="432" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:3" ht="40" customHeight="1">
       <c r="A432" s="4"/>
       <c r="B432" s="5"/>
       <c r="C432" s="5"/>
     </row>
-    <row r="433" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:3" ht="40" customHeight="1">
       <c r="A433" s="4"/>
       <c r="B433" s="5"/>
       <c r="C433" s="5"/>
     </row>
-    <row r="434" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:3" ht="40" customHeight="1">
       <c r="A434" s="4"/>
       <c r="B434" s="5"/>
       <c r="C434" s="5"/>
     </row>
-    <row r="435" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:3" ht="40" customHeight="1">
       <c r="A435" s="4"/>
       <c r="B435" s="5"/>
       <c r="C435" s="5"/>
     </row>
-    <row r="436" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:3" ht="40" customHeight="1">
       <c r="A436" s="4"/>
       <c r="B436" s="5"/>
       <c r="C436" s="5"/>
     </row>
-    <row r="437" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:3" ht="40" customHeight="1">
       <c r="A437" s="4"/>
       <c r="B437" s="5"/>
       <c r="C437" s="5"/>
     </row>
-    <row r="438" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:3" ht="40" customHeight="1">
       <c r="A438" s="4"/>
       <c r="B438" s="5"/>
       <c r="C438" s="5"/>
     </row>
-    <row r="439" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:3" ht="40" customHeight="1">
       <c r="A439" s="4"/>
       <c r="B439" s="5"/>
       <c r="C439" s="5"/>
     </row>
-    <row r="440" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:3" ht="40" customHeight="1">
       <c r="A440" s="4"/>
       <c r="B440" s="5"/>
       <c r="C440" s="5"/>
     </row>
-    <row r="441" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:3" ht="40" customHeight="1">
       <c r="A441" s="4"/>
       <c r="B441" s="5"/>
       <c r="C441" s="5"/>
     </row>
-    <row r="442" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:3" ht="40" customHeight="1">
       <c r="A442" s="4"/>
       <c r="B442" s="5"/>
       <c r="C442" s="5"/>
     </row>
-    <row r="443" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:3" ht="40" customHeight="1">
       <c r="A443" s="4"/>
       <c r="B443" s="5"/>
       <c r="C443" s="5"/>
     </row>
-    <row r="444" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:3" ht="40" customHeight="1">
       <c r="A444" s="4"/>
       <c r="B444" s="5"/>
       <c r="C444" s="5"/>
     </row>
-    <row r="445" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:3" ht="40" customHeight="1">
       <c r="A445" s="4"/>
       <c r="B445" s="5"/>
       <c r="C445" s="5"/>
     </row>
-    <row r="446" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:3" ht="40" customHeight="1">
       <c r="A446" s="4"/>
       <c r="B446" s="5"/>
       <c r="C446" s="5"/>
     </row>
-    <row r="447" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:3" ht="40" customHeight="1">
       <c r="A447" s="4"/>
       <c r="B447" s="5"/>
       <c r="C447" s="5"/>
     </row>
-    <row r="448" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:3" ht="40" customHeight="1">
       <c r="A448" s="4"/>
       <c r="B448" s="5"/>
       <c r="C448" s="5"/>

--- a/files/data.xlsx
+++ b/files/data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ferrara/Desktop/salvatore non toccare/monitoraggio/files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ferrars/Desktop/monitoraggio/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F8BE0E8-D187-B646-A211-3D442B74995E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F23E53F6-4583-B345-AC8E-66460B776864}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1600" yWindow="600" windowWidth="10000" windowHeight="16320" xr2:uid="{F1546C66-1100-0F4C-AEC5-783BC2578DB8}"/>
+    <workbookView xWindow="1600" yWindow="600" windowWidth="21780" windowHeight="16320" activeTab="1" xr2:uid="{F1546C66-1100-0F4C-AEC5-783BC2578DB8}"/>
   </bookViews>
   <sheets>
     <sheet name="vix" sheetId="2" r:id="rId1"/>
@@ -143,7 +143,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normale" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2156,7 +2156,7 @@
         <v>16.68</v>
       </c>
     </row>
-    <row r="153" spans="1:3" ht="24">
+    <row r="153" spans="1:3" ht="23">
       <c r="A153" s="4">
         <v>45695</v>
       </c>
@@ -2167,7 +2167,7 @@
         <v>17.350000000000001</v>
       </c>
     </row>
-    <row r="154" spans="1:3" ht="24">
+    <row r="154" spans="1:3" ht="23">
       <c r="A154" s="4">
         <v>45698</v>
       </c>
@@ -2178,7 +2178,7 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="155" spans="1:3" ht="24">
+    <row r="155" spans="1:3" ht="23">
       <c r="A155" s="4">
         <v>45699</v>
       </c>
@@ -2189,7 +2189,7 @@
         <v>16.77</v>
       </c>
     </row>
-    <row r="156" spans="1:3" ht="24">
+    <row r="156" spans="1:3" ht="23">
       <c r="A156" s="4">
         <v>45700</v>
       </c>
@@ -2200,7 +2200,7 @@
         <v>16.8</v>
       </c>
     </row>
-    <row r="157" spans="1:3" ht="24">
+    <row r="157" spans="1:3" ht="23">
       <c r="A157" s="4">
         <v>45701</v>
       </c>
@@ -2211,7 +2211,7 @@
         <v>16.13</v>
       </c>
     </row>
-    <row r="158" spans="1:3" ht="24">
+    <row r="158" spans="1:3" ht="23">
       <c r="A158" s="4">
         <v>45702</v>
       </c>
@@ -2222,7 +2222,7 @@
         <v>16.010000000000002</v>
       </c>
     </row>
-    <row r="159" spans="1:3" ht="24">
+    <row r="159" spans="1:3" ht="23">
       <c r="A159" s="4">
         <v>45705</v>
       </c>
@@ -2233,7 +2233,7 @@
         <v>16.010000000000002</v>
       </c>
     </row>
-    <row r="160" spans="1:3" ht="24">
+    <row r="160" spans="1:3" ht="23">
       <c r="A160" s="4">
         <v>45706</v>
       </c>
@@ -2244,7 +2244,7 @@
         <v>15.66</v>
       </c>
     </row>
-    <row r="161" spans="1:3" ht="24">
+    <row r="161" spans="1:3" ht="23">
       <c r="A161" s="4">
         <v>45707</v>
       </c>
@@ -2255,7 +2255,7 @@
         <v>15.94</v>
       </c>
     </row>
-    <row r="162" spans="1:3" ht="24">
+    <row r="162" spans="1:3" ht="23">
       <c r="A162" s="4">
         <v>45708</v>
       </c>
@@ -2266,7 +2266,7 @@
         <v>17.03</v>
       </c>
     </row>
-    <row r="163" spans="1:3" ht="24">
+    <row r="163" spans="1:3" ht="23">
       <c r="A163" s="4">
         <v>45709</v>
       </c>
@@ -2277,7 +2277,7 @@
         <v>18.3</v>
       </c>
     </row>
-    <row r="164" spans="1:3" ht="24">
+    <row r="164" spans="1:3" ht="23">
       <c r="A164" s="4">
         <v>45712</v>
       </c>
@@ -2288,7 +2288,7 @@
         <v>18.43</v>
       </c>
     </row>
-    <row r="165" spans="1:3" ht="24">
+    <row r="165" spans="1:3" ht="23">
       <c r="A165" s="4">
         <v>45713</v>
       </c>
@@ -2299,7 +2299,7 @@
         <v>18.48</v>
       </c>
     </row>
-    <row r="166" spans="1:3" ht="24">
+    <row r="166" spans="1:3" ht="23">
       <c r="A166" s="4">
         <v>45714</v>
       </c>
@@ -2310,7 +2310,7 @@
         <v>18.13</v>
       </c>
     </row>
-    <row r="167" spans="1:3" ht="24">
+    <row r="167" spans="1:3" ht="23">
       <c r="A167" s="4">
         <v>45715</v>
       </c>
@@ -2321,7 +2321,7 @@
         <v>19.309999999999999</v>
       </c>
     </row>
-    <row r="168" spans="1:3" ht="24">
+    <row r="168" spans="1:3" ht="23">
       <c r="A168" s="4">
         <v>45716</v>
       </c>
@@ -2332,7 +2332,7 @@
         <v>18.829999999999998</v>
       </c>
     </row>
-    <row r="169" spans="1:3" ht="24">
+    <row r="169" spans="1:3" ht="23">
       <c r="A169" s="4">
         <v>45719</v>
       </c>
@@ -2343,7 +2343,7 @@
         <v>20.66</v>
       </c>
     </row>
-    <row r="170" spans="1:3" ht="24">
+    <row r="170" spans="1:3" ht="23">
       <c r="A170" s="4">
         <v>45720</v>
       </c>
@@ -2354,7 +2354,7 @@
         <v>21.24</v>
       </c>
     </row>
-    <row r="171" spans="1:3" ht="24">
+    <row r="171" spans="1:3" ht="23">
       <c r="A171" s="4">
         <v>45721</v>
       </c>
@@ -2365,7 +2365,7 @@
         <v>20.13</v>
       </c>
     </row>
-    <row r="172" spans="1:3" ht="24">
+    <row r="172" spans="1:3" ht="23">
       <c r="A172" s="4">
         <v>45722</v>
       </c>
@@ -2376,7 +2376,7 @@
         <v>22.83</v>
       </c>
     </row>
-    <row r="173" spans="1:3" ht="24">
+    <row r="173" spans="1:3" ht="23">
       <c r="A173" s="4">
         <v>45723</v>
       </c>
@@ -2387,7 +2387,7 @@
         <v>21.63</v>
       </c>
     </row>
-    <row r="174" spans="1:3" ht="24">
+    <row r="174" spans="1:3" ht="23">
       <c r="A174" s="4">
         <v>45726</v>
       </c>
@@ -2398,7 +2398,7 @@
         <v>25.33</v>
       </c>
     </row>
-    <row r="175" spans="1:3" ht="24">
+    <row r="175" spans="1:3" ht="23">
       <c r="A175" s="4">
         <v>45727</v>
       </c>
@@ -2409,7 +2409,7 @@
         <v>24.61</v>
       </c>
     </row>
-    <row r="176" spans="1:3" ht="24">
+    <row r="176" spans="1:3" ht="23">
       <c r="A176" s="4">
         <v>45728</v>
       </c>
@@ -2420,7 +2420,7 @@
         <v>22.98</v>
       </c>
     </row>
-    <row r="177" spans="1:3" ht="24">
+    <row r="177" spans="1:3" ht="23">
       <c r="A177" s="4">
         <v>45729</v>
       </c>
@@ -2431,7 +2431,7 @@
         <v>24.41</v>
       </c>
     </row>
-    <row r="178" spans="1:3" ht="24">
+    <row r="178" spans="1:3" ht="23">
       <c r="A178" s="4">
         <v>45730</v>
       </c>
@@ -2442,7 +2442,7 @@
         <v>21.52</v>
       </c>
     </row>
-    <row r="179" spans="1:3" ht="24">
+    <row r="179" spans="1:3" ht="23">
       <c r="A179" s="4">
         <v>45733</v>
       </c>
@@ -2453,7 +2453,7 @@
         <v>19.920000000000002</v>
       </c>
     </row>
-    <row r="180" spans="1:3" ht="24">
+    <row r="180" spans="1:3" ht="23">
       <c r="A180" s="4">
         <v>45734</v>
       </c>
@@ -2464,7 +2464,7 @@
         <v>20.48</v>
       </c>
     </row>
-    <row r="181" spans="1:3" ht="24">
+    <row r="181" spans="1:3" ht="23">
       <c r="A181" s="4">
         <v>45735</v>
       </c>
@@ -2475,7 +2475,7 @@
         <v>19.75</v>
       </c>
     </row>
-    <row r="182" spans="1:3" ht="24">
+    <row r="182" spans="1:3" ht="23">
       <c r="A182" s="4">
         <v>45736</v>
       </c>
@@ -2486,7 +2486,7 @@
         <v>19.47</v>
       </c>
     </row>
-    <row r="183" spans="1:3" ht="24">
+    <row r="183" spans="1:3" ht="23">
       <c r="A183" s="4">
         <v>45737</v>
       </c>
@@ -2497,7 +2497,7 @@
         <v>19.47</v>
       </c>
     </row>
-    <row r="184" spans="1:3" ht="24">
+    <row r="184" spans="1:3" ht="23">
       <c r="A184" s="4">
         <v>45740</v>
       </c>
@@ -2508,7 +2508,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="185" spans="1:3" ht="24">
+    <row r="185" spans="1:3" ht="23">
       <c r="A185" s="4">
         <v>45741</v>
       </c>
@@ -2519,7 +2519,7 @@
         <v>18.66</v>
       </c>
     </row>
-    <row r="186" spans="1:3" ht="24">
+    <row r="186" spans="1:3" ht="23">
       <c r="A186" s="4">
         <v>45742</v>
       </c>
@@ -2530,7 +2530,7 @@
         <v>19.149999999999999</v>
       </c>
     </row>
-    <row r="187" spans="1:3" ht="24">
+    <row r="187" spans="1:3" ht="23">
       <c r="A187" s="4">
         <v>45743</v>
       </c>
@@ -2541,7 +2541,7 @@
         <v>19.16</v>
       </c>
     </row>
-    <row r="188" spans="1:3" ht="24">
+    <row r="188" spans="1:3" ht="23">
       <c r="A188" s="4">
         <v>45744</v>
       </c>
@@ -2552,7 +2552,7 @@
         <v>20.55</v>
       </c>
     </row>
-    <row r="189" spans="1:3" ht="24">
+    <row r="189" spans="1:3" ht="23">
       <c r="A189" s="4">
         <v>45747</v>
       </c>
@@ -2563,7 +2563,7 @@
         <v>20.49</v>
       </c>
     </row>
-    <row r="190" spans="1:3" ht="24">
+    <row r="190" spans="1:3" ht="23">
       <c r="A190" s="4">
         <v>45748</v>
       </c>
@@ -2574,7 +2574,7 @@
         <v>20.51</v>
       </c>
     </row>
-    <row r="191" spans="1:3" ht="24">
+    <row r="191" spans="1:3" ht="23">
       <c r="A191" s="4">
         <v>45749</v>
       </c>
@@ -2585,7 +2585,7 @@
         <v>20.02</v>
       </c>
     </row>
-    <row r="192" spans="1:3" ht="24">
+    <row r="192" spans="1:3" ht="23">
       <c r="A192" s="4">
         <v>45750</v>
       </c>
@@ -2596,7 +2596,7 @@
         <v>24.19</v>
       </c>
     </row>
-    <row r="193" spans="1:3" ht="24">
+    <row r="193" spans="1:3" ht="23">
       <c r="A193" s="4">
         <v>45751</v>
       </c>
@@ -2607,7 +2607,7 @@
         <v>28.52</v>
       </c>
     </row>
-    <row r="194" spans="1:3" ht="24">
+    <row r="194" spans="1:3" ht="23">
       <c r="A194" s="4">
         <v>45754</v>
       </c>
@@ -2618,7 +2618,7 @@
         <v>26.07</v>
       </c>
     </row>
-    <row r="195" spans="1:3" ht="24">
+    <row r="195" spans="1:3" ht="23">
       <c r="A195" s="4">
         <v>45755</v>
       </c>
@@ -2629,7 +2629,7 @@
         <v>27.91</v>
       </c>
     </row>
-    <row r="196" spans="1:3" ht="24">
+    <row r="196" spans="1:3" ht="23">
       <c r="A196" s="4">
         <v>45756</v>
       </c>
@@ -2640,7 +2640,7 @@
         <v>23.83</v>
       </c>
     </row>
-    <row r="197" spans="1:3" ht="24">
+    <row r="197" spans="1:3" ht="23">
       <c r="A197" s="4">
         <v>45757</v>
       </c>
@@ -2651,7 +2651,7 @@
         <v>27.57</v>
       </c>
     </row>
-    <row r="198" spans="1:3" ht="24">
+    <row r="198" spans="1:3" ht="23">
       <c r="A198" s="4">
         <v>45758</v>
       </c>
@@ -2662,7 +2662,7 @@
         <v>27.14</v>
       </c>
     </row>
-    <row r="199" spans="1:3" ht="24">
+    <row r="199" spans="1:3" ht="23">
       <c r="A199" s="4">
         <v>45761</v>
       </c>
@@ -2673,7 +2673,7 @@
         <v>29.86</v>
       </c>
     </row>
-    <row r="200" spans="1:3" ht="24">
+    <row r="200" spans="1:3" ht="23">
       <c r="A200" s="4">
         <v>45762</v>
       </c>
@@ -2684,7 +2684,7 @@
         <v>29.9</v>
       </c>
     </row>
-    <row r="201" spans="1:3" ht="24">
+    <row r="201" spans="1:3" ht="23">
       <c r="A201" s="4">
         <v>45763</v>
       </c>
@@ -2695,7 +2695,7 @@
         <v>31.91</v>
       </c>
     </row>
-    <row r="202" spans="1:3" ht="24">
+    <row r="202" spans="1:3" ht="23">
       <c r="A202" s="4">
         <v>45764</v>
       </c>
@@ -2706,7 +2706,7 @@
         <v>26.73</v>
       </c>
     </row>
-    <row r="203" spans="1:3" ht="24">
+    <row r="203" spans="1:3" ht="23">
       <c r="A203" s="4">
         <v>45769</v>
       </c>
@@ -2717,7 +2717,7 @@
         <v>26.54</v>
       </c>
     </row>
-    <row r="204" spans="1:3" ht="24">
+    <row r="204" spans="1:3" ht="23">
       <c r="A204" s="4">
         <v>45770</v>
       </c>
@@ -2728,7 +2728,7 @@
         <v>25.44</v>
       </c>
     </row>
-    <row r="205" spans="1:3" ht="24">
+    <row r="205" spans="1:3" ht="23">
       <c r="A205" s="4">
         <v>45771</v>
       </c>
@@ -2739,7 +2739,7 @@
         <v>24.57</v>
       </c>
     </row>
-    <row r="206" spans="1:3" ht="24">
+    <row r="206" spans="1:3" ht="23">
       <c r="A206" s="4">
         <v>45772</v>
       </c>
@@ -2750,7 +2750,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="207" spans="1:3" ht="24">
+    <row r="207" spans="1:3" ht="23">
       <c r="A207" s="4">
         <v>45775</v>
       </c>
@@ -2761,7 +2761,7 @@
         <v>23.68</v>
       </c>
     </row>
-    <row r="208" spans="1:3" ht="24">
+    <row r="208" spans="1:3" ht="23">
       <c r="A208" s="4">
         <v>45776</v>
       </c>
@@ -2772,7 +2772,7 @@
         <v>23.38</v>
       </c>
     </row>
-    <row r="209" spans="1:3" ht="24">
+    <row r="209" spans="1:3" ht="23">
       <c r="A209" s="4">
         <v>45777</v>
       </c>
@@ -2783,7 +2783,7 @@
         <v>24.01</v>
       </c>
     </row>
-    <row r="210" spans="1:3" ht="24">
+    <row r="210" spans="1:3" ht="23">
       <c r="A210" s="4">
         <v>45779</v>
       </c>
@@ -2794,7 +2794,7 @@
         <v>22.48</v>
       </c>
     </row>
-    <row r="211" spans="1:3" ht="24">
+    <row r="211" spans="1:3" ht="23">
       <c r="A211" s="4">
         <v>45782</v>
       </c>
@@ -2805,7 +2805,7 @@
         <v>23.18</v>
       </c>
     </row>
-    <row r="212" spans="1:3" ht="24">
+    <row r="212" spans="1:3" ht="23">
       <c r="A212" s="4">
         <v>45783</v>
       </c>
@@ -2816,7 +2816,7 @@
         <v>24.11</v>
       </c>
     </row>
-    <row r="213" spans="1:3" ht="24">
+    <row r="213" spans="1:3" ht="23">
       <c r="A213" s="4">
         <v>45784</v>
       </c>
@@ -2827,7 +2827,7 @@
         <v>23.32</v>
       </c>
     </row>
-    <row r="214" spans="1:3" ht="24">
+    <row r="214" spans="1:3" ht="23">
       <c r="A214" s="4">
         <v>45785</v>
       </c>
@@ -2838,7 +2838,7 @@
         <v>22.29</v>
       </c>
     </row>
-    <row r="215" spans="1:3" ht="24">
+    <row r="215" spans="1:3" ht="23">
       <c r="A215" s="4">
         <v>45786</v>
       </c>
@@ -2849,7 +2849,7 @@
         <v>22.01</v>
       </c>
     </row>
-    <row r="216" spans="1:3" ht="24">
+    <row r="216" spans="1:3" ht="23">
       <c r="A216" s="4">
         <v>45789</v>
       </c>
@@ -2860,7 +2860,7 @@
         <v>18.57</v>
       </c>
     </row>
-    <row r="217" spans="1:3" ht="24">
+    <row r="217" spans="1:3" ht="23">
       <c r="A217" s="4">
         <v>45790</v>
       </c>
@@ -2871,7 +2871,7 @@
         <v>18.440000000000001</v>
       </c>
     </row>
-    <row r="218" spans="1:3" ht="24">
+    <row r="218" spans="1:3" ht="23">
       <c r="A218" s="4">
         <v>45791</v>
       </c>
@@ -2882,7 +2882,7 @@
         <v>18.78</v>
       </c>
     </row>
-    <row r="219" spans="1:3" ht="24">
+    <row r="219" spans="1:3" ht="23">
       <c r="A219" s="4">
         <v>45792</v>
       </c>
@@ -2893,7 +2893,7 @@
         <v>18.23</v>
       </c>
     </row>
-    <row r="220" spans="1:3" ht="24">
+    <row r="220" spans="1:3" ht="23">
       <c r="A220" s="4">
         <v>45793</v>
       </c>
@@ -2904,7 +2904,7 @@
         <v>17.93</v>
       </c>
     </row>
-    <row r="221" spans="1:3" ht="24">
+    <row r="221" spans="1:3" ht="23">
       <c r="A221" s="4">
         <v>45796</v>
       </c>
@@ -2915,7 +2915,7 @@
         <v>19.649999999999999</v>
       </c>
     </row>
-    <row r="222" spans="1:3" ht="24">
+    <row r="222" spans="1:3" ht="23">
       <c r="A222" s="4">
         <v>45797</v>
       </c>
@@ -2926,7 +2926,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="223" spans="1:3" ht="24">
+    <row r="223" spans="1:3" ht="23">
       <c r="A223" s="4">
         <v>45798</v>
       </c>
@@ -2937,7 +2937,7 @@
         <v>20.79</v>
       </c>
     </row>
-    <row r="224" spans="1:3" ht="24">
+    <row r="224" spans="1:3" ht="23">
       <c r="A224" s="4">
         <v>45799</v>
       </c>
@@ -2948,7 +2948,7 @@
         <v>21.24</v>
       </c>
     </row>
-    <row r="225" spans="1:3" ht="24">
+    <row r="225" spans="1:3" ht="23">
       <c r="A225" s="4">
         <v>45800</v>
       </c>
@@ -2959,7 +2959,7 @@
         <v>22.28</v>
       </c>
     </row>
-    <row r="226" spans="1:3" ht="24">
+    <row r="226" spans="1:3" ht="23">
       <c r="A226" s="4">
         <v>45803</v>
       </c>
@@ -2970,7 +2970,7 @@
         <v>20.93</v>
       </c>
     </row>
-    <row r="227" spans="1:3" ht="24">
+    <row r="227" spans="1:3" ht="23">
       <c r="A227" s="4">
         <v>45804</v>
       </c>
@@ -2981,7 +2981,7 @@
         <v>20.52</v>
       </c>
     </row>
-    <row r="228" spans="1:3" ht="24">
+    <row r="228" spans="1:3" ht="23">
       <c r="A228" s="4">
         <v>45805</v>
       </c>
@@ -2992,7 +2992,7 @@
         <v>20.79</v>
       </c>
     </row>
-    <row r="229" spans="1:3" ht="24">
+    <row r="229" spans="1:3" ht="23">
       <c r="A229" s="4">
         <v>45807</v>
       </c>
@@ -3003,7 +3003,7 @@
         <v>21.04</v>
       </c>
     </row>
-    <row r="230" spans="1:3" ht="24">
+    <row r="230" spans="1:3" ht="23">
       <c r="A230" s="4">
         <v>45810</v>
       </c>
@@ -3014,7 +3014,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="231" spans="1:3" ht="24">
+    <row r="231" spans="1:3" ht="23">
       <c r="A231" s="4">
         <v>45811</v>
       </c>
@@ -3025,7 +3025,7 @@
         <v>20.57</v>
       </c>
     </row>
-    <row r="232" spans="1:3" ht="24">
+    <row r="232" spans="1:3" ht="23">
       <c r="A232" s="4">
         <v>45812</v>
       </c>
@@ -3036,7 +3036,7 @@
         <v>20.57</v>
       </c>
     </row>
-    <row r="233" spans="1:3" ht="24">
+    <row r="233" spans="1:3" ht="23">
       <c r="A233" s="4">
         <v>45813</v>
       </c>
@@ -3047,7 +3047,7 @@
         <v>20.89</v>
       </c>
     </row>
-    <row r="234" spans="1:3" ht="24">
+    <row r="234" spans="1:3" ht="23">
       <c r="A234" s="4">
         <v>45814</v>
       </c>
@@ -3058,7 +3058,7 @@
         <v>20.149999999999999</v>
       </c>
     </row>
-    <row r="235" spans="1:3" ht="24">
+    <row r="235" spans="1:3" ht="23">
       <c r="A235" s="4">
         <v>45818</v>
       </c>
@@ -3069,7 +3069,7 @@
         <v>19.97</v>
       </c>
     </row>
-    <row r="236" spans="1:3" ht="24">
+    <row r="236" spans="1:3" ht="23">
       <c r="A236" s="4">
         <v>45819</v>
       </c>
@@ -3080,7 +3080,7 @@
         <v>20.09</v>
       </c>
     </row>
-    <row r="237" spans="1:3" ht="24">
+    <row r="237" spans="1:3" ht="23">
       <c r="A237" s="4">
         <v>45820</v>
       </c>
@@ -3091,7 +3091,7 @@
         <v>20.3</v>
       </c>
     </row>
-    <row r="238" spans="1:3" ht="24">
+    <row r="238" spans="1:3" ht="23">
       <c r="A238" s="4">
         <v>45821</v>
       </c>
@@ -3102,7 +3102,7 @@
         <v>21.82</v>
       </c>
     </row>
-    <row r="239" spans="1:3" ht="24">
+    <row r="239" spans="1:3" ht="23">
       <c r="A239" s="4">
         <v>45824</v>
       </c>
@@ -3113,7 +3113,7 @@
         <v>20.28</v>
       </c>
     </row>
-    <row r="240" spans="1:3" ht="24">
+    <row r="240" spans="1:3" ht="23">
       <c r="A240" s="4">
         <v>45825</v>
       </c>
@@ -3124,7 +3124,7 @@
         <v>21.41</v>
       </c>
     </row>
-    <row r="241" spans="1:3" ht="24">
+    <row r="241" spans="1:3" ht="23">
       <c r="A241" s="4">
         <v>45826</v>
       </c>
@@ -3135,7 +3135,7 @@
         <v>20.81</v>
       </c>
     </row>
-    <row r="242" spans="1:3" ht="24">
+    <row r="242" spans="1:3" ht="23">
       <c r="A242" s="4">
         <v>45827</v>
       </c>
@@ -3146,7 +3146,7 @@
         <v>21.13</v>
       </c>
     </row>
-    <row r="243" spans="1:3" ht="24">
+    <row r="243" spans="1:3" ht="23">
       <c r="A243" s="4">
         <v>45828</v>
       </c>
@@ -3157,7 +3157,7 @@
         <v>21.65</v>
       </c>
     </row>
-    <row r="244" spans="1:3" ht="24">
+    <row r="244" spans="1:3" ht="23">
       <c r="A244" s="4">
         <v>45831</v>
       </c>
@@ -3168,7 +3168,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="245" spans="1:3" ht="24">
+    <row r="245" spans="1:3" ht="23">
       <c r="A245" s="4">
         <v>45832</v>
       </c>
@@ -3179,7 +3179,7 @@
         <v>19.25</v>
       </c>
     </row>
-    <row r="246" spans="1:3" ht="24">
+    <row r="246" spans="1:3" ht="23">
       <c r="A246" s="4">
         <v>45833</v>
       </c>
@@ -3190,7 +3190,7 @@
         <v>19.02</v>
       </c>
     </row>
-    <row r="247" spans="1:3" ht="24">
+    <row r="247" spans="1:3" ht="23">
       <c r="A247" s="4">
         <v>45834</v>
       </c>
@@ -3201,7 +3201,7 @@
         <v>18.91</v>
       </c>
     </row>
-    <row r="248" spans="1:3" ht="24">
+    <row r="248" spans="1:3" ht="23">
       <c r="A248" s="4">
         <v>45835</v>
       </c>
@@ -3212,7 +3212,7 @@
         <v>18.850000000000001</v>
       </c>
     </row>
-    <row r="249" spans="1:3" ht="24">
+    <row r="249" spans="1:3" ht="23">
       <c r="A249" s="4">
         <v>45838</v>
       </c>
@@ -3223,7 +3223,7 @@
         <v>18.71</v>
       </c>
     </row>
-    <row r="250" spans="1:3" ht="24">
+    <row r="250" spans="1:3" ht="23">
       <c r="A250" s="4">
         <v>45839</v>
       </c>
@@ -3234,7 +3234,7 @@
         <v>18.649999999999999</v>
       </c>
     </row>
-    <row r="251" spans="1:3" ht="24">
+    <row r="251" spans="1:3" ht="23">
       <c r="A251" s="4">
         <v>45840</v>
       </c>
@@ -3245,7 +3245,7 @@
         <v>18.559999999999999</v>
       </c>
     </row>
-    <row r="252" spans="1:3" ht="24">
+    <row r="252" spans="1:3" ht="23">
       <c r="A252" s="4">
         <v>45841</v>
       </c>
@@ -3256,7 +3256,7 @@
         <v>18.32</v>
       </c>
     </row>
-    <row r="253" spans="1:3" ht="24">
+    <row r="253" spans="1:3" ht="23">
       <c r="A253" s="4">
         <v>45842</v>
       </c>
@@ -3267,7 +3267,7 @@
         <v>18.75</v>
       </c>
     </row>
-    <row r="254" spans="1:3" ht="24">
+    <row r="254" spans="1:3" ht="23">
       <c r="A254" s="4">
         <v>45845</v>
       </c>
@@ -3278,7 +3278,7 @@
         <v>18.239999999999998</v>
       </c>
     </row>
-    <row r="255" spans="1:3" ht="24">
+    <row r="255" spans="1:3" ht="23">
       <c r="A255" s="4">
         <v>45846</v>
       </c>
@@ -3289,7 +3289,7 @@
         <v>17.82</v>
       </c>
     </row>
-    <row r="256" spans="1:3" ht="24">
+    <row r="256" spans="1:3" ht="23">
       <c r="A256" s="4">
         <v>45847</v>
       </c>
@@ -3300,7 +3300,7 @@
         <v>17.260000000000002</v>
       </c>
     </row>
-    <row r="257" spans="1:3" ht="24">
+    <row r="257" spans="1:3" ht="23">
       <c r="A257" s="4">
         <v>45848</v>
       </c>
@@ -3311,7 +3311,7 @@
         <v>17.11</v>
       </c>
     </row>
-    <row r="258" spans="1:3" ht="24">
+    <row r="258" spans="1:3" ht="23">
       <c r="A258" s="4">
         <v>45849</v>
       </c>
@@ -3322,7 +3322,7 @@
         <v>16.399999999999999</v>
       </c>
     </row>
-    <row r="259" spans="1:3" ht="24">
+    <row r="259" spans="1:3" ht="23">
       <c r="A259" s="4">
         <v>45852</v>
       </c>
@@ -3333,7 +3333,7 @@
         <v>17.2</v>
       </c>
     </row>
-    <row r="260" spans="1:3" ht="24">
+    <row r="260" spans="1:3" ht="23">
       <c r="A260" s="4">
         <v>45853</v>
       </c>
@@ -3344,7 +3344,7 @@
         <v>17.38</v>
       </c>
     </row>
-    <row r="261" spans="1:3" ht="24">
+    <row r="261" spans="1:3" ht="23">
       <c r="A261" s="4">
         <v>45854</v>
       </c>
@@ -3355,7 +3355,7 @@
         <v>17.16</v>
       </c>
     </row>
-    <row r="262" spans="1:3" ht="24">
+    <row r="262" spans="1:3" ht="23">
       <c r="A262" s="4">
         <v>45855</v>
       </c>
@@ -3366,7 +3366,7 @@
         <v>16.52</v>
       </c>
     </row>
-    <row r="263" spans="1:3" ht="24">
+    <row r="263" spans="1:3" ht="23">
       <c r="A263" s="4">
         <v>45856</v>
       </c>
@@ -3377,7 +3377,7 @@
         <v>16.41</v>
       </c>
     </row>
-    <row r="264" spans="1:3" ht="24">
+    <row r="264" spans="1:3" ht="23">
       <c r="A264" s="4">
         <v>45859</v>
       </c>
@@ -3388,7 +3388,7 @@
         <v>16.649999999999999</v>
       </c>
     </row>
-    <row r="265" spans="1:3" ht="24">
+    <row r="265" spans="1:3" ht="23">
       <c r="A265" s="4">
         <v>45860</v>
       </c>
@@ -3399,7 +3399,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="266" spans="1:3" ht="24">
+    <row r="266" spans="1:3" ht="23">
       <c r="A266" s="4">
         <v>45861</v>
       </c>
@@ -3410,7 +3410,7 @@
         <v>15.37</v>
       </c>
     </row>
-    <row r="267" spans="1:3" ht="24">
+    <row r="267" spans="1:3" ht="23">
       <c r="A267" s="4">
         <v>45862</v>
       </c>
@@ -3421,7 +3421,7 @@
         <v>15.39</v>
       </c>
     </row>
-    <row r="268" spans="1:3" ht="24">
+    <row r="268" spans="1:3" ht="23">
       <c r="A268" s="4">
         <v>45863</v>
       </c>
@@ -3432,7 +3432,7 @@
         <v>14.93</v>
       </c>
     </row>
-    <row r="269" spans="1:3" ht="24">
+    <row r="269" spans="1:3" ht="23">
       <c r="A269" s="4">
         <v>45866</v>
       </c>
@@ -3443,7 +3443,7 @@
         <v>15.03</v>
       </c>
     </row>
-    <row r="270" spans="1:3" ht="24">
+    <row r="270" spans="1:3" ht="23">
       <c r="A270" s="4">
         <v>45867</v>
       </c>
@@ -3454,7 +3454,7 @@
         <v>15.98</v>
       </c>
     </row>
-    <row r="271" spans="1:3" ht="24">
+    <row r="271" spans="1:3" ht="23">
       <c r="A271" s="4">
         <v>45868</v>
       </c>
@@ -3465,7 +3465,7 @@
         <v>15.48</v>
       </c>
     </row>
-    <row r="272" spans="1:3" ht="24">
+    <row r="272" spans="1:3" ht="23">
       <c r="A272" s="4">
         <v>45869</v>
       </c>
@@ -3476,7 +3476,7 @@
         <v>16.72</v>
       </c>
     </row>
-    <row r="273" spans="1:3" ht="24">
+    <row r="273" spans="1:3" ht="23">
       <c r="A273" s="4">
         <v>45873</v>
       </c>
@@ -3487,7 +3487,7 @@
         <v>17.52</v>
       </c>
     </row>
-    <row r="274" spans="1:3" ht="24">
+    <row r="274" spans="1:3" ht="23">
       <c r="A274" s="4">
         <v>45874</v>
       </c>
@@ -3498,7 +3498,7 @@
         <v>17.850000000000001</v>
       </c>
     </row>
-    <row r="275" spans="1:3" ht="24">
+    <row r="275" spans="1:3" ht="23">
       <c r="A275" s="4">
         <v>45875</v>
       </c>
@@ -3509,7 +3509,7 @@
         <v>16.77</v>
       </c>
     </row>
-    <row r="276" spans="1:3" ht="24">
+    <row r="276" spans="1:3" ht="23">
       <c r="A276" s="4">
         <v>45876</v>
       </c>
@@ -3520,7 +3520,7 @@
         <v>16.57</v>
       </c>
     </row>
-    <row r="277" spans="1:3" ht="24">
+    <row r="277" spans="1:3" ht="23">
       <c r="A277" s="4">
         <v>45877</v>
       </c>
@@ -3531,7 +3531,7 @@
         <v>15.15</v>
       </c>
     </row>
-    <row r="278" spans="1:3" ht="24">
+    <row r="278" spans="1:3" ht="23">
       <c r="A278" s="4">
         <v>45880</v>
       </c>
@@ -3542,7 +3542,7 @@
         <v>16.25</v>
       </c>
     </row>
-    <row r="279" spans="1:3" ht="24">
+    <row r="279" spans="1:3" ht="23">
       <c r="A279" s="4">
         <v>45881</v>
       </c>
@@ -3553,7 +3553,7 @@
         <v>14.73</v>
       </c>
     </row>
-    <row r="280" spans="1:3" ht="24">
+    <row r="280" spans="1:3" ht="23">
       <c r="A280" s="4">
         <v>45882</v>
       </c>
@@ -3564,7 +3564,7 @@
         <v>14.49</v>
       </c>
     </row>
-    <row r="281" spans="1:3" ht="24">
+    <row r="281" spans="1:3" ht="23">
       <c r="A281" s="4">
         <v>45883</v>
       </c>
@@ -3575,7 +3575,7 @@
         <v>14.83</v>
       </c>
     </row>
-    <row r="282" spans="1:3" ht="24">
+    <row r="282" spans="1:3" ht="23">
       <c r="A282" s="4">
         <v>45884</v>
       </c>
@@ -3586,7 +3586,7 @@
         <v>15.09</v>
       </c>
     </row>
-    <row r="283" spans="1:3" ht="24">
+    <row r="283" spans="1:3" ht="23">
       <c r="A283" s="4">
         <v>45887</v>
       </c>
@@ -3597,7 +3597,7 @@
         <v>14.99</v>
       </c>
     </row>
-    <row r="284" spans="1:3" ht="24">
+    <row r="284" spans="1:3" ht="23">
       <c r="A284" s="4">
         <v>45888</v>
       </c>
@@ -3608,7 +3608,7 @@
         <v>15.57</v>
       </c>
     </row>
-    <row r="285" spans="1:3" ht="24">
+    <row r="285" spans="1:3" ht="23">
       <c r="A285" s="4">
         <v>45889</v>
       </c>
@@ -3619,7 +3619,7 @@
         <v>15.69</v>
       </c>
     </row>
-    <row r="286" spans="1:3" ht="24">
+    <row r="286" spans="1:3" ht="23">
       <c r="A286" s="4">
         <v>45890</v>
       </c>
@@ -3630,7 +3630,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="287" spans="1:3" ht="24">
+    <row r="287" spans="1:3" ht="23">
       <c r="A287" s="4">
         <v>45891</v>
       </c>
@@ -3641,7 +3641,7 @@
         <v>14.22</v>
       </c>
     </row>
-    <row r="288" spans="1:3" ht="24">
+    <row r="288" spans="1:3" ht="23">
       <c r="A288" s="4">
         <v>45894</v>
       </c>
@@ -3652,7 +3652,7 @@
         <v>14.79</v>
       </c>
     </row>
-    <row r="289" spans="1:3" ht="24">
+    <row r="289" spans="1:3" ht="23">
       <c r="A289" s="4">
         <v>45895</v>
       </c>
@@ -3663,7 +3663,7 @@
         <v>14.62</v>
       </c>
     </row>
-    <row r="290" spans="1:3" ht="24">
+    <row r="290" spans="1:3" ht="23">
       <c r="A290" s="4">
         <v>45896</v>
       </c>
@@ -3674,7 +3674,7 @@
         <v>14.85</v>
       </c>
     </row>
-    <row r="291" spans="1:3" ht="24">
+    <row r="291" spans="1:3" ht="23">
       <c r="A291" s="4">
         <v>45897</v>
       </c>
@@ -3685,7 +3685,7 @@
         <v>14.43</v>
       </c>
     </row>
-    <row r="292" spans="1:3" ht="24">
+    <row r="292" spans="1:3" ht="23">
       <c r="A292" s="4">
         <v>45898</v>
       </c>
@@ -3696,7 +3696,7 @@
         <v>15.36</v>
       </c>
     </row>
-    <row r="293" spans="1:3" ht="24">
+    <row r="293" spans="1:3" ht="23">
       <c r="A293" s="4">
         <v>45901</v>
       </c>
@@ -3707,7 +3707,7 @@
         <v>16.12</v>
       </c>
     </row>
-    <row r="294" spans="1:3" ht="24">
+    <row r="294" spans="1:3" ht="23">
       <c r="A294" s="4">
         <v>45902</v>
       </c>
@@ -3718,7 +3718,7 @@
         <v>17.170000000000002</v>
       </c>
     </row>
-    <row r="295" spans="1:3" ht="24">
+    <row r="295" spans="1:3" ht="23">
       <c r="A295" s="4">
         <v>45903</v>
       </c>
@@ -3729,7 +3729,7 @@
         <v>16.350000000000001</v>
       </c>
     </row>
-    <row r="296" spans="1:3" ht="24">
+    <row r="296" spans="1:3" ht="23">
       <c r="A296" s="4">
         <v>45904</v>
       </c>
@@ -3740,7 +3740,7 @@
         <v>15.3</v>
       </c>
     </row>
-    <row r="297" spans="1:3" ht="24">
+    <row r="297" spans="1:3" ht="23">
       <c r="A297" s="4">
         <v>45905</v>
       </c>
@@ -3751,7 +3751,7 @@
         <v>15.18</v>
       </c>
     </row>
-    <row r="298" spans="1:3" ht="24">
+    <row r="298" spans="1:3" ht="23">
       <c r="A298" s="4">
         <v>45908</v>
       </c>
@@ -3762,7 +3762,7 @@
         <v>15.11</v>
       </c>
     </row>
-    <row r="299" spans="1:3" ht="24">
+    <row r="299" spans="1:3" ht="23">
       <c r="A299" s="4">
         <v>45909</v>
       </c>
@@ -3773,7 +3773,7 @@
         <v>15.04</v>
       </c>
     </row>
-    <row r="300" spans="1:3" ht="24">
+    <row r="300" spans="1:3" ht="23">
       <c r="A300" s="4">
         <v>45910</v>
       </c>
@@ -3784,7 +3784,7 @@
         <v>15.35</v>
       </c>
     </row>
-    <row r="301" spans="1:3" ht="24">
+    <row r="301" spans="1:3" ht="23">
       <c r="A301" s="4">
         <v>45911</v>
       </c>
@@ -3795,7 +3795,7 @@
         <v>14.71</v>
       </c>
     </row>
-    <row r="302" spans="1:3" ht="24">
+    <row r="302" spans="1:3" ht="23">
       <c r="A302" s="4">
         <v>45912</v>
       </c>
@@ -3806,7 +3806,7 @@
         <v>14.76</v>
       </c>
     </row>
-    <row r="303" spans="1:3" ht="24">
+    <row r="303" spans="1:3" ht="23">
       <c r="A303" s="4">
         <v>45915</v>
       </c>
@@ -3817,7 +3817,7 @@
         <v>15.69</v>
       </c>
     </row>
-    <row r="304" spans="1:3" ht="24">
+    <row r="304" spans="1:3" ht="23">
       <c r="A304" s="4">
         <v>45916</v>
       </c>
@@ -3828,7 +3828,7 @@
         <v>16.36</v>
       </c>
     </row>
-    <row r="305" spans="1:3" ht="24">
+    <row r="305" spans="1:3" ht="23">
       <c r="A305" s="4">
         <v>45917</v>
       </c>
@@ -3839,7 +3839,7 @@
         <v>15.72</v>
       </c>
     </row>
-    <row r="306" spans="1:3" ht="24">
+    <row r="306" spans="1:3" ht="23">
       <c r="A306" s="4">
         <v>45918</v>
       </c>
@@ -3850,7 +3850,7 @@
         <v>15.7</v>
       </c>
     </row>
-    <row r="307" spans="1:3" ht="24">
+    <row r="307" spans="1:3" ht="23">
       <c r="A307" s="4">
         <v>45919</v>
       </c>
@@ -3861,7 +3861,7 @@
         <v>15.45</v>
       </c>
     </row>
-    <row r="308" spans="1:3" ht="24">
+    <row r="308" spans="1:3" ht="23">
       <c r="A308" s="4">
         <v>45922</v>
       </c>
@@ -3872,7 +3872,7 @@
         <v>16.100000000000001</v>
       </c>
     </row>
-    <row r="309" spans="1:3" ht="24">
+    <row r="309" spans="1:3" ht="23">
       <c r="A309" s="4">
         <v>45923</v>
       </c>
@@ -3883,7 +3883,7 @@
         <v>16.64</v>
       </c>
     </row>
-    <row r="310" spans="1:3" ht="24">
+    <row r="310" spans="1:3" ht="23">
       <c r="A310" s="4">
         <v>45924</v>
       </c>
@@ -3894,7 +3894,7 @@
         <v>16.18</v>
       </c>
     </row>
-    <row r="311" spans="1:3" ht="24">
+    <row r="311" spans="1:3" ht="23">
       <c r="A311" s="4">
         <v>45925</v>
       </c>
@@ -3905,7 +3905,7 @@
         <v>16.739999999999998</v>
       </c>
     </row>
-    <row r="312" spans="1:3" ht="24">
+    <row r="312" spans="1:3" ht="23">
       <c r="A312" s="4">
         <v>45926</v>
       </c>
@@ -3916,7 +3916,7 @@
         <v>15.29</v>
       </c>
     </row>
-    <row r="313" spans="1:3" ht="24">
+    <row r="313" spans="1:3" ht="23">
       <c r="A313" s="4">
         <v>45929</v>
       </c>
@@ -3927,7 +3927,7 @@
         <v>16.12</v>
       </c>
     </row>
-    <row r="314" spans="1:3" ht="24">
+    <row r="314" spans="1:3" ht="23">
       <c r="A314" s="4">
         <v>45930</v>
       </c>
@@ -3938,7 +3938,7 @@
         <v>16.28</v>
       </c>
     </row>
-    <row r="315" spans="1:3" ht="24">
+    <row r="315" spans="1:3" ht="23">
       <c r="A315" s="4">
         <v>45931</v>
       </c>
@@ -3949,7 +3949,7 @@
         <v>16.29</v>
       </c>
     </row>
-    <row r="316" spans="1:3" ht="24">
+    <row r="316" spans="1:3" ht="23">
       <c r="A316" s="4">
         <v>45932</v>
       </c>
@@ -3960,7 +3960,7 @@
         <v>16.63</v>
       </c>
     </row>
-    <row r="317" spans="1:3" ht="24">
+    <row r="317" spans="1:3" ht="23">
       <c r="A317" s="4">
         <v>45933</v>
       </c>
@@ -3971,7 +3971,7 @@
         <v>16.649999999999999</v>
       </c>
     </row>
-    <row r="318" spans="1:3" ht="24">
+    <row r="318" spans="1:3" ht="23">
       <c r="A318" s="4">
         <v>45936</v>
       </c>
@@ -3982,7 +3982,7 @@
         <v>16.37</v>
       </c>
     </row>
-    <row r="319" spans="1:3" ht="24">
+    <row r="319" spans="1:3" ht="23">
       <c r="A319" s="4">
         <v>45937</v>
       </c>
@@ -3993,7 +3993,7 @@
         <v>17.239999999999998</v>
       </c>
     </row>
-    <row r="320" spans="1:3" ht="24">
+    <row r="320" spans="1:3" ht="23">
       <c r="A320" s="4">
         <v>45938</v>
       </c>
@@ -4004,7 +4004,7 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="321" spans="1:3" ht="24">
+    <row r="321" spans="1:3" ht="23">
       <c r="A321" s="4">
         <v>45939</v>
       </c>
@@ -4015,7 +4015,7 @@
         <v>16.43</v>
       </c>
     </row>
-    <row r="322" spans="1:3" ht="24">
+    <row r="322" spans="1:3" ht="23">
       <c r="A322" s="4">
         <v>45940</v>
       </c>
@@ -4026,7 +4026,7 @@
         <v>21.66</v>
       </c>
     </row>
-    <row r="323" spans="1:3" ht="24">
+    <row r="323" spans="1:3" ht="23">
       <c r="A323" s="4">
         <v>45943</v>
       </c>
@@ -4037,7 +4037,7 @@
         <v>19.03</v>
       </c>
     </row>
-    <row r="324" spans="1:3" ht="24">
+    <row r="324" spans="1:3" ht="23">
       <c r="A324" s="4">
         <v>45944</v>
       </c>
@@ -4048,7 +4048,7 @@
         <v>20.81</v>
       </c>
     </row>
-    <row r="325" spans="1:3" ht="24">
+    <row r="325" spans="1:3" ht="23">
       <c r="A325" s="4">
         <v>45945</v>
       </c>
@@ -4059,7 +4059,7 @@
         <v>20.64</v>
       </c>
     </row>
-    <row r="326" spans="1:3" ht="24">
+    <row r="326" spans="1:3" ht="23">
       <c r="A326" s="4">
         <v>45946</v>
       </c>
@@ -4070,7 +4070,7 @@
         <v>25.31</v>
       </c>
     </row>
-    <row r="327" spans="1:3" ht="24">
+    <row r="327" spans="1:3" ht="23">
       <c r="A327" s="4">
         <v>45947</v>
       </c>
@@ -4081,7 +4081,7 @@
         <v>20.78</v>
       </c>
     </row>
-    <row r="328" spans="1:3" ht="24">
+    <row r="328" spans="1:3" ht="23">
       <c r="A328" s="4">
         <v>45950</v>
       </c>
@@ -4092,7 +4092,7 @@
         <v>18.23</v>
       </c>
     </row>
-    <row r="329" spans="1:3" ht="24">
+    <row r="329" spans="1:3" ht="23">
       <c r="A329" s="4">
         <v>45951</v>
       </c>
@@ -4103,7 +4103,7 @@
         <v>17.87</v>
       </c>
     </row>
-    <row r="330" spans="1:3" ht="24">
+    <row r="330" spans="1:3" ht="23">
       <c r="A330" s="4">
         <v>45952</v>
       </c>
@@ -4114,7 +4114,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="331" spans="1:3" ht="24">
+    <row r="331" spans="1:3" ht="23">
       <c r="A331" s="4">
         <v>45953</v>
       </c>
@@ -4125,7 +4125,7 @@
         <v>17.3</v>
       </c>
     </row>
-    <row r="332" spans="1:3" ht="24">
+    <row r="332" spans="1:3" ht="23">
       <c r="A332" s="4">
         <v>45954</v>
       </c>
@@ -4136,7 +4136,7 @@
         <v>16.37</v>
       </c>
     </row>
-    <row r="333" spans="1:3" ht="24">
+    <row r="333" spans="1:3" ht="23">
       <c r="A333" s="4">
         <v>45957</v>
       </c>
@@ -4147,7 +4147,7 @@
         <v>15.79</v>
       </c>
     </row>
-    <row r="334" spans="1:3" ht="24">
+    <row r="334" spans="1:3" ht="23">
       <c r="A334" s="4">
         <v>45958</v>
       </c>
@@ -4158,7 +4158,7 @@
         <v>16.420000000000002</v>
       </c>
     </row>
-    <row r="335" spans="1:3" ht="24">
+    <row r="335" spans="1:3" ht="23">
       <c r="A335" s="4">
         <v>45959</v>
       </c>
@@ -4169,7 +4169,7 @@
         <v>16.920000000000002</v>
       </c>
     </row>
-    <row r="336" spans="1:3" ht="24">
+    <row r="336" spans="1:3" ht="23">
       <c r="A336" s="4">
         <v>45960</v>
       </c>
@@ -4180,7 +4180,7 @@
         <v>16.91</v>
       </c>
     </row>
-    <row r="337" spans="1:3" ht="24">
+    <row r="337" spans="1:3" ht="23">
       <c r="A337" s="4">
         <v>45961</v>
       </c>
@@ -4191,7 +4191,7 @@
         <v>17.440000000000001</v>
       </c>
     </row>
-    <row r="338" spans="1:3" ht="24">
+    <row r="338" spans="1:3" ht="23">
       <c r="A338" s="4">
         <v>45964</v>
       </c>
@@ -4202,7 +4202,7 @@
         <v>17.170000000000002</v>
       </c>
     </row>
-    <row r="339" spans="1:3" ht="24">
+    <row r="339" spans="1:3" ht="23">
       <c r="A339" s="4">
         <v>45965</v>
       </c>
@@ -4213,7 +4213,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="340" spans="1:3" ht="24">
+    <row r="340" spans="1:3" ht="23">
       <c r="A340" s="4">
         <v>45966</v>
       </c>
@@ -4224,7 +4224,7 @@
         <v>18.010000000000002</v>
       </c>
     </row>
-    <row r="341" spans="1:3" ht="24">
+    <row r="341" spans="1:3" ht="23">
       <c r="A341" s="4">
         <v>45967</v>
       </c>
@@ -4235,7 +4235,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="342" spans="1:3" ht="24">
+    <row r="342" spans="1:3" ht="23">
       <c r="A342" s="4">
         <v>45968</v>
       </c>
@@ -4246,7 +4246,7 @@
         <v>19.079999999999998</v>
       </c>
     </row>
-    <row r="343" spans="1:3" ht="24">
+    <row r="343" spans="1:3" ht="23">
       <c r="A343" s="4">
         <v>45971</v>
       </c>
@@ -4257,7 +4257,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="344" spans="1:3" ht="24">
+    <row r="344" spans="1:3" ht="23">
       <c r="A344" s="4">
         <v>45972</v>
       </c>
@@ -4268,7 +4268,7 @@
         <v>17.28</v>
       </c>
     </row>
-    <row r="345" spans="1:3" ht="24">
+    <row r="345" spans="1:3" ht="23">
       <c r="A345" s="4">
         <v>45973</v>
       </c>
@@ -4279,7 +4279,7 @@
         <v>17.510000000000002</v>
       </c>
     </row>
-    <row r="346" spans="1:3" ht="24">
+    <row r="346" spans="1:3" ht="23">
       <c r="A346" s="4">
         <v>45974</v>
       </c>
@@ -4290,7 +4290,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="347" spans="1:3" ht="24">
+    <row r="347" spans="1:3" ht="23">
       <c r="A347" s="4">
         <v>45975</v>
       </c>
@@ -4301,7 +4301,7 @@
         <v>19.829999999999998</v>
       </c>
     </row>
-    <row r="348" spans="1:3" ht="24">
+    <row r="348" spans="1:3" ht="23">
       <c r="A348" s="4">
         <v>45978</v>
       </c>
@@ -4312,7 +4312,7 @@
         <v>22.38</v>
       </c>
     </row>
-    <row r="349" spans="1:3" ht="24">
+    <row r="349" spans="1:3" ht="23">
       <c r="A349" s="4">
         <v>45979</v>
       </c>
@@ -4323,7 +4323,7 @@
         <v>24.69</v>
       </c>
     </row>
-    <row r="350" spans="1:3" ht="24">
+    <row r="350" spans="1:3" ht="23">
       <c r="A350" s="4">
         <v>45980</v>
       </c>
@@ -4334,7 +4334,7 @@
         <v>23.66</v>
       </c>
     </row>
-    <row r="351" spans="1:3" ht="24">
+    <row r="351" spans="1:3" ht="23">
       <c r="A351" s="4">
         <v>45981</v>
       </c>
@@ -4345,7 +4345,7 @@
         <v>26.42</v>
       </c>
     </row>
-    <row r="352" spans="1:3" ht="24">
+    <row r="352" spans="1:3" ht="23">
       <c r="A352" s="4">
         <v>45982</v>
       </c>
@@ -4356,7 +4356,7 @@
         <v>23.43</v>
       </c>
     </row>
-    <row r="353" spans="1:3" ht="24">
+    <row r="353" spans="1:3" ht="23">
       <c r="A353" s="4">
         <v>45985</v>
       </c>
@@ -4367,7 +4367,7 @@
         <v>20.52</v>
       </c>
     </row>
-    <row r="354" spans="1:3" ht="24">
+    <row r="354" spans="1:3" ht="23">
       <c r="A354" s="4">
         <v>45986</v>
       </c>
@@ -4378,7 +4378,7 @@
         <v>18.559999999999999</v>
       </c>
     </row>
-    <row r="355" spans="1:3" ht="24">
+    <row r="355" spans="1:3" ht="23">
       <c r="A355" s="4">
         <v>45987</v>
       </c>
@@ -4389,7 +4389,7 @@
         <v>17.190000000000001</v>
       </c>
     </row>
-    <row r="356" spans="1:3" ht="24">
+    <row r="356" spans="1:3" ht="23">
       <c r="A356" s="4">
         <v>45988</v>
       </c>
@@ -4400,7 +4400,7 @@
         <v>17.21</v>
       </c>
     </row>
-    <row r="357" spans="1:3" ht="24">
+    <row r="357" spans="1:3" ht="23">
       <c r="A357" s="4">
         <v>45989</v>
       </c>
@@ -4411,7 +4411,7 @@
         <v>16.350000000000001</v>
       </c>
     </row>
-    <row r="358" spans="1:3" ht="24">
+    <row r="358" spans="1:3" ht="23">
       <c r="A358" s="4">
         <v>45992</v>
       </c>
@@ -4422,7 +4422,7 @@
         <v>17.239999999999998</v>
       </c>
     </row>
-    <row r="359" spans="1:3" ht="24">
+    <row r="359" spans="1:3" ht="23">
       <c r="A359" s="4">
         <v>45993</v>
       </c>
@@ -4433,7 +4433,7 @@
         <v>16.59</v>
       </c>
     </row>
-    <row r="360" spans="1:3" ht="24">
+    <row r="360" spans="1:3" ht="23">
       <c r="A360" s="4">
         <v>45994</v>
       </c>
@@ -4444,7 +4444,7 @@
         <v>16.079999999999998</v>
       </c>
     </row>
-    <row r="361" spans="1:3" ht="24">
+    <row r="361" spans="1:3" ht="23">
       <c r="A361" s="4">
         <v>45995</v>
       </c>
@@ -4455,7 +4455,7 @@
         <v>15.78</v>
       </c>
     </row>
-    <row r="362" spans="1:3" ht="24">
+    <row r="362" spans="1:3" ht="23">
       <c r="A362" s="4">
         <v>45996</v>
       </c>
@@ -4466,7 +4466,7 @@
         <v>15.41</v>
       </c>
     </row>
-    <row r="363" spans="1:3" ht="24">
+    <row r="363" spans="1:3" ht="23">
       <c r="A363" s="4">
         <v>45999</v>
       </c>
@@ -4477,7 +4477,7 @@
         <v>16.66</v>
       </c>
     </row>
-    <row r="364" spans="1:3" ht="24">
+    <row r="364" spans="1:3" ht="23">
       <c r="A364" s="4">
         <v>46000</v>
       </c>
@@ -4488,7 +4488,7 @@
         <v>16.93</v>
       </c>
     </row>
-    <row r="365" spans="1:3" ht="24">
+    <row r="365" spans="1:3" ht="23">
       <c r="A365" s="4">
         <v>46001</v>
       </c>
@@ -4499,7 +4499,7 @@
         <v>15.77</v>
       </c>
     </row>
-    <row r="366" spans="1:3" ht="24">
+    <row r="366" spans="1:3" ht="23">
       <c r="A366" s="4">
         <v>46002</v>
       </c>
@@ -4510,7 +4510,7 @@
         <v>14.85</v>
       </c>
     </row>
-    <row r="367" spans="1:3" ht="24">
+    <row r="367" spans="1:3" ht="23">
       <c r="A367" s="4">
         <v>46003</v>
       </c>
@@ -4521,7 +4521,7 @@
         <v>15.74</v>
       </c>
     </row>
-    <row r="368" spans="1:3" ht="24">
+    <row r="368" spans="1:3" ht="23">
       <c r="A368" s="4">
         <v>46006</v>
       </c>
@@ -4532,7 +4532,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="369" spans="1:3" ht="24">
+    <row r="369" spans="1:3" ht="23">
       <c r="A369" s="4">
         <v>46007</v>
       </c>
@@ -4543,7 +4543,7 @@
         <v>16.48</v>
       </c>
     </row>
-    <row r="370" spans="1:3" ht="24">
+    <row r="370" spans="1:3" ht="23">
       <c r="A370" s="4">
         <v>46008</v>
       </c>
@@ -4554,7 +4554,7 @@
         <v>17.62</v>
       </c>
     </row>
-    <row r="371" spans="1:3" ht="24">
+    <row r="371" spans="1:3" ht="23">
       <c r="A371" s="4">
         <v>46009</v>
       </c>
@@ -4565,7 +4565,7 @@
         <v>16.87</v>
       </c>
     </row>
-    <row r="372" spans="1:3" ht="24">
+    <row r="372" spans="1:3" ht="23">
       <c r="A372" s="4">
         <v>46010</v>
       </c>
@@ -4576,7 +4576,7 @@
         <v>14.91</v>
       </c>
     </row>
-    <row r="373" spans="1:3" ht="24">
+    <row r="373" spans="1:3" ht="23">
       <c r="A373" s="4">
         <v>46013</v>
       </c>
@@ -4587,7 +4587,7 @@
         <v>14.08</v>
       </c>
     </row>
-    <row r="374" spans="1:3" ht="24">
+    <row r="374" spans="1:3" ht="23">
       <c r="A374" s="4">
         <v>46014</v>
       </c>
@@ -4598,7 +4598,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="375" spans="1:3" ht="24">
+    <row r="375" spans="1:3" ht="23">
       <c r="A375" s="4">
         <v>46015</v>
       </c>
@@ -4609,7 +4609,7 @@
         <v>13.47</v>
       </c>
     </row>
-    <row r="376" spans="1:3" ht="24">
+    <row r="376" spans="1:3" ht="23">
       <c r="A376" s="4">
         <v>46017</v>
       </c>
@@ -4620,7 +4620,7 @@
         <v>13.6</v>
       </c>
     </row>
-    <row r="377" spans="1:3" ht="24">
+    <row r="377" spans="1:3" ht="23">
       <c r="A377" s="4">
         <v>46020</v>
       </c>
@@ -4631,7 +4631,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="378" spans="1:3" ht="24">
+    <row r="378" spans="1:3" ht="23">
       <c r="A378" s="4">
         <v>46021</v>
       </c>
@@ -4642,7 +4642,7 @@
         <v>14.33</v>
       </c>
     </row>
-    <row r="379" spans="1:3" ht="24">
+    <row r="379" spans="1:3" ht="23">
       <c r="A379" s="4">
         <v>46022</v>
       </c>
@@ -4653,7 +4653,7 @@
         <v>14.95</v>
       </c>
     </row>
-    <row r="380" spans="1:3" ht="24">
+    <row r="380" spans="1:3" ht="23">
       <c r="A380" s="4">
         <v>46024</v>
       </c>
@@ -4664,7 +4664,7 @@
         <v>14.51</v>
       </c>
     </row>
-    <row r="381" spans="1:3" ht="24">
+    <row r="381" spans="1:3" ht="23">
       <c r="A381" s="4">
         <v>46027</v>
       </c>
@@ -4675,7 +4675,7 @@
         <v>14.9</v>
       </c>
     </row>
-    <row r="382" spans="1:3" ht="24">
+    <row r="382" spans="1:3" ht="23">
       <c r="A382" s="4">
         <v>46028</v>
       </c>
@@ -4686,7 +4686,7 @@
         <v>14.75</v>
       </c>
     </row>
-    <row r="383" spans="1:3" ht="24">
+    <row r="383" spans="1:3" ht="23">
       <c r="A383" s="4">
         <v>46029</v>
       </c>
@@ -4697,7 +4697,7 @@
         <v>15.38</v>
       </c>
     </row>
-    <row r="384" spans="1:3" ht="24">
+    <row r="384" spans="1:3" ht="23">
       <c r="A384" s="4">
         <v>46030</v>
       </c>
@@ -4708,7 +4708,7 @@
         <v>15.45</v>
       </c>
     </row>
-    <row r="385" spans="1:3" ht="24">
+    <row r="385" spans="1:3" ht="23">
       <c r="A385" s="4">
         <v>46031</v>
       </c>
@@ -4719,7 +4719,7 @@
         <v>14.49</v>
       </c>
     </row>
-    <row r="386" spans="1:3" ht="24">
+    <row r="386" spans="1:3" ht="23">
       <c r="A386" s="4">
         <v>46034</v>
       </c>
@@ -4730,7 +4730,7 @@
         <v>15.12</v>
       </c>
     </row>
-    <row r="387" spans="1:3" ht="24">
+    <row r="387" spans="1:3" ht="23">
       <c r="A387" s="4">
         <v>46035</v>
       </c>
@@ -4741,7 +4741,7 @@
         <v>15.98</v>
       </c>
     </row>
-    <row r="388" spans="1:3" ht="24">
+    <row r="388" spans="1:3" ht="23">
       <c r="A388" s="4">
         <v>46036</v>
       </c>
@@ -4752,7 +4752,7 @@
         <v>16.75</v>
       </c>
     </row>
-    <row r="389" spans="1:3" ht="24">
+    <row r="389" spans="1:3" ht="23">
       <c r="A389" s="4">
         <v>46037</v>
       </c>
@@ -4763,7 +4763,7 @@
         <v>15.84</v>
       </c>
     </row>
-    <row r="390" spans="1:3" ht="24">
+    <row r="390" spans="1:3" ht="23">
       <c r="A390" s="4">
         <v>46038</v>
       </c>
@@ -4774,7 +4774,7 @@
         <v>15.86</v>
       </c>
     </row>
-    <row r="391" spans="1:3" ht="24">
+    <row r="391" spans="1:3" ht="23">
       <c r="A391" s="4">
         <v>46041</v>
       </c>
@@ -4785,7 +4785,7 @@
         <v>18.84</v>
       </c>
     </row>
-    <row r="392" spans="1:3" ht="24">
+    <row r="392" spans="1:3" ht="23">
       <c r="A392" s="4">
         <v>46042</v>
       </c>
@@ -4796,7 +4796,7 @@
         <v>20.09</v>
       </c>
     </row>
-    <row r="393" spans="1:3" ht="24">
+    <row r="393" spans="1:3" ht="23">
       <c r="A393" s="4">
         <v>46043</v>
       </c>
@@ -4807,7 +4807,7 @@
         <v>16.899999999999999</v>
       </c>
     </row>
-    <row r="394" spans="1:3" ht="24">
+    <row r="394" spans="1:3" ht="23">
       <c r="A394" s="4">
         <v>46044</v>
       </c>
@@ -4818,7 +4818,7 @@
         <v>15.64</v>
       </c>
     </row>
-    <row r="395" spans="1:3" ht="24">
+    <row r="395" spans="1:3" ht="23">
       <c r="A395" s="4">
         <v>46045</v>
       </c>
@@ -4829,7 +4829,7 @@
         <v>16.09</v>
       </c>
     </row>
-    <row r="396" spans="1:3" ht="24">
+    <row r="396" spans="1:3" ht="23">
       <c r="A396" s="4">
         <v>46048</v>
       </c>
@@ -4840,7 +4840,7 @@
         <v>16.149999999999999</v>
       </c>
     </row>
-    <row r="397" spans="1:3" ht="24">
+    <row r="397" spans="1:3" ht="23">
       <c r="A397" s="4">
         <v>46049</v>
       </c>
@@ -4851,7 +4851,7 @@
         <v>16.350000000000001</v>
       </c>
     </row>
-    <row r="398" spans="1:3" ht="24">
+    <row r="398" spans="1:3" ht="23">
       <c r="A398" s="4">
         <v>46050</v>
       </c>
@@ -4862,7 +4862,7 @@
         <v>16.350000000000001</v>
       </c>
     </row>
-    <row r="399" spans="1:3" ht="24">
+    <row r="399" spans="1:3" ht="23">
       <c r="A399" s="4">
         <v>46051</v>
       </c>
@@ -4873,7 +4873,7 @@
         <v>16.88</v>
       </c>
     </row>
-    <row r="400" spans="1:3" ht="24">
+    <row r="400" spans="1:3" ht="23">
       <c r="A400" s="4">
         <v>46052</v>
       </c>
@@ -4884,7 +4884,7 @@
         <v>17.440000000000001</v>
       </c>
     </row>
-    <row r="401" spans="1:3" ht="24">
+    <row r="401" spans="1:3" ht="23">
       <c r="A401" s="4">
         <v>46055</v>
       </c>
@@ -4895,7 +4895,7 @@
         <v>16.34</v>
       </c>
     </row>
-    <row r="402" spans="1:3" ht="24">
+    <row r="402" spans="1:3" ht="23">
       <c r="A402" s="4">
         <v>46056</v>
       </c>
@@ -4906,7 +4906,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="403" spans="1:3" ht="24">
+    <row r="403" spans="1:3" ht="23">
       <c r="A403" s="4">
         <v>46057</v>
       </c>
@@ -4917,7 +4917,7 @@
         <v>18.64</v>
       </c>
     </row>
-    <row r="404" spans="1:3" ht="24">
+    <row r="404" spans="1:3" ht="23">
       <c r="A404" s="4">
         <v>46058</v>
       </c>
@@ -4928,7 +4928,7 @@
         <v>21.77</v>
       </c>
     </row>
-    <row r="405" spans="1:3" ht="24">
+    <row r="405" spans="1:3" ht="23">
       <c r="A405" s="4">
         <v>46059</v>
       </c>
@@ -4939,7 +4939,7 @@
         <v>17.66</v>
       </c>
     </row>
-    <row r="406" spans="1:3" ht="24">
+    <row r="406" spans="1:3" ht="23">
       <c r="A406" s="4">
         <v>46062</v>
       </c>
@@ -4950,7 +4950,7 @@
         <v>17.36</v>
       </c>
     </row>
-    <row r="407" spans="1:3" ht="24">
+    <row r="407" spans="1:3" ht="23">
       <c r="A407" s="4">
         <v>46063</v>
       </c>
@@ -4961,7 +4961,7 @@
         <v>17.79</v>
       </c>
     </row>
-    <row r="408" spans="1:3" ht="24">
+    <row r="408" spans="1:3" ht="23">
       <c r="A408" s="4">
         <v>46064</v>
       </c>
@@ -4972,7 +4972,7 @@
         <v>17.649999999999999</v>
       </c>
     </row>
-    <row r="409" spans="1:3" ht="24">
+    <row r="409" spans="1:3" ht="23">
       <c r="A409" s="4">
         <v>46065</v>
       </c>
@@ -4983,7 +4983,7 @@
         <v>20.82</v>
       </c>
     </row>
-    <row r="410" spans="1:3" ht="24">
+    <row r="410" spans="1:3" ht="23">
       <c r="A410" s="4">
         <v>46066</v>
       </c>
@@ -4994,7 +4994,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="411" spans="1:3" ht="24">
+    <row r="411" spans="1:3" ht="23">
       <c r="A411" s="4">
         <v>46069</v>
       </c>
@@ -5005,7 +5005,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="412" spans="1:3" ht="24">
+    <row r="412" spans="1:3" ht="23">
       <c r="A412" s="4">
         <v>46070</v>
       </c>
@@ -5016,7 +5016,7 @@
         <v>20.29</v>
       </c>
     </row>
-    <row r="413" spans="1:3" ht="24">
+    <row r="413" spans="1:3" ht="23">
       <c r="A413" s="4">
         <v>46071</v>
       </c>
@@ -5027,7 +5027,7 @@
         <v>19.62</v>
       </c>
     </row>
-    <row r="414" spans="1:3" ht="24">
+    <row r="414" spans="1:3" ht="23">
       <c r="A414" s="4">
         <v>46072</v>
       </c>
@@ -5038,7 +5038,7 @@
         <v>20.23</v>
       </c>
     </row>
-    <row r="415" spans="1:3" ht="24">
+    <row r="415" spans="1:3" ht="23">
       <c r="A415" s="4">
         <v>46073</v>
       </c>
@@ -5049,7 +5049,7 @@
         <v>19.09</v>
       </c>
     </row>
-    <row r="416" spans="1:3" ht="24">
+    <row r="416" spans="1:3" ht="23">
       <c r="A416" s="4">
         <v>46076</v>
       </c>
@@ -5060,7 +5060,7 @@
         <v>21.01</v>
       </c>
     </row>
-    <row r="417" spans="1:3" ht="24">
+    <row r="417" spans="1:3" ht="23">
       <c r="A417" s="4">
         <v>46077</v>
       </c>
@@ -5071,7 +5071,7 @@
         <v>19.55</v>
       </c>
     </row>
-    <row r="418" spans="1:3" ht="24">
+    <row r="418" spans="1:3" ht="23">
       <c r="A418" s="4">
         <v>46078</v>
       </c>
@@ -5082,7 +5082,7 @@
         <v>18.02</v>
       </c>
     </row>
-    <row r="419" spans="1:3" ht="24">
+    <row r="419" spans="1:3" ht="23">
       <c r="A419" s="4">
         <v>46079</v>
       </c>
@@ -5093,7 +5093,7 @@
         <v>18.63</v>
       </c>
     </row>
-    <row r="420" spans="1:3" ht="24">
+    <row r="420" spans="1:3" ht="23">
       <c r="A420" s="4">
         <v>46080</v>
       </c>
@@ -5131,7 +5131,7 @@
         <v>46085</v>
       </c>
       <c r="B423" s="5">
-        <v>58.266471003626428</v>
+        <v>60.968774201158048</v>
       </c>
       <c r="C423" s="6">
         <v>21.15</v>
@@ -5142,7 +5142,7 @@
         <v>46086</v>
       </c>
       <c r="B424" s="5">
-        <v>59.186971398995546</v>
+        <v>61.88927459652718</v>
       </c>
       <c r="C424" s="6">
         <v>23.75</v>
@@ -5153,53 +5153,53 @@
         <v>46087</v>
       </c>
       <c r="B425" s="5">
-        <v>62.484811680261231</v>
+        <v>65.187114877792851</v>
       </c>
       <c r="C425" s="6">
         <v>29.49</v>
       </c>
     </row>
-    <row r="426" spans="1:3" ht="24">
+    <row r="426" spans="1:3" ht="23">
       <c r="A426" s="4"/>
       <c r="B426" s="5"/>
       <c r="C426" s="6"/>
     </row>
-    <row r="427" spans="1:3" ht="24">
+    <row r="427" spans="1:3" ht="23">
       <c r="A427" s="4"/>
       <c r="B427" s="5"/>
       <c r="C427" s="6"/>
     </row>
-    <row r="428" spans="1:3" ht="24">
+    <row r="428" spans="1:3" ht="23">
       <c r="A428" s="4"/>
       <c r="B428" s="5"/>
       <c r="C428" s="6"/>
     </row>
-    <row r="429" spans="1:3" ht="24">
+    <row r="429" spans="1:3" ht="23">
       <c r="A429" s="4"/>
       <c r="B429" s="5"/>
       <c r="C429" s="6"/>
     </row>
-    <row r="430" spans="1:3" ht="24">
+    <row r="430" spans="1:3" ht="23">
       <c r="A430" s="4"/>
       <c r="B430" s="5"/>
       <c r="C430" s="6"/>
     </row>
-    <row r="431" spans="1:3" ht="24">
+    <row r="431" spans="1:3" ht="23">
       <c r="A431" s="4"/>
       <c r="B431" s="5"/>
       <c r="C431" s="6"/>
     </row>
-    <row r="432" spans="1:3" ht="24">
+    <row r="432" spans="1:3" ht="23">
       <c r="A432" s="4"/>
       <c r="B432" s="5"/>
       <c r="C432" s="6"/>
     </row>
-    <row r="433" spans="1:3" ht="24">
+    <row r="433" spans="1:3" ht="23">
       <c r="A433" s="4"/>
       <c r="B433" s="5"/>
       <c r="C433" s="6"/>
     </row>
-    <row r="434" spans="1:3" ht="24">
+    <row r="434" spans="1:3" ht="23">
       <c r="A434" s="4"/>
       <c r="B434" s="5"/>
       <c r="C434" s="6"/>
@@ -9938,7 +9938,7 @@
         <v>46085</v>
       </c>
       <c r="B423" s="5">
-        <v>58.266471003626428</v>
+        <v>60.968774201158048</v>
       </c>
       <c r="C423" s="5">
         <v>41.422940610175367</v>
@@ -9949,7 +9949,7 @@
         <v>46086</v>
       </c>
       <c r="B424" s="5">
-        <v>59.186971398995546</v>
+        <v>61.88927459652718</v>
       </c>
       <c r="C424" s="5">
         <v>40.82853645329314</v>
@@ -9960,7 +9960,7 @@
         <v>46087</v>
       </c>
       <c r="B425" s="5">
-        <v>62.484811680261231</v>
+        <v>65.187114877792851</v>
       </c>
       <c r="C425" s="5">
         <v>39.480846860545853</v>

--- a/files/data.xlsx
+++ b/files/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ferrars/Desktop/monitoraggio/files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ferrara/Desktop/salvatore non toccare/monitoraggio/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F23E53F6-4583-B345-AC8E-66460B776864}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEACB507-3F53-5447-9810-34F609424FB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1600" yWindow="600" windowWidth="21780" windowHeight="16320" activeTab="1" xr2:uid="{F1546C66-1100-0F4C-AEC5-783BC2578DB8}"/>
+    <workbookView xWindow="18220" yWindow="600" windowWidth="21780" windowHeight="16320" xr2:uid="{F1546C66-1100-0F4C-AEC5-783BC2578DB8}"/>
   </bookViews>
   <sheets>
     <sheet name="vix" sheetId="2" r:id="rId1"/>
@@ -143,7 +143,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -5160,29 +5160,59 @@
       </c>
     </row>
     <row r="426" spans="1:3" ht="23">
-      <c r="A426" s="4"/>
-      <c r="B426" s="5"/>
-      <c r="C426" s="6"/>
+      <c r="A426" s="4">
+        <v>46090</v>
+      </c>
+      <c r="B426" s="5">
+        <v>63.903480246886431</v>
+      </c>
+      <c r="C426" s="6">
+        <v>25.5</v>
+      </c>
     </row>
     <row r="427" spans="1:3" ht="23">
-      <c r="A427" s="4"/>
-      <c r="B427" s="5"/>
-      <c r="C427" s="6"/>
+      <c r="A427" s="4">
+        <v>46091</v>
+      </c>
+      <c r="B427" s="5">
+        <v>64.940785813661137</v>
+      </c>
+      <c r="C427" s="6">
+        <v>24.93</v>
+      </c>
     </row>
     <row r="428" spans="1:3" ht="23">
-      <c r="A428" s="4"/>
-      <c r="B428" s="5"/>
-      <c r="C428" s="6"/>
+      <c r="A428" s="4">
+        <v>46092</v>
+      </c>
+      <c r="B428" s="5">
+        <v>64.246598656123538</v>
+      </c>
+      <c r="C428" s="6">
+        <v>24.23</v>
+      </c>
     </row>
     <row r="429" spans="1:3" ht="23">
-      <c r="A429" s="4"/>
-      <c r="B429" s="5"/>
-      <c r="C429" s="6"/>
+      <c r="A429" s="4">
+        <v>46093</v>
+      </c>
+      <c r="B429" s="5">
+        <v>65.141997953156562</v>
+      </c>
+      <c r="C429" s="6">
+        <v>27.29</v>
+      </c>
     </row>
     <row r="430" spans="1:3" ht="23">
-      <c r="A430" s="4"/>
-      <c r="B430" s="5"/>
-      <c r="C430" s="6"/>
+      <c r="A430" s="4">
+        <v>46094</v>
+      </c>
+      <c r="B430" s="5">
+        <v>64.960031154799111</v>
+      </c>
+      <c r="C430" s="6">
+        <v>27.19</v>
+      </c>
     </row>
     <row r="431" spans="1:3" ht="23">
       <c r="A431" s="4"/>
@@ -9967,29 +9997,59 @@
       </c>
     </row>
     <row r="426" spans="1:3" ht="40" customHeight="1">
-      <c r="A426" s="4"/>
-      <c r="B426" s="5"/>
-      <c r="C426" s="5"/>
+      <c r="A426" s="4">
+        <v>46090</v>
+      </c>
+      <c r="B426" s="5">
+        <v>63.903480246886431</v>
+      </c>
+      <c r="C426" s="5">
+        <v>40.326197877465241</v>
+      </c>
     </row>
     <row r="427" spans="1:3" ht="40" customHeight="1">
-      <c r="A427" s="4"/>
-      <c r="B427" s="5"/>
-      <c r="C427" s="5"/>
+      <c r="A427" s="4">
+        <v>46091</v>
+      </c>
+      <c r="B427" s="5">
+        <v>64.940785813661137</v>
+      </c>
+      <c r="C427" s="5">
+        <v>40.12381707503517</v>
+      </c>
     </row>
     <row r="428" spans="1:3" ht="40" customHeight="1">
-      <c r="A428" s="4"/>
-      <c r="B428" s="5"/>
-      <c r="C428" s="5"/>
+      <c r="A428" s="4">
+        <v>46092</v>
+      </c>
+      <c r="B428" s="5">
+        <v>64.246598656123538</v>
+      </c>
+      <c r="C428" s="5">
+        <v>40.009567150137762</v>
+      </c>
     </row>
     <row r="429" spans="1:3" ht="40" customHeight="1">
-      <c r="A429" s="4"/>
-      <c r="B429" s="5"/>
-      <c r="C429" s="5"/>
+      <c r="A429" s="4">
+        <v>46093</v>
+      </c>
+      <c r="B429" s="5">
+        <v>65.141997953156562</v>
+      </c>
+      <c r="C429" s="5">
+        <v>38.493598458312967</v>
+      </c>
     </row>
     <row r="430" spans="1:3" ht="40" customHeight="1">
-      <c r="A430" s="4"/>
-      <c r="B430" s="5"/>
-      <c r="C430" s="5"/>
+      <c r="A430" s="4">
+        <v>46094</v>
+      </c>
+      <c r="B430" s="5">
+        <v>64.960031154799111</v>
+      </c>
+      <c r="C430" s="5">
+        <v>37.87016909093488</v>
+      </c>
     </row>
     <row r="431" spans="1:3" ht="40" customHeight="1">
       <c r="A431" s="4"/>

--- a/files/data.xlsx
+++ b/files/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ferrara/Desktop/salvatore non toccare/monitoraggio/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEACB507-3F53-5447-9810-34F609424FB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F65B963-7E87-4E46-B9FF-376A6ADD27DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18220" yWindow="600" windowWidth="21780" windowHeight="16320" xr2:uid="{F1546C66-1100-0F4C-AEC5-783BC2578DB8}"/>
+    <workbookView xWindow="1400" yWindow="660" windowWidth="10440" windowHeight="16320" xr2:uid="{F1546C66-1100-0F4C-AEC5-783BC2578DB8}"/>
   </bookViews>
   <sheets>
     <sheet name="vix" sheetId="2" r:id="rId1"/>
@@ -5215,29 +5215,59 @@
       </c>
     </row>
     <row r="431" spans="1:3" ht="23">
-      <c r="A431" s="4"/>
-      <c r="B431" s="5"/>
-      <c r="C431" s="6"/>
+      <c r="A431" s="4">
+        <v>46097</v>
+      </c>
+      <c r="B431" s="5">
+        <v>63.532838454538833</v>
+      </c>
+      <c r="C431" s="6">
+        <v>23.51</v>
+      </c>
     </row>
     <row r="432" spans="1:3" ht="23">
-      <c r="A432" s="4"/>
-      <c r="B432" s="5"/>
-      <c r="C432" s="6"/>
+      <c r="A432" s="4">
+        <v>46098</v>
+      </c>
+      <c r="B432" s="5">
+        <v>62.418265938097164</v>
+      </c>
+      <c r="C432" s="6">
+        <v>22.37</v>
+      </c>
     </row>
     <row r="433" spans="1:3" ht="23">
-      <c r="A433" s="4"/>
-      <c r="B433" s="5"/>
-      <c r="C433" s="6"/>
+      <c r="A433" s="4">
+        <v>46099</v>
+      </c>
+      <c r="B433" s="5">
+        <v>63.005336386550972</v>
+      </c>
+      <c r="C433" s="6">
+        <v>25.09</v>
+      </c>
     </row>
     <row r="434" spans="1:3" ht="23">
-      <c r="A434" s="4"/>
-      <c r="B434" s="5"/>
-      <c r="C434" s="6"/>
+      <c r="A434" s="4">
+        <v>46100</v>
+      </c>
+      <c r="B434" s="5">
+        <v>62.389875287868399</v>
+      </c>
+      <c r="C434" s="6">
+        <v>24.06</v>
+      </c>
     </row>
     <row r="435" spans="1:3" ht="23">
-      <c r="A435" s="4"/>
-      <c r="B435" s="5"/>
-      <c r="C435" s="6"/>
+      <c r="A435" s="4">
+        <v>46101</v>
+      </c>
+      <c r="B435" s="5">
+        <v>64.32872838323037</v>
+      </c>
+      <c r="C435" s="6">
+        <v>26.78</v>
+      </c>
     </row>
     <row r="436" spans="1:3" ht="23">
       <c r="A436" s="4"/>
@@ -10052,29 +10082,59 @@
       </c>
     </row>
     <row r="431" spans="1:3" ht="40" customHeight="1">
-      <c r="A431" s="4"/>
-      <c r="B431" s="5"/>
-      <c r="C431" s="5"/>
+      <c r="A431" s="4">
+        <v>46097</v>
+      </c>
+      <c r="B431" s="5">
+        <v>63.532838454538833</v>
+      </c>
+      <c r="C431" s="5">
+        <v>38.90085490119116</v>
+      </c>
     </row>
     <row r="432" spans="1:3" ht="40" customHeight="1">
-      <c r="A432" s="4"/>
-      <c r="B432" s="5"/>
-      <c r="C432" s="5"/>
+      <c r="A432" s="4">
+        <v>46098</v>
+      </c>
+      <c r="B432" s="5">
+        <v>62.418265938097164</v>
+      </c>
+      <c r="C432" s="5">
+        <v>39.917334939803148</v>
+      </c>
     </row>
     <row r="433" spans="1:3" ht="40" customHeight="1">
-      <c r="A433" s="4"/>
-      <c r="B433" s="5"/>
-      <c r="C433" s="5"/>
+      <c r="A433" s="4">
+        <v>46099</v>
+      </c>
+      <c r="B433" s="5">
+        <v>63.005336386550972</v>
+      </c>
+      <c r="C433" s="5">
+        <v>38.486110345688246</v>
+      </c>
     </row>
     <row r="434" spans="1:3" ht="40" customHeight="1">
-      <c r="A434" s="4"/>
-      <c r="B434" s="5"/>
-      <c r="C434" s="5"/>
+      <c r="A434" s="4">
+        <v>46100</v>
+      </c>
+      <c r="B434" s="5">
+        <v>62.389875287868399</v>
+      </c>
+      <c r="C434" s="5">
+        <v>38.231180313344844</v>
+      </c>
     </row>
     <row r="435" spans="1:3" ht="40" customHeight="1">
-      <c r="A435" s="4"/>
-      <c r="B435" s="5"/>
-      <c r="C435" s="5"/>
+      <c r="A435" s="4">
+        <v>46101</v>
+      </c>
+      <c r="B435" s="5">
+        <v>64.32872838323037</v>
+      </c>
+      <c r="C435" s="5">
+        <v>36.703047089274911</v>
+      </c>
     </row>
     <row r="436" spans="1:3" ht="40" customHeight="1">
       <c r="A436" s="4"/>

--- a/files/data.xlsx
+++ b/files/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ferrara/Desktop/salvatore non toccare/monitoraggio/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F65B963-7E87-4E46-B9FF-376A6ADD27DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8FC7A01-95AB-DE4F-B1F7-FFD24EB00C61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1400" yWindow="660" windowWidth="10440" windowHeight="16320" xr2:uid="{F1546C66-1100-0F4C-AEC5-783BC2578DB8}"/>
+    <workbookView xWindow="1400" yWindow="660" windowWidth="10440" windowHeight="16320" activeTab="1" xr2:uid="{F1546C66-1100-0F4C-AEC5-783BC2578DB8}"/>
   </bookViews>
   <sheets>
     <sheet name="vix" sheetId="2" r:id="rId1"/>
@@ -5270,29 +5270,59 @@
       </c>
     </row>
     <row r="436" spans="1:3" ht="23">
-      <c r="A436" s="4"/>
-      <c r="B436" s="5"/>
-      <c r="C436" s="6"/>
+      <c r="A436" s="4">
+        <v>46104</v>
+      </c>
+      <c r="B436" s="5">
+        <v>63.64762841659838</v>
+      </c>
+      <c r="C436" s="6">
+        <v>26.15</v>
+      </c>
     </row>
     <row r="437" spans="1:3" ht="23">
-      <c r="A437" s="4"/>
-      <c r="B437" s="5"/>
-      <c r="C437" s="6"/>
+      <c r="A437" s="4">
+        <v>46105</v>
+      </c>
+      <c r="B437" s="5">
+        <v>64.281027626084537</v>
+      </c>
+      <c r="C437" s="6">
+        <v>26.95</v>
+      </c>
     </row>
     <row r="438" spans="1:3" ht="23">
-      <c r="A438" s="4"/>
-      <c r="B438" s="5"/>
-      <c r="C438" s="6"/>
+      <c r="A438" s="4">
+        <v>46106</v>
+      </c>
+      <c r="B438" s="5">
+        <v>63.630012808869466</v>
+      </c>
+      <c r="C438" s="6">
+        <v>25.33</v>
+      </c>
     </row>
     <row r="439" spans="1:3" ht="23">
-      <c r="A439" s="4"/>
-      <c r="B439" s="5"/>
-      <c r="C439" s="6"/>
+      <c r="A439" s="4">
+        <v>46107</v>
+      </c>
+      <c r="B439" s="5">
+        <v>65.152082824090172</v>
+      </c>
+      <c r="C439" s="6">
+        <v>27.44</v>
+      </c>
     </row>
     <row r="440" spans="1:3" ht="23">
-      <c r="A440" s="4"/>
-      <c r="B440" s="5"/>
-      <c r="C440" s="6"/>
+      <c r="A440" s="4">
+        <v>46108</v>
+      </c>
+      <c r="B440" s="5">
+        <v>65.429541497350939</v>
+      </c>
+      <c r="C440" s="6">
+        <v>31.05</v>
+      </c>
     </row>
     <row r="441" spans="1:3" ht="23">
       <c r="A441" s="4"/>
@@ -10137,29 +10167,59 @@
       </c>
     </row>
     <row r="436" spans="1:3" ht="40" customHeight="1">
-      <c r="A436" s="4"/>
-      <c r="B436" s="5"/>
-      <c r="C436" s="5"/>
+      <c r="A436" s="4">
+        <v>46104</v>
+      </c>
+      <c r="B436" s="5">
+        <v>63.64762841659838</v>
+      </c>
+      <c r="C436" s="5">
+        <v>37.85133066803192</v>
+      </c>
     </row>
     <row r="437" spans="1:3" ht="40" customHeight="1">
-      <c r="A437" s="4"/>
-      <c r="B437" s="5"/>
-      <c r="C437" s="5"/>
+      <c r="A437" s="4">
+        <v>46105</v>
+      </c>
+      <c r="B437" s="5">
+        <v>64.281027626084537</v>
+      </c>
+      <c r="C437" s="5">
+        <v>37.417064554974857</v>
+      </c>
     </row>
     <row r="438" spans="1:3" ht="40" customHeight="1">
-      <c r="A438" s="4"/>
-      <c r="B438" s="5"/>
-      <c r="C438" s="5"/>
+      <c r="A438" s="4">
+        <v>46106</v>
+      </c>
+      <c r="B438" s="5">
+        <v>63.630012808869466</v>
+      </c>
+      <c r="C438" s="5">
+        <v>37.941722749814701</v>
+      </c>
     </row>
     <row r="439" spans="1:3" ht="40" customHeight="1">
-      <c r="A439" s="4"/>
-      <c r="B439" s="5"/>
-      <c r="C439" s="5"/>
+      <c r="A439" s="4">
+        <v>46107</v>
+      </c>
+      <c r="B439" s="5">
+        <v>65.152082824090172</v>
+      </c>
+      <c r="C439" s="5">
+        <v>36.18332717899078</v>
+      </c>
     </row>
     <row r="440" spans="1:3" ht="40" customHeight="1">
-      <c r="A440" s="4"/>
-      <c r="B440" s="5"/>
-      <c r="C440" s="5"/>
+      <c r="A440" s="4">
+        <v>46108</v>
+      </c>
+      <c r="B440" s="5">
+        <v>65.429541497350939</v>
+      </c>
+      <c r="C440" s="5">
+        <v>34.440254196327501</v>
+      </c>
     </row>
     <row r="441" spans="1:3" ht="40" customHeight="1">
       <c r="A441" s="4"/>

--- a/files/data.xlsx
+++ b/files/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ferrara/Desktop/salvatore non toccare/monitoraggio/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8FC7A01-95AB-DE4F-B1F7-FFD24EB00C61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC843EF0-83EC-2446-A198-8D2FDF34193D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1400" yWindow="660" windowWidth="10440" windowHeight="16320" activeTab="1" xr2:uid="{F1546C66-1100-0F4C-AEC5-783BC2578DB8}"/>
+    <workbookView xWindow="1400" yWindow="660" windowWidth="10440" windowHeight="16320" xr2:uid="{F1546C66-1100-0F4C-AEC5-783BC2578DB8}"/>
   </bookViews>
   <sheets>
     <sheet name="vix" sheetId="2" r:id="rId1"/>
@@ -5325,29 +5325,59 @@
       </c>
     </row>
     <row r="441" spans="1:3" ht="23">
-      <c r="A441" s="4"/>
-      <c r="B441" s="5"/>
-      <c r="C441" s="6"/>
+      <c r="A441" s="4">
+        <v>46111</v>
+      </c>
+      <c r="B441" s="5">
+        <v>62.776220720286204</v>
+      </c>
+      <c r="C441" s="6">
+        <v>30.61</v>
+      </c>
     </row>
     <row r="442" spans="1:3" ht="23">
-      <c r="A442" s="4"/>
-      <c r="B442" s="5"/>
-      <c r="C442" s="6"/>
+      <c r="A442" s="4">
+        <v>46112</v>
+      </c>
+      <c r="B442" s="5">
+        <v>60.341793673313028</v>
+      </c>
+      <c r="C442" s="6">
+        <v>25.25</v>
+      </c>
     </row>
     <row r="443" spans="1:3" ht="23">
-      <c r="A443" s="4"/>
-      <c r="B443" s="5"/>
-      <c r="C443" s="6"/>
+      <c r="A443" s="4">
+        <v>46113</v>
+      </c>
+      <c r="B443" s="5">
+        <v>60.07704600135483</v>
+      </c>
+      <c r="C443" s="6">
+        <v>24.54</v>
+      </c>
     </row>
     <row r="444" spans="1:3" ht="23">
-      <c r="A444" s="4"/>
-      <c r="B444" s="5"/>
-      <c r="C444" s="6"/>
+      <c r="A444" s="4">
+        <v>46114</v>
+      </c>
+      <c r="B444" s="5">
+        <v>59.836193280231534</v>
+      </c>
+      <c r="C444" s="6">
+        <v>23.87</v>
+      </c>
     </row>
     <row r="445" spans="1:3" ht="23">
-      <c r="A445" s="4"/>
-      <c r="B445" s="5"/>
-      <c r="C445" s="6"/>
+      <c r="A445" s="4">
+        <v>46115</v>
+      </c>
+      <c r="B445" s="5">
+        <v>59.836193280231534</v>
+      </c>
+      <c r="C445" s="6">
+        <v>23.87</v>
+      </c>
     </row>
     <row r="446" spans="1:3" ht="23">
       <c r="A446" s="4"/>
@@ -10222,29 +10252,59 @@
       </c>
     </row>
     <row r="441" spans="1:3" ht="40" customHeight="1">
-      <c r="A441" s="4"/>
-      <c r="B441" s="5"/>
-      <c r="C441" s="5"/>
+      <c r="A441" s="4">
+        <v>46111</v>
+      </c>
+      <c r="B441" s="5">
+        <v>62.776220720286204</v>
+      </c>
+      <c r="C441" s="5">
+        <v>34.06526840479026</v>
+      </c>
     </row>
     <row r="442" spans="1:3" ht="40" customHeight="1">
-      <c r="A442" s="4"/>
-      <c r="B442" s="5"/>
-      <c r="C442" s="5"/>
+      <c r="A442" s="4">
+        <v>46112</v>
+      </c>
+      <c r="B442" s="5">
+        <v>60.341793673313028</v>
+      </c>
+      <c r="C442" s="5">
+        <v>36.882029981359644</v>
+      </c>
     </row>
     <row r="443" spans="1:3" ht="40" customHeight="1">
-      <c r="A443" s="4"/>
-      <c r="B443" s="5"/>
-      <c r="C443" s="5"/>
+      <c r="A443" s="4">
+        <v>46113</v>
+      </c>
+      <c r="B443" s="5">
+        <v>60.07704600135483</v>
+      </c>
+      <c r="C443" s="5">
+        <v>37.594775160397845</v>
+      </c>
     </row>
     <row r="444" spans="1:3" ht="40" customHeight="1">
-      <c r="A444" s="4"/>
-      <c r="B444" s="5"/>
-      <c r="C444" s="5"/>
+      <c r="A444" s="4">
+        <v>46114</v>
+      </c>
+      <c r="B444" s="5">
+        <v>59.836193280231534</v>
+      </c>
+      <c r="C444" s="5">
+        <v>37.662750993831025</v>
+      </c>
     </row>
     <row r="445" spans="1:3" ht="40" customHeight="1">
-      <c r="A445" s="4"/>
-      <c r="B445" s="5"/>
-      <c r="C445" s="5"/>
+      <c r="A445" s="4">
+        <v>46115</v>
+      </c>
+      <c r="B445" s="5">
+        <v>59.836193280231534</v>
+      </c>
+      <c r="C445" s="5">
+        <v>37.662750993831025</v>
+      </c>
     </row>
     <row r="446" spans="1:3" ht="40" customHeight="1">
       <c r="A446" s="4"/>

--- a/files/data.xlsx
+++ b/files/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ferrara/Desktop/salvatore non toccare/monitoraggio/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC843EF0-83EC-2446-A198-8D2FDF34193D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A46308D4-BA61-0748-BC75-B215FE755D87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1400" yWindow="660" windowWidth="10440" windowHeight="16320" xr2:uid="{F1546C66-1100-0F4C-AEC5-783BC2578DB8}"/>
+    <workbookView xWindow="1400" yWindow="660" windowWidth="10440" windowHeight="16320" activeTab="1" xr2:uid="{F1546C66-1100-0F4C-AEC5-783BC2578DB8}"/>
   </bookViews>
   <sheets>
     <sheet name="vix" sheetId="2" r:id="rId1"/>
@@ -475,7 +475,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2D1AE83-71FF-D646-9DA6-2F2BACDC27FF}">
-  <dimension ref="A1:C448"/>
+  <dimension ref="A1:C504"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="15.1640625" style="1" bestFit="1" customWidth="1"/>
@@ -5380,19 +5380,329 @@
       </c>
     </row>
     <row r="446" spans="1:3" ht="23">
-      <c r="A446" s="4"/>
-      <c r="B446" s="5"/>
-      <c r="C446" s="6"/>
+      <c r="A446" s="4">
+        <v>46118</v>
+      </c>
+      <c r="B446" s="5">
+        <v>59.836193280231534</v>
+      </c>
+      <c r="C446" s="6">
+        <v>24.17</v>
+      </c>
     </row>
     <row r="447" spans="1:3" ht="23">
-      <c r="A447" s="4"/>
-      <c r="B447" s="5"/>
-      <c r="C447" s="6"/>
+      <c r="A447" s="4">
+        <v>46119</v>
+      </c>
+      <c r="B447" s="5">
+        <v>60.238926110148824</v>
+      </c>
+      <c r="C447" s="6">
+        <v>25.78</v>
+      </c>
     </row>
     <row r="448" spans="1:3" ht="23">
-      <c r="A448" s="4"/>
-      <c r="B448" s="5"/>
-      <c r="C448" s="6"/>
+      <c r="A448" s="4">
+        <v>46120</v>
+      </c>
+      <c r="B448" s="5">
+        <v>59.513435713431441</v>
+      </c>
+      <c r="C448" s="6">
+        <v>21.04</v>
+      </c>
+    </row>
+    <row r="449" spans="1:3" ht="23">
+      <c r="A449" s="4">
+        <v>46121</v>
+      </c>
+      <c r="B449" s="5">
+        <v>59.420669422640039</v>
+      </c>
+      <c r="C449" s="6">
+        <v>19.489999999999998</v>
+      </c>
+    </row>
+    <row r="450" spans="1:3" ht="23">
+      <c r="A450" s="4">
+        <v>46122</v>
+      </c>
+      <c r="B450" s="5">
+        <v>59.245281505835813</v>
+      </c>
+      <c r="C450" s="6">
+        <v>19.23</v>
+      </c>
+    </row>
+    <row r="451" spans="1:3" ht="23">
+      <c r="A451" s="4"/>
+      <c r="B451" s="5"/>
+      <c r="C451" s="6"/>
+    </row>
+    <row r="452" spans="1:3" ht="23">
+      <c r="A452" s="4"/>
+      <c r="B452" s="5"/>
+      <c r="C452" s="6"/>
+    </row>
+    <row r="453" spans="1:3" ht="23">
+      <c r="A453" s="4"/>
+      <c r="B453" s="5"/>
+      <c r="C453" s="6"/>
+    </row>
+    <row r="454" spans="1:3" ht="23">
+      <c r="A454" s="4"/>
+      <c r="B454" s="5"/>
+      <c r="C454" s="6"/>
+    </row>
+    <row r="455" spans="1:3" ht="23">
+      <c r="A455" s="4"/>
+      <c r="B455" s="5"/>
+      <c r="C455" s="6"/>
+    </row>
+    <row r="456" spans="1:3" ht="23">
+      <c r="A456" s="4"/>
+      <c r="B456" s="5"/>
+      <c r="C456" s="6"/>
+    </row>
+    <row r="457" spans="1:3" ht="23">
+      <c r="A457" s="4"/>
+      <c r="B457" s="5"/>
+      <c r="C457" s="6"/>
+    </row>
+    <row r="458" spans="1:3" ht="23">
+      <c r="A458" s="4"/>
+      <c r="B458" s="5"/>
+      <c r="C458" s="6"/>
+    </row>
+    <row r="459" spans="1:3" ht="23">
+      <c r="A459" s="4"/>
+      <c r="B459" s="5"/>
+      <c r="C459" s="6"/>
+    </row>
+    <row r="460" spans="1:3" ht="23">
+      <c r="A460" s="4"/>
+      <c r="B460" s="5"/>
+      <c r="C460" s="6"/>
+    </row>
+    <row r="461" spans="1:3" ht="23">
+      <c r="A461" s="4"/>
+      <c r="B461" s="5"/>
+      <c r="C461" s="6"/>
+    </row>
+    <row r="462" spans="1:3" ht="23">
+      <c r="A462" s="4"/>
+      <c r="B462" s="5"/>
+      <c r="C462" s="6"/>
+    </row>
+    <row r="463" spans="1:3" ht="23">
+      <c r="A463" s="4"/>
+      <c r="B463" s="5"/>
+      <c r="C463" s="6"/>
+    </row>
+    <row r="464" spans="1:3" ht="23">
+      <c r="A464" s="4"/>
+      <c r="B464" s="5"/>
+      <c r="C464" s="6"/>
+    </row>
+    <row r="465" spans="1:3" ht="23">
+      <c r="A465" s="4"/>
+      <c r="B465" s="5"/>
+      <c r="C465" s="6"/>
+    </row>
+    <row r="466" spans="1:3" ht="23">
+      <c r="A466" s="4"/>
+      <c r="B466" s="5"/>
+      <c r="C466" s="6"/>
+    </row>
+    <row r="467" spans="1:3" ht="23">
+      <c r="A467" s="4"/>
+      <c r="B467" s="5"/>
+      <c r="C467" s="6"/>
+    </row>
+    <row r="468" spans="1:3" ht="23">
+      <c r="A468" s="4"/>
+      <c r="B468" s="5"/>
+      <c r="C468" s="6"/>
+    </row>
+    <row r="469" spans="1:3" ht="23">
+      <c r="A469" s="4"/>
+      <c r="B469" s="5"/>
+      <c r="C469" s="6"/>
+    </row>
+    <row r="470" spans="1:3" ht="23">
+      <c r="A470" s="4"/>
+      <c r="B470" s="5"/>
+      <c r="C470" s="6"/>
+    </row>
+    <row r="471" spans="1:3" ht="23">
+      <c r="A471" s="4"/>
+      <c r="B471" s="5"/>
+      <c r="C471" s="6"/>
+    </row>
+    <row r="472" spans="1:3" ht="23">
+      <c r="A472" s="4"/>
+      <c r="B472" s="5"/>
+      <c r="C472" s="6"/>
+    </row>
+    <row r="473" spans="1:3" ht="23">
+      <c r="A473" s="4"/>
+      <c r="B473" s="5"/>
+      <c r="C473" s="6"/>
+    </row>
+    <row r="474" spans="1:3" ht="23">
+      <c r="A474" s="4"/>
+      <c r="B474" s="5"/>
+      <c r="C474" s="6"/>
+    </row>
+    <row r="475" spans="1:3" ht="23">
+      <c r="A475" s="4"/>
+      <c r="B475" s="5"/>
+      <c r="C475" s="6"/>
+    </row>
+    <row r="476" spans="1:3" ht="23">
+      <c r="A476" s="4"/>
+      <c r="B476" s="5"/>
+      <c r="C476" s="6"/>
+    </row>
+    <row r="477" spans="1:3" ht="23">
+      <c r="A477" s="4"/>
+      <c r="B477" s="5"/>
+      <c r="C477" s="6"/>
+    </row>
+    <row r="478" spans="1:3" ht="23">
+      <c r="A478" s="4"/>
+      <c r="B478" s="5"/>
+      <c r="C478" s="6"/>
+    </row>
+    <row r="479" spans="1:3" ht="23">
+      <c r="A479" s="4"/>
+      <c r="B479" s="5"/>
+      <c r="C479" s="6"/>
+    </row>
+    <row r="480" spans="1:3" ht="23">
+      <c r="A480" s="4"/>
+      <c r="B480" s="5"/>
+      <c r="C480" s="6"/>
+    </row>
+    <row r="481" spans="1:3" ht="23">
+      <c r="A481" s="4"/>
+      <c r="B481" s="5"/>
+      <c r="C481" s="6"/>
+    </row>
+    <row r="482" spans="1:3" ht="23">
+      <c r="A482" s="4"/>
+      <c r="B482" s="5"/>
+      <c r="C482" s="6"/>
+    </row>
+    <row r="483" spans="1:3" ht="23">
+      <c r="A483" s="4"/>
+      <c r="B483" s="5"/>
+      <c r="C483" s="6"/>
+    </row>
+    <row r="484" spans="1:3" ht="23">
+      <c r="A484" s="4"/>
+      <c r="B484" s="5"/>
+      <c r="C484" s="6"/>
+    </row>
+    <row r="485" spans="1:3" ht="23">
+      <c r="A485" s="4"/>
+      <c r="B485" s="5"/>
+      <c r="C485" s="6"/>
+    </row>
+    <row r="486" spans="1:3" ht="23">
+      <c r="A486" s="4"/>
+      <c r="B486" s="5"/>
+      <c r="C486" s="6"/>
+    </row>
+    <row r="487" spans="1:3" ht="23">
+      <c r="A487" s="4"/>
+      <c r="B487" s="5"/>
+      <c r="C487" s="6"/>
+    </row>
+    <row r="488" spans="1:3" ht="23">
+      <c r="A488" s="4"/>
+      <c r="B488" s="5"/>
+      <c r="C488" s="6"/>
+    </row>
+    <row r="489" spans="1:3" ht="23">
+      <c r="A489" s="4"/>
+      <c r="B489" s="5"/>
+      <c r="C489" s="6"/>
+    </row>
+    <row r="490" spans="1:3" ht="23">
+      <c r="A490" s="4"/>
+      <c r="B490" s="5"/>
+      <c r="C490" s="6"/>
+    </row>
+    <row r="491" spans="1:3" ht="23">
+      <c r="A491" s="4"/>
+      <c r="B491" s="5"/>
+      <c r="C491" s="6"/>
+    </row>
+    <row r="492" spans="1:3" ht="23">
+      <c r="A492" s="4"/>
+      <c r="B492" s="5"/>
+      <c r="C492" s="6"/>
+    </row>
+    <row r="493" spans="1:3" ht="23">
+      <c r="A493" s="4"/>
+      <c r="B493" s="5"/>
+      <c r="C493" s="6"/>
+    </row>
+    <row r="494" spans="1:3" ht="23">
+      <c r="A494" s="4"/>
+      <c r="B494" s="5"/>
+      <c r="C494" s="6"/>
+    </row>
+    <row r="495" spans="1:3" ht="23">
+      <c r="A495" s="4"/>
+      <c r="B495" s="5"/>
+      <c r="C495" s="6"/>
+    </row>
+    <row r="496" spans="1:3" ht="23">
+      <c r="A496" s="4"/>
+      <c r="B496" s="5"/>
+      <c r="C496" s="6"/>
+    </row>
+    <row r="497" spans="1:3" ht="23">
+      <c r="A497" s="4"/>
+      <c r="B497" s="5"/>
+      <c r="C497" s="6"/>
+    </row>
+    <row r="498" spans="1:3" ht="23">
+      <c r="A498" s="4"/>
+      <c r="B498" s="5"/>
+      <c r="C498" s="6"/>
+    </row>
+    <row r="499" spans="1:3" ht="23">
+      <c r="A499" s="4"/>
+      <c r="B499" s="5"/>
+      <c r="C499" s="6"/>
+    </row>
+    <row r="500" spans="1:3" ht="23">
+      <c r="A500" s="4"/>
+      <c r="B500" s="5"/>
+      <c r="C500" s="6"/>
+    </row>
+    <row r="501" spans="1:3" ht="23">
+      <c r="A501" s="4"/>
+      <c r="B501" s="5"/>
+      <c r="C501" s="6"/>
+    </row>
+    <row r="502" spans="1:3" ht="23">
+      <c r="A502" s="4"/>
+      <c r="B502" s="5"/>
+      <c r="C502" s="6"/>
+    </row>
+    <row r="503" spans="1:3" ht="23">
+      <c r="A503" s="4"/>
+      <c r="B503" s="5"/>
+      <c r="C503" s="6"/>
+    </row>
+    <row r="504" spans="1:3" ht="23">
+      <c r="A504" s="4"/>
+      <c r="B504" s="5"/>
+      <c r="C504" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5401,7 +5711,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7E960FF-368A-3E44-924C-861BEDCA6476}">
-  <dimension ref="A1:D448"/>
+  <dimension ref="A1:D1567"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="40" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="15.1640625" style="1" bestFit="1" customWidth="1"/>
@@ -10307,19 +10617,5644 @@
       </c>
     </row>
     <row r="446" spans="1:3" ht="40" customHeight="1">
-      <c r="A446" s="4"/>
-      <c r="B446" s="5"/>
-      <c r="C446" s="5"/>
+      <c r="A446" s="4">
+        <v>46118</v>
+      </c>
+      <c r="B446" s="5">
+        <v>59.836193280231534</v>
+      </c>
+      <c r="C446" s="5">
+        <v>38.095953788343465</v>
+      </c>
     </row>
     <row r="447" spans="1:3" ht="40" customHeight="1">
-      <c r="A447" s="4"/>
-      <c r="B447" s="5"/>
-      <c r="C447" s="5"/>
+      <c r="A447" s="4">
+        <v>46119</v>
+      </c>
+      <c r="B447" s="5">
+        <v>60.238926110148824</v>
+      </c>
+      <c r="C447" s="5">
+        <v>38.182369604057278</v>
+      </c>
     </row>
     <row r="448" spans="1:3" ht="40" customHeight="1">
-      <c r="A448" s="4"/>
-      <c r="B448" s="5"/>
-      <c r="C448" s="5"/>
+      <c r="A448" s="4">
+        <v>46120</v>
+      </c>
+      <c r="B448" s="5">
+        <v>59.513435713431441</v>
+      </c>
+      <c r="C448" s="5">
+        <v>40.660149269498085</v>
+      </c>
+    </row>
+    <row r="449" spans="1:3" ht="40" customHeight="1">
+      <c r="A449" s="4">
+        <v>46121</v>
+      </c>
+      <c r="B449" s="5">
+        <v>59.420669422640039</v>
+      </c>
+      <c r="C449" s="5">
+        <v>41.237340906261082</v>
+      </c>
+    </row>
+    <row r="450" spans="1:3" ht="40" customHeight="1">
+      <c r="A450" s="4">
+        <v>46122</v>
+      </c>
+      <c r="B450" s="5">
+        <v>59.245281505835813</v>
+      </c>
+      <c r="C450" s="5">
+        <v>41.120710066054791</v>
+      </c>
+    </row>
+    <row r="451" spans="1:3" ht="40" customHeight="1">
+      <c r="A451" s="4"/>
+      <c r="B451" s="5"/>
+      <c r="C451" s="5"/>
+    </row>
+    <row r="452" spans="1:3" ht="40" customHeight="1">
+      <c r="A452" s="4"/>
+      <c r="B452" s="5"/>
+      <c r="C452" s="5"/>
+    </row>
+    <row r="453" spans="1:3" ht="40" customHeight="1">
+      <c r="A453" s="4"/>
+      <c r="B453" s="5"/>
+      <c r="C453" s="5"/>
+    </row>
+    <row r="454" spans="1:3" ht="40" customHeight="1">
+      <c r="A454" s="4"/>
+      <c r="B454" s="5"/>
+      <c r="C454" s="5"/>
+    </row>
+    <row r="455" spans="1:3" ht="40" customHeight="1">
+      <c r="A455" s="4"/>
+      <c r="B455" s="5"/>
+      <c r="C455" s="5"/>
+    </row>
+    <row r="456" spans="1:3" ht="40" customHeight="1">
+      <c r="A456" s="4"/>
+      <c r="B456" s="5"/>
+      <c r="C456" s="5"/>
+    </row>
+    <row r="457" spans="1:3" ht="40" customHeight="1">
+      <c r="A457" s="4"/>
+      <c r="B457" s="5"/>
+      <c r="C457" s="5"/>
+    </row>
+    <row r="458" spans="1:3" ht="40" customHeight="1">
+      <c r="A458" s="4"/>
+      <c r="B458" s="5"/>
+      <c r="C458" s="5"/>
+    </row>
+    <row r="459" spans="1:3" ht="40" customHeight="1">
+      <c r="A459" s="4"/>
+      <c r="B459" s="5"/>
+      <c r="C459" s="5"/>
+    </row>
+    <row r="460" spans="1:3" ht="40" customHeight="1">
+      <c r="A460" s="4"/>
+      <c r="B460" s="5"/>
+      <c r="C460" s="5"/>
+    </row>
+    <row r="461" spans="1:3" ht="40" customHeight="1">
+      <c r="A461" s="4"/>
+      <c r="B461" s="5"/>
+      <c r="C461" s="5"/>
+    </row>
+    <row r="462" spans="1:3" ht="40" customHeight="1">
+      <c r="A462" s="4"/>
+      <c r="B462" s="5"/>
+      <c r="C462" s="5"/>
+    </row>
+    <row r="463" spans="1:3" ht="40" customHeight="1">
+      <c r="A463" s="4"/>
+      <c r="B463" s="5"/>
+      <c r="C463" s="5"/>
+    </row>
+    <row r="464" spans="1:3" ht="40" customHeight="1">
+      <c r="A464" s="4"/>
+      <c r="B464" s="5"/>
+      <c r="C464" s="5"/>
+    </row>
+    <row r="465" spans="1:3" ht="40" customHeight="1">
+      <c r="A465" s="4"/>
+      <c r="B465" s="5"/>
+      <c r="C465" s="5"/>
+    </row>
+    <row r="466" spans="1:3" ht="40" customHeight="1">
+      <c r="A466" s="4"/>
+      <c r="B466" s="5"/>
+      <c r="C466" s="5"/>
+    </row>
+    <row r="467" spans="1:3" ht="40" customHeight="1">
+      <c r="A467" s="4"/>
+      <c r="B467" s="5"/>
+      <c r="C467" s="5"/>
+    </row>
+    <row r="468" spans="1:3" ht="40" customHeight="1">
+      <c r="A468" s="4"/>
+      <c r="B468" s="5"/>
+      <c r="C468" s="5"/>
+    </row>
+    <row r="469" spans="1:3" ht="40" customHeight="1">
+      <c r="A469" s="4"/>
+      <c r="B469" s="5"/>
+      <c r="C469" s="5"/>
+    </row>
+    <row r="470" spans="1:3" ht="40" customHeight="1">
+      <c r="A470" s="4"/>
+      <c r="B470" s="5"/>
+      <c r="C470" s="5"/>
+    </row>
+    <row r="471" spans="1:3" ht="40" customHeight="1">
+      <c r="A471" s="4"/>
+      <c r="B471" s="5"/>
+      <c r="C471" s="5"/>
+    </row>
+    <row r="472" spans="1:3" ht="40" customHeight="1">
+      <c r="A472" s="4"/>
+      <c r="B472" s="5"/>
+      <c r="C472" s="5"/>
+    </row>
+    <row r="473" spans="1:3" ht="40" customHeight="1">
+      <c r="A473" s="4"/>
+      <c r="B473" s="5"/>
+      <c r="C473" s="5"/>
+    </row>
+    <row r="474" spans="1:3" ht="40" customHeight="1">
+      <c r="A474" s="4"/>
+      <c r="B474" s="5"/>
+      <c r="C474" s="5"/>
+    </row>
+    <row r="475" spans="1:3" ht="40" customHeight="1">
+      <c r="A475" s="4"/>
+      <c r="B475" s="5"/>
+      <c r="C475" s="5"/>
+    </row>
+    <row r="476" spans="1:3" ht="40" customHeight="1">
+      <c r="A476" s="4"/>
+      <c r="B476" s="5"/>
+      <c r="C476" s="5"/>
+    </row>
+    <row r="477" spans="1:3" ht="40" customHeight="1">
+      <c r="A477" s="4"/>
+      <c r="B477" s="5"/>
+      <c r="C477" s="5"/>
+    </row>
+    <row r="478" spans="1:3" ht="40" customHeight="1">
+      <c r="A478" s="4"/>
+      <c r="B478" s="5"/>
+      <c r="C478" s="5"/>
+    </row>
+    <row r="479" spans="1:3" ht="40" customHeight="1">
+      <c r="A479" s="4"/>
+      <c r="B479" s="5"/>
+      <c r="C479" s="5"/>
+    </row>
+    <row r="480" spans="1:3" ht="40" customHeight="1">
+      <c r="A480" s="4"/>
+      <c r="B480" s="5"/>
+      <c r="C480" s="5"/>
+    </row>
+    <row r="481" spans="1:3" ht="40" customHeight="1">
+      <c r="A481" s="4"/>
+      <c r="B481" s="5"/>
+      <c r="C481" s="5"/>
+    </row>
+    <row r="482" spans="1:3" ht="40" customHeight="1">
+      <c r="A482" s="4"/>
+      <c r="B482" s="5"/>
+      <c r="C482" s="5"/>
+    </row>
+    <row r="483" spans="1:3" ht="40" customHeight="1">
+      <c r="A483" s="4"/>
+      <c r="B483" s="5"/>
+      <c r="C483" s="5"/>
+    </row>
+    <row r="484" spans="1:3" ht="40" customHeight="1">
+      <c r="A484" s="4"/>
+      <c r="B484" s="5"/>
+      <c r="C484" s="5"/>
+    </row>
+    <row r="485" spans="1:3" ht="40" customHeight="1">
+      <c r="A485" s="4"/>
+      <c r="B485" s="5"/>
+      <c r="C485" s="5"/>
+    </row>
+    <row r="486" spans="1:3" ht="40" customHeight="1">
+      <c r="A486" s="4"/>
+      <c r="B486" s="5"/>
+      <c r="C486" s="5"/>
+    </row>
+    <row r="487" spans="1:3" ht="40" customHeight="1">
+      <c r="A487" s="4"/>
+      <c r="B487" s="5"/>
+      <c r="C487" s="5"/>
+    </row>
+    <row r="488" spans="1:3" ht="40" customHeight="1">
+      <c r="A488" s="4"/>
+      <c r="B488" s="5"/>
+      <c r="C488" s="5"/>
+    </row>
+    <row r="489" spans="1:3" ht="40" customHeight="1">
+      <c r="A489" s="4"/>
+      <c r="B489" s="5"/>
+      <c r="C489" s="5"/>
+    </row>
+    <row r="490" spans="1:3" ht="40" customHeight="1">
+      <c r="A490" s="4"/>
+      <c r="B490" s="5"/>
+      <c r="C490" s="5"/>
+    </row>
+    <row r="491" spans="1:3" ht="40" customHeight="1">
+      <c r="A491" s="4"/>
+      <c r="B491" s="5"/>
+      <c r="C491" s="5"/>
+    </row>
+    <row r="492" spans="1:3" ht="40" customHeight="1">
+      <c r="A492" s="4"/>
+      <c r="B492" s="5"/>
+      <c r="C492" s="5"/>
+    </row>
+    <row r="493" spans="1:3" ht="40" customHeight="1">
+      <c r="A493" s="4"/>
+      <c r="B493" s="5"/>
+      <c r="C493" s="5"/>
+    </row>
+    <row r="494" spans="1:3" ht="40" customHeight="1">
+      <c r="A494" s="4"/>
+      <c r="B494" s="5"/>
+      <c r="C494" s="5"/>
+    </row>
+    <row r="495" spans="1:3" ht="40" customHeight="1">
+      <c r="A495" s="4"/>
+      <c r="B495" s="5"/>
+      <c r="C495" s="5"/>
+    </row>
+    <row r="496" spans="1:3" ht="40" customHeight="1">
+      <c r="A496" s="4"/>
+      <c r="B496" s="5"/>
+      <c r="C496" s="5"/>
+    </row>
+    <row r="497" spans="1:3" ht="40" customHeight="1">
+      <c r="A497" s="4"/>
+      <c r="B497" s="5"/>
+      <c r="C497" s="5"/>
+    </row>
+    <row r="498" spans="1:3" ht="40" customHeight="1">
+      <c r="A498" s="4"/>
+      <c r="B498" s="5"/>
+      <c r="C498" s="5"/>
+    </row>
+    <row r="499" spans="1:3" ht="40" customHeight="1">
+      <c r="A499" s="4"/>
+      <c r="B499" s="5"/>
+      <c r="C499" s="5"/>
+    </row>
+    <row r="500" spans="1:3" ht="40" customHeight="1">
+      <c r="A500" s="4"/>
+      <c r="B500" s="5"/>
+      <c r="C500" s="5"/>
+    </row>
+    <row r="501" spans="1:3" ht="40" customHeight="1">
+      <c r="A501" s="4"/>
+      <c r="B501" s="5"/>
+      <c r="C501" s="5"/>
+    </row>
+    <row r="502" spans="1:3" ht="40" customHeight="1">
+      <c r="A502" s="4"/>
+      <c r="B502" s="5"/>
+      <c r="C502" s="5"/>
+    </row>
+    <row r="503" spans="1:3" ht="40" customHeight="1">
+      <c r="A503" s="4"/>
+      <c r="B503" s="5"/>
+      <c r="C503" s="5"/>
+    </row>
+    <row r="504" spans="1:3" ht="40" customHeight="1">
+      <c r="A504" s="4"/>
+      <c r="B504" s="5"/>
+      <c r="C504" s="5"/>
+    </row>
+    <row r="505" spans="1:3" ht="40" customHeight="1">
+      <c r="A505" s="4"/>
+      <c r="B505" s="5"/>
+      <c r="C505" s="5"/>
+    </row>
+    <row r="506" spans="1:3" ht="40" customHeight="1">
+      <c r="A506" s="4"/>
+      <c r="B506" s="5"/>
+      <c r="C506" s="5"/>
+    </row>
+    <row r="507" spans="1:3" ht="40" customHeight="1">
+      <c r="A507" s="4"/>
+      <c r="B507" s="5"/>
+      <c r="C507" s="5"/>
+    </row>
+    <row r="508" spans="1:3" ht="40" customHeight="1">
+      <c r="A508" s="4"/>
+      <c r="B508" s="5"/>
+      <c r="C508" s="5"/>
+    </row>
+    <row r="509" spans="1:3" ht="40" customHeight="1">
+      <c r="A509" s="4"/>
+      <c r="B509" s="5"/>
+      <c r="C509" s="5"/>
+    </row>
+    <row r="510" spans="1:3" ht="40" customHeight="1">
+      <c r="A510" s="4"/>
+      <c r="B510" s="5"/>
+      <c r="C510" s="5"/>
+    </row>
+    <row r="511" spans="1:3" ht="40" customHeight="1">
+      <c r="A511" s="4"/>
+      <c r="B511" s="5"/>
+      <c r="C511" s="5"/>
+    </row>
+    <row r="512" spans="1:3" ht="40" customHeight="1">
+      <c r="A512" s="4"/>
+      <c r="B512" s="5"/>
+      <c r="C512" s="5"/>
+    </row>
+    <row r="513" spans="1:3" ht="40" customHeight="1">
+      <c r="A513" s="4"/>
+      <c r="B513" s="5"/>
+      <c r="C513" s="5"/>
+    </row>
+    <row r="514" spans="1:3" ht="40" customHeight="1">
+      <c r="A514" s="4"/>
+      <c r="B514" s="5"/>
+      <c r="C514" s="5"/>
+    </row>
+    <row r="515" spans="1:3" ht="40" customHeight="1">
+      <c r="A515" s="4"/>
+      <c r="B515" s="5"/>
+      <c r="C515" s="5"/>
+    </row>
+    <row r="516" spans="1:3" ht="40" customHeight="1">
+      <c r="A516" s="4"/>
+      <c r="B516" s="5"/>
+      <c r="C516" s="5"/>
+    </row>
+    <row r="517" spans="1:3" ht="40" customHeight="1">
+      <c r="A517" s="4"/>
+      <c r="B517" s="5"/>
+      <c r="C517" s="5"/>
+    </row>
+    <row r="518" spans="1:3" ht="40" customHeight="1">
+      <c r="A518" s="4"/>
+      <c r="B518" s="5"/>
+      <c r="C518" s="5"/>
+    </row>
+    <row r="519" spans="1:3" ht="40" customHeight="1">
+      <c r="A519" s="4"/>
+      <c r="B519" s="5"/>
+      <c r="C519" s="5"/>
+    </row>
+    <row r="520" spans="1:3" ht="40" customHeight="1">
+      <c r="A520" s="4"/>
+      <c r="B520" s="5"/>
+      <c r="C520" s="5"/>
+    </row>
+    <row r="521" spans="1:3" ht="40" customHeight="1">
+      <c r="A521" s="4"/>
+      <c r="B521" s="5"/>
+      <c r="C521" s="5"/>
+    </row>
+    <row r="522" spans="1:3" ht="40" customHeight="1">
+      <c r="A522" s="4"/>
+      <c r="B522" s="5"/>
+      <c r="C522" s="5"/>
+    </row>
+    <row r="523" spans="1:3" ht="40" customHeight="1">
+      <c r="A523" s="4"/>
+      <c r="B523" s="5"/>
+      <c r="C523" s="5"/>
+    </row>
+    <row r="524" spans="1:3" ht="40" customHeight="1">
+      <c r="A524" s="4"/>
+      <c r="B524" s="5"/>
+      <c r="C524" s="5"/>
+    </row>
+    <row r="525" spans="1:3" ht="40" customHeight="1">
+      <c r="A525" s="4"/>
+      <c r="B525" s="5"/>
+      <c r="C525" s="5"/>
+    </row>
+    <row r="526" spans="1:3" ht="40" customHeight="1">
+      <c r="A526" s="4"/>
+      <c r="B526" s="5"/>
+      <c r="C526" s="5"/>
+    </row>
+    <row r="527" spans="1:3" ht="40" customHeight="1">
+      <c r="A527" s="4"/>
+      <c r="B527" s="5"/>
+      <c r="C527" s="5"/>
+    </row>
+    <row r="528" spans="1:3" ht="40" customHeight="1">
+      <c r="A528" s="4"/>
+      <c r="B528" s="5"/>
+      <c r="C528" s="5"/>
+    </row>
+    <row r="529" spans="1:3" ht="40" customHeight="1">
+      <c r="A529" s="4"/>
+      <c r="B529" s="5"/>
+      <c r="C529" s="5"/>
+    </row>
+    <row r="530" spans="1:3" ht="40" customHeight="1">
+      <c r="A530" s="4"/>
+      <c r="B530" s="5"/>
+      <c r="C530" s="5"/>
+    </row>
+    <row r="531" spans="1:3" ht="40" customHeight="1">
+      <c r="A531" s="4"/>
+      <c r="B531" s="5"/>
+      <c r="C531" s="5"/>
+    </row>
+    <row r="532" spans="1:3" ht="40" customHeight="1">
+      <c r="A532" s="4"/>
+      <c r="B532" s="5"/>
+      <c r="C532" s="5"/>
+    </row>
+    <row r="533" spans="1:3" ht="40" customHeight="1">
+      <c r="A533" s="4"/>
+      <c r="B533" s="5"/>
+      <c r="C533" s="5"/>
+    </row>
+    <row r="534" spans="1:3" ht="40" customHeight="1">
+      <c r="A534" s="4"/>
+      <c r="B534" s="5"/>
+      <c r="C534" s="5"/>
+    </row>
+    <row r="535" spans="1:3" ht="40" customHeight="1">
+      <c r="A535" s="4"/>
+      <c r="B535" s="5"/>
+      <c r="C535" s="5"/>
+    </row>
+    <row r="536" spans="1:3" ht="40" customHeight="1">
+      <c r="A536" s="4"/>
+      <c r="B536" s="5"/>
+      <c r="C536" s="5"/>
+    </row>
+    <row r="537" spans="1:3" ht="40" customHeight="1">
+      <c r="A537" s="4"/>
+      <c r="B537" s="5"/>
+      <c r="C537" s="5"/>
+    </row>
+    <row r="538" spans="1:3" ht="40" customHeight="1">
+      <c r="A538" s="4"/>
+      <c r="B538" s="5"/>
+      <c r="C538" s="5"/>
+    </row>
+    <row r="539" spans="1:3" ht="40" customHeight="1">
+      <c r="A539" s="4"/>
+      <c r="B539" s="5"/>
+      <c r="C539" s="5"/>
+    </row>
+    <row r="540" spans="1:3" ht="40" customHeight="1">
+      <c r="A540" s="4"/>
+      <c r="B540" s="5"/>
+      <c r="C540" s="5"/>
+    </row>
+    <row r="541" spans="1:3" ht="40" customHeight="1">
+      <c r="A541" s="4"/>
+      <c r="B541" s="5"/>
+      <c r="C541" s="5"/>
+    </row>
+    <row r="542" spans="1:3" ht="40" customHeight="1">
+      <c r="A542" s="4"/>
+      <c r="B542" s="5"/>
+      <c r="C542" s="5"/>
+    </row>
+    <row r="543" spans="1:3" ht="40" customHeight="1">
+      <c r="A543" s="4"/>
+      <c r="B543" s="5"/>
+      <c r="C543" s="5"/>
+    </row>
+    <row r="544" spans="1:3" ht="40" customHeight="1">
+      <c r="A544" s="4"/>
+      <c r="B544" s="5"/>
+      <c r="C544" s="5"/>
+    </row>
+    <row r="545" spans="1:3" ht="40" customHeight="1">
+      <c r="A545" s="4"/>
+      <c r="B545" s="5"/>
+      <c r="C545" s="5"/>
+    </row>
+    <row r="546" spans="1:3" ht="40" customHeight="1">
+      <c r="A546" s="4"/>
+      <c r="B546" s="5"/>
+      <c r="C546" s="5"/>
+    </row>
+    <row r="547" spans="1:3" ht="40" customHeight="1">
+      <c r="A547" s="4"/>
+      <c r="B547" s="5"/>
+      <c r="C547" s="5"/>
+    </row>
+    <row r="548" spans="1:3" ht="40" customHeight="1">
+      <c r="A548" s="4"/>
+      <c r="B548" s="5"/>
+      <c r="C548" s="5"/>
+    </row>
+    <row r="549" spans="1:3" ht="40" customHeight="1">
+      <c r="A549" s="4"/>
+      <c r="B549" s="5"/>
+      <c r="C549" s="5"/>
+    </row>
+    <row r="550" spans="1:3" ht="40" customHeight="1">
+      <c r="A550" s="4"/>
+      <c r="B550" s="5"/>
+      <c r="C550" s="5"/>
+    </row>
+    <row r="551" spans="1:3" ht="40" customHeight="1">
+      <c r="A551" s="4"/>
+      <c r="B551" s="5"/>
+      <c r="C551" s="5"/>
+    </row>
+    <row r="552" spans="1:3" ht="40" customHeight="1">
+      <c r="A552" s="4"/>
+      <c r="B552" s="5"/>
+      <c r="C552" s="5"/>
+    </row>
+    <row r="553" spans="1:3" ht="40" customHeight="1">
+      <c r="A553" s="4"/>
+      <c r="B553" s="5"/>
+      <c r="C553" s="5"/>
+    </row>
+    <row r="554" spans="1:3" ht="40" customHeight="1">
+      <c r="A554" s="4"/>
+      <c r="B554" s="5"/>
+      <c r="C554" s="5"/>
+    </row>
+    <row r="555" spans="1:3" ht="40" customHeight="1">
+      <c r="A555" s="4"/>
+      <c r="B555" s="5"/>
+      <c r="C555" s="5"/>
+    </row>
+    <row r="556" spans="1:3" ht="40" customHeight="1">
+      <c r="A556" s="4"/>
+      <c r="B556" s="5"/>
+      <c r="C556" s="5"/>
+    </row>
+    <row r="557" spans="1:3" ht="40" customHeight="1">
+      <c r="A557" s="4"/>
+      <c r="B557" s="5"/>
+      <c r="C557" s="5"/>
+    </row>
+    <row r="558" spans="1:3" ht="40" customHeight="1">
+      <c r="A558" s="4"/>
+      <c r="B558" s="5"/>
+      <c r="C558" s="5"/>
+    </row>
+    <row r="559" spans="1:3" ht="40" customHeight="1">
+      <c r="A559" s="4"/>
+      <c r="B559" s="5"/>
+      <c r="C559" s="5"/>
+    </row>
+    <row r="560" spans="1:3" ht="40" customHeight="1">
+      <c r="A560" s="4"/>
+      <c r="B560" s="5"/>
+      <c r="C560" s="5"/>
+    </row>
+    <row r="561" spans="1:3" ht="40" customHeight="1">
+      <c r="A561" s="4"/>
+      <c r="B561" s="5"/>
+      <c r="C561" s="5"/>
+    </row>
+    <row r="562" spans="1:3" ht="40" customHeight="1">
+      <c r="A562" s="4"/>
+      <c r="B562" s="5"/>
+      <c r="C562" s="5"/>
+    </row>
+    <row r="563" spans="1:3" ht="40" customHeight="1">
+      <c r="A563" s="4"/>
+      <c r="B563" s="5"/>
+      <c r="C563" s="5"/>
+    </row>
+    <row r="564" spans="1:3" ht="40" customHeight="1">
+      <c r="A564" s="4"/>
+      <c r="B564" s="5"/>
+      <c r="C564" s="5"/>
+    </row>
+    <row r="565" spans="1:3" ht="40" customHeight="1">
+      <c r="A565" s="4"/>
+      <c r="B565" s="5"/>
+      <c r="C565" s="5"/>
+    </row>
+    <row r="566" spans="1:3" ht="40" customHeight="1">
+      <c r="A566" s="4"/>
+      <c r="B566" s="5"/>
+      <c r="C566" s="5"/>
+    </row>
+    <row r="567" spans="1:3" ht="40" customHeight="1">
+      <c r="A567" s="4"/>
+      <c r="B567" s="5"/>
+      <c r="C567" s="5"/>
+    </row>
+    <row r="568" spans="1:3" ht="40" customHeight="1">
+      <c r="A568" s="4"/>
+      <c r="B568" s="5"/>
+      <c r="C568" s="5"/>
+    </row>
+    <row r="569" spans="1:3" ht="40" customHeight="1">
+      <c r="A569" s="4"/>
+      <c r="B569" s="5"/>
+      <c r="C569" s="5"/>
+    </row>
+    <row r="570" spans="1:3" ht="40" customHeight="1">
+      <c r="A570" s="4"/>
+      <c r="B570" s="5"/>
+      <c r="C570" s="5"/>
+    </row>
+    <row r="571" spans="1:3" ht="40" customHeight="1">
+      <c r="A571" s="4"/>
+      <c r="B571" s="5"/>
+      <c r="C571" s="5"/>
+    </row>
+    <row r="572" spans="1:3" ht="40" customHeight="1">
+      <c r="A572" s="4"/>
+      <c r="B572" s="5"/>
+      <c r="C572" s="5"/>
+    </row>
+    <row r="573" spans="1:3" ht="40" customHeight="1">
+      <c r="A573" s="4"/>
+      <c r="B573" s="5"/>
+      <c r="C573" s="5"/>
+    </row>
+    <row r="574" spans="1:3" ht="40" customHeight="1">
+      <c r="A574" s="4"/>
+      <c r="B574" s="5"/>
+      <c r="C574" s="5"/>
+    </row>
+    <row r="575" spans="1:3" ht="40" customHeight="1">
+      <c r="A575" s="4"/>
+      <c r="B575" s="5"/>
+      <c r="C575" s="5"/>
+    </row>
+    <row r="576" spans="1:3" ht="40" customHeight="1">
+      <c r="A576" s="4"/>
+      <c r="B576" s="5"/>
+      <c r="C576" s="5"/>
+    </row>
+    <row r="577" spans="1:3" ht="40" customHeight="1">
+      <c r="A577" s="4"/>
+      <c r="B577" s="5"/>
+      <c r="C577" s="5"/>
+    </row>
+    <row r="578" spans="1:3" ht="40" customHeight="1">
+      <c r="A578" s="4"/>
+      <c r="B578" s="5"/>
+      <c r="C578" s="5"/>
+    </row>
+    <row r="579" spans="1:3" ht="40" customHeight="1">
+      <c r="A579" s="4"/>
+      <c r="B579" s="5"/>
+      <c r="C579" s="5"/>
+    </row>
+    <row r="580" spans="1:3" ht="40" customHeight="1">
+      <c r="A580" s="4"/>
+      <c r="B580" s="5"/>
+      <c r="C580" s="5"/>
+    </row>
+    <row r="581" spans="1:3" ht="40" customHeight="1">
+      <c r="A581" s="4"/>
+      <c r="B581" s="5"/>
+      <c r="C581" s="5"/>
+    </row>
+    <row r="582" spans="1:3" ht="40" customHeight="1">
+      <c r="A582" s="4"/>
+      <c r="B582" s="5"/>
+      <c r="C582" s="5"/>
+    </row>
+    <row r="583" spans="1:3" ht="40" customHeight="1">
+      <c r="A583" s="4"/>
+      <c r="B583" s="5"/>
+      <c r="C583" s="5"/>
+    </row>
+    <row r="584" spans="1:3" ht="40" customHeight="1">
+      <c r="A584" s="4"/>
+      <c r="B584" s="5"/>
+      <c r="C584" s="5"/>
+    </row>
+    <row r="585" spans="1:3" ht="40" customHeight="1">
+      <c r="A585" s="4"/>
+      <c r="B585" s="5"/>
+      <c r="C585" s="5"/>
+    </row>
+    <row r="586" spans="1:3" ht="40" customHeight="1">
+      <c r="A586" s="4"/>
+      <c r="B586" s="5"/>
+      <c r="C586" s="5"/>
+    </row>
+    <row r="587" spans="1:3" ht="40" customHeight="1">
+      <c r="A587" s="4"/>
+      <c r="B587" s="5"/>
+      <c r="C587" s="5"/>
+    </row>
+    <row r="588" spans="1:3" ht="40" customHeight="1">
+      <c r="A588" s="4"/>
+      <c r="B588" s="5"/>
+      <c r="C588" s="5"/>
+    </row>
+    <row r="589" spans="1:3" ht="40" customHeight="1">
+      <c r="A589" s="4"/>
+      <c r="B589" s="5"/>
+      <c r="C589" s="5"/>
+    </row>
+    <row r="590" spans="1:3" ht="40" customHeight="1">
+      <c r="A590" s="4"/>
+      <c r="B590" s="5"/>
+      <c r="C590" s="5"/>
+    </row>
+    <row r="591" spans="1:3" ht="40" customHeight="1">
+      <c r="A591" s="4"/>
+      <c r="B591" s="5"/>
+      <c r="C591" s="5"/>
+    </row>
+    <row r="592" spans="1:3" ht="40" customHeight="1">
+      <c r="A592" s="4"/>
+      <c r="B592" s="5"/>
+      <c r="C592" s="5"/>
+    </row>
+    <row r="593" spans="1:3" ht="40" customHeight="1">
+      <c r="A593" s="4"/>
+      <c r="B593" s="5"/>
+      <c r="C593" s="5"/>
+    </row>
+    <row r="594" spans="1:3" ht="40" customHeight="1">
+      <c r="A594" s="4"/>
+      <c r="B594" s="5"/>
+      <c r="C594" s="5"/>
+    </row>
+    <row r="595" spans="1:3" ht="40" customHeight="1">
+      <c r="A595" s="4"/>
+      <c r="B595" s="5"/>
+      <c r="C595" s="5"/>
+    </row>
+    <row r="596" spans="1:3" ht="40" customHeight="1">
+      <c r="A596" s="4"/>
+      <c r="B596" s="5"/>
+      <c r="C596" s="5"/>
+    </row>
+    <row r="597" spans="1:3" ht="40" customHeight="1">
+      <c r="A597" s="4"/>
+      <c r="B597" s="5"/>
+      <c r="C597" s="5"/>
+    </row>
+    <row r="598" spans="1:3" ht="40" customHeight="1">
+      <c r="A598" s="4"/>
+      <c r="B598" s="5"/>
+      <c r="C598" s="5"/>
+    </row>
+    <row r="599" spans="1:3" ht="40" customHeight="1">
+      <c r="A599" s="4"/>
+      <c r="B599" s="5"/>
+      <c r="C599" s="5"/>
+    </row>
+    <row r="600" spans="1:3" ht="40" customHeight="1">
+      <c r="A600" s="4"/>
+      <c r="B600" s="5"/>
+      <c r="C600" s="5"/>
+    </row>
+    <row r="601" spans="1:3" ht="40" customHeight="1">
+      <c r="A601" s="4"/>
+      <c r="B601" s="5"/>
+      <c r="C601" s="5"/>
+    </row>
+    <row r="602" spans="1:3" ht="40" customHeight="1">
+      <c r="A602" s="4"/>
+      <c r="B602" s="5"/>
+      <c r="C602" s="5"/>
+    </row>
+    <row r="603" spans="1:3" ht="40" customHeight="1">
+      <c r="A603" s="4"/>
+      <c r="B603" s="5"/>
+      <c r="C603" s="5"/>
+    </row>
+    <row r="604" spans="1:3" ht="40" customHeight="1">
+      <c r="A604" s="4"/>
+      <c r="B604" s="5"/>
+      <c r="C604" s="5"/>
+    </row>
+    <row r="605" spans="1:3" ht="40" customHeight="1">
+      <c r="A605" s="4"/>
+      <c r="B605" s="5"/>
+      <c r="C605" s="5"/>
+    </row>
+    <row r="606" spans="1:3" ht="40" customHeight="1">
+      <c r="A606" s="4"/>
+      <c r="B606" s="5"/>
+      <c r="C606" s="5"/>
+    </row>
+    <row r="607" spans="1:3" ht="40" customHeight="1">
+      <c r="A607" s="4"/>
+      <c r="B607" s="5"/>
+      <c r="C607" s="5"/>
+    </row>
+    <row r="608" spans="1:3" ht="40" customHeight="1">
+      <c r="A608" s="4"/>
+      <c r="B608" s="5"/>
+      <c r="C608" s="5"/>
+    </row>
+    <row r="609" spans="1:3" ht="40" customHeight="1">
+      <c r="A609" s="4"/>
+      <c r="B609" s="5"/>
+      <c r="C609" s="5"/>
+    </row>
+    <row r="610" spans="1:3" ht="40" customHeight="1">
+      <c r="A610" s="4"/>
+      <c r="B610" s="5"/>
+      <c r="C610" s="5"/>
+    </row>
+    <row r="611" spans="1:3" ht="40" customHeight="1">
+      <c r="A611" s="4"/>
+      <c r="B611" s="5"/>
+      <c r="C611" s="5"/>
+    </row>
+    <row r="612" spans="1:3" ht="40" customHeight="1">
+      <c r="A612" s="4"/>
+      <c r="B612" s="5"/>
+      <c r="C612" s="5"/>
+    </row>
+    <row r="613" spans="1:3" ht="40" customHeight="1">
+      <c r="A613" s="4"/>
+      <c r="B613" s="5"/>
+      <c r="C613" s="5"/>
+    </row>
+    <row r="614" spans="1:3" ht="40" customHeight="1">
+      <c r="A614" s="4"/>
+      <c r="B614" s="5"/>
+      <c r="C614" s="5"/>
+    </row>
+    <row r="615" spans="1:3" ht="40" customHeight="1">
+      <c r="A615" s="4"/>
+      <c r="B615" s="5"/>
+      <c r="C615" s="5"/>
+    </row>
+    <row r="616" spans="1:3" ht="40" customHeight="1">
+      <c r="A616" s="4"/>
+      <c r="B616" s="5"/>
+      <c r="C616" s="5"/>
+    </row>
+    <row r="617" spans="1:3" ht="40" customHeight="1">
+      <c r="A617" s="4"/>
+      <c r="B617" s="5"/>
+      <c r="C617" s="5"/>
+    </row>
+    <row r="618" spans="1:3" ht="40" customHeight="1">
+      <c r="A618" s="4"/>
+      <c r="B618" s="5"/>
+      <c r="C618" s="5"/>
+    </row>
+    <row r="619" spans="1:3" ht="40" customHeight="1">
+      <c r="A619" s="4"/>
+      <c r="B619" s="5"/>
+      <c r="C619" s="5"/>
+    </row>
+    <row r="620" spans="1:3" ht="40" customHeight="1">
+      <c r="A620" s="4"/>
+      <c r="B620" s="5"/>
+      <c r="C620" s="5"/>
+    </row>
+    <row r="621" spans="1:3" ht="40" customHeight="1">
+      <c r="A621" s="4"/>
+      <c r="B621" s="5"/>
+      <c r="C621" s="5"/>
+    </row>
+    <row r="622" spans="1:3" ht="40" customHeight="1">
+      <c r="A622" s="4"/>
+      <c r="B622" s="5"/>
+      <c r="C622" s="5"/>
+    </row>
+    <row r="623" spans="1:3" ht="40" customHeight="1">
+      <c r="A623" s="4"/>
+      <c r="B623" s="5"/>
+      <c r="C623" s="5"/>
+    </row>
+    <row r="624" spans="1:3" ht="40" customHeight="1">
+      <c r="A624" s="4"/>
+      <c r="B624" s="5"/>
+      <c r="C624" s="5"/>
+    </row>
+    <row r="625" spans="1:3" ht="40" customHeight="1">
+      <c r="A625" s="4"/>
+      <c r="B625" s="5"/>
+      <c r="C625" s="5"/>
+    </row>
+    <row r="626" spans="1:3" ht="40" customHeight="1">
+      <c r="A626" s="4"/>
+      <c r="B626" s="5"/>
+      <c r="C626" s="5"/>
+    </row>
+    <row r="627" spans="1:3" ht="40" customHeight="1">
+      <c r="A627" s="4"/>
+      <c r="B627" s="5"/>
+      <c r="C627" s="5"/>
+    </row>
+    <row r="628" spans="1:3" ht="40" customHeight="1">
+      <c r="A628" s="4"/>
+      <c r="B628" s="5"/>
+      <c r="C628" s="5"/>
+    </row>
+    <row r="629" spans="1:3" ht="40" customHeight="1">
+      <c r="A629" s="4"/>
+      <c r="B629" s="5"/>
+      <c r="C629" s="5"/>
+    </row>
+    <row r="630" spans="1:3" ht="40" customHeight="1">
+      <c r="A630" s="4"/>
+      <c r="B630" s="5"/>
+      <c r="C630" s="5"/>
+    </row>
+    <row r="631" spans="1:3" ht="40" customHeight="1">
+      <c r="A631" s="4"/>
+      <c r="B631" s="5"/>
+      <c r="C631" s="5"/>
+    </row>
+    <row r="632" spans="1:3" ht="40" customHeight="1">
+      <c r="A632" s="4"/>
+      <c r="B632" s="5"/>
+      <c r="C632" s="5"/>
+    </row>
+    <row r="633" spans="1:3" ht="40" customHeight="1">
+      <c r="A633" s="4"/>
+      <c r="B633" s="5"/>
+      <c r="C633" s="5"/>
+    </row>
+    <row r="634" spans="1:3" ht="40" customHeight="1">
+      <c r="A634" s="4"/>
+      <c r="B634" s="5"/>
+      <c r="C634" s="5"/>
+    </row>
+    <row r="635" spans="1:3" ht="40" customHeight="1">
+      <c r="A635" s="4"/>
+      <c r="B635" s="5"/>
+      <c r="C635" s="5"/>
+    </row>
+    <row r="636" spans="1:3" ht="40" customHeight="1">
+      <c r="A636" s="4"/>
+      <c r="B636" s="5"/>
+      <c r="C636" s="5"/>
+    </row>
+    <row r="637" spans="1:3" ht="40" customHeight="1">
+      <c r="A637" s="4"/>
+      <c r="B637" s="5"/>
+      <c r="C637" s="5"/>
+    </row>
+    <row r="638" spans="1:3" ht="40" customHeight="1">
+      <c r="A638" s="4"/>
+      <c r="B638" s="5"/>
+      <c r="C638" s="5"/>
+    </row>
+    <row r="639" spans="1:3" ht="40" customHeight="1">
+      <c r="A639" s="4"/>
+      <c r="B639" s="5"/>
+      <c r="C639" s="5"/>
+    </row>
+    <row r="640" spans="1:3" ht="40" customHeight="1">
+      <c r="A640" s="4"/>
+      <c r="B640" s="5"/>
+      <c r="C640" s="5"/>
+    </row>
+    <row r="641" spans="1:3" ht="40" customHeight="1">
+      <c r="A641" s="4"/>
+      <c r="B641" s="5"/>
+      <c r="C641" s="5"/>
+    </row>
+    <row r="642" spans="1:3" ht="40" customHeight="1">
+      <c r="A642" s="4"/>
+      <c r="B642" s="5"/>
+      <c r="C642" s="5"/>
+    </row>
+    <row r="643" spans="1:3" ht="40" customHeight="1">
+      <c r="A643" s="4"/>
+      <c r="B643" s="5"/>
+      <c r="C643" s="5"/>
+    </row>
+    <row r="644" spans="1:3" ht="40" customHeight="1">
+      <c r="A644" s="4"/>
+      <c r="B644" s="5"/>
+      <c r="C644" s="5"/>
+    </row>
+    <row r="645" spans="1:3" ht="40" customHeight="1">
+      <c r="A645" s="4"/>
+      <c r="B645" s="5"/>
+      <c r="C645" s="5"/>
+    </row>
+    <row r="646" spans="1:3" ht="40" customHeight="1">
+      <c r="A646" s="4"/>
+      <c r="B646" s="5"/>
+      <c r="C646" s="5"/>
+    </row>
+    <row r="647" spans="1:3" ht="40" customHeight="1">
+      <c r="A647" s="4"/>
+      <c r="B647" s="5"/>
+      <c r="C647" s="5"/>
+    </row>
+    <row r="648" spans="1:3" ht="40" customHeight="1">
+      <c r="A648" s="4"/>
+      <c r="B648" s="5"/>
+      <c r="C648" s="5"/>
+    </row>
+    <row r="649" spans="1:3" ht="40" customHeight="1">
+      <c r="A649" s="4"/>
+      <c r="B649" s="5"/>
+      <c r="C649" s="5"/>
+    </row>
+    <row r="650" spans="1:3" ht="40" customHeight="1">
+      <c r="A650" s="4"/>
+      <c r="B650" s="5"/>
+      <c r="C650" s="5"/>
+    </row>
+    <row r="651" spans="1:3" ht="40" customHeight="1">
+      <c r="A651" s="4"/>
+      <c r="B651" s="5"/>
+      <c r="C651" s="5"/>
+    </row>
+    <row r="652" spans="1:3" ht="40" customHeight="1">
+      <c r="A652" s="4"/>
+      <c r="B652" s="5"/>
+      <c r="C652" s="5"/>
+    </row>
+    <row r="653" spans="1:3" ht="40" customHeight="1">
+      <c r="A653" s="4"/>
+      <c r="B653" s="5"/>
+      <c r="C653" s="5"/>
+    </row>
+    <row r="654" spans="1:3" ht="40" customHeight="1">
+      <c r="A654" s="4"/>
+      <c r="B654" s="5"/>
+      <c r="C654" s="5"/>
+    </row>
+    <row r="655" spans="1:3" ht="40" customHeight="1">
+      <c r="A655" s="4"/>
+      <c r="B655" s="5"/>
+      <c r="C655" s="5"/>
+    </row>
+    <row r="656" spans="1:3" ht="40" customHeight="1">
+      <c r="A656" s="4"/>
+      <c r="B656" s="5"/>
+      <c r="C656" s="5"/>
+    </row>
+    <row r="657" spans="1:3" ht="40" customHeight="1">
+      <c r="A657" s="4"/>
+      <c r="B657" s="5"/>
+      <c r="C657" s="5"/>
+    </row>
+    <row r="658" spans="1:3" ht="40" customHeight="1">
+      <c r="A658" s="4"/>
+      <c r="B658" s="5"/>
+      <c r="C658" s="5"/>
+    </row>
+    <row r="659" spans="1:3" ht="40" customHeight="1">
+      <c r="A659" s="4"/>
+      <c r="B659" s="5"/>
+      <c r="C659" s="5"/>
+    </row>
+    <row r="660" spans="1:3" ht="40" customHeight="1">
+      <c r="A660" s="4"/>
+      <c r="B660" s="5"/>
+      <c r="C660" s="5"/>
+    </row>
+    <row r="661" spans="1:3" ht="40" customHeight="1">
+      <c r="A661" s="4"/>
+      <c r="B661" s="5"/>
+      <c r="C661" s="5"/>
+    </row>
+    <row r="662" spans="1:3" ht="40" customHeight="1">
+      <c r="A662" s="4"/>
+      <c r="B662" s="5"/>
+      <c r="C662" s="5"/>
+    </row>
+    <row r="663" spans="1:3" ht="40" customHeight="1">
+      <c r="A663" s="4"/>
+      <c r="B663" s="5"/>
+      <c r="C663" s="5"/>
+    </row>
+    <row r="664" spans="1:3" ht="40" customHeight="1">
+      <c r="A664" s="4"/>
+      <c r="B664" s="5"/>
+      <c r="C664" s="5"/>
+    </row>
+    <row r="665" spans="1:3" ht="40" customHeight="1">
+      <c r="A665" s="4"/>
+      <c r="B665" s="5"/>
+      <c r="C665" s="5"/>
+    </row>
+    <row r="666" spans="1:3" ht="40" customHeight="1">
+      <c r="A666" s="4"/>
+      <c r="B666" s="5"/>
+      <c r="C666" s="5"/>
+    </row>
+    <row r="667" spans="1:3" ht="40" customHeight="1">
+      <c r="A667" s="4"/>
+      <c r="B667" s="5"/>
+      <c r="C667" s="5"/>
+    </row>
+    <row r="668" spans="1:3" ht="40" customHeight="1">
+      <c r="A668" s="4"/>
+      <c r="B668" s="5"/>
+      <c r="C668" s="5"/>
+    </row>
+    <row r="669" spans="1:3" ht="40" customHeight="1">
+      <c r="A669" s="4"/>
+      <c r="B669" s="5"/>
+      <c r="C669" s="5"/>
+    </row>
+    <row r="670" spans="1:3" ht="40" customHeight="1">
+      <c r="A670" s="4"/>
+      <c r="B670" s="5"/>
+      <c r="C670" s="5"/>
+    </row>
+    <row r="671" spans="1:3" ht="40" customHeight="1">
+      <c r="A671" s="4"/>
+      <c r="B671" s="5"/>
+      <c r="C671" s="5"/>
+    </row>
+    <row r="672" spans="1:3" ht="40" customHeight="1">
+      <c r="A672" s="4"/>
+      <c r="B672" s="5"/>
+      <c r="C672" s="5"/>
+    </row>
+    <row r="673" spans="1:3" ht="40" customHeight="1">
+      <c r="A673" s="4"/>
+      <c r="B673" s="5"/>
+      <c r="C673" s="5"/>
+    </row>
+    <row r="674" spans="1:3" ht="40" customHeight="1">
+      <c r="A674" s="4"/>
+      <c r="B674" s="5"/>
+      <c r="C674" s="5"/>
+    </row>
+    <row r="675" spans="1:3" ht="40" customHeight="1">
+      <c r="A675" s="4"/>
+      <c r="B675" s="5"/>
+      <c r="C675" s="5"/>
+    </row>
+    <row r="676" spans="1:3" ht="40" customHeight="1">
+      <c r="A676" s="4"/>
+      <c r="B676" s="5"/>
+      <c r="C676" s="5"/>
+    </row>
+    <row r="677" spans="1:3" ht="40" customHeight="1">
+      <c r="A677" s="4"/>
+      <c r="B677" s="5"/>
+      <c r="C677" s="5"/>
+    </row>
+    <row r="678" spans="1:3" ht="40" customHeight="1">
+      <c r="A678" s="4"/>
+      <c r="B678" s="5"/>
+      <c r="C678" s="5"/>
+    </row>
+    <row r="679" spans="1:3" ht="40" customHeight="1">
+      <c r="A679" s="4"/>
+      <c r="B679" s="5"/>
+      <c r="C679" s="5"/>
+    </row>
+    <row r="680" spans="1:3" ht="40" customHeight="1">
+      <c r="A680" s="4"/>
+      <c r="B680" s="5"/>
+      <c r="C680" s="5"/>
+    </row>
+    <row r="681" spans="1:3" ht="40" customHeight="1">
+      <c r="A681" s="4"/>
+      <c r="B681" s="5"/>
+      <c r="C681" s="5"/>
+    </row>
+    <row r="682" spans="1:3" ht="40" customHeight="1">
+      <c r="A682" s="4"/>
+      <c r="B682" s="5"/>
+      <c r="C682" s="5"/>
+    </row>
+    <row r="683" spans="1:3" ht="40" customHeight="1">
+      <c r="A683" s="4"/>
+      <c r="B683" s="5"/>
+      <c r="C683" s="5"/>
+    </row>
+    <row r="684" spans="1:3" ht="40" customHeight="1">
+      <c r="A684" s="4"/>
+      <c r="B684" s="5"/>
+      <c r="C684" s="5"/>
+    </row>
+    <row r="685" spans="1:3" ht="40" customHeight="1">
+      <c r="A685" s="4"/>
+      <c r="B685" s="5"/>
+      <c r="C685" s="5"/>
+    </row>
+    <row r="686" spans="1:3" ht="40" customHeight="1">
+      <c r="A686" s="4"/>
+      <c r="B686" s="5"/>
+      <c r="C686" s="5"/>
+    </row>
+    <row r="687" spans="1:3" ht="40" customHeight="1">
+      <c r="A687" s="4"/>
+      <c r="B687" s="5"/>
+      <c r="C687" s="5"/>
+    </row>
+    <row r="688" spans="1:3" ht="40" customHeight="1">
+      <c r="A688" s="4"/>
+      <c r="B688" s="5"/>
+      <c r="C688" s="5"/>
+    </row>
+    <row r="689" spans="1:3" ht="40" customHeight="1">
+      <c r="A689" s="4"/>
+      <c r="B689" s="5"/>
+      <c r="C689" s="5"/>
+    </row>
+    <row r="690" spans="1:3" ht="40" customHeight="1">
+      <c r="A690" s="4"/>
+      <c r="B690" s="5"/>
+      <c r="C690" s="5"/>
+    </row>
+    <row r="691" spans="1:3" ht="40" customHeight="1">
+      <c r="A691" s="4"/>
+      <c r="B691" s="5"/>
+      <c r="C691" s="5"/>
+    </row>
+    <row r="692" spans="1:3" ht="40" customHeight="1">
+      <c r="A692" s="4"/>
+      <c r="B692" s="5"/>
+      <c r="C692" s="5"/>
+    </row>
+    <row r="693" spans="1:3" ht="40" customHeight="1">
+      <c r="A693" s="4"/>
+      <c r="B693" s="5"/>
+      <c r="C693" s="5"/>
+    </row>
+    <row r="694" spans="1:3" ht="40" customHeight="1">
+      <c r="A694" s="4"/>
+      <c r="B694" s="5"/>
+      <c r="C694" s="5"/>
+    </row>
+    <row r="695" spans="1:3" ht="40" customHeight="1">
+      <c r="A695" s="4"/>
+      <c r="B695" s="5"/>
+      <c r="C695" s="5"/>
+    </row>
+    <row r="696" spans="1:3" ht="40" customHeight="1">
+      <c r="A696" s="4"/>
+      <c r="B696" s="5"/>
+      <c r="C696" s="5"/>
+    </row>
+    <row r="697" spans="1:3" ht="40" customHeight="1">
+      <c r="A697" s="4"/>
+      <c r="B697" s="5"/>
+      <c r="C697" s="5"/>
+    </row>
+    <row r="698" spans="1:3" ht="40" customHeight="1">
+      <c r="A698" s="4"/>
+      <c r="B698" s="5"/>
+      <c r="C698" s="5"/>
+    </row>
+    <row r="699" spans="1:3" ht="40" customHeight="1">
+      <c r="A699" s="4"/>
+      <c r="B699" s="5"/>
+      <c r="C699" s="5"/>
+    </row>
+    <row r="700" spans="1:3" ht="40" customHeight="1">
+      <c r="A700" s="4"/>
+      <c r="B700" s="5"/>
+      <c r="C700" s="5"/>
+    </row>
+    <row r="701" spans="1:3" ht="40" customHeight="1">
+      <c r="A701" s="4"/>
+      <c r="B701" s="5"/>
+      <c r="C701" s="5"/>
+    </row>
+    <row r="702" spans="1:3" ht="40" customHeight="1">
+      <c r="A702" s="4"/>
+      <c r="B702" s="5"/>
+      <c r="C702" s="5"/>
+    </row>
+    <row r="703" spans="1:3" ht="40" customHeight="1">
+      <c r="A703" s="4"/>
+      <c r="B703" s="5"/>
+      <c r="C703" s="5"/>
+    </row>
+    <row r="704" spans="1:3" ht="40" customHeight="1">
+      <c r="A704" s="4"/>
+      <c r="B704" s="5"/>
+      <c r="C704" s="5"/>
+    </row>
+    <row r="705" spans="1:3" ht="40" customHeight="1">
+      <c r="A705" s="4"/>
+      <c r="B705" s="5"/>
+      <c r="C705" s="5"/>
+    </row>
+    <row r="706" spans="1:3" ht="40" customHeight="1">
+      <c r="A706" s="4"/>
+      <c r="B706" s="5"/>
+      <c r="C706" s="5"/>
+    </row>
+    <row r="707" spans="1:3" ht="40" customHeight="1">
+      <c r="A707" s="4"/>
+      <c r="B707" s="5"/>
+      <c r="C707" s="5"/>
+    </row>
+    <row r="708" spans="1:3" ht="40" customHeight="1">
+      <c r="A708" s="4"/>
+      <c r="B708" s="5"/>
+      <c r="C708" s="5"/>
+    </row>
+    <row r="709" spans="1:3" ht="40" customHeight="1">
+      <c r="A709" s="4"/>
+      <c r="B709" s="5"/>
+      <c r="C709" s="5"/>
+    </row>
+    <row r="710" spans="1:3" ht="40" customHeight="1">
+      <c r="A710" s="4"/>
+      <c r="B710" s="5"/>
+      <c r="C710" s="5"/>
+    </row>
+    <row r="711" spans="1:3" ht="40" customHeight="1">
+      <c r="A711" s="4"/>
+      <c r="B711" s="5"/>
+      <c r="C711" s="5"/>
+    </row>
+    <row r="712" spans="1:3" ht="40" customHeight="1">
+      <c r="A712" s="4"/>
+      <c r="B712" s="5"/>
+      <c r="C712" s="5"/>
+    </row>
+    <row r="713" spans="1:3" ht="40" customHeight="1">
+      <c r="A713" s="4"/>
+      <c r="B713" s="5"/>
+      <c r="C713" s="5"/>
+    </row>
+    <row r="714" spans="1:3" ht="40" customHeight="1">
+      <c r="A714" s="4"/>
+      <c r="B714" s="5"/>
+      <c r="C714" s="5"/>
+    </row>
+    <row r="715" spans="1:3" ht="40" customHeight="1">
+      <c r="A715" s="4"/>
+      <c r="B715" s="5"/>
+      <c r="C715" s="5"/>
+    </row>
+    <row r="716" spans="1:3" ht="40" customHeight="1">
+      <c r="A716" s="4"/>
+      <c r="B716" s="5"/>
+      <c r="C716" s="5"/>
+    </row>
+    <row r="717" spans="1:3" ht="40" customHeight="1">
+      <c r="A717" s="4"/>
+      <c r="B717" s="5"/>
+      <c r="C717" s="5"/>
+    </row>
+    <row r="718" spans="1:3" ht="40" customHeight="1">
+      <c r="A718" s="4"/>
+      <c r="B718" s="5"/>
+      <c r="C718" s="5"/>
+    </row>
+    <row r="719" spans="1:3" ht="40" customHeight="1">
+      <c r="A719" s="4"/>
+      <c r="B719" s="5"/>
+      <c r="C719" s="5"/>
+    </row>
+    <row r="720" spans="1:3" ht="40" customHeight="1">
+      <c r="A720" s="4"/>
+      <c r="B720" s="5"/>
+      <c r="C720" s="5"/>
+    </row>
+    <row r="721" spans="1:3" ht="40" customHeight="1">
+      <c r="A721" s="4"/>
+      <c r="B721" s="5"/>
+      <c r="C721" s="5"/>
+    </row>
+    <row r="722" spans="1:3" ht="40" customHeight="1">
+      <c r="A722" s="4"/>
+      <c r="B722" s="5"/>
+      <c r="C722" s="5"/>
+    </row>
+    <row r="723" spans="1:3" ht="40" customHeight="1">
+      <c r="A723" s="4"/>
+      <c r="B723" s="5"/>
+      <c r="C723" s="5"/>
+    </row>
+    <row r="724" spans="1:3" ht="40" customHeight="1">
+      <c r="A724" s="4"/>
+      <c r="B724" s="5"/>
+      <c r="C724" s="5"/>
+    </row>
+    <row r="725" spans="1:3" ht="40" customHeight="1">
+      <c r="A725" s="4"/>
+      <c r="B725" s="5"/>
+      <c r="C725" s="5"/>
+    </row>
+    <row r="726" spans="1:3" ht="40" customHeight="1">
+      <c r="A726" s="4"/>
+      <c r="B726" s="5"/>
+      <c r="C726" s="5"/>
+    </row>
+    <row r="727" spans="1:3" ht="40" customHeight="1">
+      <c r="A727" s="4"/>
+      <c r="B727" s="5"/>
+      <c r="C727" s="5"/>
+    </row>
+    <row r="728" spans="1:3" ht="40" customHeight="1">
+      <c r="A728" s="4"/>
+      <c r="B728" s="5"/>
+      <c r="C728" s="5"/>
+    </row>
+    <row r="729" spans="1:3" ht="40" customHeight="1">
+      <c r="A729" s="4"/>
+      <c r="B729" s="5"/>
+      <c r="C729" s="5"/>
+    </row>
+    <row r="730" spans="1:3" ht="40" customHeight="1">
+      <c r="A730" s="4"/>
+      <c r="B730" s="5"/>
+      <c r="C730" s="5"/>
+    </row>
+    <row r="731" spans="1:3" ht="40" customHeight="1">
+      <c r="A731" s="4"/>
+      <c r="B731" s="5"/>
+      <c r="C731" s="5"/>
+    </row>
+    <row r="732" spans="1:3" ht="40" customHeight="1">
+      <c r="A732" s="4"/>
+      <c r="B732" s="5"/>
+      <c r="C732" s="5"/>
+    </row>
+    <row r="733" spans="1:3" ht="40" customHeight="1">
+      <c r="A733" s="4"/>
+      <c r="B733" s="5"/>
+      <c r="C733" s="5"/>
+    </row>
+    <row r="734" spans="1:3" ht="40" customHeight="1">
+      <c r="A734" s="4"/>
+      <c r="B734" s="5"/>
+      <c r="C734" s="5"/>
+    </row>
+    <row r="735" spans="1:3" ht="40" customHeight="1">
+      <c r="A735" s="4"/>
+      <c r="B735" s="5"/>
+      <c r="C735" s="5"/>
+    </row>
+    <row r="736" spans="1:3" ht="40" customHeight="1">
+      <c r="A736" s="4"/>
+      <c r="B736" s="5"/>
+      <c r="C736" s="5"/>
+    </row>
+    <row r="737" spans="1:3" ht="40" customHeight="1">
+      <c r="A737" s="4"/>
+      <c r="B737" s="5"/>
+      <c r="C737" s="5"/>
+    </row>
+    <row r="738" spans="1:3" ht="40" customHeight="1">
+      <c r="A738" s="4"/>
+      <c r="B738" s="5"/>
+      <c r="C738" s="5"/>
+    </row>
+    <row r="739" spans="1:3" ht="40" customHeight="1">
+      <c r="A739" s="4"/>
+      <c r="B739" s="5"/>
+      <c r="C739" s="5"/>
+    </row>
+    <row r="740" spans="1:3" ht="40" customHeight="1">
+      <c r="A740" s="4"/>
+      <c r="B740" s="5"/>
+      <c r="C740" s="5"/>
+    </row>
+    <row r="741" spans="1:3" ht="40" customHeight="1">
+      <c r="A741" s="4"/>
+      <c r="B741" s="5"/>
+      <c r="C741" s="5"/>
+    </row>
+    <row r="742" spans="1:3" ht="40" customHeight="1">
+      <c r="A742" s="4"/>
+      <c r="B742" s="5"/>
+      <c r="C742" s="5"/>
+    </row>
+    <row r="743" spans="1:3" ht="40" customHeight="1">
+      <c r="A743" s="4"/>
+      <c r="B743" s="5"/>
+      <c r="C743" s="5"/>
+    </row>
+    <row r="744" spans="1:3" ht="40" customHeight="1">
+      <c r="A744" s="4"/>
+      <c r="B744" s="5"/>
+      <c r="C744" s="5"/>
+    </row>
+    <row r="745" spans="1:3" ht="40" customHeight="1">
+      <c r="A745" s="4"/>
+      <c r="B745" s="5"/>
+      <c r="C745" s="5"/>
+    </row>
+    <row r="746" spans="1:3" ht="40" customHeight="1">
+      <c r="A746" s="4"/>
+      <c r="B746" s="5"/>
+      <c r="C746" s="5"/>
+    </row>
+    <row r="747" spans="1:3" ht="40" customHeight="1">
+      <c r="A747" s="4"/>
+      <c r="B747" s="5"/>
+      <c r="C747" s="5"/>
+    </row>
+    <row r="748" spans="1:3" ht="40" customHeight="1">
+      <c r="A748" s="4"/>
+      <c r="B748" s="5"/>
+      <c r="C748" s="5"/>
+    </row>
+    <row r="749" spans="1:3" ht="40" customHeight="1">
+      <c r="A749" s="4"/>
+      <c r="B749" s="5"/>
+      <c r="C749" s="5"/>
+    </row>
+    <row r="750" spans="1:3" ht="40" customHeight="1">
+      <c r="A750" s="4"/>
+      <c r="B750" s="5"/>
+      <c r="C750" s="5"/>
+    </row>
+    <row r="751" spans="1:3" ht="40" customHeight="1">
+      <c r="A751" s="4"/>
+      <c r="B751" s="5"/>
+      <c r="C751" s="5"/>
+    </row>
+    <row r="752" spans="1:3" ht="40" customHeight="1">
+      <c r="A752" s="4"/>
+      <c r="B752" s="5"/>
+      <c r="C752" s="5"/>
+    </row>
+    <row r="753" spans="1:3" ht="40" customHeight="1">
+      <c r="A753" s="4"/>
+      <c r="B753" s="5"/>
+      <c r="C753" s="5"/>
+    </row>
+    <row r="754" spans="1:3" ht="40" customHeight="1">
+      <c r="A754" s="4"/>
+      <c r="B754" s="5"/>
+      <c r="C754" s="5"/>
+    </row>
+    <row r="755" spans="1:3" ht="40" customHeight="1">
+      <c r="A755" s="4"/>
+      <c r="B755" s="5"/>
+      <c r="C755" s="5"/>
+    </row>
+    <row r="756" spans="1:3" ht="40" customHeight="1">
+      <c r="A756" s="4"/>
+      <c r="B756" s="5"/>
+      <c r="C756" s="5"/>
+    </row>
+    <row r="757" spans="1:3" ht="40" customHeight="1">
+      <c r="A757" s="4"/>
+      <c r="B757" s="5"/>
+      <c r="C757" s="5"/>
+    </row>
+    <row r="758" spans="1:3" ht="40" customHeight="1">
+      <c r="A758" s="4"/>
+      <c r="B758" s="5"/>
+      <c r="C758" s="5"/>
+    </row>
+    <row r="759" spans="1:3" ht="40" customHeight="1">
+      <c r="A759" s="4"/>
+      <c r="B759" s="5"/>
+      <c r="C759" s="5"/>
+    </row>
+    <row r="760" spans="1:3" ht="40" customHeight="1">
+      <c r="A760" s="4"/>
+      <c r="B760" s="5"/>
+      <c r="C760" s="5"/>
+    </row>
+    <row r="761" spans="1:3" ht="40" customHeight="1">
+      <c r="A761" s="4"/>
+      <c r="B761" s="5"/>
+      <c r="C761" s="5"/>
+    </row>
+    <row r="762" spans="1:3" ht="40" customHeight="1">
+      <c r="A762" s="4"/>
+      <c r="B762" s="5"/>
+      <c r="C762" s="5"/>
+    </row>
+    <row r="763" spans="1:3" ht="40" customHeight="1">
+      <c r="A763" s="4"/>
+      <c r="B763" s="5"/>
+      <c r="C763" s="5"/>
+    </row>
+    <row r="764" spans="1:3" ht="40" customHeight="1">
+      <c r="A764" s="4"/>
+      <c r="B764" s="5"/>
+      <c r="C764" s="5"/>
+    </row>
+    <row r="765" spans="1:3" ht="40" customHeight="1">
+      <c r="A765" s="4"/>
+      <c r="B765" s="5"/>
+      <c r="C765" s="5"/>
+    </row>
+    <row r="766" spans="1:3" ht="40" customHeight="1">
+      <c r="A766" s="4"/>
+      <c r="B766" s="5"/>
+      <c r="C766" s="5"/>
+    </row>
+    <row r="767" spans="1:3" ht="40" customHeight="1">
+      <c r="A767" s="4"/>
+      <c r="B767" s="5"/>
+      <c r="C767" s="5"/>
+    </row>
+    <row r="768" spans="1:3" ht="40" customHeight="1">
+      <c r="A768" s="4"/>
+      <c r="B768" s="5"/>
+      <c r="C768" s="5"/>
+    </row>
+    <row r="769" spans="1:3" ht="40" customHeight="1">
+      <c r="A769" s="4"/>
+      <c r="B769" s="5"/>
+      <c r="C769" s="5"/>
+    </row>
+    <row r="770" spans="1:3" ht="40" customHeight="1">
+      <c r="A770" s="4"/>
+      <c r="B770" s="5"/>
+      <c r="C770" s="5"/>
+    </row>
+    <row r="771" spans="1:3" ht="40" customHeight="1">
+      <c r="A771" s="4"/>
+      <c r="B771" s="5"/>
+      <c r="C771" s="5"/>
+    </row>
+    <row r="772" spans="1:3" ht="40" customHeight="1">
+      <c r="A772" s="4"/>
+      <c r="B772" s="5"/>
+      <c r="C772" s="5"/>
+    </row>
+    <row r="773" spans="1:3" ht="40" customHeight="1">
+      <c r="A773" s="4"/>
+      <c r="B773" s="5"/>
+      <c r="C773" s="5"/>
+    </row>
+    <row r="774" spans="1:3" ht="40" customHeight="1">
+      <c r="A774" s="4"/>
+      <c r="B774" s="5"/>
+      <c r="C774" s="5"/>
+    </row>
+    <row r="775" spans="1:3" ht="40" customHeight="1">
+      <c r="A775" s="4"/>
+      <c r="B775" s="5"/>
+      <c r="C775" s="5"/>
+    </row>
+    <row r="776" spans="1:3" ht="40" customHeight="1">
+      <c r="A776" s="4"/>
+      <c r="B776" s="5"/>
+      <c r="C776" s="5"/>
+    </row>
+    <row r="777" spans="1:3" ht="40" customHeight="1">
+      <c r="A777" s="4"/>
+      <c r="B777" s="5"/>
+      <c r="C777" s="5"/>
+    </row>
+    <row r="778" spans="1:3" ht="40" customHeight="1">
+      <c r="A778" s="4"/>
+      <c r="B778" s="5"/>
+      <c r="C778" s="5"/>
+    </row>
+    <row r="779" spans="1:3" ht="40" customHeight="1">
+      <c r="A779" s="4"/>
+      <c r="B779" s="5"/>
+      <c r="C779" s="5"/>
+    </row>
+    <row r="780" spans="1:3" ht="40" customHeight="1">
+      <c r="A780" s="4"/>
+      <c r="B780" s="5"/>
+      <c r="C780" s="5"/>
+    </row>
+    <row r="781" spans="1:3" ht="40" customHeight="1">
+      <c r="A781" s="4"/>
+      <c r="B781" s="5"/>
+      <c r="C781" s="5"/>
+    </row>
+    <row r="782" spans="1:3" ht="40" customHeight="1">
+      <c r="A782" s="4"/>
+      <c r="B782" s="5"/>
+      <c r="C782" s="5"/>
+    </row>
+    <row r="783" spans="1:3" ht="40" customHeight="1">
+      <c r="A783" s="4"/>
+      <c r="B783" s="5"/>
+      <c r="C783" s="5"/>
+    </row>
+    <row r="784" spans="1:3" ht="40" customHeight="1">
+      <c r="A784" s="4"/>
+      <c r="B784" s="5"/>
+      <c r="C784" s="5"/>
+    </row>
+    <row r="785" spans="1:3" ht="40" customHeight="1">
+      <c r="A785" s="4"/>
+      <c r="B785" s="5"/>
+      <c r="C785" s="5"/>
+    </row>
+    <row r="786" spans="1:3" ht="40" customHeight="1">
+      <c r="A786" s="4"/>
+      <c r="B786" s="5"/>
+      <c r="C786" s="5"/>
+    </row>
+    <row r="787" spans="1:3" ht="40" customHeight="1">
+      <c r="A787" s="4"/>
+      <c r="B787" s="5"/>
+      <c r="C787" s="5"/>
+    </row>
+    <row r="788" spans="1:3" ht="40" customHeight="1">
+      <c r="A788" s="4"/>
+      <c r="B788" s="5"/>
+      <c r="C788" s="5"/>
+    </row>
+    <row r="789" spans="1:3" ht="40" customHeight="1">
+      <c r="A789" s="4"/>
+      <c r="B789" s="5"/>
+      <c r="C789" s="5"/>
+    </row>
+    <row r="790" spans="1:3" ht="40" customHeight="1">
+      <c r="A790" s="4"/>
+      <c r="B790" s="5"/>
+      <c r="C790" s="5"/>
+    </row>
+    <row r="791" spans="1:3" ht="40" customHeight="1">
+      <c r="A791" s="4"/>
+      <c r="B791" s="5"/>
+      <c r="C791" s="5"/>
+    </row>
+    <row r="792" spans="1:3" ht="40" customHeight="1">
+      <c r="A792" s="4"/>
+      <c r="B792" s="5"/>
+      <c r="C792" s="5"/>
+    </row>
+    <row r="793" spans="1:3" ht="40" customHeight="1">
+      <c r="A793" s="4"/>
+      <c r="B793" s="5"/>
+      <c r="C793" s="5"/>
+    </row>
+    <row r="794" spans="1:3" ht="40" customHeight="1">
+      <c r="A794" s="4"/>
+      <c r="B794" s="5"/>
+      <c r="C794" s="5"/>
+    </row>
+    <row r="795" spans="1:3" ht="40" customHeight="1">
+      <c r="A795" s="4"/>
+      <c r="B795" s="5"/>
+      <c r="C795" s="5"/>
+    </row>
+    <row r="796" spans="1:3" ht="40" customHeight="1">
+      <c r="A796" s="4"/>
+      <c r="B796" s="5"/>
+      <c r="C796" s="5"/>
+    </row>
+    <row r="797" spans="1:3" ht="40" customHeight="1">
+      <c r="A797" s="4"/>
+      <c r="B797" s="5"/>
+      <c r="C797" s="5"/>
+    </row>
+    <row r="798" spans="1:3" ht="40" customHeight="1">
+      <c r="A798" s="4"/>
+      <c r="B798" s="5"/>
+      <c r="C798" s="5"/>
+    </row>
+    <row r="799" spans="1:3" ht="40" customHeight="1">
+      <c r="A799" s="4"/>
+      <c r="B799" s="5"/>
+      <c r="C799" s="5"/>
+    </row>
+    <row r="800" spans="1:3" ht="40" customHeight="1">
+      <c r="A800" s="4"/>
+      <c r="B800" s="5"/>
+      <c r="C800" s="5"/>
+    </row>
+    <row r="801" spans="1:3" ht="40" customHeight="1">
+      <c r="A801" s="4"/>
+      <c r="B801" s="5"/>
+      <c r="C801" s="5"/>
+    </row>
+    <row r="802" spans="1:3" ht="40" customHeight="1">
+      <c r="A802" s="4"/>
+      <c r="B802" s="5"/>
+      <c r="C802" s="5"/>
+    </row>
+    <row r="803" spans="1:3" ht="40" customHeight="1">
+      <c r="A803" s="4"/>
+      <c r="B803" s="5"/>
+      <c r="C803" s="5"/>
+    </row>
+    <row r="804" spans="1:3" ht="40" customHeight="1">
+      <c r="A804" s="4"/>
+      <c r="B804" s="5"/>
+      <c r="C804" s="5"/>
+    </row>
+    <row r="805" spans="1:3" ht="40" customHeight="1">
+      <c r="A805" s="4"/>
+      <c r="B805" s="5"/>
+      <c r="C805" s="5"/>
+    </row>
+    <row r="806" spans="1:3" ht="40" customHeight="1">
+      <c r="A806" s="4"/>
+      <c r="B806" s="5"/>
+      <c r="C806" s="5"/>
+    </row>
+    <row r="807" spans="1:3" ht="40" customHeight="1">
+      <c r="A807" s="4"/>
+      <c r="B807" s="5"/>
+      <c r="C807" s="5"/>
+    </row>
+    <row r="808" spans="1:3" ht="40" customHeight="1">
+      <c r="A808" s="4"/>
+      <c r="B808" s="5"/>
+      <c r="C808" s="5"/>
+    </row>
+    <row r="809" spans="1:3" ht="40" customHeight="1">
+      <c r="A809" s="4"/>
+      <c r="B809" s="5"/>
+      <c r="C809" s="5"/>
+    </row>
+    <row r="810" spans="1:3" ht="40" customHeight="1">
+      <c r="A810" s="4"/>
+      <c r="B810" s="5"/>
+      <c r="C810" s="5"/>
+    </row>
+    <row r="811" spans="1:3" ht="40" customHeight="1">
+      <c r="A811" s="4"/>
+      <c r="B811" s="5"/>
+      <c r="C811" s="5"/>
+    </row>
+    <row r="812" spans="1:3" ht="40" customHeight="1">
+      <c r="A812" s="4"/>
+      <c r="B812" s="5"/>
+      <c r="C812" s="5"/>
+    </row>
+    <row r="813" spans="1:3" ht="40" customHeight="1">
+      <c r="A813" s="4"/>
+      <c r="B813" s="5"/>
+      <c r="C813" s="5"/>
+    </row>
+    <row r="814" spans="1:3" ht="40" customHeight="1">
+      <c r="A814" s="4"/>
+      <c r="B814" s="5"/>
+      <c r="C814" s="5"/>
+    </row>
+    <row r="815" spans="1:3" ht="40" customHeight="1">
+      <c r="A815" s="4"/>
+      <c r="B815" s="5"/>
+      <c r="C815" s="5"/>
+    </row>
+    <row r="816" spans="1:3" ht="40" customHeight="1">
+      <c r="A816" s="4"/>
+      <c r="B816" s="5"/>
+      <c r="C816" s="5"/>
+    </row>
+    <row r="817" spans="1:3" ht="40" customHeight="1">
+      <c r="A817" s="4"/>
+      <c r="B817" s="5"/>
+      <c r="C817" s="5"/>
+    </row>
+    <row r="818" spans="1:3" ht="40" customHeight="1">
+      <c r="A818" s="4"/>
+      <c r="B818" s="5"/>
+      <c r="C818" s="5"/>
+    </row>
+    <row r="819" spans="1:3" ht="40" customHeight="1">
+      <c r="A819" s="4"/>
+      <c r="B819" s="5"/>
+      <c r="C819" s="5"/>
+    </row>
+    <row r="820" spans="1:3" ht="40" customHeight="1">
+      <c r="A820" s="4"/>
+      <c r="B820" s="5"/>
+      <c r="C820" s="5"/>
+    </row>
+    <row r="821" spans="1:3" ht="40" customHeight="1">
+      <c r="A821" s="4"/>
+      <c r="B821" s="5"/>
+      <c r="C821" s="5"/>
+    </row>
+    <row r="822" spans="1:3" ht="40" customHeight="1">
+      <c r="A822" s="4"/>
+      <c r="B822" s="5"/>
+      <c r="C822" s="5"/>
+    </row>
+    <row r="823" spans="1:3" ht="40" customHeight="1">
+      <c r="A823" s="4"/>
+      <c r="B823" s="5"/>
+      <c r="C823" s="5"/>
+    </row>
+    <row r="824" spans="1:3" ht="40" customHeight="1">
+      <c r="A824" s="4"/>
+      <c r="B824" s="5"/>
+      <c r="C824" s="5"/>
+    </row>
+    <row r="825" spans="1:3" ht="40" customHeight="1">
+      <c r="A825" s="4"/>
+      <c r="B825" s="5"/>
+      <c r="C825" s="5"/>
+    </row>
+    <row r="826" spans="1:3" ht="40" customHeight="1">
+      <c r="A826" s="4"/>
+      <c r="B826" s="5"/>
+      <c r="C826" s="5"/>
+    </row>
+    <row r="827" spans="1:3" ht="40" customHeight="1">
+      <c r="A827" s="4"/>
+      <c r="B827" s="5"/>
+      <c r="C827" s="5"/>
+    </row>
+    <row r="828" spans="1:3" ht="40" customHeight="1">
+      <c r="A828" s="4"/>
+      <c r="B828" s="5"/>
+      <c r="C828" s="5"/>
+    </row>
+    <row r="829" spans="1:3" ht="40" customHeight="1">
+      <c r="A829" s="4"/>
+      <c r="B829" s="5"/>
+      <c r="C829" s="5"/>
+    </row>
+    <row r="830" spans="1:3" ht="40" customHeight="1">
+      <c r="A830" s="4"/>
+      <c r="B830" s="5"/>
+      <c r="C830" s="5"/>
+    </row>
+    <row r="831" spans="1:3" ht="40" customHeight="1">
+      <c r="A831" s="4"/>
+      <c r="B831" s="5"/>
+      <c r="C831" s="5"/>
+    </row>
+    <row r="832" spans="1:3" ht="40" customHeight="1">
+      <c r="A832" s="4"/>
+      <c r="B832" s="5"/>
+      <c r="C832" s="5"/>
+    </row>
+    <row r="833" spans="1:3" ht="40" customHeight="1">
+      <c r="A833" s="4"/>
+      <c r="B833" s="5"/>
+      <c r="C833" s="5"/>
+    </row>
+    <row r="834" spans="1:3" ht="40" customHeight="1">
+      <c r="A834" s="4"/>
+      <c r="B834" s="5"/>
+      <c r="C834" s="5"/>
+    </row>
+    <row r="835" spans="1:3" ht="40" customHeight="1">
+      <c r="A835" s="4"/>
+      <c r="B835" s="5"/>
+      <c r="C835" s="5"/>
+    </row>
+    <row r="836" spans="1:3" ht="40" customHeight="1">
+      <c r="A836" s="4"/>
+      <c r="B836" s="5"/>
+      <c r="C836" s="5"/>
+    </row>
+    <row r="837" spans="1:3" ht="40" customHeight="1">
+      <c r="A837" s="4"/>
+      <c r="B837" s="5"/>
+      <c r="C837" s="5"/>
+    </row>
+    <row r="838" spans="1:3" ht="40" customHeight="1">
+      <c r="A838" s="4"/>
+      <c r="B838" s="5"/>
+      <c r="C838" s="5"/>
+    </row>
+    <row r="839" spans="1:3" ht="40" customHeight="1">
+      <c r="A839" s="4"/>
+      <c r="B839" s="5"/>
+      <c r="C839" s="5"/>
+    </row>
+    <row r="840" spans="1:3" ht="40" customHeight="1">
+      <c r="A840" s="4"/>
+      <c r="B840" s="5"/>
+      <c r="C840" s="5"/>
+    </row>
+    <row r="841" spans="1:3" ht="40" customHeight="1">
+      <c r="A841" s="4"/>
+      <c r="B841" s="5"/>
+      <c r="C841" s="5"/>
+    </row>
+    <row r="842" spans="1:3" ht="40" customHeight="1">
+      <c r="A842" s="4"/>
+      <c r="B842" s="5"/>
+      <c r="C842" s="5"/>
+    </row>
+    <row r="843" spans="1:3" ht="40" customHeight="1">
+      <c r="A843" s="4"/>
+      <c r="B843" s="5"/>
+      <c r="C843" s="5"/>
+    </row>
+    <row r="844" spans="1:3" ht="40" customHeight="1">
+      <c r="A844" s="4"/>
+      <c r="B844" s="5"/>
+      <c r="C844" s="5"/>
+    </row>
+    <row r="845" spans="1:3" ht="40" customHeight="1">
+      <c r="A845" s="4"/>
+      <c r="B845" s="5"/>
+      <c r="C845" s="5"/>
+    </row>
+    <row r="846" spans="1:3" ht="40" customHeight="1">
+      <c r="A846" s="4"/>
+      <c r="B846" s="5"/>
+      <c r="C846" s="5"/>
+    </row>
+    <row r="847" spans="1:3" ht="40" customHeight="1">
+      <c r="A847" s="4"/>
+      <c r="B847" s="5"/>
+      <c r="C847" s="5"/>
+    </row>
+    <row r="848" spans="1:3" ht="40" customHeight="1">
+      <c r="A848" s="4"/>
+      <c r="B848" s="5"/>
+      <c r="C848" s="5"/>
+    </row>
+    <row r="849" spans="1:3" ht="40" customHeight="1">
+      <c r="A849" s="4"/>
+      <c r="B849" s="5"/>
+      <c r="C849" s="5"/>
+    </row>
+    <row r="850" spans="1:3" ht="40" customHeight="1">
+      <c r="A850" s="4"/>
+      <c r="B850" s="5"/>
+      <c r="C850" s="5"/>
+    </row>
+    <row r="851" spans="1:3" ht="40" customHeight="1">
+      <c r="A851" s="4"/>
+      <c r="B851" s="5"/>
+      <c r="C851" s="5"/>
+    </row>
+    <row r="852" spans="1:3" ht="40" customHeight="1">
+      <c r="A852" s="4"/>
+      <c r="B852" s="5"/>
+      <c r="C852" s="5"/>
+    </row>
+    <row r="853" spans="1:3" ht="40" customHeight="1">
+      <c r="A853" s="4"/>
+      <c r="B853" s="5"/>
+      <c r="C853" s="5"/>
+    </row>
+    <row r="854" spans="1:3" ht="40" customHeight="1">
+      <c r="A854" s="4"/>
+      <c r="B854" s="5"/>
+      <c r="C854" s="5"/>
+    </row>
+    <row r="855" spans="1:3" ht="40" customHeight="1">
+      <c r="A855" s="4"/>
+      <c r="B855" s="5"/>
+      <c r="C855" s="5"/>
+    </row>
+    <row r="856" spans="1:3" ht="40" customHeight="1">
+      <c r="A856" s="4"/>
+      <c r="B856" s="5"/>
+      <c r="C856" s="5"/>
+    </row>
+    <row r="857" spans="1:3" ht="40" customHeight="1">
+      <c r="A857" s="4"/>
+      <c r="B857" s="5"/>
+      <c r="C857" s="5"/>
+    </row>
+    <row r="858" spans="1:3" ht="40" customHeight="1">
+      <c r="A858" s="4"/>
+      <c r="B858" s="5"/>
+      <c r="C858" s="5"/>
+    </row>
+    <row r="859" spans="1:3" ht="40" customHeight="1">
+      <c r="A859" s="4"/>
+      <c r="B859" s="5"/>
+      <c r="C859" s="5"/>
+    </row>
+    <row r="860" spans="1:3" ht="40" customHeight="1">
+      <c r="A860" s="4"/>
+      <c r="B860" s="5"/>
+      <c r="C860" s="5"/>
+    </row>
+    <row r="861" spans="1:3" ht="40" customHeight="1">
+      <c r="A861" s="4"/>
+      <c r="B861" s="5"/>
+      <c r="C861" s="5"/>
+    </row>
+    <row r="862" spans="1:3" ht="40" customHeight="1">
+      <c r="A862" s="4"/>
+      <c r="B862" s="5"/>
+      <c r="C862" s="5"/>
+    </row>
+    <row r="863" spans="1:3" ht="40" customHeight="1">
+      <c r="A863" s="4"/>
+      <c r="B863" s="5"/>
+      <c r="C863" s="5"/>
+    </row>
+    <row r="864" spans="1:3" ht="40" customHeight="1">
+      <c r="A864" s="4"/>
+      <c r="B864" s="5"/>
+      <c r="C864" s="5"/>
+    </row>
+    <row r="865" spans="1:3" ht="40" customHeight="1">
+      <c r="A865" s="4"/>
+      <c r="B865" s="5"/>
+      <c r="C865" s="5"/>
+    </row>
+    <row r="866" spans="1:3" ht="40" customHeight="1">
+      <c r="A866" s="4"/>
+      <c r="B866" s="5"/>
+      <c r="C866" s="5"/>
+    </row>
+    <row r="867" spans="1:3" ht="40" customHeight="1">
+      <c r="A867" s="4"/>
+      <c r="B867" s="5"/>
+      <c r="C867" s="5"/>
+    </row>
+    <row r="868" spans="1:3" ht="40" customHeight="1">
+      <c r="A868" s="4"/>
+      <c r="B868" s="5"/>
+      <c r="C868" s="5"/>
+    </row>
+    <row r="869" spans="1:3" ht="40" customHeight="1">
+      <c r="A869" s="4"/>
+      <c r="B869" s="5"/>
+      <c r="C869" s="5"/>
+    </row>
+    <row r="870" spans="1:3" ht="40" customHeight="1">
+      <c r="A870" s="4"/>
+      <c r="B870" s="5"/>
+      <c r="C870" s="5"/>
+    </row>
+    <row r="871" spans="1:3" ht="40" customHeight="1">
+      <c r="A871" s="4"/>
+      <c r="B871" s="5"/>
+      <c r="C871" s="5"/>
+    </row>
+    <row r="872" spans="1:3" ht="40" customHeight="1">
+      <c r="A872" s="4"/>
+      <c r="B872" s="5"/>
+      <c r="C872" s="5"/>
+    </row>
+    <row r="873" spans="1:3" ht="40" customHeight="1">
+      <c r="A873" s="4"/>
+      <c r="B873" s="5"/>
+      <c r="C873" s="5"/>
+    </row>
+    <row r="874" spans="1:3" ht="40" customHeight="1">
+      <c r="A874" s="4"/>
+      <c r="B874" s="5"/>
+      <c r="C874" s="5"/>
+    </row>
+    <row r="875" spans="1:3" ht="40" customHeight="1">
+      <c r="A875" s="4"/>
+      <c r="B875" s="5"/>
+      <c r="C875" s="5"/>
+    </row>
+    <row r="876" spans="1:3" ht="40" customHeight="1">
+      <c r="A876" s="4"/>
+      <c r="B876" s="5"/>
+      <c r="C876" s="5"/>
+    </row>
+    <row r="877" spans="1:3" ht="40" customHeight="1">
+      <c r="A877" s="4"/>
+      <c r="B877" s="5"/>
+      <c r="C877" s="5"/>
+    </row>
+    <row r="878" spans="1:3" ht="40" customHeight="1">
+      <c r="A878" s="4"/>
+      <c r="B878" s="5"/>
+      <c r="C878" s="5"/>
+    </row>
+    <row r="879" spans="1:3" ht="40" customHeight="1">
+      <c r="A879" s="4"/>
+      <c r="B879" s="5"/>
+      <c r="C879" s="5"/>
+    </row>
+    <row r="880" spans="1:3" ht="40" customHeight="1">
+      <c r="A880" s="4"/>
+      <c r="B880" s="5"/>
+      <c r="C880" s="5"/>
+    </row>
+    <row r="881" spans="1:3" ht="40" customHeight="1">
+      <c r="A881" s="4"/>
+      <c r="B881" s="5"/>
+      <c r="C881" s="5"/>
+    </row>
+    <row r="882" spans="1:3" ht="40" customHeight="1">
+      <c r="A882" s="4"/>
+      <c r="B882" s="5"/>
+      <c r="C882" s="5"/>
+    </row>
+    <row r="883" spans="1:3" ht="40" customHeight="1">
+      <c r="A883" s="4"/>
+      <c r="B883" s="5"/>
+      <c r="C883" s="5"/>
+    </row>
+    <row r="884" spans="1:3" ht="40" customHeight="1">
+      <c r="A884" s="4"/>
+      <c r="B884" s="5"/>
+      <c r="C884" s="5"/>
+    </row>
+    <row r="885" spans="1:3" ht="40" customHeight="1">
+      <c r="A885" s="4"/>
+      <c r="B885" s="5"/>
+      <c r="C885" s="5"/>
+    </row>
+    <row r="886" spans="1:3" ht="40" customHeight="1">
+      <c r="A886" s="4"/>
+      <c r="B886" s="5"/>
+      <c r="C886" s="5"/>
+    </row>
+    <row r="887" spans="1:3" ht="40" customHeight="1">
+      <c r="A887" s="4"/>
+      <c r="B887" s="5"/>
+      <c r="C887" s="5"/>
+    </row>
+    <row r="888" spans="1:3" ht="40" customHeight="1">
+      <c r="A888" s="4"/>
+      <c r="B888" s="5"/>
+      <c r="C888" s="5"/>
+    </row>
+    <row r="889" spans="1:3" ht="40" customHeight="1">
+      <c r="A889" s="4"/>
+      <c r="B889" s="5"/>
+      <c r="C889" s="5"/>
+    </row>
+    <row r="890" spans="1:3" ht="40" customHeight="1">
+      <c r="A890" s="4"/>
+      <c r="B890" s="5"/>
+      <c r="C890" s="5"/>
+    </row>
+    <row r="891" spans="1:3" ht="40" customHeight="1">
+      <c r="A891" s="4"/>
+      <c r="B891" s="5"/>
+      <c r="C891" s="5"/>
+    </row>
+    <row r="892" spans="1:3" ht="40" customHeight="1">
+      <c r="A892" s="4"/>
+      <c r="B892" s="5"/>
+      <c r="C892" s="5"/>
+    </row>
+    <row r="893" spans="1:3" ht="40" customHeight="1">
+      <c r="A893" s="4"/>
+      <c r="B893" s="5"/>
+      <c r="C893" s="5"/>
+    </row>
+    <row r="894" spans="1:3" ht="40" customHeight="1">
+      <c r="A894" s="4"/>
+      <c r="B894" s="5"/>
+      <c r="C894" s="5"/>
+    </row>
+    <row r="895" spans="1:3" ht="40" customHeight="1">
+      <c r="A895" s="4"/>
+      <c r="B895" s="5"/>
+      <c r="C895" s="5"/>
+    </row>
+    <row r="896" spans="1:3" ht="40" customHeight="1">
+      <c r="A896" s="4"/>
+      <c r="B896" s="5"/>
+      <c r="C896" s="5"/>
+    </row>
+    <row r="897" spans="1:3" ht="40" customHeight="1">
+      <c r="A897" s="4"/>
+      <c r="B897" s="5"/>
+      <c r="C897" s="5"/>
+    </row>
+    <row r="898" spans="1:3" ht="40" customHeight="1">
+      <c r="A898" s="4"/>
+      <c r="B898" s="5"/>
+      <c r="C898" s="5"/>
+    </row>
+    <row r="899" spans="1:3" ht="40" customHeight="1">
+      <c r="A899" s="4"/>
+      <c r="B899" s="5"/>
+      <c r="C899" s="5"/>
+    </row>
+    <row r="900" spans="1:3" ht="40" customHeight="1">
+      <c r="A900" s="4"/>
+      <c r="B900" s="5"/>
+      <c r="C900" s="5"/>
+    </row>
+    <row r="901" spans="1:3" ht="40" customHeight="1">
+      <c r="A901" s="4"/>
+      <c r="B901" s="5"/>
+      <c r="C901" s="5"/>
+    </row>
+    <row r="902" spans="1:3" ht="40" customHeight="1">
+      <c r="A902" s="4"/>
+      <c r="B902" s="5"/>
+      <c r="C902" s="5"/>
+    </row>
+    <row r="903" spans="1:3" ht="40" customHeight="1">
+      <c r="A903" s="4"/>
+      <c r="B903" s="5"/>
+      <c r="C903" s="5"/>
+    </row>
+    <row r="904" spans="1:3" ht="40" customHeight="1">
+      <c r="A904" s="4"/>
+      <c r="B904" s="5"/>
+      <c r="C904" s="5"/>
+    </row>
+    <row r="905" spans="1:3" ht="40" customHeight="1">
+      <c r="A905" s="4"/>
+      <c r="B905" s="5"/>
+      <c r="C905" s="5"/>
+    </row>
+    <row r="906" spans="1:3" ht="40" customHeight="1">
+      <c r="A906" s="4"/>
+      <c r="B906" s="5"/>
+      <c r="C906" s="5"/>
+    </row>
+    <row r="907" spans="1:3" ht="40" customHeight="1">
+      <c r="A907" s="4"/>
+      <c r="B907" s="5"/>
+      <c r="C907" s="5"/>
+    </row>
+    <row r="908" spans="1:3" ht="40" customHeight="1">
+      <c r="A908" s="4"/>
+      <c r="B908" s="5"/>
+      <c r="C908" s="5"/>
+    </row>
+    <row r="909" spans="1:3" ht="40" customHeight="1">
+      <c r="A909" s="4"/>
+      <c r="B909" s="5"/>
+      <c r="C909" s="5"/>
+    </row>
+    <row r="910" spans="1:3" ht="40" customHeight="1">
+      <c r="A910" s="4"/>
+      <c r="B910" s="5"/>
+      <c r="C910" s="5"/>
+    </row>
+    <row r="911" spans="1:3" ht="40" customHeight="1">
+      <c r="A911" s="4"/>
+      <c r="B911" s="5"/>
+      <c r="C911" s="5"/>
+    </row>
+    <row r="912" spans="1:3" ht="40" customHeight="1">
+      <c r="A912" s="4"/>
+      <c r="B912" s="5"/>
+      <c r="C912" s="5"/>
+    </row>
+    <row r="913" spans="1:3" ht="40" customHeight="1">
+      <c r="A913" s="4"/>
+      <c r="B913" s="5"/>
+      <c r="C913" s="5"/>
+    </row>
+    <row r="914" spans="1:3" ht="40" customHeight="1">
+      <c r="A914" s="4"/>
+      <c r="B914" s="5"/>
+      <c r="C914" s="5"/>
+    </row>
+    <row r="915" spans="1:3" ht="40" customHeight="1">
+      <c r="A915" s="4"/>
+      <c r="B915" s="5"/>
+      <c r="C915" s="5"/>
+    </row>
+    <row r="916" spans="1:3" ht="40" customHeight="1">
+      <c r="A916" s="4"/>
+      <c r="B916" s="5"/>
+      <c r="C916" s="5"/>
+    </row>
+    <row r="917" spans="1:3" ht="40" customHeight="1">
+      <c r="A917" s="4"/>
+      <c r="B917" s="5"/>
+      <c r="C917" s="5"/>
+    </row>
+    <row r="918" spans="1:3" ht="40" customHeight="1">
+      <c r="A918" s="4"/>
+      <c r="B918" s="5"/>
+      <c r="C918" s="5"/>
+    </row>
+    <row r="919" spans="1:3" ht="40" customHeight="1">
+      <c r="A919" s="4"/>
+      <c r="B919" s="5"/>
+      <c r="C919" s="5"/>
+    </row>
+    <row r="920" spans="1:3" ht="40" customHeight="1">
+      <c r="A920" s="4"/>
+      <c r="B920" s="5"/>
+      <c r="C920" s="5"/>
+    </row>
+    <row r="921" spans="1:3" ht="40" customHeight="1">
+      <c r="A921" s="4"/>
+      <c r="B921" s="5"/>
+      <c r="C921" s="5"/>
+    </row>
+    <row r="922" spans="1:3" ht="40" customHeight="1">
+      <c r="A922" s="4"/>
+      <c r="B922" s="5"/>
+      <c r="C922" s="5"/>
+    </row>
+    <row r="923" spans="1:3" ht="40" customHeight="1">
+      <c r="A923" s="4"/>
+      <c r="B923" s="5"/>
+      <c r="C923" s="5"/>
+    </row>
+    <row r="924" spans="1:3" ht="40" customHeight="1">
+      <c r="A924" s="4"/>
+      <c r="B924" s="5"/>
+      <c r="C924" s="5"/>
+    </row>
+    <row r="925" spans="1:3" ht="40" customHeight="1">
+      <c r="A925" s="4"/>
+      <c r="B925" s="5"/>
+      <c r="C925" s="5"/>
+    </row>
+    <row r="926" spans="1:3" ht="40" customHeight="1">
+      <c r="A926" s="4"/>
+      <c r="B926" s="5"/>
+      <c r="C926" s="5"/>
+    </row>
+    <row r="927" spans="1:3" ht="40" customHeight="1">
+      <c r="A927" s="4"/>
+      <c r="B927" s="5"/>
+      <c r="C927" s="5"/>
+    </row>
+    <row r="928" spans="1:3" ht="40" customHeight="1">
+      <c r="A928" s="4"/>
+      <c r="B928" s="5"/>
+      <c r="C928" s="5"/>
+    </row>
+    <row r="929" spans="1:3" ht="40" customHeight="1">
+      <c r="A929" s="4"/>
+      <c r="B929" s="5"/>
+      <c r="C929" s="5"/>
+    </row>
+    <row r="930" spans="1:3" ht="40" customHeight="1">
+      <c r="A930" s="4"/>
+      <c r="B930" s="5"/>
+      <c r="C930" s="5"/>
+    </row>
+    <row r="931" spans="1:3" ht="40" customHeight="1">
+      <c r="A931" s="4"/>
+      <c r="B931" s="5"/>
+      <c r="C931" s="5"/>
+    </row>
+    <row r="932" spans="1:3" ht="40" customHeight="1">
+      <c r="A932" s="4"/>
+      <c r="B932" s="5"/>
+      <c r="C932" s="5"/>
+    </row>
+    <row r="933" spans="1:3" ht="40" customHeight="1">
+      <c r="A933" s="4"/>
+      <c r="B933" s="5"/>
+      <c r="C933" s="5"/>
+    </row>
+    <row r="934" spans="1:3" ht="40" customHeight="1">
+      <c r="A934" s="4"/>
+      <c r="B934" s="5"/>
+      <c r="C934" s="5"/>
+    </row>
+    <row r="935" spans="1:3" ht="40" customHeight="1">
+      <c r="A935" s="4"/>
+      <c r="B935" s="5"/>
+      <c r="C935" s="5"/>
+    </row>
+    <row r="936" spans="1:3" ht="40" customHeight="1">
+      <c r="A936" s="4"/>
+      <c r="B936" s="5"/>
+      <c r="C936" s="5"/>
+    </row>
+    <row r="937" spans="1:3" ht="40" customHeight="1">
+      <c r="A937" s="4"/>
+      <c r="B937" s="5"/>
+      <c r="C937" s="5"/>
+    </row>
+    <row r="938" spans="1:3" ht="40" customHeight="1">
+      <c r="A938" s="4"/>
+      <c r="B938" s="5"/>
+      <c r="C938" s="5"/>
+    </row>
+    <row r="939" spans="1:3" ht="40" customHeight="1">
+      <c r="A939" s="4"/>
+      <c r="B939" s="5"/>
+      <c r="C939" s="5"/>
+    </row>
+    <row r="940" spans="1:3" ht="40" customHeight="1">
+      <c r="A940" s="4"/>
+      <c r="B940" s="5"/>
+      <c r="C940" s="5"/>
+    </row>
+    <row r="941" spans="1:3" ht="40" customHeight="1">
+      <c r="A941" s="4"/>
+      <c r="B941" s="5"/>
+      <c r="C941" s="5"/>
+    </row>
+    <row r="942" spans="1:3" ht="40" customHeight="1">
+      <c r="A942" s="4"/>
+      <c r="B942" s="5"/>
+      <c r="C942" s="5"/>
+    </row>
+    <row r="943" spans="1:3" ht="40" customHeight="1">
+      <c r="A943" s="4"/>
+      <c r="B943" s="5"/>
+      <c r="C943" s="5"/>
+    </row>
+    <row r="944" spans="1:3" ht="40" customHeight="1">
+      <c r="A944" s="4"/>
+      <c r="B944" s="5"/>
+      <c r="C944" s="5"/>
+    </row>
+    <row r="945" spans="1:3" ht="40" customHeight="1">
+      <c r="A945" s="4"/>
+      <c r="B945" s="5"/>
+      <c r="C945" s="5"/>
+    </row>
+    <row r="946" spans="1:3" ht="40" customHeight="1">
+      <c r="A946" s="4"/>
+      <c r="B946" s="5"/>
+      <c r="C946" s="5"/>
+    </row>
+    <row r="947" spans="1:3" ht="40" customHeight="1">
+      <c r="A947" s="4"/>
+      <c r="B947" s="5"/>
+      <c r="C947" s="5"/>
+    </row>
+    <row r="948" spans="1:3" ht="40" customHeight="1">
+      <c r="A948" s="4"/>
+      <c r="B948" s="5"/>
+      <c r="C948" s="5"/>
+    </row>
+    <row r="949" spans="1:3" ht="40" customHeight="1">
+      <c r="A949" s="4"/>
+      <c r="B949" s="5"/>
+      <c r="C949" s="5"/>
+    </row>
+    <row r="950" spans="1:3" ht="40" customHeight="1">
+      <c r="A950" s="4"/>
+      <c r="B950" s="5"/>
+      <c r="C950" s="5"/>
+    </row>
+    <row r="951" spans="1:3" ht="40" customHeight="1">
+      <c r="A951" s="4"/>
+      <c r="B951" s="5"/>
+      <c r="C951" s="5"/>
+    </row>
+    <row r="952" spans="1:3" ht="40" customHeight="1">
+      <c r="A952" s="4"/>
+      <c r="B952" s="5"/>
+      <c r="C952" s="5"/>
+    </row>
+    <row r="953" spans="1:3" ht="40" customHeight="1">
+      <c r="A953" s="4"/>
+      <c r="B953" s="5"/>
+      <c r="C953" s="5"/>
+    </row>
+    <row r="954" spans="1:3" ht="40" customHeight="1">
+      <c r="A954" s="4"/>
+      <c r="B954" s="5"/>
+      <c r="C954" s="5"/>
+    </row>
+    <row r="955" spans="1:3" ht="40" customHeight="1">
+      <c r="A955" s="4"/>
+      <c r="B955" s="5"/>
+      <c r="C955" s="5"/>
+    </row>
+    <row r="956" spans="1:3" ht="40" customHeight="1">
+      <c r="A956" s="4"/>
+      <c r="B956" s="5"/>
+      <c r="C956" s="5"/>
+    </row>
+    <row r="957" spans="1:3" ht="40" customHeight="1">
+      <c r="A957" s="4"/>
+      <c r="B957" s="5"/>
+      <c r="C957" s="5"/>
+    </row>
+    <row r="958" spans="1:3" ht="40" customHeight="1">
+      <c r="A958" s="4"/>
+      <c r="B958" s="5"/>
+      <c r="C958" s="5"/>
+    </row>
+    <row r="959" spans="1:3" ht="40" customHeight="1">
+      <c r="A959" s="4"/>
+      <c r="B959" s="5"/>
+      <c r="C959" s="5"/>
+    </row>
+    <row r="960" spans="1:3" ht="40" customHeight="1">
+      <c r="A960" s="4"/>
+      <c r="B960" s="5"/>
+      <c r="C960" s="5"/>
+    </row>
+    <row r="961" spans="1:3" ht="40" customHeight="1">
+      <c r="A961" s="4"/>
+      <c r="B961" s="5"/>
+      <c r="C961" s="5"/>
+    </row>
+    <row r="962" spans="1:3" ht="40" customHeight="1">
+      <c r="A962" s="4"/>
+      <c r="B962" s="5"/>
+      <c r="C962" s="5"/>
+    </row>
+    <row r="963" spans="1:3" ht="40" customHeight="1">
+      <c r="A963" s="4"/>
+      <c r="B963" s="5"/>
+      <c r="C963" s="5"/>
+    </row>
+    <row r="964" spans="1:3" ht="40" customHeight="1">
+      <c r="A964" s="4"/>
+      <c r="B964" s="5"/>
+      <c r="C964" s="5"/>
+    </row>
+    <row r="965" spans="1:3" ht="40" customHeight="1">
+      <c r="A965" s="4"/>
+      <c r="B965" s="5"/>
+      <c r="C965" s="5"/>
+    </row>
+    <row r="966" spans="1:3" ht="40" customHeight="1">
+      <c r="A966" s="4"/>
+      <c r="B966" s="5"/>
+      <c r="C966" s="5"/>
+    </row>
+    <row r="967" spans="1:3" ht="40" customHeight="1">
+      <c r="A967" s="4"/>
+      <c r="B967" s="5"/>
+      <c r="C967" s="5"/>
+    </row>
+    <row r="968" spans="1:3" ht="40" customHeight="1">
+      <c r="A968" s="4"/>
+      <c r="B968" s="5"/>
+      <c r="C968" s="5"/>
+    </row>
+    <row r="969" spans="1:3" ht="40" customHeight="1">
+      <c r="A969" s="4"/>
+      <c r="B969" s="5"/>
+      <c r="C969" s="5"/>
+    </row>
+    <row r="970" spans="1:3" ht="40" customHeight="1">
+      <c r="A970" s="4"/>
+      <c r="B970" s="5"/>
+      <c r="C970" s="5"/>
+    </row>
+    <row r="971" spans="1:3" ht="40" customHeight="1">
+      <c r="A971" s="4"/>
+      <c r="B971" s="5"/>
+      <c r="C971" s="5"/>
+    </row>
+    <row r="972" spans="1:3" ht="40" customHeight="1">
+      <c r="A972" s="4"/>
+      <c r="B972" s="5"/>
+      <c r="C972" s="5"/>
+    </row>
+    <row r="973" spans="1:3" ht="40" customHeight="1">
+      <c r="A973" s="4"/>
+      <c r="B973" s="5"/>
+      <c r="C973" s="5"/>
+    </row>
+    <row r="974" spans="1:3" ht="40" customHeight="1">
+      <c r="A974" s="4"/>
+      <c r="B974" s="5"/>
+      <c r="C974" s="5"/>
+    </row>
+    <row r="975" spans="1:3" ht="40" customHeight="1">
+      <c r="A975" s="4"/>
+      <c r="B975" s="5"/>
+      <c r="C975" s="5"/>
+    </row>
+    <row r="976" spans="1:3" ht="40" customHeight="1">
+      <c r="A976" s="4"/>
+      <c r="B976" s="5"/>
+      <c r="C976" s="5"/>
+    </row>
+    <row r="977" spans="1:3" ht="40" customHeight="1">
+      <c r="A977" s="4"/>
+      <c r="B977" s="5"/>
+      <c r="C977" s="5"/>
+    </row>
+    <row r="978" spans="1:3" ht="40" customHeight="1">
+      <c r="A978" s="4"/>
+      <c r="B978" s="5"/>
+      <c r="C978" s="5"/>
+    </row>
+    <row r="979" spans="1:3" ht="40" customHeight="1">
+      <c r="A979" s="4"/>
+      <c r="B979" s="5"/>
+      <c r="C979" s="5"/>
+    </row>
+    <row r="980" spans="1:3" ht="40" customHeight="1">
+      <c r="A980" s="4"/>
+      <c r="B980" s="5"/>
+      <c r="C980" s="5"/>
+    </row>
+    <row r="981" spans="1:3" ht="40" customHeight="1">
+      <c r="A981" s="4"/>
+      <c r="B981" s="5"/>
+      <c r="C981" s="5"/>
+    </row>
+    <row r="982" spans="1:3" ht="40" customHeight="1">
+      <c r="A982" s="4"/>
+      <c r="B982" s="5"/>
+      <c r="C982" s="5"/>
+    </row>
+    <row r="983" spans="1:3" ht="40" customHeight="1">
+      <c r="A983" s="4"/>
+      <c r="B983" s="5"/>
+      <c r="C983" s="5"/>
+    </row>
+    <row r="984" spans="1:3" ht="40" customHeight="1">
+      <c r="A984" s="4"/>
+      <c r="B984" s="5"/>
+      <c r="C984" s="5"/>
+    </row>
+    <row r="985" spans="1:3" ht="40" customHeight="1">
+      <c r="A985" s="4"/>
+      <c r="B985" s="5"/>
+      <c r="C985" s="5"/>
+    </row>
+    <row r="986" spans="1:3" ht="40" customHeight="1">
+      <c r="A986" s="4"/>
+      <c r="B986" s="5"/>
+      <c r="C986" s="5"/>
+    </row>
+    <row r="987" spans="1:3" ht="40" customHeight="1">
+      <c r="A987" s="4"/>
+      <c r="B987" s="5"/>
+      <c r="C987" s="5"/>
+    </row>
+    <row r="988" spans="1:3" ht="40" customHeight="1">
+      <c r="A988" s="4"/>
+      <c r="B988" s="5"/>
+      <c r="C988" s="5"/>
+    </row>
+    <row r="989" spans="1:3" ht="40" customHeight="1">
+      <c r="A989" s="4"/>
+      <c r="B989" s="5"/>
+      <c r="C989" s="5"/>
+    </row>
+    <row r="990" spans="1:3" ht="40" customHeight="1">
+      <c r="A990" s="4"/>
+      <c r="B990" s="5"/>
+      <c r="C990" s="5"/>
+    </row>
+    <row r="991" spans="1:3" ht="40" customHeight="1">
+      <c r="A991" s="4"/>
+      <c r="B991" s="5"/>
+      <c r="C991" s="5"/>
+    </row>
+    <row r="992" spans="1:3" ht="40" customHeight="1">
+      <c r="A992" s="4"/>
+      <c r="B992" s="5"/>
+      <c r="C992" s="5"/>
+    </row>
+    <row r="993" spans="1:3" ht="40" customHeight="1">
+      <c r="A993" s="4"/>
+      <c r="B993" s="5"/>
+      <c r="C993" s="5"/>
+    </row>
+    <row r="994" spans="1:3" ht="40" customHeight="1">
+      <c r="A994" s="4"/>
+      <c r="B994" s="5"/>
+      <c r="C994" s="5"/>
+    </row>
+    <row r="995" spans="1:3" ht="40" customHeight="1">
+      <c r="A995" s="4"/>
+      <c r="B995" s="5"/>
+      <c r="C995" s="5"/>
+    </row>
+    <row r="996" spans="1:3" ht="40" customHeight="1">
+      <c r="A996" s="4"/>
+      <c r="B996" s="5"/>
+      <c r="C996" s="5"/>
+    </row>
+    <row r="997" spans="1:3" ht="40" customHeight="1">
+      <c r="A997" s="4"/>
+      <c r="B997" s="5"/>
+      <c r="C997" s="5"/>
+    </row>
+    <row r="998" spans="1:3" ht="40" customHeight="1">
+      <c r="A998" s="4"/>
+      <c r="B998" s="5"/>
+      <c r="C998" s="5"/>
+    </row>
+    <row r="999" spans="1:3" ht="40" customHeight="1">
+      <c r="A999" s="4"/>
+      <c r="B999" s="5"/>
+      <c r="C999" s="5"/>
+    </row>
+    <row r="1000" spans="1:3" ht="40" customHeight="1">
+      <c r="A1000" s="4"/>
+      <c r="B1000" s="5"/>
+      <c r="C1000" s="5"/>
+    </row>
+    <row r="1001" spans="1:3" ht="40" customHeight="1">
+      <c r="A1001" s="4"/>
+      <c r="B1001" s="5"/>
+      <c r="C1001" s="5"/>
+    </row>
+    <row r="1002" spans="1:3" ht="40" customHeight="1">
+      <c r="A1002" s="4"/>
+      <c r="B1002" s="5"/>
+      <c r="C1002" s="5"/>
+    </row>
+    <row r="1003" spans="1:3" ht="40" customHeight="1">
+      <c r="A1003" s="4"/>
+      <c r="B1003" s="5"/>
+      <c r="C1003" s="5"/>
+    </row>
+    <row r="1004" spans="1:3" ht="40" customHeight="1">
+      <c r="A1004" s="4"/>
+      <c r="B1004" s="5"/>
+      <c r="C1004" s="5"/>
+    </row>
+    <row r="1005" spans="1:3" ht="40" customHeight="1">
+      <c r="A1005" s="4"/>
+      <c r="B1005" s="5"/>
+      <c r="C1005" s="5"/>
+    </row>
+    <row r="1006" spans="1:3" ht="40" customHeight="1">
+      <c r="A1006" s="4"/>
+      <c r="B1006" s="5"/>
+      <c r="C1006" s="5"/>
+    </row>
+    <row r="1007" spans="1:3" ht="40" customHeight="1">
+      <c r="A1007" s="4"/>
+      <c r="B1007" s="5"/>
+      <c r="C1007" s="5"/>
+    </row>
+    <row r="1008" spans="1:3" ht="40" customHeight="1">
+      <c r="A1008" s="4"/>
+      <c r="B1008" s="5"/>
+      <c r="C1008" s="5"/>
+    </row>
+    <row r="1009" spans="1:3" ht="40" customHeight="1">
+      <c r="A1009" s="4"/>
+      <c r="B1009" s="5"/>
+      <c r="C1009" s="5"/>
+    </row>
+    <row r="1010" spans="1:3" ht="40" customHeight="1">
+      <c r="A1010" s="4"/>
+      <c r="B1010" s="5"/>
+      <c r="C1010" s="5"/>
+    </row>
+    <row r="1011" spans="1:3" ht="40" customHeight="1">
+      <c r="A1011" s="4"/>
+      <c r="B1011" s="5"/>
+      <c r="C1011" s="5"/>
+    </row>
+    <row r="1012" spans="1:3" ht="40" customHeight="1">
+      <c r="A1012" s="4"/>
+      <c r="B1012" s="5"/>
+      <c r="C1012" s="5"/>
+    </row>
+    <row r="1013" spans="1:3" ht="40" customHeight="1">
+      <c r="A1013" s="4"/>
+      <c r="B1013" s="5"/>
+      <c r="C1013" s="5"/>
+    </row>
+    <row r="1014" spans="1:3" ht="40" customHeight="1">
+      <c r="A1014" s="4"/>
+      <c r="B1014" s="5"/>
+      <c r="C1014" s="5"/>
+    </row>
+    <row r="1015" spans="1:3" ht="40" customHeight="1">
+      <c r="A1015" s="4"/>
+      <c r="B1015" s="5"/>
+      <c r="C1015" s="5"/>
+    </row>
+    <row r="1016" spans="1:3" ht="40" customHeight="1">
+      <c r="A1016" s="4"/>
+      <c r="B1016" s="5"/>
+      <c r="C1016" s="5"/>
+    </row>
+    <row r="1017" spans="1:3" ht="40" customHeight="1">
+      <c r="A1017" s="4"/>
+      <c r="B1017" s="5"/>
+      <c r="C1017" s="5"/>
+    </row>
+    <row r="1018" spans="1:3" ht="40" customHeight="1">
+      <c r="A1018" s="4"/>
+      <c r="B1018" s="5"/>
+      <c r="C1018" s="5"/>
+    </row>
+    <row r="1019" spans="1:3" ht="40" customHeight="1">
+      <c r="A1019" s="4"/>
+      <c r="B1019" s="5"/>
+      <c r="C1019" s="5"/>
+    </row>
+    <row r="1020" spans="1:3" ht="40" customHeight="1">
+      <c r="A1020" s="4"/>
+      <c r="B1020" s="5"/>
+      <c r="C1020" s="5"/>
+    </row>
+    <row r="1021" spans="1:3" ht="40" customHeight="1">
+      <c r="A1021" s="4"/>
+      <c r="B1021" s="5"/>
+      <c r="C1021" s="5"/>
+    </row>
+    <row r="1022" spans="1:3" ht="40" customHeight="1">
+      <c r="A1022" s="4"/>
+      <c r="B1022" s="5"/>
+      <c r="C1022" s="5"/>
+    </row>
+    <row r="1023" spans="1:3" ht="40" customHeight="1">
+      <c r="A1023" s="4"/>
+      <c r="B1023" s="5"/>
+      <c r="C1023" s="5"/>
+    </row>
+    <row r="1024" spans="1:3" ht="40" customHeight="1">
+      <c r="A1024" s="4"/>
+      <c r="B1024" s="5"/>
+      <c r="C1024" s="5"/>
+    </row>
+    <row r="1025" spans="1:3" ht="40" customHeight="1">
+      <c r="A1025" s="4"/>
+      <c r="B1025" s="5"/>
+      <c r="C1025" s="5"/>
+    </row>
+    <row r="1026" spans="1:3" ht="40" customHeight="1">
+      <c r="A1026" s="4"/>
+      <c r="B1026" s="5"/>
+      <c r="C1026" s="5"/>
+    </row>
+    <row r="1027" spans="1:3" ht="40" customHeight="1">
+      <c r="A1027" s="4"/>
+      <c r="B1027" s="5"/>
+      <c r="C1027" s="5"/>
+    </row>
+    <row r="1028" spans="1:3" ht="40" customHeight="1">
+      <c r="A1028" s="4"/>
+      <c r="B1028" s="5"/>
+      <c r="C1028" s="5"/>
+    </row>
+    <row r="1029" spans="1:3" ht="40" customHeight="1">
+      <c r="A1029" s="4"/>
+      <c r="B1029" s="5"/>
+      <c r="C1029" s="5"/>
+    </row>
+    <row r="1030" spans="1:3" ht="40" customHeight="1">
+      <c r="A1030" s="4"/>
+      <c r="B1030" s="5"/>
+      <c r="C1030" s="5"/>
+    </row>
+    <row r="1031" spans="1:3" ht="40" customHeight="1">
+      <c r="A1031" s="4"/>
+      <c r="B1031" s="5"/>
+      <c r="C1031" s="5"/>
+    </row>
+    <row r="1032" spans="1:3" ht="40" customHeight="1">
+      <c r="A1032" s="4"/>
+      <c r="B1032" s="5"/>
+      <c r="C1032" s="5"/>
+    </row>
+    <row r="1033" spans="1:3" ht="40" customHeight="1">
+      <c r="A1033" s="4"/>
+      <c r="B1033" s="5"/>
+      <c r="C1033" s="5"/>
+    </row>
+    <row r="1034" spans="1:3" ht="40" customHeight="1">
+      <c r="A1034" s="4"/>
+      <c r="B1034" s="5"/>
+      <c r="C1034" s="5"/>
+    </row>
+    <row r="1035" spans="1:3" ht="40" customHeight="1">
+      <c r="A1035" s="4"/>
+      <c r="B1035" s="5"/>
+      <c r="C1035" s="5"/>
+    </row>
+    <row r="1036" spans="1:3" ht="40" customHeight="1">
+      <c r="A1036" s="4"/>
+      <c r="B1036" s="5"/>
+      <c r="C1036" s="5"/>
+    </row>
+    <row r="1037" spans="1:3" ht="40" customHeight="1">
+      <c r="A1037" s="4"/>
+      <c r="B1037" s="5"/>
+      <c r="C1037" s="5"/>
+    </row>
+    <row r="1038" spans="1:3" ht="40" customHeight="1">
+      <c r="A1038" s="4"/>
+      <c r="B1038" s="5"/>
+      <c r="C1038" s="5"/>
+    </row>
+    <row r="1039" spans="1:3" ht="40" customHeight="1">
+      <c r="A1039" s="4"/>
+      <c r="B1039" s="5"/>
+      <c r="C1039" s="5"/>
+    </row>
+    <row r="1040" spans="1:3" ht="40" customHeight="1">
+      <c r="A1040" s="4"/>
+      <c r="B1040" s="5"/>
+      <c r="C1040" s="5"/>
+    </row>
+    <row r="1041" spans="1:3" ht="40" customHeight="1">
+      <c r="A1041" s="4"/>
+      <c r="B1041" s="5"/>
+      <c r="C1041" s="5"/>
+    </row>
+    <row r="1042" spans="1:3" ht="40" customHeight="1">
+      <c r="A1042" s="4"/>
+      <c r="B1042" s="5"/>
+      <c r="C1042" s="5"/>
+    </row>
+    <row r="1043" spans="1:3" ht="40" customHeight="1">
+      <c r="A1043" s="4"/>
+      <c r="B1043" s="5"/>
+      <c r="C1043" s="5"/>
+    </row>
+    <row r="1044" spans="1:3" ht="40" customHeight="1">
+      <c r="A1044" s="4"/>
+      <c r="B1044" s="5"/>
+      <c r="C1044" s="5"/>
+    </row>
+    <row r="1045" spans="1:3" ht="40" customHeight="1">
+      <c r="A1045" s="4"/>
+      <c r="B1045" s="5"/>
+      <c r="C1045" s="5"/>
+    </row>
+    <row r="1046" spans="1:3" ht="40" customHeight="1">
+      <c r="A1046" s="4"/>
+      <c r="B1046" s="5"/>
+      <c r="C1046" s="5"/>
+    </row>
+    <row r="1047" spans="1:3" ht="40" customHeight="1">
+      <c r="A1047" s="4"/>
+      <c r="B1047" s="5"/>
+      <c r="C1047" s="5"/>
+    </row>
+    <row r="1048" spans="1:3" ht="40" customHeight="1">
+      <c r="A1048" s="4"/>
+      <c r="B1048" s="5"/>
+      <c r="C1048" s="5"/>
+    </row>
+    <row r="1049" spans="1:3" ht="40" customHeight="1">
+      <c r="A1049" s="4"/>
+      <c r="B1049" s="5"/>
+      <c r="C1049" s="5"/>
+    </row>
+    <row r="1050" spans="1:3" ht="40" customHeight="1">
+      <c r="A1050" s="4"/>
+      <c r="B1050" s="5"/>
+      <c r="C1050" s="5"/>
+    </row>
+    <row r="1051" spans="1:3" ht="40" customHeight="1">
+      <c r="A1051" s="4"/>
+      <c r="B1051" s="5"/>
+      <c r="C1051" s="5"/>
+    </row>
+    <row r="1052" spans="1:3" ht="40" customHeight="1">
+      <c r="A1052" s="4"/>
+      <c r="B1052" s="5"/>
+      <c r="C1052" s="5"/>
+    </row>
+    <row r="1053" spans="1:3" ht="40" customHeight="1">
+      <c r="A1053" s="4"/>
+      <c r="B1053" s="5"/>
+      <c r="C1053" s="5"/>
+    </row>
+    <row r="1054" spans="1:3" ht="40" customHeight="1">
+      <c r="A1054" s="4"/>
+      <c r="B1054" s="5"/>
+      <c r="C1054" s="5"/>
+    </row>
+    <row r="1055" spans="1:3" ht="40" customHeight="1">
+      <c r="A1055" s="4"/>
+      <c r="B1055" s="5"/>
+      <c r="C1055" s="5"/>
+    </row>
+    <row r="1056" spans="1:3" ht="40" customHeight="1">
+      <c r="A1056" s="4"/>
+      <c r="B1056" s="5"/>
+      <c r="C1056" s="5"/>
+    </row>
+    <row r="1057" spans="1:3" ht="40" customHeight="1">
+      <c r="A1057" s="4"/>
+      <c r="B1057" s="5"/>
+      <c r="C1057" s="5"/>
+    </row>
+    <row r="1058" spans="1:3" ht="40" customHeight="1">
+      <c r="A1058" s="4"/>
+      <c r="B1058" s="5"/>
+      <c r="C1058" s="5"/>
+    </row>
+    <row r="1059" spans="1:3" ht="40" customHeight="1">
+      <c r="A1059" s="4"/>
+      <c r="B1059" s="5"/>
+      <c r="C1059" s="5"/>
+    </row>
+    <row r="1060" spans="1:3" ht="40" customHeight="1">
+      <c r="A1060" s="4"/>
+      <c r="B1060" s="5"/>
+      <c r="C1060" s="5"/>
+    </row>
+    <row r="1061" spans="1:3" ht="40" customHeight="1">
+      <c r="A1061" s="4"/>
+      <c r="B1061" s="5"/>
+      <c r="C1061" s="5"/>
+    </row>
+    <row r="1062" spans="1:3" ht="40" customHeight="1">
+      <c r="A1062" s="4"/>
+      <c r="B1062" s="5"/>
+      <c r="C1062" s="5"/>
+    </row>
+    <row r="1063" spans="1:3" ht="40" customHeight="1">
+      <c r="A1063" s="4"/>
+      <c r="B1063" s="5"/>
+      <c r="C1063" s="5"/>
+    </row>
+    <row r="1064" spans="1:3" ht="40" customHeight="1">
+      <c r="A1064" s="4"/>
+      <c r="B1064" s="5"/>
+      <c r="C1064" s="5"/>
+    </row>
+    <row r="1065" spans="1:3" ht="40" customHeight="1">
+      <c r="A1065" s="4"/>
+      <c r="B1065" s="5"/>
+      <c r="C1065" s="5"/>
+    </row>
+    <row r="1066" spans="1:3" ht="40" customHeight="1">
+      <c r="A1066" s="4"/>
+      <c r="B1066" s="5"/>
+      <c r="C1066" s="5"/>
+    </row>
+    <row r="1067" spans="1:3" ht="40" customHeight="1">
+      <c r="A1067" s="4"/>
+      <c r="B1067" s="5"/>
+      <c r="C1067" s="5"/>
+    </row>
+    <row r="1068" spans="1:3" ht="40" customHeight="1">
+      <c r="A1068" s="4"/>
+      <c r="B1068" s="5"/>
+      <c r="C1068" s="5"/>
+    </row>
+    <row r="1069" spans="1:3" ht="40" customHeight="1">
+      <c r="A1069" s="4"/>
+      <c r="B1069" s="5"/>
+      <c r="C1069" s="5"/>
+    </row>
+    <row r="1070" spans="1:3" ht="40" customHeight="1">
+      <c r="A1070" s="4"/>
+      <c r="B1070" s="5"/>
+      <c r="C1070" s="5"/>
+    </row>
+    <row r="1071" spans="1:3" ht="40" customHeight="1">
+      <c r="A1071" s="4"/>
+      <c r="B1071" s="5"/>
+      <c r="C1071" s="5"/>
+    </row>
+    <row r="1072" spans="1:3" ht="40" customHeight="1">
+      <c r="A1072" s="4"/>
+      <c r="B1072" s="5"/>
+      <c r="C1072" s="5"/>
+    </row>
+    <row r="1073" spans="1:3" ht="40" customHeight="1">
+      <c r="A1073" s="4"/>
+      <c r="B1073" s="5"/>
+      <c r="C1073" s="5"/>
+    </row>
+    <row r="1074" spans="1:3" ht="40" customHeight="1">
+      <c r="A1074" s="4"/>
+      <c r="B1074" s="5"/>
+      <c r="C1074" s="5"/>
+    </row>
+    <row r="1075" spans="1:3" ht="40" customHeight="1">
+      <c r="A1075" s="4"/>
+      <c r="B1075" s="5"/>
+      <c r="C1075" s="5"/>
+    </row>
+    <row r="1076" spans="1:3" ht="40" customHeight="1">
+      <c r="A1076" s="4"/>
+      <c r="B1076" s="5"/>
+      <c r="C1076" s="5"/>
+    </row>
+    <row r="1077" spans="1:3" ht="40" customHeight="1">
+      <c r="A1077" s="4"/>
+      <c r="B1077" s="5"/>
+      <c r="C1077" s="5"/>
+    </row>
+    <row r="1078" spans="1:3" ht="40" customHeight="1">
+      <c r="A1078" s="4"/>
+      <c r="B1078" s="5"/>
+      <c r="C1078" s="5"/>
+    </row>
+    <row r="1079" spans="1:3" ht="40" customHeight="1">
+      <c r="A1079" s="4"/>
+      <c r="B1079" s="5"/>
+      <c r="C1079" s="5"/>
+    </row>
+    <row r="1080" spans="1:3" ht="40" customHeight="1">
+      <c r="A1080" s="4"/>
+      <c r="B1080" s="5"/>
+      <c r="C1080" s="5"/>
+    </row>
+    <row r="1081" spans="1:3" ht="40" customHeight="1">
+      <c r="A1081" s="4"/>
+      <c r="B1081" s="5"/>
+      <c r="C1081" s="5"/>
+    </row>
+    <row r="1082" spans="1:3" ht="40" customHeight="1">
+      <c r="A1082" s="4"/>
+      <c r="B1082" s="5"/>
+      <c r="C1082" s="5"/>
+    </row>
+    <row r="1083" spans="1:3" ht="40" customHeight="1">
+      <c r="A1083" s="4"/>
+      <c r="B1083" s="5"/>
+      <c r="C1083" s="5"/>
+    </row>
+    <row r="1084" spans="1:3" ht="40" customHeight="1">
+      <c r="A1084" s="4"/>
+      <c r="B1084" s="5"/>
+      <c r="C1084" s="5"/>
+    </row>
+    <row r="1085" spans="1:3" ht="40" customHeight="1">
+      <c r="A1085" s="4"/>
+      <c r="B1085" s="5"/>
+      <c r="C1085" s="5"/>
+    </row>
+    <row r="1086" spans="1:3" ht="40" customHeight="1">
+      <c r="A1086" s="4"/>
+      <c r="B1086" s="5"/>
+      <c r="C1086" s="5"/>
+    </row>
+    <row r="1087" spans="1:3" ht="40" customHeight="1">
+      <c r="A1087" s="4"/>
+      <c r="B1087" s="5"/>
+      <c r="C1087" s="5"/>
+    </row>
+    <row r="1088" spans="1:3" ht="40" customHeight="1">
+      <c r="A1088" s="4"/>
+      <c r="B1088" s="5"/>
+      <c r="C1088" s="5"/>
+    </row>
+    <row r="1089" spans="1:3" ht="40" customHeight="1">
+      <c r="A1089" s="4"/>
+      <c r="B1089" s="5"/>
+      <c r="C1089" s="5"/>
+    </row>
+    <row r="1090" spans="1:3" ht="40" customHeight="1">
+      <c r="A1090" s="4"/>
+      <c r="B1090" s="5"/>
+      <c r="C1090" s="5"/>
+    </row>
+    <row r="1091" spans="1:3" ht="40" customHeight="1">
+      <c r="A1091" s="4"/>
+      <c r="B1091" s="5"/>
+      <c r="C1091" s="5"/>
+    </row>
+    <row r="1092" spans="1:3" ht="40" customHeight="1">
+      <c r="A1092" s="4"/>
+      <c r="B1092" s="5"/>
+      <c r="C1092" s="5"/>
+    </row>
+    <row r="1093" spans="1:3" ht="40" customHeight="1">
+      <c r="A1093" s="4"/>
+      <c r="B1093" s="5"/>
+      <c r="C1093" s="5"/>
+    </row>
+    <row r="1094" spans="1:3" ht="40" customHeight="1">
+      <c r="A1094" s="4"/>
+      <c r="B1094" s="5"/>
+      <c r="C1094" s="5"/>
+    </row>
+    <row r="1095" spans="1:3" ht="40" customHeight="1">
+      <c r="A1095" s="4"/>
+      <c r="B1095" s="5"/>
+      <c r="C1095" s="5"/>
+    </row>
+    <row r="1096" spans="1:3" ht="40" customHeight="1">
+      <c r="A1096" s="4"/>
+      <c r="B1096" s="5"/>
+      <c r="C1096" s="5"/>
+    </row>
+    <row r="1097" spans="1:3" ht="40" customHeight="1">
+      <c r="A1097" s="4"/>
+      <c r="B1097" s="5"/>
+      <c r="C1097" s="5"/>
+    </row>
+    <row r="1098" spans="1:3" ht="40" customHeight="1">
+      <c r="A1098" s="4"/>
+      <c r="B1098" s="5"/>
+      <c r="C1098" s="5"/>
+    </row>
+    <row r="1099" spans="1:3" ht="40" customHeight="1">
+      <c r="A1099" s="4"/>
+      <c r="B1099" s="5"/>
+      <c r="C1099" s="5"/>
+    </row>
+    <row r="1100" spans="1:3" ht="40" customHeight="1">
+      <c r="A1100" s="4"/>
+      <c r="B1100" s="5"/>
+      <c r="C1100" s="5"/>
+    </row>
+    <row r="1101" spans="1:3" ht="40" customHeight="1">
+      <c r="A1101" s="4"/>
+      <c r="B1101" s="5"/>
+      <c r="C1101" s="5"/>
+    </row>
+    <row r="1102" spans="1:3" ht="40" customHeight="1">
+      <c r="A1102" s="4"/>
+      <c r="B1102" s="5"/>
+      <c r="C1102" s="5"/>
+    </row>
+    <row r="1103" spans="1:3" ht="40" customHeight="1">
+      <c r="A1103" s="4"/>
+      <c r="B1103" s="5"/>
+      <c r="C1103" s="5"/>
+    </row>
+    <row r="1104" spans="1:3" ht="40" customHeight="1">
+      <c r="A1104" s="4"/>
+      <c r="B1104" s="5"/>
+      <c r="C1104" s="5"/>
+    </row>
+    <row r="1105" spans="1:3" ht="40" customHeight="1">
+      <c r="A1105" s="4"/>
+      <c r="B1105" s="5"/>
+      <c r="C1105" s="5"/>
+    </row>
+    <row r="1106" spans="1:3" ht="40" customHeight="1">
+      <c r="A1106" s="4"/>
+      <c r="B1106" s="5"/>
+      <c r="C1106" s="5"/>
+    </row>
+    <row r="1107" spans="1:3" ht="40" customHeight="1">
+      <c r="A1107" s="4"/>
+      <c r="B1107" s="5"/>
+      <c r="C1107" s="5"/>
+    </row>
+    <row r="1108" spans="1:3" ht="40" customHeight="1">
+      <c r="A1108" s="4"/>
+      <c r="B1108" s="5"/>
+      <c r="C1108" s="5"/>
+    </row>
+    <row r="1109" spans="1:3" ht="40" customHeight="1">
+      <c r="A1109" s="4"/>
+      <c r="B1109" s="5"/>
+      <c r="C1109" s="5"/>
+    </row>
+    <row r="1110" spans="1:3" ht="40" customHeight="1">
+      <c r="A1110" s="4"/>
+      <c r="B1110" s="5"/>
+      <c r="C1110" s="5"/>
+    </row>
+    <row r="1111" spans="1:3" ht="40" customHeight="1">
+      <c r="A1111" s="4"/>
+      <c r="B1111" s="5"/>
+      <c r="C1111" s="5"/>
+    </row>
+    <row r="1112" spans="1:3" ht="40" customHeight="1">
+      <c r="A1112" s="4"/>
+      <c r="B1112" s="5"/>
+      <c r="C1112" s="5"/>
+    </row>
+    <row r="1113" spans="1:3" ht="40" customHeight="1">
+      <c r="A1113" s="4"/>
+      <c r="B1113" s="5"/>
+      <c r="C1113" s="5"/>
+    </row>
+    <row r="1114" spans="1:3" ht="40" customHeight="1">
+      <c r="A1114" s="4"/>
+      <c r="B1114" s="5"/>
+      <c r="C1114" s="5"/>
+    </row>
+    <row r="1115" spans="1:3" ht="40" customHeight="1">
+      <c r="A1115" s="4"/>
+      <c r="B1115" s="5"/>
+      <c r="C1115" s="5"/>
+    </row>
+    <row r="1116" spans="1:3" ht="40" customHeight="1">
+      <c r="A1116" s="4"/>
+      <c r="B1116" s="5"/>
+      <c r="C1116" s="5"/>
+    </row>
+    <row r="1117" spans="1:3" ht="40" customHeight="1">
+      <c r="A1117" s="4"/>
+      <c r="B1117" s="5"/>
+      <c r="C1117" s="5"/>
+    </row>
+    <row r="1118" spans="1:3" ht="40" customHeight="1">
+      <c r="A1118" s="4"/>
+      <c r="B1118" s="5"/>
+      <c r="C1118" s="5"/>
+    </row>
+    <row r="1119" spans="1:3" ht="40" customHeight="1">
+      <c r="A1119" s="4"/>
+      <c r="B1119" s="5"/>
+      <c r="C1119" s="5"/>
+    </row>
+    <row r="1120" spans="1:3" ht="40" customHeight="1">
+      <c r="A1120" s="4"/>
+      <c r="B1120" s="5"/>
+      <c r="C1120" s="5"/>
+    </row>
+    <row r="1121" spans="1:3" ht="40" customHeight="1">
+      <c r="A1121" s="4"/>
+      <c r="B1121" s="5"/>
+      <c r="C1121" s="5"/>
+    </row>
+    <row r="1122" spans="1:3" ht="40" customHeight="1">
+      <c r="A1122" s="4"/>
+      <c r="B1122" s="5"/>
+      <c r="C1122" s="5"/>
+    </row>
+    <row r="1123" spans="1:3" ht="40" customHeight="1">
+      <c r="A1123" s="4"/>
+      <c r="B1123" s="5"/>
+      <c r="C1123" s="5"/>
+    </row>
+    <row r="1124" spans="1:3" ht="40" customHeight="1">
+      <c r="A1124" s="4"/>
+      <c r="B1124" s="5"/>
+      <c r="C1124" s="5"/>
+    </row>
+    <row r="1125" spans="1:3" ht="40" customHeight="1">
+      <c r="A1125" s="4"/>
+      <c r="B1125" s="5"/>
+      <c r="C1125" s="5"/>
+    </row>
+    <row r="1126" spans="1:3" ht="40" customHeight="1">
+      <c r="A1126" s="4"/>
+      <c r="B1126" s="5"/>
+      <c r="C1126" s="5"/>
+    </row>
+    <row r="1127" spans="1:3" ht="40" customHeight="1">
+      <c r="A1127" s="4"/>
+      <c r="B1127" s="5"/>
+      <c r="C1127" s="5"/>
+    </row>
+    <row r="1128" spans="1:3" ht="40" customHeight="1">
+      <c r="A1128" s="4"/>
+      <c r="B1128" s="5"/>
+      <c r="C1128" s="5"/>
+    </row>
+    <row r="1129" spans="1:3" ht="40" customHeight="1">
+      <c r="A1129" s="4"/>
+      <c r="B1129" s="5"/>
+      <c r="C1129" s="5"/>
+    </row>
+    <row r="1130" spans="1:3" ht="40" customHeight="1">
+      <c r="A1130" s="4"/>
+      <c r="B1130" s="5"/>
+      <c r="C1130" s="5"/>
+    </row>
+    <row r="1131" spans="1:3" ht="40" customHeight="1">
+      <c r="A1131" s="4"/>
+      <c r="B1131" s="5"/>
+      <c r="C1131" s="5"/>
+    </row>
+    <row r="1132" spans="1:3" ht="40" customHeight="1">
+      <c r="A1132" s="4"/>
+      <c r="B1132" s="5"/>
+      <c r="C1132" s="5"/>
+    </row>
+    <row r="1133" spans="1:3" ht="40" customHeight="1">
+      <c r="A1133" s="4"/>
+      <c r="B1133" s="5"/>
+      <c r="C1133" s="5"/>
+    </row>
+    <row r="1134" spans="1:3" ht="40" customHeight="1">
+      <c r="A1134" s="4"/>
+      <c r="B1134" s="5"/>
+      <c r="C1134" s="5"/>
+    </row>
+    <row r="1135" spans="1:3" ht="40" customHeight="1">
+      <c r="A1135" s="4"/>
+      <c r="B1135" s="5"/>
+      <c r="C1135" s="5"/>
+    </row>
+    <row r="1136" spans="1:3" ht="40" customHeight="1">
+      <c r="A1136" s="4"/>
+      <c r="B1136" s="5"/>
+      <c r="C1136" s="5"/>
+    </row>
+    <row r="1137" spans="1:3" ht="40" customHeight="1">
+      <c r="A1137" s="4"/>
+      <c r="B1137" s="5"/>
+      <c r="C1137" s="5"/>
+    </row>
+    <row r="1138" spans="1:3" ht="40" customHeight="1">
+      <c r="A1138" s="4"/>
+      <c r="B1138" s="5"/>
+      <c r="C1138" s="5"/>
+    </row>
+    <row r="1139" spans="1:3" ht="40" customHeight="1">
+      <c r="A1139" s="4"/>
+      <c r="B1139" s="5"/>
+      <c r="C1139" s="5"/>
+    </row>
+    <row r="1140" spans="1:3" ht="40" customHeight="1">
+      <c r="A1140" s="4"/>
+      <c r="B1140" s="5"/>
+      <c r="C1140" s="5"/>
+    </row>
+    <row r="1141" spans="1:3" ht="40" customHeight="1">
+      <c r="A1141" s="4"/>
+      <c r="B1141" s="5"/>
+      <c r="C1141" s="5"/>
+    </row>
+    <row r="1142" spans="1:3" ht="40" customHeight="1">
+      <c r="A1142" s="4"/>
+      <c r="B1142" s="5"/>
+      <c r="C1142" s="5"/>
+    </row>
+    <row r="1143" spans="1:3" ht="40" customHeight="1">
+      <c r="A1143" s="4"/>
+      <c r="B1143" s="5"/>
+      <c r="C1143" s="5"/>
+    </row>
+    <row r="1144" spans="1:3" ht="40" customHeight="1">
+      <c r="A1144" s="4"/>
+      <c r="B1144" s="5"/>
+      <c r="C1144" s="5"/>
+    </row>
+    <row r="1145" spans="1:3" ht="40" customHeight="1">
+      <c r="A1145" s="4"/>
+      <c r="B1145" s="5"/>
+      <c r="C1145" s="5"/>
+    </row>
+    <row r="1146" spans="1:3" ht="40" customHeight="1">
+      <c r="A1146" s="4"/>
+      <c r="B1146" s="5"/>
+      <c r="C1146" s="5"/>
+    </row>
+    <row r="1147" spans="1:3" ht="40" customHeight="1">
+      <c r="A1147" s="4"/>
+      <c r="B1147" s="5"/>
+      <c r="C1147" s="5"/>
+    </row>
+    <row r="1148" spans="1:3" ht="40" customHeight="1">
+      <c r="A1148" s="4"/>
+      <c r="B1148" s="5"/>
+      <c r="C1148" s="5"/>
+    </row>
+    <row r="1149" spans="1:3" ht="40" customHeight="1">
+      <c r="A1149" s="4"/>
+      <c r="B1149" s="5"/>
+      <c r="C1149" s="5"/>
+    </row>
+    <row r="1150" spans="1:3" ht="40" customHeight="1">
+      <c r="A1150" s="4"/>
+      <c r="B1150" s="5"/>
+      <c r="C1150" s="5"/>
+    </row>
+    <row r="1151" spans="1:3" ht="40" customHeight="1">
+      <c r="A1151" s="4"/>
+      <c r="B1151" s="5"/>
+      <c r="C1151" s="5"/>
+    </row>
+    <row r="1152" spans="1:3" ht="40" customHeight="1">
+      <c r="A1152" s="4"/>
+      <c r="B1152" s="5"/>
+      <c r="C1152" s="5"/>
+    </row>
+    <row r="1153" spans="1:3" ht="40" customHeight="1">
+      <c r="A1153" s="4"/>
+      <c r="B1153" s="5"/>
+      <c r="C1153" s="5"/>
+    </row>
+    <row r="1154" spans="1:3" ht="40" customHeight="1">
+      <c r="A1154" s="4"/>
+      <c r="B1154" s="5"/>
+      <c r="C1154" s="5"/>
+    </row>
+    <row r="1155" spans="1:3" ht="40" customHeight="1">
+      <c r="A1155" s="4"/>
+      <c r="B1155" s="5"/>
+      <c r="C1155" s="5"/>
+    </row>
+    <row r="1156" spans="1:3" ht="40" customHeight="1">
+      <c r="A1156" s="4"/>
+      <c r="B1156" s="5"/>
+      <c r="C1156" s="5"/>
+    </row>
+    <row r="1157" spans="1:3" ht="40" customHeight="1">
+      <c r="A1157" s="4"/>
+      <c r="B1157" s="5"/>
+      <c r="C1157" s="5"/>
+    </row>
+    <row r="1158" spans="1:3" ht="40" customHeight="1">
+      <c r="A1158" s="4"/>
+      <c r="B1158" s="5"/>
+      <c r="C1158" s="5"/>
+    </row>
+    <row r="1159" spans="1:3" ht="40" customHeight="1">
+      <c r="A1159" s="4"/>
+      <c r="B1159" s="5"/>
+      <c r="C1159" s="5"/>
+    </row>
+    <row r="1160" spans="1:3" ht="40" customHeight="1">
+      <c r="A1160" s="4"/>
+      <c r="B1160" s="5"/>
+      <c r="C1160" s="5"/>
+    </row>
+    <row r="1161" spans="1:3" ht="40" customHeight="1">
+      <c r="A1161" s="4"/>
+      <c r="B1161" s="5"/>
+      <c r="C1161" s="5"/>
+    </row>
+    <row r="1162" spans="1:3" ht="40" customHeight="1">
+      <c r="A1162" s="4"/>
+      <c r="B1162" s="5"/>
+      <c r="C1162" s="5"/>
+    </row>
+    <row r="1163" spans="1:3" ht="40" customHeight="1">
+      <c r="A1163" s="4"/>
+      <c r="B1163" s="5"/>
+      <c r="C1163" s="5"/>
+    </row>
+    <row r="1164" spans="1:3" ht="40" customHeight="1">
+      <c r="A1164" s="4"/>
+      <c r="B1164" s="5"/>
+      <c r="C1164" s="5"/>
+    </row>
+    <row r="1165" spans="1:3" ht="40" customHeight="1">
+      <c r="A1165" s="4"/>
+      <c r="B1165" s="5"/>
+      <c r="C1165" s="5"/>
+    </row>
+    <row r="1166" spans="1:3" ht="40" customHeight="1">
+      <c r="A1166" s="4"/>
+      <c r="B1166" s="5"/>
+      <c r="C1166" s="5"/>
+    </row>
+    <row r="1167" spans="1:3" ht="40" customHeight="1">
+      <c r="A1167" s="4"/>
+      <c r="B1167" s="5"/>
+      <c r="C1167" s="5"/>
+    </row>
+    <row r="1168" spans="1:3" ht="40" customHeight="1">
+      <c r="A1168" s="4"/>
+      <c r="B1168" s="5"/>
+      <c r="C1168" s="5"/>
+    </row>
+    <row r="1169" spans="1:3" ht="40" customHeight="1">
+      <c r="A1169" s="4"/>
+      <c r="B1169" s="5"/>
+      <c r="C1169" s="5"/>
+    </row>
+    <row r="1170" spans="1:3" ht="40" customHeight="1">
+      <c r="A1170" s="4"/>
+      <c r="B1170" s="5"/>
+      <c r="C1170" s="5"/>
+    </row>
+    <row r="1171" spans="1:3" ht="40" customHeight="1">
+      <c r="A1171" s="4"/>
+      <c r="B1171" s="5"/>
+      <c r="C1171" s="5"/>
+    </row>
+    <row r="1172" spans="1:3" ht="40" customHeight="1">
+      <c r="A1172" s="4"/>
+      <c r="B1172" s="5"/>
+      <c r="C1172" s="5"/>
+    </row>
+    <row r="1173" spans="1:3" ht="40" customHeight="1">
+      <c r="A1173" s="4"/>
+      <c r="B1173" s="5"/>
+      <c r="C1173" s="5"/>
+    </row>
+    <row r="1174" spans="1:3" ht="40" customHeight="1">
+      <c r="A1174" s="4"/>
+      <c r="B1174" s="5"/>
+      <c r="C1174" s="5"/>
+    </row>
+    <row r="1175" spans="1:3" ht="40" customHeight="1">
+      <c r="A1175" s="4"/>
+      <c r="B1175" s="5"/>
+      <c r="C1175" s="5"/>
+    </row>
+    <row r="1176" spans="1:3" ht="40" customHeight="1">
+      <c r="A1176" s="4"/>
+      <c r="B1176" s="5"/>
+      <c r="C1176" s="5"/>
+    </row>
+    <row r="1177" spans="1:3" ht="40" customHeight="1">
+      <c r="A1177" s="4"/>
+      <c r="B1177" s="5"/>
+      <c r="C1177" s="5"/>
+    </row>
+    <row r="1178" spans="1:3" ht="40" customHeight="1">
+      <c r="A1178" s="4"/>
+      <c r="B1178" s="5"/>
+      <c r="C1178" s="5"/>
+    </row>
+    <row r="1179" spans="1:3" ht="40" customHeight="1">
+      <c r="A1179" s="4"/>
+      <c r="B1179" s="5"/>
+      <c r="C1179" s="5"/>
+    </row>
+    <row r="1180" spans="1:3" ht="40" customHeight="1">
+      <c r="A1180" s="4"/>
+      <c r="B1180" s="5"/>
+      <c r="C1180" s="5"/>
+    </row>
+    <row r="1181" spans="1:3" ht="40" customHeight="1">
+      <c r="A1181" s="4"/>
+      <c r="B1181" s="5"/>
+      <c r="C1181" s="5"/>
+    </row>
+    <row r="1182" spans="1:3" ht="40" customHeight="1">
+      <c r="A1182" s="4"/>
+      <c r="B1182" s="5"/>
+      <c r="C1182" s="5"/>
+    </row>
+    <row r="1183" spans="1:3" ht="40" customHeight="1">
+      <c r="A1183" s="4"/>
+      <c r="B1183" s="5"/>
+      <c r="C1183" s="5"/>
+    </row>
+    <row r="1184" spans="1:3" ht="40" customHeight="1">
+      <c r="A1184" s="4"/>
+      <c r="B1184" s="5"/>
+      <c r="C1184" s="5"/>
+    </row>
+    <row r="1185" spans="1:3" ht="40" customHeight="1">
+      <c r="A1185" s="4"/>
+      <c r="B1185" s="5"/>
+      <c r="C1185" s="5"/>
+    </row>
+    <row r="1186" spans="1:3" ht="40" customHeight="1">
+      <c r="A1186" s="4"/>
+      <c r="B1186" s="5"/>
+      <c r="C1186" s="5"/>
+    </row>
+    <row r="1187" spans="1:3" ht="40" customHeight="1">
+      <c r="A1187" s="4"/>
+      <c r="B1187" s="5"/>
+      <c r="C1187" s="5"/>
+    </row>
+    <row r="1188" spans="1:3" ht="40" customHeight="1">
+      <c r="A1188" s="4"/>
+      <c r="B1188" s="5"/>
+      <c r="C1188" s="5"/>
+    </row>
+    <row r="1189" spans="1:3" ht="40" customHeight="1">
+      <c r="A1189" s="4"/>
+      <c r="B1189" s="5"/>
+      <c r="C1189" s="5"/>
+    </row>
+    <row r="1190" spans="1:3" ht="40" customHeight="1">
+      <c r="A1190" s="4"/>
+      <c r="B1190" s="5"/>
+      <c r="C1190" s="5"/>
+    </row>
+    <row r="1191" spans="1:3" ht="40" customHeight="1">
+      <c r="A1191" s="4"/>
+      <c r="B1191" s="5"/>
+      <c r="C1191" s="5"/>
+    </row>
+    <row r="1192" spans="1:3" ht="40" customHeight="1">
+      <c r="A1192" s="4"/>
+      <c r="B1192" s="5"/>
+      <c r="C1192" s="5"/>
+    </row>
+    <row r="1193" spans="1:3" ht="40" customHeight="1">
+      <c r="A1193" s="4"/>
+      <c r="B1193" s="5"/>
+      <c r="C1193" s="5"/>
+    </row>
+    <row r="1194" spans="1:3" ht="40" customHeight="1">
+      <c r="A1194" s="4"/>
+      <c r="B1194" s="5"/>
+      <c r="C1194" s="5"/>
+    </row>
+    <row r="1195" spans="1:3" ht="40" customHeight="1">
+      <c r="A1195" s="4"/>
+      <c r="B1195" s="5"/>
+      <c r="C1195" s="5"/>
+    </row>
+    <row r="1196" spans="1:3" ht="40" customHeight="1">
+      <c r="A1196" s="4"/>
+      <c r="B1196" s="5"/>
+      <c r="C1196" s="5"/>
+    </row>
+    <row r="1197" spans="1:3" ht="40" customHeight="1">
+      <c r="A1197" s="4"/>
+      <c r="B1197" s="5"/>
+      <c r="C1197" s="5"/>
+    </row>
+    <row r="1198" spans="1:3" ht="40" customHeight="1">
+      <c r="A1198" s="4"/>
+      <c r="B1198" s="5"/>
+      <c r="C1198" s="5"/>
+    </row>
+    <row r="1199" spans="1:3" ht="40" customHeight="1">
+      <c r="A1199" s="4"/>
+      <c r="B1199" s="5"/>
+      <c r="C1199" s="5"/>
+    </row>
+    <row r="1200" spans="1:3" ht="40" customHeight="1">
+      <c r="A1200" s="4"/>
+      <c r="B1200" s="5"/>
+      <c r="C1200" s="5"/>
+    </row>
+    <row r="1201" spans="1:3" ht="40" customHeight="1">
+      <c r="A1201" s="4"/>
+      <c r="B1201" s="5"/>
+      <c r="C1201" s="5"/>
+    </row>
+    <row r="1202" spans="1:3" ht="40" customHeight="1">
+      <c r="A1202" s="4"/>
+      <c r="B1202" s="5"/>
+      <c r="C1202" s="5"/>
+    </row>
+    <row r="1203" spans="1:3" ht="40" customHeight="1">
+      <c r="A1203" s="4"/>
+      <c r="B1203" s="5"/>
+      <c r="C1203" s="5"/>
+    </row>
+    <row r="1204" spans="1:3" ht="40" customHeight="1">
+      <c r="A1204" s="4"/>
+      <c r="B1204" s="5"/>
+      <c r="C1204" s="5"/>
+    </row>
+    <row r="1205" spans="1:3" ht="40" customHeight="1">
+      <c r="A1205" s="4"/>
+      <c r="B1205" s="5"/>
+      <c r="C1205" s="5"/>
+    </row>
+    <row r="1206" spans="1:3" ht="40" customHeight="1">
+      <c r="A1206" s="4"/>
+      <c r="B1206" s="5"/>
+      <c r="C1206" s="5"/>
+    </row>
+    <row r="1207" spans="1:3" ht="40" customHeight="1">
+      <c r="A1207" s="4"/>
+      <c r="B1207" s="5"/>
+      <c r="C1207" s="5"/>
+    </row>
+    <row r="1208" spans="1:3" ht="40" customHeight="1">
+      <c r="A1208" s="4"/>
+      <c r="B1208" s="5"/>
+      <c r="C1208" s="5"/>
+    </row>
+    <row r="1209" spans="1:3" ht="40" customHeight="1">
+      <c r="A1209" s="4"/>
+      <c r="B1209" s="5"/>
+      <c r="C1209" s="5"/>
+    </row>
+    <row r="1210" spans="1:3" ht="40" customHeight="1">
+      <c r="A1210" s="4"/>
+      <c r="B1210" s="5"/>
+      <c r="C1210" s="5"/>
+    </row>
+    <row r="1211" spans="1:3" ht="40" customHeight="1">
+      <c r="A1211" s="4"/>
+      <c r="B1211" s="5"/>
+      <c r="C1211" s="5"/>
+    </row>
+    <row r="1212" spans="1:3" ht="40" customHeight="1">
+      <c r="A1212" s="4"/>
+      <c r="B1212" s="5"/>
+      <c r="C1212" s="5"/>
+    </row>
+    <row r="1213" spans="1:3" ht="40" customHeight="1">
+      <c r="A1213" s="4"/>
+      <c r="B1213" s="5"/>
+      <c r="C1213" s="5"/>
+    </row>
+    <row r="1214" spans="1:3" ht="40" customHeight="1">
+      <c r="A1214" s="4"/>
+      <c r="B1214" s="5"/>
+      <c r="C1214" s="5"/>
+    </row>
+    <row r="1215" spans="1:3" ht="40" customHeight="1">
+      <c r="A1215" s="4"/>
+      <c r="B1215" s="5"/>
+      <c r="C1215" s="5"/>
+    </row>
+    <row r="1216" spans="1:3" ht="40" customHeight="1">
+      <c r="A1216" s="4"/>
+      <c r="B1216" s="5"/>
+      <c r="C1216" s="5"/>
+    </row>
+    <row r="1217" spans="1:3" ht="40" customHeight="1">
+      <c r="A1217" s="4"/>
+      <c r="B1217" s="5"/>
+      <c r="C1217" s="5"/>
+    </row>
+    <row r="1218" spans="1:3" ht="40" customHeight="1">
+      <c r="A1218" s="4"/>
+      <c r="B1218" s="5"/>
+      <c r="C1218" s="5"/>
+    </row>
+    <row r="1219" spans="1:3" ht="40" customHeight="1">
+      <c r="A1219" s="4"/>
+      <c r="B1219" s="5"/>
+      <c r="C1219" s="5"/>
+    </row>
+    <row r="1220" spans="1:3" ht="40" customHeight="1">
+      <c r="A1220" s="4"/>
+      <c r="B1220" s="5"/>
+      <c r="C1220" s="5"/>
+    </row>
+    <row r="1221" spans="1:3" ht="40" customHeight="1">
+      <c r="A1221" s="4"/>
+      <c r="B1221" s="5"/>
+      <c r="C1221" s="5"/>
+    </row>
+    <row r="1222" spans="1:3" ht="40" customHeight="1">
+      <c r="A1222" s="4"/>
+      <c r="B1222" s="5"/>
+      <c r="C1222" s="5"/>
+    </row>
+    <row r="1223" spans="1:3" ht="40" customHeight="1">
+      <c r="A1223" s="4"/>
+      <c r="B1223" s="5"/>
+      <c r="C1223" s="5"/>
+    </row>
+    <row r="1224" spans="1:3" ht="40" customHeight="1">
+      <c r="A1224" s="4"/>
+      <c r="B1224" s="5"/>
+      <c r="C1224" s="5"/>
+    </row>
+    <row r="1225" spans="1:3" ht="40" customHeight="1">
+      <c r="A1225" s="4"/>
+      <c r="B1225" s="5"/>
+      <c r="C1225" s="5"/>
+    </row>
+    <row r="1226" spans="1:3" ht="40" customHeight="1">
+      <c r="A1226" s="4"/>
+      <c r="B1226" s="5"/>
+      <c r="C1226" s="5"/>
+    </row>
+    <row r="1227" spans="1:3" ht="40" customHeight="1">
+      <c r="A1227" s="4"/>
+      <c r="B1227" s="5"/>
+      <c r="C1227" s="5"/>
+    </row>
+    <row r="1228" spans="1:3" ht="40" customHeight="1">
+      <c r="A1228" s="4"/>
+      <c r="B1228" s="5"/>
+      <c r="C1228" s="5"/>
+    </row>
+    <row r="1229" spans="1:3" ht="40" customHeight="1">
+      <c r="A1229" s="4"/>
+      <c r="B1229" s="5"/>
+      <c r="C1229" s="5"/>
+    </row>
+    <row r="1230" spans="1:3" ht="40" customHeight="1">
+      <c r="A1230" s="4"/>
+      <c r="B1230" s="5"/>
+      <c r="C1230" s="5"/>
+    </row>
+    <row r="1231" spans="1:3" ht="40" customHeight="1">
+      <c r="A1231" s="4"/>
+      <c r="B1231" s="5"/>
+      <c r="C1231" s="5"/>
+    </row>
+    <row r="1232" spans="1:3" ht="40" customHeight="1">
+      <c r="A1232" s="4"/>
+      <c r="B1232" s="5"/>
+      <c r="C1232" s="5"/>
+    </row>
+    <row r="1233" spans="1:3" ht="40" customHeight="1">
+      <c r="A1233" s="4"/>
+      <c r="B1233" s="5"/>
+      <c r="C1233" s="5"/>
+    </row>
+    <row r="1234" spans="1:3" ht="40" customHeight="1">
+      <c r="A1234" s="4"/>
+      <c r="B1234" s="5"/>
+      <c r="C1234" s="5"/>
+    </row>
+    <row r="1235" spans="1:3" ht="40" customHeight="1">
+      <c r="A1235" s="4"/>
+      <c r="B1235" s="5"/>
+      <c r="C1235" s="5"/>
+    </row>
+    <row r="1236" spans="1:3" ht="40" customHeight="1">
+      <c r="A1236" s="4"/>
+      <c r="B1236" s="5"/>
+      <c r="C1236" s="5"/>
+    </row>
+    <row r="1237" spans="1:3" ht="40" customHeight="1">
+      <c r="A1237" s="4"/>
+      <c r="B1237" s="5"/>
+      <c r="C1237" s="5"/>
+    </row>
+    <row r="1238" spans="1:3" ht="40" customHeight="1">
+      <c r="A1238" s="4"/>
+      <c r="B1238" s="5"/>
+      <c r="C1238" s="5"/>
+    </row>
+    <row r="1239" spans="1:3" ht="40" customHeight="1">
+      <c r="A1239" s="4"/>
+      <c r="B1239" s="5"/>
+      <c r="C1239" s="5"/>
+    </row>
+    <row r="1240" spans="1:3" ht="40" customHeight="1">
+      <c r="A1240" s="4"/>
+      <c r="B1240" s="5"/>
+      <c r="C1240" s="5"/>
+    </row>
+    <row r="1241" spans="1:3" ht="40" customHeight="1">
+      <c r="A1241" s="4"/>
+      <c r="B1241" s="5"/>
+      <c r="C1241" s="5"/>
+    </row>
+    <row r="1242" spans="1:3" ht="40" customHeight="1">
+      <c r="A1242" s="4"/>
+      <c r="B1242" s="5"/>
+      <c r="C1242" s="5"/>
+    </row>
+    <row r="1243" spans="1:3" ht="40" customHeight="1">
+      <c r="A1243" s="4"/>
+      <c r="B1243" s="5"/>
+      <c r="C1243" s="5"/>
+    </row>
+    <row r="1244" spans="1:3" ht="40" customHeight="1">
+      <c r="A1244" s="4"/>
+      <c r="B1244" s="5"/>
+      <c r="C1244" s="5"/>
+    </row>
+    <row r="1245" spans="1:3" ht="40" customHeight="1">
+      <c r="A1245" s="4"/>
+      <c r="B1245" s="5"/>
+      <c r="C1245" s="5"/>
+    </row>
+    <row r="1246" spans="1:3" ht="40" customHeight="1">
+      <c r="A1246" s="4"/>
+      <c r="B1246" s="5"/>
+      <c r="C1246" s="5"/>
+    </row>
+    <row r="1247" spans="1:3" ht="40" customHeight="1">
+      <c r="A1247" s="4"/>
+      <c r="B1247" s="5"/>
+      <c r="C1247" s="5"/>
+    </row>
+    <row r="1248" spans="1:3" ht="40" customHeight="1">
+      <c r="A1248" s="4"/>
+      <c r="B1248" s="5"/>
+      <c r="C1248" s="5"/>
+    </row>
+    <row r="1249" spans="1:3" ht="40" customHeight="1">
+      <c r="A1249" s="4"/>
+      <c r="B1249" s="5"/>
+      <c r="C1249" s="5"/>
+    </row>
+    <row r="1250" spans="1:3" ht="40" customHeight="1">
+      <c r="A1250" s="4"/>
+      <c r="B1250" s="5"/>
+      <c r="C1250" s="5"/>
+    </row>
+    <row r="1251" spans="1:3" ht="40" customHeight="1">
+      <c r="A1251" s="4"/>
+      <c r="B1251" s="5"/>
+      <c r="C1251" s="5"/>
+    </row>
+    <row r="1252" spans="1:3" ht="40" customHeight="1">
+      <c r="A1252" s="4"/>
+      <c r="B1252" s="5"/>
+      <c r="C1252" s="5"/>
+    </row>
+    <row r="1253" spans="1:3" ht="40" customHeight="1">
+      <c r="A1253" s="4"/>
+      <c r="B1253" s="5"/>
+      <c r="C1253" s="5"/>
+    </row>
+    <row r="1254" spans="1:3" ht="40" customHeight="1">
+      <c r="A1254" s="4"/>
+      <c r="B1254" s="5"/>
+      <c r="C1254" s="5"/>
+    </row>
+    <row r="1255" spans="1:3" ht="40" customHeight="1">
+      <c r="A1255" s="4"/>
+      <c r="B1255" s="5"/>
+      <c r="C1255" s="5"/>
+    </row>
+    <row r="1256" spans="1:3" ht="40" customHeight="1">
+      <c r="A1256" s="4"/>
+      <c r="B1256" s="5"/>
+      <c r="C1256" s="5"/>
+    </row>
+    <row r="1257" spans="1:3" ht="40" customHeight="1">
+      <c r="A1257" s="4"/>
+      <c r="B1257" s="5"/>
+      <c r="C1257" s="5"/>
+    </row>
+    <row r="1258" spans="1:3" ht="40" customHeight="1">
+      <c r="A1258" s="4"/>
+      <c r="B1258" s="5"/>
+      <c r="C1258" s="5"/>
+    </row>
+    <row r="1259" spans="1:3" ht="40" customHeight="1">
+      <c r="A1259" s="4"/>
+      <c r="B1259" s="5"/>
+      <c r="C1259" s="5"/>
+    </row>
+    <row r="1260" spans="1:3" ht="40" customHeight="1">
+      <c r="A1260" s="4"/>
+      <c r="B1260" s="5"/>
+      <c r="C1260" s="5"/>
+    </row>
+    <row r="1261" spans="1:3" ht="40" customHeight="1">
+      <c r="A1261" s="4"/>
+      <c r="B1261" s="5"/>
+      <c r="C1261" s="5"/>
+    </row>
+    <row r="1262" spans="1:3" ht="40" customHeight="1">
+      <c r="A1262" s="4"/>
+      <c r="B1262" s="5"/>
+      <c r="C1262" s="5"/>
+    </row>
+    <row r="1263" spans="1:3" ht="40" customHeight="1">
+      <c r="A1263" s="4"/>
+      <c r="B1263" s="5"/>
+      <c r="C1263" s="5"/>
+    </row>
+    <row r="1264" spans="1:3" ht="40" customHeight="1">
+      <c r="A1264" s="4"/>
+      <c r="B1264" s="5"/>
+      <c r="C1264" s="5"/>
+    </row>
+    <row r="1265" spans="1:3" ht="40" customHeight="1">
+      <c r="A1265" s="4"/>
+      <c r="B1265" s="5"/>
+      <c r="C1265" s="5"/>
+    </row>
+    <row r="1266" spans="1:3" ht="40" customHeight="1">
+      <c r="A1266" s="4"/>
+      <c r="B1266" s="5"/>
+      <c r="C1266" s="5"/>
+    </row>
+    <row r="1267" spans="1:3" ht="40" customHeight="1">
+      <c r="A1267" s="4"/>
+      <c r="B1267" s="5"/>
+      <c r="C1267" s="5"/>
+    </row>
+    <row r="1268" spans="1:3" ht="40" customHeight="1">
+      <c r="A1268" s="4"/>
+      <c r="B1268" s="5"/>
+      <c r="C1268" s="5"/>
+    </row>
+    <row r="1269" spans="1:3" ht="40" customHeight="1">
+      <c r="A1269" s="4"/>
+      <c r="B1269" s="5"/>
+      <c r="C1269" s="5"/>
+    </row>
+    <row r="1270" spans="1:3" ht="40" customHeight="1">
+      <c r="A1270" s="4"/>
+      <c r="B1270" s="5"/>
+      <c r="C1270" s="5"/>
+    </row>
+    <row r="1271" spans="1:3" ht="40" customHeight="1">
+      <c r="A1271" s="4"/>
+      <c r="B1271" s="5"/>
+      <c r="C1271" s="5"/>
+    </row>
+    <row r="1272" spans="1:3" ht="40" customHeight="1">
+      <c r="A1272" s="4"/>
+      <c r="B1272" s="5"/>
+      <c r="C1272" s="5"/>
+    </row>
+    <row r="1273" spans="1:3" ht="40" customHeight="1">
+      <c r="A1273" s="4"/>
+      <c r="B1273" s="5"/>
+      <c r="C1273" s="5"/>
+    </row>
+    <row r="1274" spans="1:3" ht="40" customHeight="1">
+      <c r="A1274" s="4"/>
+      <c r="B1274" s="5"/>
+      <c r="C1274" s="5"/>
+    </row>
+    <row r="1275" spans="1:3" ht="40" customHeight="1">
+      <c r="A1275" s="4"/>
+      <c r="B1275" s="5"/>
+      <c r="C1275" s="5"/>
+    </row>
+    <row r="1276" spans="1:3" ht="40" customHeight="1">
+      <c r="A1276" s="4"/>
+      <c r="B1276" s="5"/>
+      <c r="C1276" s="5"/>
+    </row>
+    <row r="1277" spans="1:3" ht="40" customHeight="1">
+      <c r="A1277" s="4"/>
+      <c r="B1277" s="5"/>
+      <c r="C1277" s="5"/>
+    </row>
+    <row r="1278" spans="1:3" ht="40" customHeight="1">
+      <c r="A1278" s="4"/>
+      <c r="B1278" s="5"/>
+      <c r="C1278" s="5"/>
+    </row>
+    <row r="1279" spans="1:3" ht="40" customHeight="1">
+      <c r="A1279" s="4"/>
+      <c r="B1279" s="5"/>
+      <c r="C1279" s="5"/>
+    </row>
+    <row r="1280" spans="1:3" ht="40" customHeight="1">
+      <c r="A1280" s="4"/>
+      <c r="B1280" s="5"/>
+      <c r="C1280" s="5"/>
+    </row>
+    <row r="1281" spans="1:3" ht="40" customHeight="1">
+      <c r="A1281" s="4"/>
+      <c r="B1281" s="5"/>
+      <c r="C1281" s="5"/>
+    </row>
+    <row r="1282" spans="1:3" ht="40" customHeight="1">
+      <c r="A1282" s="4"/>
+      <c r="B1282" s="5"/>
+      <c r="C1282" s="5"/>
+    </row>
+    <row r="1283" spans="1:3" ht="40" customHeight="1">
+      <c r="A1283" s="4"/>
+      <c r="B1283" s="5"/>
+      <c r="C1283" s="5"/>
+    </row>
+    <row r="1284" spans="1:3" ht="40" customHeight="1">
+      <c r="A1284" s="4"/>
+      <c r="B1284" s="5"/>
+      <c r="C1284" s="5"/>
+    </row>
+    <row r="1285" spans="1:3" ht="40" customHeight="1">
+      <c r="A1285" s="4"/>
+      <c r="B1285" s="5"/>
+      <c r="C1285" s="5"/>
+    </row>
+    <row r="1286" spans="1:3" ht="40" customHeight="1">
+      <c r="A1286" s="4"/>
+      <c r="B1286" s="5"/>
+      <c r="C1286" s="5"/>
+    </row>
+    <row r="1287" spans="1:3" ht="40" customHeight="1">
+      <c r="A1287" s="4"/>
+      <c r="B1287" s="5"/>
+      <c r="C1287" s="5"/>
+    </row>
+    <row r="1288" spans="1:3" ht="40" customHeight="1">
+      <c r="A1288" s="4"/>
+      <c r="B1288" s="5"/>
+      <c r="C1288" s="5"/>
+    </row>
+    <row r="1289" spans="1:3" ht="40" customHeight="1">
+      <c r="A1289" s="4"/>
+      <c r="B1289" s="5"/>
+      <c r="C1289" s="5"/>
+    </row>
+    <row r="1290" spans="1:3" ht="40" customHeight="1">
+      <c r="A1290" s="4"/>
+      <c r="B1290" s="5"/>
+      <c r="C1290" s="5"/>
+    </row>
+    <row r="1291" spans="1:3" ht="40" customHeight="1">
+      <c r="A1291" s="4"/>
+      <c r="B1291" s="5"/>
+      <c r="C1291" s="5"/>
+    </row>
+    <row r="1292" spans="1:3" ht="40" customHeight="1">
+      <c r="A1292" s="4"/>
+      <c r="B1292" s="5"/>
+      <c r="C1292" s="5"/>
+    </row>
+    <row r="1293" spans="1:3" ht="40" customHeight="1">
+      <c r="A1293" s="4"/>
+      <c r="B1293" s="5"/>
+      <c r="C1293" s="5"/>
+    </row>
+    <row r="1294" spans="1:3" ht="40" customHeight="1">
+      <c r="A1294" s="4"/>
+      <c r="B1294" s="5"/>
+      <c r="C1294" s="5"/>
+    </row>
+    <row r="1295" spans="1:3" ht="40" customHeight="1">
+      <c r="A1295" s="4"/>
+      <c r="B1295" s="5"/>
+      <c r="C1295" s="5"/>
+    </row>
+    <row r="1296" spans="1:3" ht="40" customHeight="1">
+      <c r="A1296" s="4"/>
+      <c r="B1296" s="5"/>
+      <c r="C1296" s="5"/>
+    </row>
+    <row r="1297" spans="1:3" ht="40" customHeight="1">
+      <c r="A1297" s="4"/>
+      <c r="B1297" s="5"/>
+      <c r="C1297" s="5"/>
+    </row>
+    <row r="1298" spans="1:3" ht="40" customHeight="1">
+      <c r="A1298" s="4"/>
+      <c r="B1298" s="5"/>
+      <c r="C1298" s="5"/>
+    </row>
+    <row r="1299" spans="1:3" ht="40" customHeight="1">
+      <c r="A1299" s="4"/>
+      <c r="B1299" s="5"/>
+      <c r="C1299" s="5"/>
+    </row>
+    <row r="1300" spans="1:3" ht="40" customHeight="1">
+      <c r="A1300" s="4"/>
+      <c r="B1300" s="5"/>
+      <c r="C1300" s="5"/>
+    </row>
+    <row r="1301" spans="1:3" ht="40" customHeight="1">
+      <c r="A1301" s="4"/>
+      <c r="B1301" s="5"/>
+      <c r="C1301" s="5"/>
+    </row>
+    <row r="1302" spans="1:3" ht="40" customHeight="1">
+      <c r="A1302" s="4"/>
+      <c r="B1302" s="5"/>
+      <c r="C1302" s="5"/>
+    </row>
+    <row r="1303" spans="1:3" ht="40" customHeight="1">
+      <c r="A1303" s="4"/>
+      <c r="B1303" s="5"/>
+      <c r="C1303" s="5"/>
+    </row>
+    <row r="1304" spans="1:3" ht="40" customHeight="1">
+      <c r="A1304" s="4"/>
+      <c r="B1304" s="5"/>
+      <c r="C1304" s="5"/>
+    </row>
+    <row r="1305" spans="1:3" ht="40" customHeight="1">
+      <c r="A1305" s="4"/>
+      <c r="B1305" s="5"/>
+      <c r="C1305" s="5"/>
+    </row>
+    <row r="1306" spans="1:3" ht="40" customHeight="1">
+      <c r="A1306" s="4"/>
+      <c r="B1306" s="5"/>
+      <c r="C1306" s="5"/>
+    </row>
+    <row r="1307" spans="1:3" ht="40" customHeight="1">
+      <c r="A1307" s="4"/>
+      <c r="B1307" s="5"/>
+      <c r="C1307" s="5"/>
+    </row>
+    <row r="1308" spans="1:3" ht="40" customHeight="1">
+      <c r="A1308" s="4"/>
+      <c r="B1308" s="5"/>
+      <c r="C1308" s="5"/>
+    </row>
+    <row r="1309" spans="1:3" ht="40" customHeight="1">
+      <c r="A1309" s="4"/>
+      <c r="B1309" s="5"/>
+      <c r="C1309" s="5"/>
+    </row>
+    <row r="1310" spans="1:3" ht="40" customHeight="1">
+      <c r="A1310" s="4"/>
+      <c r="B1310" s="5"/>
+      <c r="C1310" s="5"/>
+    </row>
+    <row r="1311" spans="1:3" ht="40" customHeight="1">
+      <c r="A1311" s="4"/>
+      <c r="B1311" s="5"/>
+      <c r="C1311" s="5"/>
+    </row>
+    <row r="1312" spans="1:3" ht="40" customHeight="1">
+      <c r="A1312" s="4"/>
+      <c r="B1312" s="5"/>
+      <c r="C1312" s="5"/>
+    </row>
+    <row r="1313" spans="1:3" ht="40" customHeight="1">
+      <c r="A1313" s="4"/>
+      <c r="B1313" s="5"/>
+      <c r="C1313" s="5"/>
+    </row>
+    <row r="1314" spans="1:3" ht="40" customHeight="1">
+      <c r="A1314" s="4"/>
+      <c r="B1314" s="5"/>
+      <c r="C1314" s="5"/>
+    </row>
+    <row r="1315" spans="1:3" ht="40" customHeight="1">
+      <c r="A1315" s="4"/>
+      <c r="B1315" s="5"/>
+      <c r="C1315" s="5"/>
+    </row>
+    <row r="1316" spans="1:3" ht="40" customHeight="1">
+      <c r="A1316" s="4"/>
+      <c r="B1316" s="5"/>
+      <c r="C1316" s="5"/>
+    </row>
+    <row r="1317" spans="1:3" ht="40" customHeight="1">
+      <c r="A1317" s="4"/>
+      <c r="B1317" s="5"/>
+      <c r="C1317" s="5"/>
+    </row>
+    <row r="1318" spans="1:3" ht="40" customHeight="1">
+      <c r="A1318" s="4"/>
+      <c r="B1318" s="5"/>
+      <c r="C1318" s="5"/>
+    </row>
+    <row r="1319" spans="1:3" ht="40" customHeight="1">
+      <c r="A1319" s="4"/>
+      <c r="B1319" s="5"/>
+      <c r="C1319" s="5"/>
+    </row>
+    <row r="1320" spans="1:3" ht="40" customHeight="1">
+      <c r="A1320" s="4"/>
+      <c r="B1320" s="5"/>
+      <c r="C1320" s="5"/>
+    </row>
+    <row r="1321" spans="1:3" ht="40" customHeight="1">
+      <c r="A1321" s="4"/>
+      <c r="B1321" s="5"/>
+      <c r="C1321" s="5"/>
+    </row>
+    <row r="1322" spans="1:3" ht="40" customHeight="1">
+      <c r="A1322" s="4"/>
+      <c r="B1322" s="5"/>
+      <c r="C1322" s="5"/>
+    </row>
+    <row r="1323" spans="1:3" ht="40" customHeight="1">
+      <c r="A1323" s="4"/>
+      <c r="B1323" s="5"/>
+      <c r="C1323" s="5"/>
+    </row>
+    <row r="1324" spans="1:3" ht="40" customHeight="1">
+      <c r="A1324" s="4"/>
+      <c r="B1324" s="5"/>
+      <c r="C1324" s="5"/>
+    </row>
+    <row r="1325" spans="1:3" ht="40" customHeight="1">
+      <c r="A1325" s="4"/>
+      <c r="B1325" s="5"/>
+      <c r="C1325" s="5"/>
+    </row>
+    <row r="1326" spans="1:3" ht="40" customHeight="1">
+      <c r="A1326" s="4"/>
+      <c r="B1326" s="5"/>
+      <c r="C1326" s="5"/>
+    </row>
+    <row r="1327" spans="1:3" ht="40" customHeight="1">
+      <c r="A1327" s="4"/>
+      <c r="B1327" s="5"/>
+      <c r="C1327" s="5"/>
+    </row>
+    <row r="1328" spans="1:3" ht="40" customHeight="1">
+      <c r="A1328" s="4"/>
+      <c r="B1328" s="5"/>
+      <c r="C1328" s="5"/>
+    </row>
+    <row r="1329" spans="1:3" ht="40" customHeight="1">
+      <c r="A1329" s="4"/>
+      <c r="B1329" s="5"/>
+      <c r="C1329" s="5"/>
+    </row>
+    <row r="1330" spans="1:3" ht="40" customHeight="1">
+      <c r="A1330" s="4"/>
+      <c r="B1330" s="5"/>
+      <c r="C1330" s="5"/>
+    </row>
+    <row r="1331" spans="1:3" ht="40" customHeight="1">
+      <c r="A1331" s="4"/>
+      <c r="B1331" s="5"/>
+      <c r="C1331" s="5"/>
+    </row>
+    <row r="1332" spans="1:3" ht="40" customHeight="1">
+      <c r="A1332" s="4"/>
+      <c r="B1332" s="5"/>
+      <c r="C1332" s="5"/>
+    </row>
+    <row r="1333" spans="1:3" ht="40" customHeight="1">
+      <c r="A1333" s="4"/>
+      <c r="B1333" s="5"/>
+      <c r="C1333" s="5"/>
+    </row>
+    <row r="1334" spans="1:3" ht="40" customHeight="1">
+      <c r="A1334" s="4"/>
+      <c r="B1334" s="5"/>
+      <c r="C1334" s="5"/>
+    </row>
+    <row r="1335" spans="1:3" ht="40" customHeight="1">
+      <c r="A1335" s="4"/>
+      <c r="B1335" s="5"/>
+      <c r="C1335" s="5"/>
+    </row>
+    <row r="1336" spans="1:3" ht="40" customHeight="1">
+      <c r="A1336" s="4"/>
+      <c r="B1336" s="5"/>
+      <c r="C1336" s="5"/>
+    </row>
+    <row r="1337" spans="1:3" ht="40" customHeight="1">
+      <c r="A1337" s="4"/>
+      <c r="B1337" s="5"/>
+      <c r="C1337" s="5"/>
+    </row>
+    <row r="1338" spans="1:3" ht="40" customHeight="1">
+      <c r="A1338" s="4"/>
+      <c r="B1338" s="5"/>
+      <c r="C1338" s="5"/>
+    </row>
+    <row r="1339" spans="1:3" ht="40" customHeight="1">
+      <c r="A1339" s="4"/>
+      <c r="B1339" s="5"/>
+      <c r="C1339" s="5"/>
+    </row>
+    <row r="1340" spans="1:3" ht="40" customHeight="1">
+      <c r="A1340" s="4"/>
+      <c r="B1340" s="5"/>
+      <c r="C1340" s="5"/>
+    </row>
+    <row r="1341" spans="1:3" ht="40" customHeight="1">
+      <c r="A1341" s="4"/>
+      <c r="B1341" s="5"/>
+      <c r="C1341" s="5"/>
+    </row>
+    <row r="1342" spans="1:3" ht="40" customHeight="1">
+      <c r="A1342" s="4"/>
+      <c r="B1342" s="5"/>
+      <c r="C1342" s="5"/>
+    </row>
+    <row r="1343" spans="1:3" ht="40" customHeight="1">
+      <c r="A1343" s="4"/>
+      <c r="B1343" s="5"/>
+      <c r="C1343" s="5"/>
+    </row>
+    <row r="1344" spans="1:3" ht="40" customHeight="1">
+      <c r="A1344" s="4"/>
+      <c r="B1344" s="5"/>
+      <c r="C1344" s="5"/>
+    </row>
+    <row r="1345" spans="1:3" ht="40" customHeight="1">
+      <c r="A1345" s="4"/>
+      <c r="B1345" s="5"/>
+      <c r="C1345" s="5"/>
+    </row>
+    <row r="1346" spans="1:3" ht="40" customHeight="1">
+      <c r="A1346" s="4"/>
+      <c r="B1346" s="5"/>
+      <c r="C1346" s="5"/>
+    </row>
+    <row r="1347" spans="1:3" ht="40" customHeight="1">
+      <c r="A1347" s="4"/>
+      <c r="B1347" s="5"/>
+      <c r="C1347" s="5"/>
+    </row>
+    <row r="1348" spans="1:3" ht="40" customHeight="1">
+      <c r="A1348" s="4"/>
+      <c r="B1348" s="5"/>
+      <c r="C1348" s="5"/>
+    </row>
+    <row r="1349" spans="1:3" ht="40" customHeight="1">
+      <c r="A1349" s="4"/>
+      <c r="B1349" s="5"/>
+      <c r="C1349" s="5"/>
+    </row>
+    <row r="1350" spans="1:3" ht="40" customHeight="1">
+      <c r="A1350" s="4"/>
+      <c r="B1350" s="5"/>
+      <c r="C1350" s="5"/>
+    </row>
+    <row r="1351" spans="1:3" ht="40" customHeight="1">
+      <c r="A1351" s="4"/>
+      <c r="B1351" s="5"/>
+      <c r="C1351" s="5"/>
+    </row>
+    <row r="1352" spans="1:3" ht="40" customHeight="1">
+      <c r="A1352" s="4"/>
+      <c r="B1352" s="5"/>
+      <c r="C1352" s="5"/>
+    </row>
+    <row r="1353" spans="1:3" ht="40" customHeight="1">
+      <c r="A1353" s="4"/>
+      <c r="B1353" s="5"/>
+      <c r="C1353" s="5"/>
+    </row>
+    <row r="1354" spans="1:3" ht="40" customHeight="1">
+      <c r="A1354" s="4"/>
+      <c r="B1354" s="5"/>
+      <c r="C1354" s="5"/>
+    </row>
+    <row r="1355" spans="1:3" ht="40" customHeight="1">
+      <c r="A1355" s="4"/>
+      <c r="B1355" s="5"/>
+      <c r="C1355" s="5"/>
+    </row>
+    <row r="1356" spans="1:3" ht="40" customHeight="1">
+      <c r="A1356" s="4"/>
+      <c r="B1356" s="5"/>
+      <c r="C1356" s="5"/>
+    </row>
+    <row r="1357" spans="1:3" ht="40" customHeight="1">
+      <c r="A1357" s="4"/>
+      <c r="B1357" s="5"/>
+      <c r="C1357" s="5"/>
+    </row>
+    <row r="1358" spans="1:3" ht="40" customHeight="1">
+      <c r="A1358" s="4"/>
+      <c r="B1358" s="5"/>
+      <c r="C1358" s="5"/>
+    </row>
+    <row r="1359" spans="1:3" ht="40" customHeight="1">
+      <c r="A1359" s="4"/>
+      <c r="B1359" s="5"/>
+      <c r="C1359" s="5"/>
+    </row>
+    <row r="1360" spans="1:3" ht="40" customHeight="1">
+      <c r="A1360" s="4"/>
+      <c r="B1360" s="5"/>
+      <c r="C1360" s="5"/>
+    </row>
+    <row r="1361" spans="1:3" ht="40" customHeight="1">
+      <c r="A1361" s="4"/>
+      <c r="B1361" s="5"/>
+      <c r="C1361" s="5"/>
+    </row>
+    <row r="1362" spans="1:3" ht="40" customHeight="1">
+      <c r="A1362" s="4"/>
+      <c r="B1362" s="5"/>
+      <c r="C1362" s="5"/>
+    </row>
+    <row r="1363" spans="1:3" ht="40" customHeight="1">
+      <c r="A1363" s="4"/>
+      <c r="B1363" s="5"/>
+      <c r="C1363" s="5"/>
+    </row>
+    <row r="1364" spans="1:3" ht="40" customHeight="1">
+      <c r="A1364" s="4"/>
+      <c r="B1364" s="5"/>
+      <c r="C1364" s="5"/>
+    </row>
+    <row r="1365" spans="1:3" ht="40" customHeight="1">
+      <c r="A1365" s="4"/>
+      <c r="B1365" s="5"/>
+      <c r="C1365" s="5"/>
+    </row>
+    <row r="1366" spans="1:3" ht="40" customHeight="1">
+      <c r="A1366" s="4"/>
+      <c r="B1366" s="5"/>
+      <c r="C1366" s="5"/>
+    </row>
+    <row r="1367" spans="1:3" ht="40" customHeight="1">
+      <c r="A1367" s="4"/>
+      <c r="B1367" s="5"/>
+      <c r="C1367" s="5"/>
+    </row>
+    <row r="1368" spans="1:3" ht="40" customHeight="1">
+      <c r="A1368" s="4"/>
+      <c r="B1368" s="5"/>
+      <c r="C1368" s="5"/>
+    </row>
+    <row r="1369" spans="1:3" ht="40" customHeight="1">
+      <c r="A1369" s="4"/>
+      <c r="B1369" s="5"/>
+      <c r="C1369" s="5"/>
+    </row>
+    <row r="1370" spans="1:3" ht="40" customHeight="1">
+      <c r="A1370" s="4"/>
+      <c r="B1370" s="5"/>
+      <c r="C1370" s="5"/>
+    </row>
+    <row r="1371" spans="1:3" ht="40" customHeight="1">
+      <c r="A1371" s="4"/>
+      <c r="B1371" s="5"/>
+      <c r="C1371" s="5"/>
+    </row>
+    <row r="1372" spans="1:3" ht="40" customHeight="1">
+      <c r="A1372" s="4"/>
+      <c r="B1372" s="5"/>
+      <c r="C1372" s="5"/>
+    </row>
+    <row r="1373" spans="1:3" ht="40" customHeight="1">
+      <c r="A1373" s="4"/>
+      <c r="B1373" s="5"/>
+      <c r="C1373" s="5"/>
+    </row>
+    <row r="1374" spans="1:3" ht="40" customHeight="1">
+      <c r="A1374" s="4"/>
+      <c r="B1374" s="5"/>
+      <c r="C1374" s="5"/>
+    </row>
+    <row r="1375" spans="1:3" ht="40" customHeight="1">
+      <c r="A1375" s="4"/>
+      <c r="B1375" s="5"/>
+      <c r="C1375" s="5"/>
+    </row>
+    <row r="1376" spans="1:3" ht="40" customHeight="1">
+      <c r="A1376" s="4"/>
+      <c r="B1376" s="5"/>
+      <c r="C1376" s="5"/>
+    </row>
+    <row r="1377" spans="1:3" ht="40" customHeight="1">
+      <c r="A1377" s="4"/>
+      <c r="B1377" s="5"/>
+      <c r="C1377" s="5"/>
+    </row>
+    <row r="1378" spans="1:3" ht="40" customHeight="1">
+      <c r="A1378" s="4"/>
+      <c r="B1378" s="5"/>
+      <c r="C1378" s="5"/>
+    </row>
+    <row r="1379" spans="1:3" ht="40" customHeight="1">
+      <c r="A1379" s="4"/>
+      <c r="B1379" s="5"/>
+      <c r="C1379" s="5"/>
+    </row>
+    <row r="1380" spans="1:3" ht="40" customHeight="1">
+      <c r="A1380" s="4"/>
+      <c r="B1380" s="5"/>
+      <c r="C1380" s="5"/>
+    </row>
+    <row r="1381" spans="1:3" ht="40" customHeight="1">
+      <c r="A1381" s="4"/>
+      <c r="B1381" s="5"/>
+      <c r="C1381" s="5"/>
+    </row>
+    <row r="1382" spans="1:3" ht="40" customHeight="1">
+      <c r="A1382" s="4"/>
+      <c r="B1382" s="5"/>
+      <c r="C1382" s="5"/>
+    </row>
+    <row r="1383" spans="1:3" ht="40" customHeight="1">
+      <c r="A1383" s="4"/>
+      <c r="B1383" s="5"/>
+      <c r="C1383" s="5"/>
+    </row>
+    <row r="1384" spans="1:3" ht="40" customHeight="1">
+      <c r="A1384" s="4"/>
+      <c r="B1384" s="5"/>
+      <c r="C1384" s="5"/>
+    </row>
+    <row r="1385" spans="1:3" ht="40" customHeight="1">
+      <c r="A1385" s="4"/>
+      <c r="B1385" s="5"/>
+      <c r="C1385" s="5"/>
+    </row>
+    <row r="1386" spans="1:3" ht="40" customHeight="1">
+      <c r="A1386" s="4"/>
+      <c r="B1386" s="5"/>
+      <c r="C1386" s="5"/>
+    </row>
+    <row r="1387" spans="1:3" ht="40" customHeight="1">
+      <c r="A1387" s="4"/>
+      <c r="B1387" s="5"/>
+      <c r="C1387" s="5"/>
+    </row>
+    <row r="1388" spans="1:3" ht="40" customHeight="1">
+      <c r="A1388" s="4"/>
+      <c r="B1388" s="5"/>
+      <c r="C1388" s="5"/>
+    </row>
+    <row r="1389" spans="1:3" ht="40" customHeight="1">
+      <c r="A1389" s="4"/>
+      <c r="B1389" s="5"/>
+      <c r="C1389" s="5"/>
+    </row>
+    <row r="1390" spans="1:3" ht="40" customHeight="1">
+      <c r="A1390" s="4"/>
+      <c r="B1390" s="5"/>
+      <c r="C1390" s="5"/>
+    </row>
+    <row r="1391" spans="1:3" ht="40" customHeight="1">
+      <c r="A1391" s="4"/>
+      <c r="B1391" s="5"/>
+      <c r="C1391" s="5"/>
+    </row>
+    <row r="1392" spans="1:3" ht="40" customHeight="1">
+      <c r="A1392" s="4"/>
+      <c r="B1392" s="5"/>
+      <c r="C1392" s="5"/>
+    </row>
+    <row r="1393" spans="1:3" ht="40" customHeight="1">
+      <c r="A1393" s="4"/>
+      <c r="B1393" s="5"/>
+      <c r="C1393" s="5"/>
+    </row>
+    <row r="1394" spans="1:3" ht="40" customHeight="1">
+      <c r="A1394" s="4"/>
+      <c r="B1394" s="5"/>
+      <c r="C1394" s="5"/>
+    </row>
+    <row r="1395" spans="1:3" ht="40" customHeight="1">
+      <c r="A1395" s="4"/>
+      <c r="B1395" s="5"/>
+      <c r="C1395" s="5"/>
+    </row>
+    <row r="1396" spans="1:3" ht="40" customHeight="1">
+      <c r="A1396" s="4"/>
+      <c r="B1396" s="5"/>
+      <c r="C1396" s="5"/>
+    </row>
+    <row r="1397" spans="1:3" ht="40" customHeight="1">
+      <c r="A1397" s="4"/>
+      <c r="B1397" s="5"/>
+      <c r="C1397" s="5"/>
+    </row>
+    <row r="1398" spans="1:3" ht="40" customHeight="1">
+      <c r="A1398" s="4"/>
+      <c r="B1398" s="5"/>
+      <c r="C1398" s="5"/>
+    </row>
+    <row r="1399" spans="1:3" ht="40" customHeight="1">
+      <c r="A1399" s="4"/>
+      <c r="B1399" s="5"/>
+      <c r="C1399" s="5"/>
+    </row>
+    <row r="1400" spans="1:3" ht="40" customHeight="1">
+      <c r="A1400" s="4"/>
+      <c r="B1400" s="5"/>
+      <c r="C1400" s="5"/>
+    </row>
+    <row r="1401" spans="1:3" ht="40" customHeight="1">
+      <c r="A1401" s="4"/>
+      <c r="B1401" s="5"/>
+      <c r="C1401" s="5"/>
+    </row>
+    <row r="1402" spans="1:3" ht="40" customHeight="1">
+      <c r="A1402" s="4"/>
+      <c r="B1402" s="5"/>
+      <c r="C1402" s="5"/>
+    </row>
+    <row r="1403" spans="1:3" ht="40" customHeight="1">
+      <c r="A1403" s="4"/>
+      <c r="B1403" s="5"/>
+      <c r="C1403" s="5"/>
+    </row>
+    <row r="1404" spans="1:3" ht="40" customHeight="1">
+      <c r="A1404" s="4"/>
+      <c r="B1404" s="5"/>
+      <c r="C1404" s="5"/>
+    </row>
+    <row r="1405" spans="1:3" ht="40" customHeight="1">
+      <c r="A1405" s="4"/>
+      <c r="B1405" s="5"/>
+      <c r="C1405" s="5"/>
+    </row>
+    <row r="1406" spans="1:3" ht="40" customHeight="1">
+      <c r="A1406" s="4"/>
+      <c r="B1406" s="5"/>
+      <c r="C1406" s="5"/>
+    </row>
+    <row r="1407" spans="1:3" ht="40" customHeight="1">
+      <c r="A1407" s="4"/>
+      <c r="B1407" s="5"/>
+      <c r="C1407" s="5"/>
+    </row>
+    <row r="1408" spans="1:3" ht="40" customHeight="1">
+      <c r="A1408" s="4"/>
+      <c r="B1408" s="5"/>
+      <c r="C1408" s="5"/>
+    </row>
+    <row r="1409" spans="1:3" ht="40" customHeight="1">
+      <c r="A1409" s="4"/>
+      <c r="B1409" s="5"/>
+      <c r="C1409" s="5"/>
+    </row>
+    <row r="1410" spans="1:3" ht="40" customHeight="1">
+      <c r="A1410" s="4"/>
+      <c r="B1410" s="5"/>
+      <c r="C1410" s="5"/>
+    </row>
+    <row r="1411" spans="1:3" ht="40" customHeight="1">
+      <c r="A1411" s="4"/>
+      <c r="B1411" s="5"/>
+      <c r="C1411" s="5"/>
+    </row>
+    <row r="1412" spans="1:3" ht="40" customHeight="1">
+      <c r="A1412" s="4"/>
+      <c r="B1412" s="5"/>
+      <c r="C1412" s="5"/>
+    </row>
+    <row r="1413" spans="1:3" ht="40" customHeight="1">
+      <c r="A1413" s="4"/>
+      <c r="B1413" s="5"/>
+      <c r="C1413" s="5"/>
+    </row>
+    <row r="1414" spans="1:3" ht="40" customHeight="1">
+      <c r="A1414" s="4"/>
+      <c r="B1414" s="5"/>
+      <c r="C1414" s="5"/>
+    </row>
+    <row r="1415" spans="1:3" ht="40" customHeight="1">
+      <c r="A1415" s="4"/>
+      <c r="B1415" s="5"/>
+      <c r="C1415" s="5"/>
+    </row>
+    <row r="1416" spans="1:3" ht="40" customHeight="1">
+      <c r="A1416" s="4"/>
+      <c r="B1416" s="5"/>
+      <c r="C1416" s="5"/>
+    </row>
+    <row r="1417" spans="1:3" ht="40" customHeight="1">
+      <c r="A1417" s="4"/>
+      <c r="B1417" s="5"/>
+      <c r="C1417" s="5"/>
+    </row>
+    <row r="1418" spans="1:3" ht="40" customHeight="1">
+      <c r="A1418" s="4"/>
+      <c r="B1418" s="5"/>
+      <c r="C1418" s="5"/>
+    </row>
+    <row r="1419" spans="1:3" ht="40" customHeight="1">
+      <c r="A1419" s="4"/>
+      <c r="B1419" s="5"/>
+      <c r="C1419" s="5"/>
+    </row>
+    <row r="1420" spans="1:3" ht="40" customHeight="1">
+      <c r="A1420" s="4"/>
+      <c r="B1420" s="5"/>
+      <c r="C1420" s="5"/>
+    </row>
+    <row r="1421" spans="1:3" ht="40" customHeight="1">
+      <c r="A1421" s="4"/>
+      <c r="B1421" s="5"/>
+      <c r="C1421" s="5"/>
+    </row>
+    <row r="1422" spans="1:3" ht="40" customHeight="1">
+      <c r="A1422" s="4"/>
+      <c r="B1422" s="5"/>
+      <c r="C1422" s="5"/>
+    </row>
+    <row r="1423" spans="1:3" ht="40" customHeight="1">
+      <c r="A1423" s="4"/>
+      <c r="B1423" s="5"/>
+      <c r="C1423" s="5"/>
+    </row>
+    <row r="1424" spans="1:3" ht="40" customHeight="1">
+      <c r="A1424" s="4"/>
+      <c r="B1424" s="5"/>
+      <c r="C1424" s="5"/>
+    </row>
+    <row r="1425" spans="1:3" ht="40" customHeight="1">
+      <c r="A1425" s="4"/>
+      <c r="B1425" s="5"/>
+      <c r="C1425" s="5"/>
+    </row>
+    <row r="1426" spans="1:3" ht="40" customHeight="1">
+      <c r="A1426" s="4"/>
+      <c r="B1426" s="5"/>
+      <c r="C1426" s="5"/>
+    </row>
+    <row r="1427" spans="1:3" ht="40" customHeight="1">
+      <c r="A1427" s="4"/>
+      <c r="B1427" s="5"/>
+      <c r="C1427" s="5"/>
+    </row>
+    <row r="1428" spans="1:3" ht="40" customHeight="1">
+      <c r="A1428" s="4"/>
+      <c r="B1428" s="5"/>
+      <c r="C1428" s="5"/>
+    </row>
+    <row r="1429" spans="1:3" ht="40" customHeight="1">
+      <c r="A1429" s="4"/>
+      <c r="B1429" s="5"/>
+      <c r="C1429" s="5"/>
+    </row>
+    <row r="1430" spans="1:3" ht="40" customHeight="1">
+      <c r="A1430" s="4"/>
+      <c r="B1430" s="5"/>
+      <c r="C1430" s="5"/>
+    </row>
+    <row r="1431" spans="1:3" ht="40" customHeight="1">
+      <c r="A1431" s="4"/>
+      <c r="B1431" s="5"/>
+      <c r="C1431" s="5"/>
+    </row>
+    <row r="1432" spans="1:3" ht="40" customHeight="1">
+      <c r="A1432" s="4"/>
+      <c r="B1432" s="5"/>
+      <c r="C1432" s="5"/>
+    </row>
+    <row r="1433" spans="1:3" ht="40" customHeight="1">
+      <c r="A1433" s="4"/>
+      <c r="B1433" s="5"/>
+      <c r="C1433" s="5"/>
+    </row>
+    <row r="1434" spans="1:3" ht="40" customHeight="1">
+      <c r="A1434" s="4"/>
+      <c r="B1434" s="5"/>
+      <c r="C1434" s="5"/>
+    </row>
+    <row r="1435" spans="1:3" ht="40" customHeight="1">
+      <c r="A1435" s="4"/>
+      <c r="B1435" s="5"/>
+      <c r="C1435" s="5"/>
+    </row>
+    <row r="1436" spans="1:3" ht="40" customHeight="1">
+      <c r="A1436" s="4"/>
+      <c r="B1436" s="5"/>
+      <c r="C1436" s="5"/>
+    </row>
+    <row r="1437" spans="1:3" ht="40" customHeight="1">
+      <c r="A1437" s="4"/>
+      <c r="B1437" s="5"/>
+      <c r="C1437" s="5"/>
+    </row>
+    <row r="1438" spans="1:3" ht="40" customHeight="1">
+      <c r="A1438" s="4"/>
+      <c r="B1438" s="5"/>
+      <c r="C1438" s="5"/>
+    </row>
+    <row r="1439" spans="1:3" ht="40" customHeight="1">
+      <c r="A1439" s="4"/>
+      <c r="B1439" s="5"/>
+      <c r="C1439" s="5"/>
+    </row>
+    <row r="1440" spans="1:3" ht="40" customHeight="1">
+      <c r="A1440" s="4"/>
+      <c r="B1440" s="5"/>
+      <c r="C1440" s="5"/>
+    </row>
+    <row r="1441" spans="1:3" ht="40" customHeight="1">
+      <c r="A1441" s="4"/>
+      <c r="B1441" s="5"/>
+      <c r="C1441" s="5"/>
+    </row>
+    <row r="1442" spans="1:3" ht="40" customHeight="1">
+      <c r="A1442" s="4"/>
+      <c r="B1442" s="5"/>
+      <c r="C1442" s="5"/>
+    </row>
+    <row r="1443" spans="1:3" ht="40" customHeight="1">
+      <c r="A1443" s="4"/>
+      <c r="B1443" s="5"/>
+      <c r="C1443" s="5"/>
+    </row>
+    <row r="1444" spans="1:3" ht="40" customHeight="1">
+      <c r="A1444" s="4"/>
+      <c r="B1444" s="5"/>
+      <c r="C1444" s="5"/>
+    </row>
+    <row r="1445" spans="1:3" ht="40" customHeight="1">
+      <c r="A1445" s="4"/>
+      <c r="B1445" s="5"/>
+      <c r="C1445" s="5"/>
+    </row>
+    <row r="1446" spans="1:3" ht="40" customHeight="1">
+      <c r="A1446" s="4"/>
+      <c r="B1446" s="5"/>
+      <c r="C1446" s="5"/>
+    </row>
+    <row r="1447" spans="1:3" ht="40" customHeight="1">
+      <c r="A1447" s="4"/>
+      <c r="B1447" s="5"/>
+      <c r="C1447" s="5"/>
+    </row>
+    <row r="1448" spans="1:3" ht="40" customHeight="1">
+      <c r="A1448" s="4"/>
+      <c r="B1448" s="5"/>
+      <c r="C1448" s="5"/>
+    </row>
+    <row r="1449" spans="1:3" ht="40" customHeight="1">
+      <c r="A1449" s="4"/>
+      <c r="B1449" s="5"/>
+      <c r="C1449" s="5"/>
+    </row>
+    <row r="1450" spans="1:3" ht="40" customHeight="1">
+      <c r="A1450" s="4"/>
+      <c r="B1450" s="5"/>
+      <c r="C1450" s="5"/>
+    </row>
+    <row r="1451" spans="1:3" ht="40" customHeight="1">
+      <c r="A1451" s="4"/>
+      <c r="B1451" s="5"/>
+      <c r="C1451" s="5"/>
+    </row>
+    <row r="1452" spans="1:3" ht="40" customHeight="1">
+      <c r="A1452" s="4"/>
+      <c r="B1452" s="5"/>
+      <c r="C1452" s="5"/>
+    </row>
+    <row r="1453" spans="1:3" ht="40" customHeight="1">
+      <c r="A1453" s="4"/>
+      <c r="B1453" s="5"/>
+      <c r="C1453" s="5"/>
+    </row>
+    <row r="1454" spans="1:3" ht="40" customHeight="1">
+      <c r="A1454" s="4"/>
+      <c r="B1454" s="5"/>
+      <c r="C1454" s="5"/>
+    </row>
+    <row r="1455" spans="1:3" ht="40" customHeight="1">
+      <c r="A1455" s="4"/>
+      <c r="B1455" s="5"/>
+      <c r="C1455" s="5"/>
+    </row>
+    <row r="1456" spans="1:3" ht="40" customHeight="1">
+      <c r="A1456" s="4"/>
+      <c r="B1456" s="5"/>
+      <c r="C1456" s="5"/>
+    </row>
+    <row r="1457" spans="1:3" ht="40" customHeight="1">
+      <c r="A1457" s="4"/>
+      <c r="B1457" s="5"/>
+      <c r="C1457" s="5"/>
+    </row>
+    <row r="1458" spans="1:3" ht="40" customHeight="1">
+      <c r="A1458" s="4"/>
+      <c r="B1458" s="5"/>
+      <c r="C1458" s="5"/>
+    </row>
+    <row r="1459" spans="1:3" ht="40" customHeight="1">
+      <c r="A1459" s="4"/>
+      <c r="B1459" s="5"/>
+      <c r="C1459" s="5"/>
+    </row>
+    <row r="1460" spans="1:3" ht="40" customHeight="1">
+      <c r="A1460" s="4"/>
+      <c r="B1460" s="5"/>
+      <c r="C1460" s="5"/>
+    </row>
+    <row r="1461" spans="1:3" ht="40" customHeight="1">
+      <c r="A1461" s="4"/>
+      <c r="B1461" s="5"/>
+      <c r="C1461" s="5"/>
+    </row>
+    <row r="1462" spans="1:3" ht="40" customHeight="1">
+      <c r="A1462" s="4"/>
+      <c r="B1462" s="5"/>
+      <c r="C1462" s="5"/>
+    </row>
+    <row r="1463" spans="1:3" ht="40" customHeight="1">
+      <c r="A1463" s="4"/>
+      <c r="B1463" s="5"/>
+      <c r="C1463" s="5"/>
+    </row>
+    <row r="1464" spans="1:3" ht="40" customHeight="1">
+      <c r="A1464" s="4"/>
+      <c r="B1464" s="5"/>
+      <c r="C1464" s="5"/>
+    </row>
+    <row r="1465" spans="1:3" ht="40" customHeight="1">
+      <c r="A1465" s="4"/>
+      <c r="B1465" s="5"/>
+      <c r="C1465" s="5"/>
+    </row>
+    <row r="1466" spans="1:3" ht="40" customHeight="1">
+      <c r="A1466" s="4"/>
+      <c r="B1466" s="5"/>
+      <c r="C1466" s="5"/>
+    </row>
+    <row r="1467" spans="1:3" ht="40" customHeight="1">
+      <c r="A1467" s="4"/>
+      <c r="B1467" s="5"/>
+      <c r="C1467" s="5"/>
+    </row>
+    <row r="1468" spans="1:3" ht="40" customHeight="1">
+      <c r="A1468" s="4"/>
+      <c r="B1468" s="5"/>
+      <c r="C1468" s="5"/>
+    </row>
+    <row r="1469" spans="1:3" ht="40" customHeight="1">
+      <c r="A1469" s="4"/>
+      <c r="B1469" s="5"/>
+      <c r="C1469" s="5"/>
+    </row>
+    <row r="1470" spans="1:3" ht="40" customHeight="1">
+      <c r="A1470" s="4"/>
+      <c r="B1470" s="5"/>
+      <c r="C1470" s="5"/>
+    </row>
+    <row r="1471" spans="1:3" ht="40" customHeight="1">
+      <c r="A1471" s="4"/>
+      <c r="B1471" s="5"/>
+      <c r="C1471" s="5"/>
+    </row>
+    <row r="1472" spans="1:3" ht="40" customHeight="1">
+      <c r="A1472" s="4"/>
+      <c r="B1472" s="5"/>
+      <c r="C1472" s="5"/>
+    </row>
+    <row r="1473" spans="1:3" ht="40" customHeight="1">
+      <c r="A1473" s="4"/>
+      <c r="B1473" s="5"/>
+      <c r="C1473" s="5"/>
+    </row>
+    <row r="1474" spans="1:3" ht="40" customHeight="1">
+      <c r="A1474" s="4"/>
+      <c r="B1474" s="5"/>
+      <c r="C1474" s="5"/>
+    </row>
+    <row r="1475" spans="1:3" ht="40" customHeight="1">
+      <c r="A1475" s="4"/>
+      <c r="B1475" s="5"/>
+      <c r="C1475" s="5"/>
+    </row>
+    <row r="1476" spans="1:3" ht="40" customHeight="1">
+      <c r="A1476" s="4"/>
+      <c r="B1476" s="5"/>
+      <c r="C1476" s="5"/>
+    </row>
+    <row r="1477" spans="1:3" ht="40" customHeight="1">
+      <c r="A1477" s="4"/>
+      <c r="B1477" s="5"/>
+      <c r="C1477" s="5"/>
+    </row>
+    <row r="1478" spans="1:3" ht="40" customHeight="1">
+      <c r="A1478" s="4"/>
+      <c r="B1478" s="5"/>
+      <c r="C1478" s="5"/>
+    </row>
+    <row r="1479" spans="1:3" ht="40" customHeight="1">
+      <c r="A1479" s="4"/>
+      <c r="B1479" s="5"/>
+      <c r="C1479" s="5"/>
+    </row>
+    <row r="1480" spans="1:3" ht="40" customHeight="1">
+      <c r="A1480" s="4"/>
+      <c r="B1480" s="5"/>
+      <c r="C1480" s="5"/>
+    </row>
+    <row r="1481" spans="1:3" ht="40" customHeight="1">
+      <c r="A1481" s="4"/>
+      <c r="B1481" s="5"/>
+      <c r="C1481" s="5"/>
+    </row>
+    <row r="1482" spans="1:3" ht="40" customHeight="1">
+      <c r="A1482" s="4"/>
+      <c r="B1482" s="5"/>
+      <c r="C1482" s="5"/>
+    </row>
+    <row r="1483" spans="1:3" ht="40" customHeight="1">
+      <c r="A1483" s="4"/>
+      <c r="B1483" s="5"/>
+      <c r="C1483" s="5"/>
+    </row>
+    <row r="1484" spans="1:3" ht="40" customHeight="1">
+      <c r="A1484" s="4"/>
+      <c r="B1484" s="5"/>
+      <c r="C1484" s="5"/>
+    </row>
+    <row r="1485" spans="1:3" ht="40" customHeight="1">
+      <c r="A1485" s="4"/>
+      <c r="B1485" s="5"/>
+      <c r="C1485" s="5"/>
+    </row>
+    <row r="1486" spans="1:3" ht="40" customHeight="1">
+      <c r="A1486" s="4"/>
+      <c r="B1486" s="5"/>
+      <c r="C1486" s="5"/>
+    </row>
+    <row r="1487" spans="1:3" ht="40" customHeight="1">
+      <c r="A1487" s="4"/>
+      <c r="B1487" s="5"/>
+      <c r="C1487" s="5"/>
+    </row>
+    <row r="1488" spans="1:3" ht="40" customHeight="1">
+      <c r="A1488" s="4"/>
+      <c r="B1488" s="5"/>
+      <c r="C1488" s="5"/>
+    </row>
+    <row r="1489" spans="1:3" ht="40" customHeight="1">
+      <c r="A1489" s="4"/>
+      <c r="B1489" s="5"/>
+      <c r="C1489" s="5"/>
+    </row>
+    <row r="1490" spans="1:3" ht="40" customHeight="1">
+      <c r="A1490" s="4"/>
+      <c r="B1490" s="5"/>
+      <c r="C1490" s="5"/>
+    </row>
+    <row r="1491" spans="1:3" ht="40" customHeight="1">
+      <c r="A1491" s="4"/>
+      <c r="B1491" s="5"/>
+      <c r="C1491" s="5"/>
+    </row>
+    <row r="1492" spans="1:3" ht="40" customHeight="1">
+      <c r="A1492" s="4"/>
+      <c r="B1492" s="5"/>
+      <c r="C1492" s="5"/>
+    </row>
+    <row r="1493" spans="1:3" ht="40" customHeight="1">
+      <c r="A1493" s="4"/>
+      <c r="B1493" s="5"/>
+      <c r="C1493" s="5"/>
+    </row>
+    <row r="1494" spans="1:3" ht="40" customHeight="1">
+      <c r="A1494" s="4"/>
+      <c r="B1494" s="5"/>
+      <c r="C1494" s="5"/>
+    </row>
+    <row r="1495" spans="1:3" ht="40" customHeight="1">
+      <c r="A1495" s="4"/>
+      <c r="B1495" s="5"/>
+      <c r="C1495" s="5"/>
+    </row>
+    <row r="1496" spans="1:3" ht="40" customHeight="1">
+      <c r="A1496" s="4"/>
+      <c r="B1496" s="5"/>
+      <c r="C1496" s="5"/>
+    </row>
+    <row r="1497" spans="1:3" ht="40" customHeight="1">
+      <c r="A1497" s="4"/>
+      <c r="B1497" s="5"/>
+      <c r="C1497" s="5"/>
+    </row>
+    <row r="1498" spans="1:3" ht="40" customHeight="1">
+      <c r="A1498" s="4"/>
+      <c r="B1498" s="5"/>
+      <c r="C1498" s="5"/>
+    </row>
+    <row r="1499" spans="1:3" ht="40" customHeight="1">
+      <c r="A1499" s="4"/>
+      <c r="B1499" s="5"/>
+      <c r="C1499" s="5"/>
+    </row>
+    <row r="1500" spans="1:3" ht="40" customHeight="1">
+      <c r="A1500" s="4"/>
+      <c r="B1500" s="5"/>
+      <c r="C1500" s="5"/>
+    </row>
+    <row r="1501" spans="1:3" ht="40" customHeight="1">
+      <c r="A1501" s="4"/>
+      <c r="B1501" s="5"/>
+      <c r="C1501" s="5"/>
+    </row>
+    <row r="1502" spans="1:3" ht="40" customHeight="1">
+      <c r="A1502" s="4"/>
+      <c r="B1502" s="5"/>
+      <c r="C1502" s="5"/>
+    </row>
+    <row r="1503" spans="1:3" ht="40" customHeight="1">
+      <c r="A1503" s="4"/>
+      <c r="B1503" s="5"/>
+      <c r="C1503" s="5"/>
+    </row>
+    <row r="1504" spans="1:3" ht="40" customHeight="1">
+      <c r="A1504" s="4"/>
+      <c r="B1504" s="5"/>
+      <c r="C1504" s="5"/>
+    </row>
+    <row r="1505" spans="1:3" ht="40" customHeight="1">
+      <c r="A1505" s="4"/>
+      <c r="B1505" s="5"/>
+      <c r="C1505" s="5"/>
+    </row>
+    <row r="1506" spans="1:3" ht="40" customHeight="1">
+      <c r="A1506" s="4"/>
+      <c r="B1506" s="5"/>
+      <c r="C1506" s="5"/>
+    </row>
+    <row r="1507" spans="1:3" ht="40" customHeight="1">
+      <c r="A1507" s="4"/>
+      <c r="B1507" s="5"/>
+      <c r="C1507" s="5"/>
+    </row>
+    <row r="1508" spans="1:3" ht="40" customHeight="1">
+      <c r="A1508" s="4"/>
+      <c r="B1508" s="5"/>
+      <c r="C1508" s="5"/>
+    </row>
+    <row r="1509" spans="1:3" ht="40" customHeight="1">
+      <c r="A1509" s="4"/>
+      <c r="B1509" s="5"/>
+      <c r="C1509" s="5"/>
+    </row>
+    <row r="1510" spans="1:3" ht="40" customHeight="1">
+      <c r="A1510" s="4"/>
+      <c r="B1510" s="5"/>
+      <c r="C1510" s="5"/>
+    </row>
+    <row r="1511" spans="1:3" ht="40" customHeight="1">
+      <c r="A1511" s="4"/>
+      <c r="B1511" s="5"/>
+      <c r="C1511" s="5"/>
+    </row>
+    <row r="1512" spans="1:3" ht="40" customHeight="1">
+      <c r="A1512" s="4"/>
+      <c r="B1512" s="5"/>
+      <c r="C1512" s="5"/>
+    </row>
+    <row r="1513" spans="1:3" ht="40" customHeight="1">
+      <c r="A1513" s="4"/>
+      <c r="B1513" s="5"/>
+      <c r="C1513" s="5"/>
+    </row>
+    <row r="1514" spans="1:3" ht="40" customHeight="1">
+      <c r="A1514" s="4"/>
+      <c r="B1514" s="5"/>
+      <c r="C1514" s="5"/>
+    </row>
+    <row r="1515" spans="1:3" ht="40" customHeight="1">
+      <c r="A1515" s="4"/>
+      <c r="B1515" s="5"/>
+      <c r="C1515" s="5"/>
+    </row>
+    <row r="1516" spans="1:3" ht="40" customHeight="1">
+      <c r="A1516" s="4"/>
+      <c r="B1516" s="5"/>
+      <c r="C1516" s="5"/>
+    </row>
+    <row r="1517" spans="1:3" ht="40" customHeight="1">
+      <c r="A1517" s="4"/>
+      <c r="B1517" s="5"/>
+      <c r="C1517" s="5"/>
+    </row>
+    <row r="1518" spans="1:3" ht="40" customHeight="1">
+      <c r="A1518" s="4"/>
+      <c r="B1518" s="5"/>
+      <c r="C1518" s="5"/>
+    </row>
+    <row r="1519" spans="1:3" ht="40" customHeight="1">
+      <c r="A1519" s="4"/>
+      <c r="B1519" s="5"/>
+      <c r="C1519" s="5"/>
+    </row>
+    <row r="1520" spans="1:3" ht="40" customHeight="1">
+      <c r="A1520" s="4"/>
+      <c r="B1520" s="5"/>
+      <c r="C1520" s="5"/>
+    </row>
+    <row r="1521" spans="1:3" ht="40" customHeight="1">
+      <c r="A1521" s="4"/>
+      <c r="B1521" s="5"/>
+      <c r="C1521" s="5"/>
+    </row>
+    <row r="1522" spans="1:3" ht="40" customHeight="1">
+      <c r="A1522" s="4"/>
+      <c r="B1522" s="5"/>
+      <c r="C1522" s="5"/>
+    </row>
+    <row r="1523" spans="1:3" ht="40" customHeight="1">
+      <c r="A1523" s="4"/>
+      <c r="B1523" s="5"/>
+      <c r="C1523" s="5"/>
+    </row>
+    <row r="1524" spans="1:3" ht="40" customHeight="1">
+      <c r="A1524" s="4"/>
+      <c r="B1524" s="5"/>
+      <c r="C1524" s="5"/>
+    </row>
+    <row r="1525" spans="1:3" ht="40" customHeight="1">
+      <c r="A1525" s="4"/>
+      <c r="B1525" s="5"/>
+      <c r="C1525" s="5"/>
+    </row>
+    <row r="1526" spans="1:3" ht="40" customHeight="1">
+      <c r="A1526" s="4"/>
+      <c r="B1526" s="5"/>
+      <c r="C1526" s="5"/>
+    </row>
+    <row r="1527" spans="1:3" ht="40" customHeight="1">
+      <c r="A1527" s="4"/>
+      <c r="B1527" s="5"/>
+      <c r="C1527" s="5"/>
+    </row>
+    <row r="1528" spans="1:3" ht="40" customHeight="1">
+      <c r="A1528" s="4"/>
+      <c r="B1528" s="5"/>
+      <c r="C1528" s="5"/>
+    </row>
+    <row r="1529" spans="1:3" ht="40" customHeight="1">
+      <c r="A1529" s="4"/>
+      <c r="B1529" s="5"/>
+      <c r="C1529" s="5"/>
+    </row>
+    <row r="1530" spans="1:3" ht="40" customHeight="1">
+      <c r="A1530" s="4"/>
+      <c r="B1530" s="5"/>
+      <c r="C1530" s="5"/>
+    </row>
+    <row r="1531" spans="1:3" ht="40" customHeight="1">
+      <c r="A1531" s="4"/>
+      <c r="B1531" s="5"/>
+      <c r="C1531" s="5"/>
+    </row>
+    <row r="1532" spans="1:3" ht="40" customHeight="1">
+      <c r="A1532" s="4"/>
+      <c r="B1532" s="5"/>
+      <c r="C1532" s="5"/>
+    </row>
+    <row r="1533" spans="1:3" ht="40" customHeight="1">
+      <c r="A1533" s="4"/>
+      <c r="B1533" s="5"/>
+      <c r="C1533" s="5"/>
+    </row>
+    <row r="1534" spans="1:3" ht="40" customHeight="1">
+      <c r="A1534" s="4"/>
+      <c r="B1534" s="5"/>
+      <c r="C1534" s="5"/>
+    </row>
+    <row r="1535" spans="1:3" ht="40" customHeight="1">
+      <c r="A1535" s="4"/>
+      <c r="B1535" s="5"/>
+      <c r="C1535" s="5"/>
+    </row>
+    <row r="1536" spans="1:3" ht="40" customHeight="1">
+      <c r="A1536" s="4"/>
+      <c r="B1536" s="5"/>
+      <c r="C1536" s="5"/>
+    </row>
+    <row r="1537" spans="1:3" ht="40" customHeight="1">
+      <c r="A1537" s="4"/>
+      <c r="B1537" s="5"/>
+      <c r="C1537" s="5"/>
+    </row>
+    <row r="1538" spans="1:3" ht="40" customHeight="1">
+      <c r="A1538" s="4"/>
+      <c r="B1538" s="5"/>
+      <c r="C1538" s="5"/>
+    </row>
+    <row r="1539" spans="1:3" ht="40" customHeight="1">
+      <c r="A1539" s="4"/>
+      <c r="B1539" s="5"/>
+      <c r="C1539" s="5"/>
+    </row>
+    <row r="1540" spans="1:3" ht="40" customHeight="1">
+      <c r="A1540" s="4"/>
+      <c r="B1540" s="5"/>
+      <c r="C1540" s="5"/>
+    </row>
+    <row r="1541" spans="1:3" ht="40" customHeight="1">
+      <c r="A1541" s="4"/>
+      <c r="B1541" s="5"/>
+      <c r="C1541" s="5"/>
+    </row>
+    <row r="1542" spans="1:3" ht="40" customHeight="1">
+      <c r="A1542" s="4"/>
+      <c r="B1542" s="5"/>
+      <c r="C1542" s="5"/>
+    </row>
+    <row r="1543" spans="1:3" ht="40" customHeight="1">
+      <c r="A1543" s="4"/>
+      <c r="B1543" s="5"/>
+      <c r="C1543" s="5"/>
+    </row>
+    <row r="1544" spans="1:3" ht="40" customHeight="1">
+      <c r="A1544" s="4"/>
+      <c r="B1544" s="5"/>
+      <c r="C1544" s="5"/>
+    </row>
+    <row r="1545" spans="1:3" ht="40" customHeight="1">
+      <c r="A1545" s="4"/>
+      <c r="B1545" s="5"/>
+      <c r="C1545" s="5"/>
+    </row>
+    <row r="1546" spans="1:3" ht="40" customHeight="1">
+      <c r="A1546" s="4"/>
+      <c r="B1546" s="5"/>
+      <c r="C1546" s="5"/>
+    </row>
+    <row r="1547" spans="1:3" ht="40" customHeight="1">
+      <c r="A1547" s="4"/>
+      <c r="B1547" s="5"/>
+      <c r="C1547" s="5"/>
+    </row>
+    <row r="1548" spans="1:3" ht="40" customHeight="1">
+      <c r="A1548" s="4"/>
+      <c r="B1548" s="5"/>
+      <c r="C1548" s="5"/>
+    </row>
+    <row r="1549" spans="1:3" ht="40" customHeight="1">
+      <c r="A1549" s="4"/>
+      <c r="B1549" s="5"/>
+      <c r="C1549" s="5"/>
+    </row>
+    <row r="1550" spans="1:3" ht="40" customHeight="1">
+      <c r="A1550" s="4"/>
+      <c r="B1550" s="5"/>
+      <c r="C1550" s="5"/>
+    </row>
+    <row r="1551" spans="1:3" ht="40" customHeight="1">
+      <c r="A1551" s="4"/>
+      <c r="B1551" s="5"/>
+      <c r="C1551" s="5"/>
+    </row>
+    <row r="1552" spans="1:3" ht="40" customHeight="1">
+      <c r="A1552" s="4"/>
+      <c r="B1552" s="5"/>
+      <c r="C1552" s="5"/>
+    </row>
+    <row r="1553" spans="1:3" ht="40" customHeight="1">
+      <c r="A1553" s="4"/>
+      <c r="B1553" s="5"/>
+      <c r="C1553" s="5"/>
+    </row>
+    <row r="1554" spans="1:3" ht="40" customHeight="1">
+      <c r="A1554" s="4"/>
+      <c r="B1554" s="5"/>
+      <c r="C1554" s="5"/>
+    </row>
+    <row r="1555" spans="1:3" ht="40" customHeight="1">
+      <c r="A1555" s="4"/>
+      <c r="B1555" s="5"/>
+      <c r="C1555" s="5"/>
+    </row>
+    <row r="1556" spans="1:3" ht="40" customHeight="1">
+      <c r="A1556" s="4"/>
+      <c r="B1556" s="5"/>
+      <c r="C1556" s="5"/>
+    </row>
+    <row r="1557" spans="1:3" ht="40" customHeight="1">
+      <c r="A1557" s="4"/>
+      <c r="B1557" s="5"/>
+      <c r="C1557" s="5"/>
+    </row>
+    <row r="1558" spans="1:3" ht="40" customHeight="1">
+      <c r="A1558" s="4"/>
+      <c r="B1558" s="5"/>
+      <c r="C1558" s="5"/>
+    </row>
+    <row r="1559" spans="1:3" ht="40" customHeight="1">
+      <c r="A1559" s="4"/>
+      <c r="B1559" s="5"/>
+      <c r="C1559" s="5"/>
+    </row>
+    <row r="1560" spans="1:3" ht="40" customHeight="1">
+      <c r="A1560" s="4"/>
+      <c r="B1560" s="5"/>
+      <c r="C1560" s="5"/>
+    </row>
+    <row r="1561" spans="1:3" ht="40" customHeight="1">
+      <c r="A1561" s="4"/>
+      <c r="B1561" s="5"/>
+      <c r="C1561" s="5"/>
+    </row>
+    <row r="1562" spans="1:3" ht="40" customHeight="1">
+      <c r="A1562" s="4"/>
+      <c r="B1562" s="5"/>
+      <c r="C1562" s="5"/>
+    </row>
+    <row r="1563" spans="1:3" ht="40" customHeight="1">
+      <c r="A1563" s="4"/>
+      <c r="B1563" s="5"/>
+      <c r="C1563" s="5"/>
+    </row>
+    <row r="1564" spans="1:3" ht="40" customHeight="1">
+      <c r="A1564" s="4"/>
+      <c r="B1564" s="5"/>
+      <c r="C1564" s="5"/>
+    </row>
+    <row r="1565" spans="1:3" ht="40" customHeight="1">
+      <c r="A1565" s="4"/>
+      <c r="B1565" s="5"/>
+      <c r="C1565" s="5"/>
+    </row>
+    <row r="1566" spans="1:3" ht="40" customHeight="1">
+      <c r="A1566" s="4"/>
+      <c r="B1566" s="5"/>
+      <c r="C1566" s="5"/>
+    </row>
+    <row r="1567" spans="1:3" ht="40" customHeight="1">
+      <c r="A1567" s="4"/>
+      <c r="B1567" s="5"/>
+      <c r="C1567" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/files/data.xlsx
+++ b/files/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ferrara/Desktop/salvatore non toccare/monitoraggio/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A46308D4-BA61-0748-BC75-B215FE755D87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{674E478D-0B75-A84E-A70C-0471AA5D20E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1400" yWindow="660" windowWidth="10440" windowHeight="16320" activeTab="1" xr2:uid="{F1546C66-1100-0F4C-AEC5-783BC2578DB8}"/>
+    <workbookView xWindow="1400" yWindow="660" windowWidth="10440" windowHeight="16320" xr2:uid="{F1546C66-1100-0F4C-AEC5-783BC2578DB8}"/>
   </bookViews>
   <sheets>
     <sheet name="vix" sheetId="2" r:id="rId1"/>
@@ -5435,29 +5435,59 @@
       </c>
     </row>
     <row r="451" spans="1:3" ht="23">
-      <c r="A451" s="4"/>
-      <c r="B451" s="5"/>
-      <c r="C451" s="6"/>
+      <c r="A451" s="4">
+        <v>46125</v>
+      </c>
+      <c r="B451" s="5">
+        <v>59.046848301346259</v>
+      </c>
+      <c r="C451" s="6">
+        <v>19.12</v>
+      </c>
     </row>
     <row r="452" spans="1:3" ht="23">
-      <c r="A452" s="4"/>
-      <c r="B452" s="5"/>
-      <c r="C452" s="6"/>
+      <c r="A452" s="4">
+        <v>46126</v>
+      </c>
+      <c r="B452" s="5">
+        <v>59.693038471799618</v>
+      </c>
+      <c r="C452" s="6">
+        <v>18.36</v>
+      </c>
     </row>
     <row r="453" spans="1:3" ht="23">
-      <c r="A453" s="4"/>
-      <c r="B453" s="5"/>
-      <c r="C453" s="6"/>
+      <c r="A453" s="4">
+        <v>46127</v>
+      </c>
+      <c r="B453" s="5">
+        <v>59.876184886039773</v>
+      </c>
+      <c r="C453" s="6">
+        <v>18.170000000000002</v>
+      </c>
     </row>
     <row r="454" spans="1:3" ht="23">
-      <c r="A454" s="4"/>
-      <c r="B454" s="5"/>
-      <c r="C454" s="6"/>
+      <c r="A454" s="4">
+        <v>46128</v>
+      </c>
+      <c r="B454" s="5">
+        <v>59.871049728698559</v>
+      </c>
+      <c r="C454" s="6">
+        <v>17.940000000000001</v>
+      </c>
     </row>
     <row r="455" spans="1:3" ht="23">
-      <c r="A455" s="4"/>
-      <c r="B455" s="5"/>
-      <c r="C455" s="6"/>
+      <c r="A455" s="4">
+        <v>46129</v>
+      </c>
+      <c r="B455" s="5">
+        <v>61.032681970926092</v>
+      </c>
+      <c r="C455" s="6">
+        <v>17.48</v>
+      </c>
     </row>
     <row r="456" spans="1:3" ht="23">
       <c r="A456" s="4"/>
@@ -10672,29 +10702,59 @@
       </c>
     </row>
     <row r="451" spans="1:3" ht="40" customHeight="1">
-      <c r="A451" s="4"/>
-      <c r="B451" s="5"/>
-      <c r="C451" s="5"/>
+      <c r="A451" s="4">
+        <v>46125</v>
+      </c>
+      <c r="B451" s="5">
+        <v>59.046848301346259</v>
+      </c>
+      <c r="C451" s="5">
+        <v>42.100540811265255</v>
+      </c>
     </row>
     <row r="452" spans="1:3" ht="40" customHeight="1">
-      <c r="A452" s="4"/>
-      <c r="B452" s="5"/>
-      <c r="C452" s="5"/>
+      <c r="A452" s="4">
+        <v>46126</v>
+      </c>
+      <c r="B452" s="5">
+        <v>59.693038471799618</v>
+      </c>
+      <c r="C452" s="5">
+        <v>43.278080893954218</v>
+      </c>
     </row>
     <row r="453" spans="1:3" ht="40" customHeight="1">
-      <c r="A453" s="4"/>
-      <c r="B453" s="5"/>
-      <c r="C453" s="5"/>
+      <c r="A453" s="4">
+        <v>46127</v>
+      </c>
+      <c r="B453" s="5">
+        <v>59.876184886039773</v>
+      </c>
+      <c r="C453" s="5">
+        <v>44.070818910832038</v>
+      </c>
     </row>
     <row r="454" spans="1:3" ht="40" customHeight="1">
-      <c r="A454" s="4"/>
-      <c r="B454" s="5"/>
-      <c r="C454" s="5"/>
+      <c r="A454" s="4">
+        <v>46128</v>
+      </c>
+      <c r="B454" s="5">
+        <v>59.871049728698559</v>
+      </c>
+      <c r="C454" s="5">
+        <v>44.304240767479847</v>
+      </c>
     </row>
     <row r="455" spans="1:3" ht="40" customHeight="1">
-      <c r="A455" s="4"/>
-      <c r="B455" s="5"/>
-      <c r="C455" s="5"/>
+      <c r="A455" s="4">
+        <v>46129</v>
+      </c>
+      <c r="B455" s="5">
+        <v>61.032681970926092</v>
+      </c>
+      <c r="C455" s="5">
+        <v>45.491177481893352</v>
+      </c>
     </row>
     <row r="456" spans="1:3" ht="40" customHeight="1">
       <c r="A456" s="4"/>

--- a/files/data.xlsx
+++ b/files/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ferrara/Desktop/salvatore non toccare/monitoraggio/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{674E478D-0B75-A84E-A70C-0471AA5D20E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68C2A25F-9BB0-AE40-8F59-6787E54A6B69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1400" yWindow="660" windowWidth="10440" windowHeight="16320" xr2:uid="{F1546C66-1100-0F4C-AEC5-783BC2578DB8}"/>
+    <workbookView xWindow="1400" yWindow="660" windowWidth="10440" windowHeight="16320" activeTab="1" xr2:uid="{F1546C66-1100-0F4C-AEC5-783BC2578DB8}"/>
   </bookViews>
   <sheets>
     <sheet name="vix" sheetId="2" r:id="rId1"/>
@@ -5490,29 +5490,59 @@
       </c>
     </row>
     <row r="456" spans="1:3" ht="23">
-      <c r="A456" s="4"/>
-      <c r="B456" s="5"/>
-      <c r="C456" s="6"/>
+      <c r="A456" s="4">
+        <v>46132</v>
+      </c>
+      <c r="B456" s="5">
+        <v>61.372804211874779</v>
+      </c>
+      <c r="C456" s="6">
+        <v>18.87</v>
+      </c>
     </row>
     <row r="457" spans="1:3" ht="23">
-      <c r="A457" s="4"/>
-      <c r="B457" s="5"/>
-      <c r="C457" s="6"/>
+      <c r="A457" s="4">
+        <v>46133</v>
+      </c>
+      <c r="B457" s="5">
+        <v>62.300669514569343</v>
+      </c>
+      <c r="C457" s="6">
+        <v>19.5</v>
+      </c>
     </row>
     <row r="458" spans="1:3" ht="23">
-      <c r="A458" s="4"/>
-      <c r="B458" s="5"/>
-      <c r="C458" s="6"/>
+      <c r="A458" s="4">
+        <v>46134</v>
+      </c>
+      <c r="B458" s="5">
+        <v>61.624953195117925</v>
+      </c>
+      <c r="C458" s="6">
+        <v>18.920000000000002</v>
+      </c>
     </row>
     <row r="459" spans="1:3" ht="23">
-      <c r="A459" s="4"/>
-      <c r="B459" s="5"/>
-      <c r="C459" s="6"/>
+      <c r="A459" s="4">
+        <v>46135</v>
+      </c>
+      <c r="B459" s="5">
+        <v>61.925744538787185</v>
+      </c>
+      <c r="C459" s="6">
+        <v>19.309999999999999</v>
+      </c>
     </row>
     <row r="460" spans="1:3" ht="23">
-      <c r="A460" s="4"/>
-      <c r="B460" s="5"/>
-      <c r="C460" s="6"/>
+      <c r="A460" s="4">
+        <v>46136</v>
+      </c>
+      <c r="B460" s="5">
+        <v>63.263170321216478</v>
+      </c>
+      <c r="C460" s="6">
+        <v>18.71</v>
+      </c>
     </row>
     <row r="461" spans="1:3" ht="23">
       <c r="A461" s="4"/>
@@ -10757,29 +10787,59 @@
       </c>
     </row>
     <row r="456" spans="1:3" ht="40" customHeight="1">
-      <c r="A456" s="4"/>
-      <c r="B456" s="5"/>
-      <c r="C456" s="5"/>
+      <c r="A456" s="4">
+        <v>46132</v>
+      </c>
+      <c r="B456" s="5">
+        <v>61.372804211874779</v>
+      </c>
+      <c r="C456" s="5">
+        <v>45.302491587833231</v>
+      </c>
     </row>
     <row r="457" spans="1:3" ht="40" customHeight="1">
-      <c r="A457" s="4"/>
-      <c r="B457" s="5"/>
-      <c r="C457" s="5"/>
+      <c r="A457" s="4">
+        <v>46133</v>
+      </c>
+      <c r="B457" s="5">
+        <v>62.300669514569343</v>
+      </c>
+      <c r="C457" s="5">
+        <v>44.628710262842048</v>
+      </c>
     </row>
     <row r="458" spans="1:3" ht="40" customHeight="1">
-      <c r="A458" s="4"/>
-      <c r="B458" s="5"/>
-      <c r="C458" s="5"/>
+      <c r="A458" s="4">
+        <v>46134</v>
+      </c>
+      <c r="B458" s="5">
+        <v>61.624953195117925</v>
+      </c>
+      <c r="C458" s="5">
+        <v>45.627229551509451</v>
+      </c>
     </row>
     <row r="459" spans="1:3" ht="40" customHeight="1">
-      <c r="A459" s="4"/>
-      <c r="B459" s="5"/>
-      <c r="C459" s="5"/>
+      <c r="A459" s="4">
+        <v>46135</v>
+      </c>
+      <c r="B459" s="5">
+        <v>61.925744538787185</v>
+      </c>
+      <c r="C459" s="5">
+        <v>45.239517090422645</v>
+      </c>
     </row>
     <row r="460" spans="1:3" ht="40" customHeight="1">
-      <c r="A460" s="4"/>
-      <c r="B460" s="5"/>
-      <c r="C460" s="5"/>
+      <c r="A460" s="4">
+        <v>46136</v>
+      </c>
+      <c r="B460" s="5">
+        <v>63.263170321216478</v>
+      </c>
+      <c r="C460" s="5">
+        <v>45.954391196518024</v>
+      </c>
     </row>
     <row r="461" spans="1:3" ht="40" customHeight="1">
       <c r="A461" s="4"/>

--- a/files/data.xlsx
+++ b/files/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ferrara/Desktop/salvatore non toccare/monitoraggio/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68C2A25F-9BB0-AE40-8F59-6787E54A6B69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9F08BE1-2AE1-004B-9CB7-E673BBDEC1F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1400" yWindow="660" windowWidth="10440" windowHeight="16320" activeTab="1" xr2:uid="{F1546C66-1100-0F4C-AEC5-783BC2578DB8}"/>
+    <workbookView xWindow="1400" yWindow="660" windowWidth="10440" windowHeight="16320" xr2:uid="{F1546C66-1100-0F4C-AEC5-783BC2578DB8}"/>
   </bookViews>
   <sheets>
     <sheet name="vix" sheetId="2" r:id="rId1"/>
@@ -5545,29 +5545,59 @@
       </c>
     </row>
     <row r="461" spans="1:3" ht="23">
-      <c r="A461" s="4"/>
-      <c r="B461" s="5"/>
-      <c r="C461" s="6"/>
+      <c r="A461" s="4">
+        <v>46139</v>
+      </c>
+      <c r="B461" s="5">
+        <v>61.615686234979272</v>
+      </c>
+      <c r="C461" s="6">
+        <v>18.02</v>
+      </c>
     </row>
     <row r="462" spans="1:3" ht="23">
-      <c r="A462" s="4"/>
-      <c r="B462" s="5"/>
-      <c r="C462" s="6"/>
+      <c r="A462" s="4">
+        <v>46140</v>
+      </c>
+      <c r="B462" s="5">
+        <v>60.328327592006737</v>
+      </c>
+      <c r="C462" s="6">
+        <v>17.829999999999998</v>
+      </c>
     </row>
     <row r="463" spans="1:3" ht="23">
-      <c r="A463" s="4"/>
-      <c r="B463" s="5"/>
-      <c r="C463" s="6"/>
+      <c r="A463" s="4">
+        <v>46141</v>
+      </c>
+      <c r="B463" s="5">
+        <v>60.766112075206244</v>
+      </c>
+      <c r="C463" s="6">
+        <v>18.809999999999999</v>
+      </c>
     </row>
     <row r="464" spans="1:3" ht="23">
-      <c r="A464" s="4"/>
-      <c r="B464" s="5"/>
-      <c r="C464" s="6"/>
+      <c r="A464" s="4">
+        <v>46142</v>
+      </c>
+      <c r="B464" s="5">
+        <v>60.781388113213033</v>
+      </c>
+      <c r="C464" s="6">
+        <v>16.89</v>
+      </c>
     </row>
     <row r="465" spans="1:3" ht="23">
-      <c r="A465" s="4"/>
-      <c r="B465" s="5"/>
-      <c r="C465" s="6"/>
+      <c r="A465" s="4">
+        <v>46143</v>
+      </c>
+      <c r="B465" s="5">
+        <v>61.360770648240717</v>
+      </c>
+      <c r="C465" s="6">
+        <v>16.989999999999998</v>
+      </c>
     </row>
     <row r="466" spans="1:3" ht="23">
       <c r="A466" s="4"/>
@@ -10842,29 +10872,59 @@
       </c>
     </row>
     <row r="461" spans="1:3" ht="40" customHeight="1">
-      <c r="A461" s="4"/>
-      <c r="B461" s="5"/>
-      <c r="C461" s="5"/>
+      <c r="A461" s="4">
+        <v>46139</v>
+      </c>
+      <c r="B461" s="5">
+        <v>61.615686234979272</v>
+      </c>
+      <c r="C461" s="5">
+        <v>46.110633090705214</v>
+      </c>
     </row>
     <row r="462" spans="1:3" ht="40" customHeight="1">
-      <c r="A462" s="4"/>
-      <c r="B462" s="5"/>
-      <c r="C462" s="5"/>
+      <c r="A462" s="4">
+        <v>46140</v>
+      </c>
+      <c r="B462" s="5">
+        <v>60.328327592006737</v>
+      </c>
+      <c r="C462" s="5">
+        <v>45.623743348158847</v>
+      </c>
     </row>
     <row r="463" spans="1:3" ht="40" customHeight="1">
-      <c r="A463" s="4"/>
-      <c r="B463" s="5"/>
-      <c r="C463" s="5"/>
+      <c r="A463" s="4">
+        <v>46141</v>
+      </c>
+      <c r="B463" s="5">
+        <v>60.766112075206244</v>
+      </c>
+      <c r="C463" s="5">
+        <v>45.581899425377998</v>
+      </c>
     </row>
     <row r="464" spans="1:3" ht="40" customHeight="1">
-      <c r="A464" s="4"/>
-      <c r="B464" s="5"/>
-      <c r="C464" s="5"/>
+      <c r="A464" s="4">
+        <v>46142</v>
+      </c>
+      <c r="B464" s="5">
+        <v>60.781388113213033</v>
+      </c>
+      <c r="C464" s="5">
+        <v>46.633134668707548</v>
+      </c>
     </row>
     <row r="465" spans="1:3" ht="40" customHeight="1">
-      <c r="A465" s="4"/>
-      <c r="B465" s="5"/>
-      <c r="C465" s="5"/>
+      <c r="A465" s="4">
+        <v>46143</v>
+      </c>
+      <c r="B465" s="5">
+        <v>61.360770648240717</v>
+      </c>
+      <c r="C465" s="5">
+        <v>46.829662737202931</v>
+      </c>
     </row>
     <row r="466" spans="1:3" ht="40" customHeight="1">
       <c r="A466" s="4"/>

--- a/files/data.xlsx
+++ b/files/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ferrara/Desktop/salvatore non toccare/monitoraggio/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9F08BE1-2AE1-004B-9CB7-E673BBDEC1F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B02BFDE1-CF66-C342-836A-C9267F6FA1D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1400" yWindow="660" windowWidth="10440" windowHeight="16320" xr2:uid="{F1546C66-1100-0F4C-AEC5-783BC2578DB8}"/>
+    <workbookView xWindow="1400" yWindow="660" windowWidth="10440" windowHeight="16320" activeTab="1" xr2:uid="{F1546C66-1100-0F4C-AEC5-783BC2578DB8}"/>
   </bookViews>
   <sheets>
     <sheet name="vix" sheetId="2" r:id="rId1"/>
@@ -5600,29 +5600,59 @@
       </c>
     </row>
     <row r="466" spans="1:3" ht="23">
-      <c r="A466" s="4"/>
-      <c r="B466" s="5"/>
-      <c r="C466" s="6"/>
+      <c r="A466" s="4">
+        <v>46146</v>
+      </c>
+      <c r="B466" s="5">
+        <v>61.061105746492338</v>
+      </c>
+      <c r="C466" s="6">
+        <v>18.29</v>
+      </c>
     </row>
     <row r="467" spans="1:3" ht="23">
-      <c r="A467" s="4"/>
-      <c r="B467" s="5"/>
-      <c r="C467" s="6"/>
+      <c r="A467" s="4">
+        <v>46147</v>
+      </c>
+      <c r="B467" s="5">
+        <v>61.656144383386767</v>
+      </c>
+      <c r="C467" s="6">
+        <v>17.38</v>
+      </c>
     </row>
     <row r="468" spans="1:3" ht="23">
-      <c r="A468" s="4"/>
-      <c r="B468" s="5"/>
-      <c r="C468" s="6"/>
+      <c r="A468" s="4">
+        <v>46148</v>
+      </c>
+      <c r="B468" s="5">
+        <v>62.020544233992922</v>
+      </c>
+      <c r="C468" s="6">
+        <v>17.39</v>
+      </c>
     </row>
     <row r="469" spans="1:3" ht="23">
-      <c r="A469" s="4"/>
-      <c r="B469" s="5"/>
-      <c r="C469" s="6"/>
+      <c r="A469" s="4">
+        <v>46149</v>
+      </c>
+      <c r="B469" s="5">
+        <v>61.650427164354603</v>
+      </c>
+      <c r="C469" s="6">
+        <v>17.079999999999998</v>
+      </c>
     </row>
     <row r="470" spans="1:3" ht="23">
-      <c r="A470" s="4"/>
-      <c r="B470" s="5"/>
-      <c r="C470" s="6"/>
+      <c r="A470" s="4">
+        <v>46150</v>
+      </c>
+      <c r="B470" s="5">
+        <v>61.858381939238505</v>
+      </c>
+      <c r="C470" s="6">
+        <v>17.190000000000001</v>
+      </c>
     </row>
     <row r="471" spans="1:3" ht="23">
       <c r="A471" s="4"/>
@@ -10927,29 +10957,59 @@
       </c>
     </row>
     <row r="466" spans="1:3" ht="40" customHeight="1">
-      <c r="A466" s="4"/>
-      <c r="B466" s="5"/>
-      <c r="C466" s="5"/>
+      <c r="A466" s="4">
+        <v>46146</v>
+      </c>
+      <c r="B466" s="5">
+        <v>61.061105746492338</v>
+      </c>
+      <c r="C466" s="5">
+        <v>46.446593230062504</v>
+      </c>
     </row>
     <row r="467" spans="1:3" ht="40" customHeight="1">
-      <c r="A467" s="4"/>
-      <c r="B467" s="5"/>
-      <c r="C467" s="5"/>
+      <c r="A467" s="4">
+        <v>46147</v>
+      </c>
+      <c r="B467" s="5">
+        <v>61.656144383386767</v>
+      </c>
+      <c r="C467" s="5">
+        <v>47.231856435199639</v>
+      </c>
     </row>
     <row r="468" spans="1:3" ht="40" customHeight="1">
-      <c r="A468" s="4"/>
-      <c r="B468" s="5"/>
-      <c r="C468" s="5"/>
+      <c r="A468" s="4">
+        <v>46148</v>
+      </c>
+      <c r="B468" s="5">
+        <v>62.020544233992922</v>
+      </c>
+      <c r="C468" s="5">
+        <v>48.625239225364105</v>
+      </c>
     </row>
     <row r="469" spans="1:3" ht="40" customHeight="1">
-      <c r="A469" s="4"/>
-      <c r="B469" s="5"/>
-      <c r="C469" s="5"/>
+      <c r="A469" s="4">
+        <v>46149</v>
+      </c>
+      <c r="B469" s="5">
+        <v>61.650427164354603</v>
+      </c>
+      <c r="C469" s="5">
+        <v>48.265977696773056</v>
+      </c>
     </row>
     <row r="470" spans="1:3" ht="40" customHeight="1">
-      <c r="A470" s="4"/>
-      <c r="B470" s="5"/>
-      <c r="C470" s="5"/>
+      <c r="A470" s="4">
+        <v>46150</v>
+      </c>
+      <c r="B470" s="5">
+        <v>61.858381939238505</v>
+      </c>
+      <c r="C470" s="5">
+        <v>49.023659578853959</v>
+      </c>
     </row>
     <row r="471" spans="1:3" ht="40" customHeight="1">
       <c r="A471" s="4"/>

--- a/files/data.xlsx
+++ b/files/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ferrara/Desktop/salvatore non toccare/monitoraggio/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B02BFDE1-CF66-C342-836A-C9267F6FA1D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{927C541D-3FE9-0F41-8AC2-DEF01E4EA1DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1400" yWindow="660" windowWidth="10440" windowHeight="16320" activeTab="1" xr2:uid="{F1546C66-1100-0F4C-AEC5-783BC2578DB8}"/>
+    <workbookView xWindow="1400" yWindow="660" windowWidth="10440" windowHeight="16320" xr2:uid="{F1546C66-1100-0F4C-AEC5-783BC2578DB8}"/>
   </bookViews>
   <sheets>
     <sheet name="vix" sheetId="2" r:id="rId1"/>
@@ -5655,29 +5655,59 @@
       </c>
     </row>
     <row r="471" spans="1:3" ht="23">
-      <c r="A471" s="4"/>
-      <c r="B471" s="5"/>
-      <c r="C471" s="6"/>
+      <c r="A471" s="4">
+        <v>46153</v>
+      </c>
+      <c r="B471" s="5">
+        <v>61.92990693269045</v>
+      </c>
+      <c r="C471" s="6">
+        <v>18.38</v>
+      </c>
     </row>
     <row r="472" spans="1:3" ht="23">
-      <c r="A472" s="4"/>
-      <c r="B472" s="5"/>
-      <c r="C472" s="6"/>
+      <c r="A472" s="4">
+        <v>46154</v>
+      </c>
+      <c r="B472" s="5">
+        <v>61.660118233615592</v>
+      </c>
+      <c r="C472" s="6">
+        <v>17.989999999999998</v>
+      </c>
     </row>
     <row r="473" spans="1:3" ht="23">
-      <c r="A473" s="4"/>
-      <c r="B473" s="5"/>
-      <c r="C473" s="6"/>
+      <c r="A473" s="4">
+        <v>46155</v>
+      </c>
+      <c r="B473" s="5">
+        <v>61.680306183428335</v>
+      </c>
+      <c r="C473" s="6">
+        <v>17.87</v>
+      </c>
     </row>
     <row r="474" spans="1:3" ht="23">
-      <c r="A474" s="4"/>
-      <c r="B474" s="5"/>
-      <c r="C474" s="6"/>
+      <c r="A474" s="4">
+        <v>46156</v>
+      </c>
+      <c r="B474" s="5">
+        <v>61.124240424363251</v>
+      </c>
+      <c r="C474" s="6">
+        <v>17.260000000000002</v>
+      </c>
     </row>
     <row r="475" spans="1:3" ht="23">
-      <c r="A475" s="4"/>
-      <c r="B475" s="5"/>
-      <c r="C475" s="6"/>
+      <c r="A475" s="4">
+        <v>46157</v>
+      </c>
+      <c r="B475" s="5">
+        <v>61.079587600072131</v>
+      </c>
+      <c r="C475" s="6">
+        <v>18.43</v>
+      </c>
     </row>
     <row r="476" spans="1:3" ht="23">
       <c r="A476" s="4"/>
@@ -11012,29 +11042,59 @@
       </c>
     </row>
     <row r="471" spans="1:3" ht="40" customHeight="1">
-      <c r="A471" s="4"/>
-      <c r="B471" s="5"/>
-      <c r="C471" s="5"/>
+      <c r="A471" s="4">
+        <v>46153</v>
+      </c>
+      <c r="B471" s="5">
+        <v>61.92990693269045</v>
+      </c>
+      <c r="C471" s="5">
+        <v>49.262624403203588</v>
+      </c>
     </row>
     <row r="472" spans="1:3" ht="40" customHeight="1">
-      <c r="A472" s="4"/>
-      <c r="B472" s="5"/>
-      <c r="C472" s="5"/>
+      <c r="A472" s="4">
+        <v>46154</v>
+      </c>
+      <c r="B472" s="5">
+        <v>61.660118233615592</v>
+      </c>
+      <c r="C472" s="5">
+        <v>49.124700306860113</v>
+      </c>
     </row>
     <row r="473" spans="1:3" ht="40" customHeight="1">
-      <c r="A473" s="4"/>
-      <c r="B473" s="5"/>
-      <c r="C473" s="5"/>
+      <c r="A473" s="4">
+        <v>46155</v>
+      </c>
+      <c r="B473" s="5">
+        <v>61.680306183428335</v>
+      </c>
+      <c r="C473" s="5">
+        <v>49.702038108138574</v>
+      </c>
     </row>
     <row r="474" spans="1:3" ht="40" customHeight="1">
-      <c r="A474" s="4"/>
-      <c r="B474" s="5"/>
-      <c r="C474" s="5"/>
+      <c r="A474" s="4">
+        <v>46156</v>
+      </c>
+      <c r="B474" s="5">
+        <v>61.124240424363251</v>
+      </c>
+      <c r="C474" s="5">
+        <v>50.448957219143118</v>
+      </c>
     </row>
     <row r="475" spans="1:3" ht="40" customHeight="1">
-      <c r="A475" s="4"/>
-      <c r="B475" s="5"/>
-      <c r="C475" s="5"/>
+      <c r="A475" s="4">
+        <v>46157</v>
+      </c>
+      <c r="B475" s="5">
+        <v>61.079587600072131</v>
+      </c>
+      <c r="C475" s="5">
+        <v>49.202095784770769</v>
+      </c>
     </row>
     <row r="476" spans="1:3" ht="40" customHeight="1">
       <c r="A476" s="4"/>

--- a/files/data.xlsx
+++ b/files/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ferrara/Desktop/salvatore non toccare/monitoraggio/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{927C541D-3FE9-0F41-8AC2-DEF01E4EA1DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3182B3F-4700-5A49-966A-3855538FD3B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1400" yWindow="660" windowWidth="10440" windowHeight="16320" xr2:uid="{F1546C66-1100-0F4C-AEC5-783BC2578DB8}"/>
+    <workbookView xWindow="1400" yWindow="660" windowWidth="10440" windowHeight="16320" activeTab="1" xr2:uid="{F1546C66-1100-0F4C-AEC5-783BC2578DB8}"/>
   </bookViews>
   <sheets>
     <sheet name="vix" sheetId="2" r:id="rId1"/>
@@ -5710,29 +5710,59 @@
       </c>
     </row>
     <row r="476" spans="1:3" ht="23">
-      <c r="A476" s="4"/>
-      <c r="B476" s="5"/>
-      <c r="C476" s="6"/>
+      <c r="A476" s="4">
+        <v>46160</v>
+      </c>
+      <c r="B476" s="5">
+        <v>60.062266748040514</v>
+      </c>
+      <c r="C476" s="6">
+        <v>17.82</v>
+      </c>
     </row>
     <row r="477" spans="1:3" ht="23">
-      <c r="A477" s="4"/>
-      <c r="B477" s="5"/>
-      <c r="C477" s="6"/>
+      <c r="A477" s="4">
+        <v>46161</v>
+      </c>
+      <c r="B477" s="5">
+        <v>59.241686597874356</v>
+      </c>
+      <c r="C477" s="6">
+        <v>18.059999999999999</v>
+      </c>
     </row>
     <row r="478" spans="1:3" ht="23">
-      <c r="A478" s="4"/>
-      <c r="B478" s="5"/>
-      <c r="C478" s="6"/>
+      <c r="A478" s="4">
+        <v>46162</v>
+      </c>
+      <c r="B478" s="5">
+        <v>59.801195140463193</v>
+      </c>
+      <c r="C478" s="6">
+        <v>17.440000000000001</v>
+      </c>
     </row>
     <row r="479" spans="1:3" ht="23">
-      <c r="A479" s="4"/>
-      <c r="B479" s="5"/>
-      <c r="C479" s="6"/>
+      <c r="A479" s="4">
+        <v>46163</v>
+      </c>
+      <c r="B479" s="5">
+        <v>58.959916973585692</v>
+      </c>
+      <c r="C479" s="6">
+        <v>16.760000000000002</v>
+      </c>
     </row>
     <row r="480" spans="1:3" ht="23">
-      <c r="A480" s="4"/>
-      <c r="B480" s="5"/>
-      <c r="C480" s="6"/>
+      <c r="A480" s="4">
+        <v>46164</v>
+      </c>
+      <c r="B480" s="5">
+        <v>59.363381164842245</v>
+      </c>
+      <c r="C480" s="6">
+        <v>16.7</v>
+      </c>
     </row>
     <row r="481" spans="1:3" ht="23">
       <c r="A481" s="4"/>
@@ -11097,29 +11127,59 @@
       </c>
     </row>
     <row r="476" spans="1:3" ht="40" customHeight="1">
-      <c r="A476" s="4"/>
-      <c r="B476" s="5"/>
-      <c r="C476" s="5"/>
+      <c r="A476" s="4">
+        <v>46160</v>
+      </c>
+      <c r="B476" s="5">
+        <v>60.062266748040514</v>
+      </c>
+      <c r="C476" s="5">
+        <v>49.114600826974765</v>
+      </c>
     </row>
     <row r="477" spans="1:3" ht="40" customHeight="1">
-      <c r="A477" s="4"/>
-      <c r="B477" s="5"/>
-      <c r="C477" s="5"/>
+      <c r="A477" s="4">
+        <v>46161</v>
+      </c>
+      <c r="B477" s="5">
+        <v>59.241686597874356</v>
+      </c>
+      <c r="C477" s="5">
+        <v>48.46949177556349</v>
+      </c>
     </row>
     <row r="478" spans="1:3" ht="40" customHeight="1">
-      <c r="A478" s="4"/>
-      <c r="B478" s="5"/>
-      <c r="C478" s="5"/>
+      <c r="A478" s="4">
+        <v>46162</v>
+      </c>
+      <c r="B478" s="5">
+        <v>59.801195140463193</v>
+      </c>
+      <c r="C478" s="5">
+        <v>49.464122271695061</v>
+      </c>
     </row>
     <row r="479" spans="1:3" ht="40" customHeight="1">
-      <c r="A479" s="4"/>
-      <c r="B479" s="5"/>
-      <c r="C479" s="5"/>
+      <c r="A479" s="4">
+        <v>46163</v>
+      </c>
+      <c r="B479" s="5">
+        <v>58.959916973585692</v>
+      </c>
+      <c r="C479" s="5">
+        <v>49.655169907354313</v>
+      </c>
     </row>
     <row r="480" spans="1:3" ht="40" customHeight="1">
-      <c r="A480" s="4"/>
-      <c r="B480" s="5"/>
-      <c r="C480" s="5"/>
+      <c r="A480" s="4">
+        <v>46164</v>
+      </c>
+      <c r="B480" s="5">
+        <v>59.363381164842245</v>
+      </c>
+      <c r="C480" s="5">
+        <v>50.78723234024396</v>
+      </c>
     </row>
     <row r="481" spans="1:3" ht="40" customHeight="1">
       <c r="A481" s="4"/>

--- a/files/data.xlsx
+++ b/files/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ferrara/Desktop/salvatore non toccare/monitoraggio/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3182B3F-4700-5A49-966A-3855538FD3B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF6A1713-A441-F54D-ACD9-9BCEF0EA25E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1400" yWindow="660" windowWidth="10440" windowHeight="16320" activeTab="1" xr2:uid="{F1546C66-1100-0F4C-AEC5-783BC2578DB8}"/>
+    <workbookView xWindow="1400" yWindow="660" windowWidth="10440" windowHeight="16320" xr2:uid="{F1546C66-1100-0F4C-AEC5-783BC2578DB8}"/>
   </bookViews>
   <sheets>
     <sheet name="vix" sheetId="2" r:id="rId1"/>
@@ -118,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -139,6 +139,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -480,7 +483,7 @@
   <cols>
     <col min="1" max="1" width="15.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.33203125" style="1" customWidth="1"/>
     <col min="4" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
@@ -5760,34 +5763,64 @@
       <c r="B480" s="5">
         <v>59.363381164842245</v>
       </c>
-      <c r="C480" s="6">
+      <c r="C480" s="8">
         <v>16.7</v>
       </c>
     </row>
     <row r="481" spans="1:3" ht="23">
-      <c r="A481" s="4"/>
-      <c r="B481" s="5"/>
-      <c r="C481" s="6"/>
+      <c r="A481" s="4">
+        <v>46167</v>
+      </c>
+      <c r="B481" s="5">
+        <v>59.421463413455008</v>
+      </c>
+      <c r="C481" s="6">
+        <v>16.59</v>
+      </c>
     </row>
     <row r="482" spans="1:3" ht="23">
-      <c r="A482" s="4"/>
-      <c r="B482" s="5"/>
-      <c r="C482" s="6"/>
+      <c r="A482" s="4">
+        <v>46168</v>
+      </c>
+      <c r="B482" s="5">
+        <v>58.923837974677383</v>
+      </c>
+      <c r="C482" s="6">
+        <v>17.010000000000002</v>
+      </c>
     </row>
     <row r="483" spans="1:3" ht="23">
-      <c r="A483" s="4"/>
-      <c r="B483" s="5"/>
-      <c r="C483" s="6"/>
+      <c r="A483" s="4">
+        <v>46169</v>
+      </c>
+      <c r="B483" s="5">
+        <v>58.581436181737104</v>
+      </c>
+      <c r="C483" s="6">
+        <v>16.29</v>
+      </c>
     </row>
     <row r="484" spans="1:3" ht="23">
-      <c r="A484" s="4"/>
-      <c r="B484" s="5"/>
-      <c r="C484" s="6"/>
+      <c r="A484" s="4">
+        <v>46170</v>
+      </c>
+      <c r="B484" s="5">
+        <v>58.437758020817554</v>
+      </c>
+      <c r="C484" s="6">
+        <v>15.74</v>
+      </c>
     </row>
     <row r="485" spans="1:3" ht="23">
-      <c r="A485" s="4"/>
-      <c r="B485" s="5"/>
-      <c r="C485" s="6"/>
+      <c r="A485" s="4">
+        <v>46171</v>
+      </c>
+      <c r="B485" s="5">
+        <v>58.12913535373383</v>
+      </c>
+      <c r="C485" s="6">
+        <v>15.32</v>
+      </c>
     </row>
     <row r="486" spans="1:3" ht="23">
       <c r="A486" s="4"/>
@@ -11182,29 +11215,59 @@
       </c>
     </row>
     <row r="481" spans="1:3" ht="40" customHeight="1">
-      <c r="A481" s="4"/>
-      <c r="B481" s="5"/>
-      <c r="C481" s="5"/>
+      <c r="A481" s="4">
+        <v>46167</v>
+      </c>
+      <c r="B481" s="5">
+        <v>59.421463413455008</v>
+      </c>
+      <c r="C481" s="5">
+        <v>50.78723234024396</v>
+      </c>
     </row>
     <row r="482" spans="1:3" ht="40" customHeight="1">
-      <c r="A482" s="4"/>
-      <c r="B482" s="5"/>
-      <c r="C482" s="5"/>
+      <c r="A482" s="4">
+        <v>46168</v>
+      </c>
+      <c r="B482" s="5">
+        <v>58.923837974677383</v>
+      </c>
+      <c r="C482" s="5">
+        <v>51.40115643899621</v>
+      </c>
     </row>
     <row r="483" spans="1:3" ht="40" customHeight="1">
-      <c r="A483" s="4"/>
-      <c r="B483" s="5"/>
-      <c r="C483" s="5"/>
+      <c r="A483" s="4">
+        <v>46169</v>
+      </c>
+      <c r="B483" s="5">
+        <v>58.581436181737104</v>
+      </c>
+      <c r="C483" s="5">
+        <v>51.447213616505451</v>
+      </c>
     </row>
     <row r="484" spans="1:3" ht="40" customHeight="1">
-      <c r="A484" s="4"/>
-      <c r="B484" s="5"/>
-      <c r="C484" s="5"/>
+      <c r="A484" s="4">
+        <v>46170</v>
+      </c>
+      <c r="B484" s="5">
+        <v>58.437758020817554</v>
+      </c>
+      <c r="C484" s="5">
+        <v>52.011334495917779</v>
+      </c>
     </row>
     <row r="485" spans="1:3" ht="40" customHeight="1">
-      <c r="A485" s="4"/>
-      <c r="B485" s="5"/>
-      <c r="C485" s="5"/>
+      <c r="A485" s="4">
+        <v>46171</v>
+      </c>
+      <c r="B485" s="5">
+        <v>58.12913535373383</v>
+      </c>
+      <c r="C485" s="5">
+        <v>52.187787830594445</v>
+      </c>
     </row>
     <row r="486" spans="1:3" ht="40" customHeight="1">
       <c r="A486" s="4"/>

--- a/files/data.xlsx
+++ b/files/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ferrara/Desktop/salvatore non toccare/monitoraggio/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF6A1713-A441-F54D-ACD9-9BCEF0EA25E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B21607A9-CE93-DB4E-875C-9F6A1DCEC0FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1400" yWindow="660" windowWidth="10440" windowHeight="16320" xr2:uid="{F1546C66-1100-0F4C-AEC5-783BC2578DB8}"/>
+    <workbookView xWindow="1400" yWindow="660" windowWidth="10440" windowHeight="16320" activeTab="1" xr2:uid="{F1546C66-1100-0F4C-AEC5-783BC2578DB8}"/>
   </bookViews>
   <sheets>
     <sheet name="vix" sheetId="2" r:id="rId1"/>
@@ -5823,29 +5823,59 @@
       </c>
     </row>
     <row r="486" spans="1:3" ht="23">
-      <c r="A486" s="4"/>
-      <c r="B486" s="5"/>
-      <c r="C486" s="6"/>
+      <c r="A486" s="4">
+        <v>46174</v>
+      </c>
+      <c r="B486" s="5">
+        <v>58.266144578324372</v>
+      </c>
+      <c r="C486" s="6">
+        <v>16.05</v>
+      </c>
     </row>
     <row r="487" spans="1:3" ht="23">
-      <c r="A487" s="4"/>
-      <c r="B487" s="5"/>
-      <c r="C487" s="6"/>
+      <c r="A487" s="4">
+        <v>46175</v>
+      </c>
+      <c r="B487" s="5">
+        <v>58.203478120545903</v>
+      </c>
+      <c r="C487" s="6">
+        <v>15.77</v>
+      </c>
     </row>
     <row r="488" spans="1:3" ht="23">
-      <c r="A488" s="4"/>
-      <c r="B488" s="5"/>
-      <c r="C488" s="6"/>
+      <c r="A488" s="4">
+        <v>46176</v>
+      </c>
+      <c r="B488" s="5">
+        <v>58.077021518152627</v>
+      </c>
+      <c r="C488" s="6">
+        <v>16.059999999999999</v>
+      </c>
     </row>
     <row r="489" spans="1:3" ht="23">
-      <c r="A489" s="4"/>
-      <c r="B489" s="5"/>
-      <c r="C489" s="6"/>
+      <c r="A489" s="4">
+        <v>46177</v>
+      </c>
+      <c r="B489" s="5">
+        <v>57.939940609023679</v>
+      </c>
+      <c r="C489" s="6">
+        <v>15.4</v>
+      </c>
     </row>
     <row r="490" spans="1:3" ht="23">
-      <c r="A490" s="4"/>
-      <c r="B490" s="5"/>
-      <c r="C490" s="6"/>
+      <c r="A490" s="4">
+        <v>46178</v>
+      </c>
+      <c r="B490" s="5">
+        <v>58.676583070226819</v>
+      </c>
+      <c r="C490" s="6">
+        <v>21.51</v>
+      </c>
     </row>
     <row r="491" spans="1:3" ht="23">
       <c r="A491" s="4"/>
@@ -11270,29 +11300,59 @@
       </c>
     </row>
     <row r="486" spans="1:3" ht="40" customHeight="1">
-      <c r="A486" s="4"/>
-      <c r="B486" s="5"/>
-      <c r="C486" s="5"/>
+      <c r="A486" s="4">
+        <v>46174</v>
+      </c>
+      <c r="B486" s="5">
+        <v>58.266144578324372</v>
+      </c>
+      <c r="C486" s="5">
+        <v>52.41606120544121</v>
+      </c>
     </row>
     <row r="487" spans="1:3" ht="40" customHeight="1">
-      <c r="A487" s="4"/>
-      <c r="B487" s="5"/>
-      <c r="C487" s="5"/>
+      <c r="A487" s="4">
+        <v>46175</v>
+      </c>
+      <c r="B487" s="5">
+        <v>58.203478120545903</v>
+      </c>
+      <c r="C487" s="5">
+        <v>52.559281072380337</v>
+      </c>
     </row>
     <row r="488" spans="1:3" ht="40" customHeight="1">
-      <c r="A488" s="4"/>
-      <c r="B488" s="5"/>
-      <c r="C488" s="5"/>
+      <c r="A488" s="4">
+        <v>46176</v>
+      </c>
+      <c r="B488" s="5">
+        <v>58.077021518152627</v>
+      </c>
+      <c r="C488" s="5">
+        <v>51.886976722258048</v>
+      </c>
     </row>
     <row r="489" spans="1:3" ht="40" customHeight="1">
-      <c r="A489" s="4"/>
-      <c r="B489" s="5"/>
-      <c r="C489" s="5"/>
+      <c r="A489" s="4">
+        <v>46177</v>
+      </c>
+      <c r="B489" s="5">
+        <v>57.939940609023679</v>
+      </c>
+      <c r="C489" s="5">
+        <v>52.279159720517619</v>
+      </c>
     </row>
     <row r="490" spans="1:3" ht="40" customHeight="1">
-      <c r="A490" s="4"/>
-      <c r="B490" s="5"/>
-      <c r="C490" s="5"/>
+      <c r="A490" s="4">
+        <v>46178</v>
+      </c>
+      <c r="B490" s="5">
+        <v>58.676583070226819</v>
+      </c>
+      <c r="C490" s="5">
+        <v>49.598228973659289</v>
+      </c>
     </row>
     <row r="491" spans="1:3" ht="40" customHeight="1">
       <c r="A491" s="4"/>

--- a/files/data.xlsx
+++ b/files/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ferrara/Desktop/salvatore non toccare/monitoraggio/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B21607A9-CE93-DB4E-875C-9F6A1DCEC0FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B0E1478-EAEA-CC4C-B557-3FD76DCD569F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1400" yWindow="660" windowWidth="10440" windowHeight="16320" activeTab="1" xr2:uid="{F1546C66-1100-0F4C-AEC5-783BC2578DB8}"/>
+    <workbookView xWindow="1400" yWindow="660" windowWidth="10440" windowHeight="16320" xr2:uid="{F1546C66-1100-0F4C-AEC5-783BC2578DB8}"/>
   </bookViews>
   <sheets>
     <sheet name="vix" sheetId="2" r:id="rId1"/>
@@ -5878,29 +5878,59 @@
       </c>
     </row>
     <row r="491" spans="1:3" ht="23">
-      <c r="A491" s="4"/>
-      <c r="B491" s="5"/>
-      <c r="C491" s="6"/>
+      <c r="A491" s="4">
+        <v>46181</v>
+      </c>
+      <c r="B491" s="5">
+        <v>58.168968857028844</v>
+      </c>
+      <c r="C491" s="6">
+        <v>18.920000000000002</v>
+      </c>
     </row>
     <row r="492" spans="1:3" ht="23">
-      <c r="A492" s="4"/>
-      <c r="B492" s="5"/>
-      <c r="C492" s="6"/>
+      <c r="A492" s="4">
+        <v>46182</v>
+      </c>
+      <c r="B492" s="5">
+        <v>58.64498508319145</v>
+      </c>
+      <c r="C492" s="6">
+        <v>19.87</v>
+      </c>
     </row>
     <row r="493" spans="1:3" ht="23">
-      <c r="A493" s="4"/>
-      <c r="B493" s="5"/>
-      <c r="C493" s="6"/>
+      <c r="A493" s="4">
+        <v>46183</v>
+      </c>
+      <c r="B493" s="5">
+        <v>58.992215615337585</v>
+      </c>
+      <c r="C493" s="6">
+        <v>22.22</v>
+      </c>
     </row>
     <row r="494" spans="1:3" ht="23">
-      <c r="A494" s="4"/>
-      <c r="B494" s="5"/>
-      <c r="C494" s="6"/>
+      <c r="A494" s="4">
+        <v>46184</v>
+      </c>
+      <c r="B494" s="5">
+        <v>59.11042750496501</v>
+      </c>
+      <c r="C494" s="6">
+        <v>19.440000000000001</v>
+      </c>
     </row>
     <row r="495" spans="1:3" ht="23">
-      <c r="A495" s="4"/>
-      <c r="B495" s="5"/>
-      <c r="C495" s="6"/>
+      <c r="A495" s="4">
+        <v>46185</v>
+      </c>
+      <c r="B495" s="5">
+        <v>58.035348013297394</v>
+      </c>
+      <c r="C495" s="6">
+        <v>17.68</v>
+      </c>
     </row>
     <row r="496" spans="1:3" ht="23">
       <c r="A496" s="4"/>
@@ -11355,29 +11385,59 @@
       </c>
     </row>
     <row r="491" spans="1:3" ht="40" customHeight="1">
-      <c r="A491" s="4"/>
-      <c r="B491" s="5"/>
-      <c r="C491" s="5"/>
+      <c r="A491" s="4">
+        <v>46181</v>
+      </c>
+      <c r="B491" s="5">
+        <v>58.168968857028844</v>
+      </c>
+      <c r="C491" s="5">
+        <v>49.80908301031171</v>
+      </c>
     </row>
     <row r="492" spans="1:3" ht="40" customHeight="1">
-      <c r="A492" s="4"/>
-      <c r="B492" s="5"/>
-      <c r="C492" s="5"/>
+      <c r="A492" s="4">
+        <v>46182</v>
+      </c>
+      <c r="B492" s="5">
+        <v>58.64498508319145</v>
+      </c>
+      <c r="C492" s="5">
+        <v>49.497665811523873</v>
+      </c>
     </row>
     <row r="493" spans="1:3" ht="40" customHeight="1">
-      <c r="A493" s="4"/>
-      <c r="B493" s="5"/>
-      <c r="C493" s="5"/>
+      <c r="A493" s="4">
+        <v>46183</v>
+      </c>
+      <c r="B493" s="5">
+        <v>58.992215615337585</v>
+      </c>
+      <c r="C493" s="5">
+        <v>47.936084697740974</v>
+      </c>
     </row>
     <row r="494" spans="1:3" ht="40" customHeight="1">
-      <c r="A494" s="4"/>
-      <c r="B494" s="5"/>
-      <c r="C494" s="5"/>
+      <c r="A494" s="4">
+        <v>46184</v>
+      </c>
+      <c r="B494" s="5">
+        <v>59.11042750496501</v>
+      </c>
+      <c r="C494" s="5">
+        <v>49.547960033778018</v>
+      </c>
     </row>
     <row r="495" spans="1:3" ht="40" customHeight="1">
-      <c r="A495" s="4"/>
-      <c r="B495" s="5"/>
-      <c r="C495" s="5"/>
+      <c r="A495" s="4">
+        <v>46185</v>
+      </c>
+      <c r="B495" s="5">
+        <v>58.035348013297394</v>
+      </c>
+      <c r="C495" s="5">
+        <v>50.076195022217831</v>
+      </c>
     </row>
     <row r="496" spans="1:3" ht="40" customHeight="1">
       <c r="A496" s="4"/>

--- a/files/data.xlsx
+++ b/files/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ferrara/Desktop/salvatore non toccare/monitoraggio/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B0E1478-EAEA-CC4C-B557-3FD76DCD569F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B7B2774-C69B-694A-A3A7-23CDAF8A2780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1400" yWindow="660" windowWidth="10440" windowHeight="16320" xr2:uid="{F1546C66-1100-0F4C-AEC5-783BC2578DB8}"/>
+    <workbookView xWindow="1400" yWindow="660" windowWidth="10440" windowHeight="16320" activeTab="1" xr2:uid="{F1546C66-1100-0F4C-AEC5-783BC2578DB8}"/>
   </bookViews>
   <sheets>
     <sheet name="vix" sheetId="2" r:id="rId1"/>
@@ -5933,29 +5933,59 @@
       </c>
     </row>
     <row r="496" spans="1:3" ht="23">
-      <c r="A496" s="4"/>
-      <c r="B496" s="5"/>
-      <c r="C496" s="6"/>
+      <c r="A496" s="4">
+        <v>46188</v>
+      </c>
+      <c r="B496" s="5">
+        <v>57.557926091674169</v>
+      </c>
+      <c r="C496" s="6">
+        <v>16.2</v>
+      </c>
     </row>
     <row r="497" spans="1:3" ht="23">
-      <c r="A497" s="4"/>
-      <c r="B497" s="5"/>
-      <c r="C497" s="6"/>
+      <c r="A497" s="4">
+        <v>46189</v>
+      </c>
+      <c r="B497" s="5">
+        <v>57.15290594586692</v>
+      </c>
+      <c r="C497" s="6">
+        <v>16.41</v>
+      </c>
     </row>
     <row r="498" spans="1:3" ht="23">
-      <c r="A498" s="4"/>
-      <c r="B498" s="5"/>
-      <c r="C498" s="6"/>
+      <c r="A498" s="4">
+        <v>46190</v>
+      </c>
+      <c r="B498" s="5">
+        <v>58.105669170473981</v>
+      </c>
+      <c r="C498" s="6">
+        <v>18.440000000000001</v>
+      </c>
     </row>
     <row r="499" spans="1:3" ht="23">
-      <c r="A499" s="4"/>
-      <c r="B499" s="5"/>
-      <c r="C499" s="6"/>
+      <c r="A499" s="4">
+        <v>46191</v>
+      </c>
+      <c r="B499" s="5">
+        <v>57.010182950372268</v>
+      </c>
+      <c r="C499" s="6">
+        <v>16.399999999999999</v>
+      </c>
     </row>
     <row r="500" spans="1:3" ht="23">
-      <c r="A500" s="4"/>
-      <c r="B500" s="5"/>
-      <c r="C500" s="6"/>
+      <c r="A500" s="4">
+        <v>46192</v>
+      </c>
+      <c r="B500" s="5">
+        <v>56.990082873145667</v>
+      </c>
+      <c r="C500" s="6">
+        <v>16.78</v>
+      </c>
     </row>
     <row r="501" spans="1:3" ht="23">
       <c r="A501" s="4"/>
@@ -11440,29 +11470,59 @@
       </c>
     </row>
     <row r="496" spans="1:3" ht="40" customHeight="1">
-      <c r="A496" s="4"/>
-      <c r="B496" s="5"/>
-      <c r="C496" s="5"/>
+      <c r="A496" s="4">
+        <v>46188</v>
+      </c>
+      <c r="B496" s="5">
+        <v>57.557926091674169</v>
+      </c>
+      <c r="C496" s="5">
+        <v>51.782134303900193</v>
+      </c>
     </row>
     <row r="497" spans="1:3" ht="40" customHeight="1">
-      <c r="A497" s="4"/>
-      <c r="B497" s="5"/>
-      <c r="C497" s="5"/>
+      <c r="A497" s="4">
+        <v>46189</v>
+      </c>
+      <c r="B497" s="5">
+        <v>57.15290594586692</v>
+      </c>
+      <c r="C497" s="5">
+        <v>51.266152549478008</v>
+      </c>
     </row>
     <row r="498" spans="1:3" ht="40" customHeight="1">
-      <c r="A498" s="4"/>
-      <c r="B498" s="5"/>
-      <c r="C498" s="5"/>
+      <c r="A498" s="4">
+        <v>46190</v>
+      </c>
+      <c r="B498" s="5">
+        <v>58.105669170473981</v>
+      </c>
+      <c r="C498" s="5">
+        <v>50.012820493320966</v>
+      </c>
     </row>
     <row r="499" spans="1:3" ht="40" customHeight="1">
-      <c r="A499" s="4"/>
-      <c r="B499" s="5"/>
-      <c r="C499" s="5"/>
+      <c r="A499" s="4">
+        <v>46191</v>
+      </c>
+      <c r="B499" s="5">
+        <v>57.010182950372268</v>
+      </c>
+      <c r="C499" s="5">
+        <v>51.048445642010122</v>
+      </c>
     </row>
     <row r="500" spans="1:3" ht="40" customHeight="1">
-      <c r="A500" s="4"/>
-      <c r="B500" s="5"/>
-      <c r="C500" s="5"/>
+      <c r="A500" s="4">
+        <v>46192</v>
+      </c>
+      <c r="B500" s="5">
+        <v>56.990082873145667</v>
+      </c>
+      <c r="C500" s="5">
+        <v>51.038538603050846</v>
+      </c>
     </row>
     <row r="501" spans="1:3" ht="40" customHeight="1">
       <c r="A501" s="4"/>

--- a/files/data.xlsx
+++ b/files/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ferrara/Desktop/salvatore non toccare/monitoraggio/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B7B2774-C69B-694A-A3A7-23CDAF8A2780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6AF0F6A-30B6-FB44-A5F9-C904084406F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1400" yWindow="660" windowWidth="10440" windowHeight="16320" activeTab="1" xr2:uid="{F1546C66-1100-0F4C-AEC5-783BC2578DB8}"/>
+    <workbookView xWindow="1400" yWindow="660" windowWidth="10440" windowHeight="16320" xr2:uid="{F1546C66-1100-0F4C-AEC5-783BC2578DB8}"/>
   </bookViews>
   <sheets>
     <sheet name="vix" sheetId="2" r:id="rId1"/>
@@ -478,7 +478,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2D1AE83-71FF-D646-9DA6-2F2BACDC27FF}">
-  <dimension ref="A1:C504"/>
+  <dimension ref="A1:C1149"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="15.1640625" style="1" bestFit="1" customWidth="1"/>
@@ -5988,24 +5988,3279 @@
       </c>
     </row>
     <row r="501" spans="1:3" ht="23">
-      <c r="A501" s="4"/>
-      <c r="B501" s="5"/>
-      <c r="C501" s="6"/>
+      <c r="A501" s="4">
+        <v>46195</v>
+      </c>
+      <c r="B501" s="5">
+        <v>56.435632456249742</v>
+      </c>
+      <c r="C501" s="6">
+        <v>17.28</v>
+      </c>
     </row>
     <row r="502" spans="1:3" ht="23">
-      <c r="A502" s="4"/>
-      <c r="B502" s="5"/>
-      <c r="C502" s="6"/>
+      <c r="A502" s="4">
+        <v>46196</v>
+      </c>
+      <c r="B502" s="5">
+        <v>58.129537801840478</v>
+      </c>
+      <c r="C502" s="6">
+        <v>19.489999999999998</v>
+      </c>
     </row>
     <row r="503" spans="1:3" ht="23">
-      <c r="A503" s="4"/>
-      <c r="B503" s="5"/>
-      <c r="C503" s="6"/>
+      <c r="A503" s="4">
+        <v>46197</v>
+      </c>
+      <c r="B503" s="5">
+        <v>58.151509845031249</v>
+      </c>
+      <c r="C503" s="6">
+        <v>18.63</v>
+      </c>
     </row>
     <row r="504" spans="1:3" ht="23">
-      <c r="A504" s="4"/>
-      <c r="B504" s="5"/>
-      <c r="C504" s="6"/>
+      <c r="A504" s="4">
+        <v>46198</v>
+      </c>
+      <c r="B504" s="5">
+        <v>58.342938446347183</v>
+      </c>
+      <c r="C504" s="6">
+        <v>18.89</v>
+      </c>
+    </row>
+    <row r="505" spans="1:3" ht="23">
+      <c r="A505" s="4">
+        <v>46199</v>
+      </c>
+      <c r="B505" s="5">
+        <v>56.954339573931222</v>
+      </c>
+      <c r="C505" s="6">
+        <v>18.41</v>
+      </c>
+    </row>
+    <row r="506" spans="1:3" ht="23">
+      <c r="A506" s="4"/>
+      <c r="B506" s="5"/>
+      <c r="C506" s="6"/>
+    </row>
+    <row r="507" spans="1:3" ht="23">
+      <c r="A507" s="4"/>
+      <c r="B507" s="5"/>
+      <c r="C507" s="6"/>
+    </row>
+    <row r="508" spans="1:3" ht="23">
+      <c r="A508" s="4"/>
+      <c r="B508" s="5"/>
+      <c r="C508" s="6"/>
+    </row>
+    <row r="509" spans="1:3" ht="23">
+      <c r="A509" s="4"/>
+      <c r="B509" s="5"/>
+      <c r="C509" s="6"/>
+    </row>
+    <row r="510" spans="1:3" ht="23">
+      <c r="A510" s="4"/>
+      <c r="B510" s="5"/>
+      <c r="C510" s="6"/>
+    </row>
+    <row r="511" spans="1:3" ht="23">
+      <c r="A511" s="4"/>
+      <c r="B511" s="5"/>
+      <c r="C511" s="6"/>
+    </row>
+    <row r="512" spans="1:3" ht="23">
+      <c r="A512" s="4"/>
+      <c r="B512" s="5"/>
+      <c r="C512" s="6"/>
+    </row>
+    <row r="513" spans="1:3" ht="23">
+      <c r="A513" s="4"/>
+      <c r="B513" s="5"/>
+      <c r="C513" s="6"/>
+    </row>
+    <row r="514" spans="1:3" ht="23">
+      <c r="A514" s="4"/>
+      <c r="B514" s="5"/>
+      <c r="C514" s="6"/>
+    </row>
+    <row r="515" spans="1:3" ht="23">
+      <c r="A515" s="4"/>
+      <c r="B515" s="5"/>
+      <c r="C515" s="6"/>
+    </row>
+    <row r="516" spans="1:3" ht="23">
+      <c r="A516" s="4"/>
+      <c r="B516" s="5"/>
+      <c r="C516" s="6"/>
+    </row>
+    <row r="517" spans="1:3" ht="23">
+      <c r="A517" s="4"/>
+      <c r="B517" s="5"/>
+      <c r="C517" s="6"/>
+    </row>
+    <row r="518" spans="1:3" ht="23">
+      <c r="A518" s="4"/>
+      <c r="B518" s="5"/>
+      <c r="C518" s="6"/>
+    </row>
+    <row r="519" spans="1:3" ht="23">
+      <c r="A519" s="4"/>
+      <c r="B519" s="5"/>
+      <c r="C519" s="6"/>
+    </row>
+    <row r="520" spans="1:3" ht="23">
+      <c r="A520" s="4"/>
+      <c r="B520" s="5"/>
+      <c r="C520" s="6"/>
+    </row>
+    <row r="521" spans="1:3" ht="23">
+      <c r="A521" s="4"/>
+      <c r="B521" s="5"/>
+      <c r="C521" s="6"/>
+    </row>
+    <row r="522" spans="1:3" ht="23">
+      <c r="A522" s="4"/>
+      <c r="B522" s="5"/>
+      <c r="C522" s="6"/>
+    </row>
+    <row r="523" spans="1:3" ht="23">
+      <c r="A523" s="4"/>
+      <c r="B523" s="5"/>
+      <c r="C523" s="6"/>
+    </row>
+    <row r="524" spans="1:3" ht="23">
+      <c r="A524" s="4"/>
+      <c r="B524" s="5"/>
+      <c r="C524" s="6"/>
+    </row>
+    <row r="525" spans="1:3" ht="23">
+      <c r="A525" s="4"/>
+      <c r="B525" s="5"/>
+      <c r="C525" s="6"/>
+    </row>
+    <row r="526" spans="1:3" ht="23">
+      <c r="A526" s="4"/>
+      <c r="B526" s="5"/>
+      <c r="C526" s="6"/>
+    </row>
+    <row r="527" spans="1:3" ht="23">
+      <c r="A527" s="4"/>
+      <c r="B527" s="5"/>
+      <c r="C527" s="6"/>
+    </row>
+    <row r="528" spans="1:3" ht="23">
+      <c r="A528" s="4"/>
+      <c r="B528" s="5"/>
+      <c r="C528" s="6"/>
+    </row>
+    <row r="529" spans="1:3" ht="23">
+      <c r="A529" s="4"/>
+      <c r="B529" s="5"/>
+      <c r="C529" s="6"/>
+    </row>
+    <row r="530" spans="1:3" ht="23">
+      <c r="A530" s="4"/>
+      <c r="B530" s="5"/>
+      <c r="C530" s="6"/>
+    </row>
+    <row r="531" spans="1:3" ht="23">
+      <c r="A531" s="4"/>
+      <c r="B531" s="5"/>
+      <c r="C531" s="6"/>
+    </row>
+    <row r="532" spans="1:3" ht="23">
+      <c r="A532" s="4"/>
+      <c r="B532" s="5"/>
+      <c r="C532" s="6"/>
+    </row>
+    <row r="533" spans="1:3" ht="23">
+      <c r="A533" s="4"/>
+      <c r="B533" s="5"/>
+      <c r="C533" s="6"/>
+    </row>
+    <row r="534" spans="1:3" ht="23">
+      <c r="A534" s="4"/>
+      <c r="B534" s="5"/>
+      <c r="C534" s="6"/>
+    </row>
+    <row r="535" spans="1:3" ht="23">
+      <c r="A535" s="4"/>
+      <c r="B535" s="5"/>
+      <c r="C535" s="6"/>
+    </row>
+    <row r="536" spans="1:3" ht="23">
+      <c r="A536" s="4"/>
+      <c r="B536" s="5"/>
+      <c r="C536" s="6"/>
+    </row>
+    <row r="537" spans="1:3" ht="23">
+      <c r="A537" s="4"/>
+      <c r="B537" s="5"/>
+      <c r="C537" s="6"/>
+    </row>
+    <row r="538" spans="1:3" ht="23">
+      <c r="A538" s="4"/>
+      <c r="B538" s="5"/>
+      <c r="C538" s="6"/>
+    </row>
+    <row r="539" spans="1:3" ht="23">
+      <c r="A539" s="4"/>
+      <c r="B539" s="5"/>
+      <c r="C539" s="6"/>
+    </row>
+    <row r="540" spans="1:3" ht="23">
+      <c r="A540" s="4"/>
+      <c r="B540" s="5"/>
+      <c r="C540" s="6"/>
+    </row>
+    <row r="541" spans="1:3" ht="23">
+      <c r="A541" s="4"/>
+      <c r="B541" s="5"/>
+      <c r="C541" s="6"/>
+    </row>
+    <row r="542" spans="1:3" ht="23">
+      <c r="A542" s="4"/>
+      <c r="B542" s="5"/>
+      <c r="C542" s="6"/>
+    </row>
+    <row r="543" spans="1:3" ht="23">
+      <c r="A543" s="4"/>
+      <c r="B543" s="5"/>
+      <c r="C543" s="6"/>
+    </row>
+    <row r="544" spans="1:3" ht="23">
+      <c r="A544" s="4"/>
+      <c r="B544" s="5"/>
+      <c r="C544" s="6"/>
+    </row>
+    <row r="545" spans="1:3" ht="23">
+      <c r="A545" s="4"/>
+      <c r="B545" s="5"/>
+      <c r="C545" s="6"/>
+    </row>
+    <row r="546" spans="1:3" ht="23">
+      <c r="A546" s="4"/>
+      <c r="B546" s="5"/>
+      <c r="C546" s="6"/>
+    </row>
+    <row r="547" spans="1:3" ht="23">
+      <c r="A547" s="4"/>
+      <c r="B547" s="5"/>
+      <c r="C547" s="6"/>
+    </row>
+    <row r="548" spans="1:3" ht="23">
+      <c r="A548" s="4"/>
+      <c r="B548" s="5"/>
+      <c r="C548" s="6"/>
+    </row>
+    <row r="549" spans="1:3" ht="23">
+      <c r="A549" s="4"/>
+      <c r="B549" s="5"/>
+      <c r="C549" s="6"/>
+    </row>
+    <row r="550" spans="1:3" ht="23">
+      <c r="A550" s="4"/>
+      <c r="B550" s="5"/>
+      <c r="C550" s="6"/>
+    </row>
+    <row r="551" spans="1:3" ht="23">
+      <c r="A551" s="4"/>
+      <c r="B551" s="5"/>
+      <c r="C551" s="6"/>
+    </row>
+    <row r="552" spans="1:3" ht="23">
+      <c r="A552" s="4"/>
+      <c r="B552" s="5"/>
+      <c r="C552" s="6"/>
+    </row>
+    <row r="553" spans="1:3" ht="23">
+      <c r="A553" s="4"/>
+      <c r="B553" s="5"/>
+      <c r="C553" s="6"/>
+    </row>
+    <row r="554" spans="1:3" ht="23">
+      <c r="A554" s="4"/>
+      <c r="B554" s="5"/>
+      <c r="C554" s="6"/>
+    </row>
+    <row r="555" spans="1:3" ht="23">
+      <c r="A555" s="4"/>
+      <c r="B555" s="5"/>
+      <c r="C555" s="6"/>
+    </row>
+    <row r="556" spans="1:3" ht="23">
+      <c r="A556" s="4"/>
+      <c r="B556" s="5"/>
+      <c r="C556" s="6"/>
+    </row>
+    <row r="557" spans="1:3" ht="23">
+      <c r="A557" s="4"/>
+      <c r="B557" s="5"/>
+      <c r="C557" s="6"/>
+    </row>
+    <row r="558" spans="1:3" ht="23">
+      <c r="A558" s="4"/>
+      <c r="B558" s="5"/>
+      <c r="C558" s="6"/>
+    </row>
+    <row r="559" spans="1:3" ht="23">
+      <c r="A559" s="4"/>
+      <c r="B559" s="5"/>
+      <c r="C559" s="6"/>
+    </row>
+    <row r="560" spans="1:3" ht="23">
+      <c r="A560" s="4"/>
+      <c r="B560" s="5"/>
+      <c r="C560" s="6"/>
+    </row>
+    <row r="561" spans="1:3" ht="23">
+      <c r="A561" s="4"/>
+      <c r="B561" s="5"/>
+      <c r="C561" s="6"/>
+    </row>
+    <row r="562" spans="1:3" ht="23">
+      <c r="A562" s="4"/>
+      <c r="B562" s="5"/>
+      <c r="C562" s="6"/>
+    </row>
+    <row r="563" spans="1:3" ht="23">
+      <c r="A563" s="4"/>
+      <c r="B563" s="5"/>
+      <c r="C563" s="6"/>
+    </row>
+    <row r="564" spans="1:3" ht="23">
+      <c r="A564" s="4"/>
+      <c r="B564" s="5"/>
+      <c r="C564" s="6"/>
+    </row>
+    <row r="565" spans="1:3" ht="23">
+      <c r="A565" s="4"/>
+      <c r="B565" s="5"/>
+      <c r="C565" s="6"/>
+    </row>
+    <row r="566" spans="1:3" ht="23">
+      <c r="A566" s="4"/>
+      <c r="B566" s="5"/>
+      <c r="C566" s="6"/>
+    </row>
+    <row r="567" spans="1:3" ht="23">
+      <c r="A567" s="4"/>
+      <c r="B567" s="5"/>
+      <c r="C567" s="6"/>
+    </row>
+    <row r="568" spans="1:3" ht="23">
+      <c r="A568" s="4"/>
+      <c r="B568" s="5"/>
+      <c r="C568" s="6"/>
+    </row>
+    <row r="569" spans="1:3" ht="23">
+      <c r="A569" s="4"/>
+      <c r="B569" s="5"/>
+      <c r="C569" s="6"/>
+    </row>
+    <row r="570" spans="1:3" ht="23">
+      <c r="A570" s="4"/>
+      <c r="B570" s="5"/>
+      <c r="C570" s="6"/>
+    </row>
+    <row r="571" spans="1:3" ht="23">
+      <c r="A571" s="4"/>
+      <c r="B571" s="5"/>
+      <c r="C571" s="6"/>
+    </row>
+    <row r="572" spans="1:3" ht="23">
+      <c r="A572" s="4"/>
+      <c r="B572" s="5"/>
+      <c r="C572" s="6"/>
+    </row>
+    <row r="573" spans="1:3" ht="23">
+      <c r="A573" s="4"/>
+      <c r="B573" s="5"/>
+      <c r="C573" s="6"/>
+    </row>
+    <row r="574" spans="1:3" ht="23">
+      <c r="A574" s="4"/>
+      <c r="B574" s="5"/>
+      <c r="C574" s="6"/>
+    </row>
+    <row r="575" spans="1:3" ht="23">
+      <c r="A575" s="4"/>
+      <c r="B575" s="5"/>
+      <c r="C575" s="6"/>
+    </row>
+    <row r="576" spans="1:3" ht="23">
+      <c r="A576" s="4"/>
+      <c r="B576" s="5"/>
+      <c r="C576" s="6"/>
+    </row>
+    <row r="577" spans="1:3" ht="23">
+      <c r="A577" s="4"/>
+      <c r="B577" s="5"/>
+      <c r="C577" s="6"/>
+    </row>
+    <row r="578" spans="1:3" ht="23">
+      <c r="A578" s="4"/>
+      <c r="B578" s="5"/>
+      <c r="C578" s="6"/>
+    </row>
+    <row r="579" spans="1:3" ht="23">
+      <c r="A579" s="4"/>
+      <c r="B579" s="5"/>
+      <c r="C579" s="6"/>
+    </row>
+    <row r="580" spans="1:3" ht="23">
+      <c r="A580" s="4"/>
+      <c r="B580" s="5"/>
+      <c r="C580" s="6"/>
+    </row>
+    <row r="581" spans="1:3" ht="23">
+      <c r="A581" s="4"/>
+      <c r="B581" s="5"/>
+      <c r="C581" s="6"/>
+    </row>
+    <row r="582" spans="1:3" ht="23">
+      <c r="A582" s="4"/>
+      <c r="B582" s="5"/>
+      <c r="C582" s="6"/>
+    </row>
+    <row r="583" spans="1:3" ht="23">
+      <c r="A583" s="4"/>
+      <c r="B583" s="5"/>
+      <c r="C583" s="6"/>
+    </row>
+    <row r="584" spans="1:3" ht="23">
+      <c r="A584" s="4"/>
+      <c r="B584" s="5"/>
+      <c r="C584" s="6"/>
+    </row>
+    <row r="585" spans="1:3" ht="23">
+      <c r="A585" s="4"/>
+      <c r="B585" s="5"/>
+      <c r="C585" s="6"/>
+    </row>
+    <row r="586" spans="1:3" ht="23">
+      <c r="A586" s="4"/>
+      <c r="B586" s="5"/>
+      <c r="C586" s="6"/>
+    </row>
+    <row r="587" spans="1:3" ht="23">
+      <c r="A587" s="4"/>
+      <c r="B587" s="5"/>
+      <c r="C587" s="6"/>
+    </row>
+    <row r="588" spans="1:3" ht="23">
+      <c r="A588" s="4"/>
+      <c r="B588" s="5"/>
+      <c r="C588" s="6"/>
+    </row>
+    <row r="589" spans="1:3" ht="23">
+      <c r="A589" s="4"/>
+      <c r="B589" s="5"/>
+      <c r="C589" s="6"/>
+    </row>
+    <row r="590" spans="1:3" ht="23">
+      <c r="A590" s="4"/>
+      <c r="B590" s="5"/>
+      <c r="C590" s="6"/>
+    </row>
+    <row r="591" spans="1:3" ht="23">
+      <c r="A591" s="4"/>
+      <c r="B591" s="5"/>
+      <c r="C591" s="6"/>
+    </row>
+    <row r="592" spans="1:3" ht="23">
+      <c r="A592" s="4"/>
+      <c r="B592" s="5"/>
+      <c r="C592" s="6"/>
+    </row>
+    <row r="593" spans="1:3" ht="23">
+      <c r="A593" s="4"/>
+      <c r="B593" s="5"/>
+      <c r="C593" s="6"/>
+    </row>
+    <row r="594" spans="1:3" ht="23">
+      <c r="A594" s="4"/>
+      <c r="B594" s="5"/>
+      <c r="C594" s="6"/>
+    </row>
+    <row r="595" spans="1:3" ht="23">
+      <c r="A595" s="4"/>
+      <c r="B595" s="5"/>
+      <c r="C595" s="6"/>
+    </row>
+    <row r="596" spans="1:3" ht="23">
+      <c r="A596" s="4"/>
+      <c r="B596" s="5"/>
+      <c r="C596" s="6"/>
+    </row>
+    <row r="597" spans="1:3" ht="23">
+      <c r="A597" s="4"/>
+      <c r="B597" s="5"/>
+      <c r="C597" s="6"/>
+    </row>
+    <row r="598" spans="1:3" ht="23">
+      <c r="A598" s="4"/>
+      <c r="B598" s="5"/>
+      <c r="C598" s="6"/>
+    </row>
+    <row r="599" spans="1:3" ht="23">
+      <c r="A599" s="4"/>
+      <c r="B599" s="5"/>
+      <c r="C599" s="6"/>
+    </row>
+    <row r="600" spans="1:3" ht="23">
+      <c r="A600" s="4"/>
+      <c r="B600" s="5"/>
+      <c r="C600" s="6"/>
+    </row>
+    <row r="601" spans="1:3" ht="23">
+      <c r="A601" s="4"/>
+      <c r="B601" s="5"/>
+      <c r="C601" s="6"/>
+    </row>
+    <row r="602" spans="1:3" ht="23">
+      <c r="A602" s="4"/>
+      <c r="B602" s="5"/>
+      <c r="C602" s="6"/>
+    </row>
+    <row r="603" spans="1:3" ht="23">
+      <c r="A603" s="4"/>
+      <c r="B603" s="5"/>
+      <c r="C603" s="6"/>
+    </row>
+    <row r="604" spans="1:3" ht="23">
+      <c r="A604" s="4"/>
+      <c r="B604" s="5"/>
+      <c r="C604" s="6"/>
+    </row>
+    <row r="605" spans="1:3" ht="23">
+      <c r="A605" s="4"/>
+      <c r="B605" s="5"/>
+      <c r="C605" s="6"/>
+    </row>
+    <row r="606" spans="1:3" ht="23">
+      <c r="A606" s="4"/>
+      <c r="B606" s="5"/>
+      <c r="C606" s="6"/>
+    </row>
+    <row r="607" spans="1:3" ht="23">
+      <c r="A607" s="4"/>
+      <c r="B607" s="5"/>
+      <c r="C607" s="6"/>
+    </row>
+    <row r="608" spans="1:3" ht="23">
+      <c r="A608" s="4"/>
+      <c r="B608" s="5"/>
+      <c r="C608" s="6"/>
+    </row>
+    <row r="609" spans="1:3" ht="23">
+      <c r="A609" s="4"/>
+      <c r="B609" s="5"/>
+      <c r="C609" s="6"/>
+    </row>
+    <row r="610" spans="1:3" ht="23">
+      <c r="A610" s="4"/>
+      <c r="B610" s="5"/>
+      <c r="C610" s="6"/>
+    </row>
+    <row r="611" spans="1:3" ht="23">
+      <c r="A611" s="4"/>
+      <c r="B611" s="5"/>
+      <c r="C611" s="6"/>
+    </row>
+    <row r="612" spans="1:3" ht="23">
+      <c r="A612" s="4"/>
+      <c r="B612" s="5"/>
+      <c r="C612" s="6"/>
+    </row>
+    <row r="613" spans="1:3" ht="23">
+      <c r="A613" s="4"/>
+      <c r="B613" s="5"/>
+      <c r="C613" s="6"/>
+    </row>
+    <row r="614" spans="1:3" ht="23">
+      <c r="A614" s="4"/>
+      <c r="B614" s="5"/>
+      <c r="C614" s="6"/>
+    </row>
+    <row r="615" spans="1:3" ht="23">
+      <c r="A615" s="4"/>
+      <c r="B615" s="5"/>
+      <c r="C615" s="6"/>
+    </row>
+    <row r="616" spans="1:3" ht="23">
+      <c r="A616" s="4"/>
+      <c r="B616" s="5"/>
+      <c r="C616" s="6"/>
+    </row>
+    <row r="617" spans="1:3" ht="23">
+      <c r="A617" s="4"/>
+      <c r="B617" s="5"/>
+      <c r="C617" s="6"/>
+    </row>
+    <row r="618" spans="1:3" ht="23">
+      <c r="A618" s="4"/>
+      <c r="B618" s="5"/>
+      <c r="C618" s="6"/>
+    </row>
+    <row r="619" spans="1:3" ht="23">
+      <c r="A619" s="4"/>
+      <c r="B619" s="5"/>
+      <c r="C619" s="6"/>
+    </row>
+    <row r="620" spans="1:3" ht="23">
+      <c r="A620" s="4"/>
+      <c r="B620" s="5"/>
+      <c r="C620" s="6"/>
+    </row>
+    <row r="621" spans="1:3" ht="23">
+      <c r="A621" s="4"/>
+      <c r="B621" s="5"/>
+      <c r="C621" s="6"/>
+    </row>
+    <row r="622" spans="1:3" ht="23">
+      <c r="A622" s="4"/>
+      <c r="B622" s="5"/>
+      <c r="C622" s="6"/>
+    </row>
+    <row r="623" spans="1:3" ht="23">
+      <c r="A623" s="4"/>
+      <c r="B623" s="5"/>
+      <c r="C623" s="6"/>
+    </row>
+    <row r="624" spans="1:3" ht="23">
+      <c r="A624" s="4"/>
+      <c r="B624" s="5"/>
+      <c r="C624" s="6"/>
+    </row>
+    <row r="625" spans="1:3" ht="23">
+      <c r="A625" s="4"/>
+      <c r="B625" s="5"/>
+      <c r="C625" s="6"/>
+    </row>
+    <row r="626" spans="1:3" ht="23">
+      <c r="A626" s="4"/>
+      <c r="B626" s="5"/>
+      <c r="C626" s="6"/>
+    </row>
+    <row r="627" spans="1:3" ht="23">
+      <c r="A627" s="4"/>
+      <c r="B627" s="5"/>
+      <c r="C627" s="6"/>
+    </row>
+    <row r="628" spans="1:3" ht="23">
+      <c r="A628" s="4"/>
+      <c r="B628" s="5"/>
+      <c r="C628" s="6"/>
+    </row>
+    <row r="629" spans="1:3" ht="23">
+      <c r="A629" s="4"/>
+      <c r="B629" s="5"/>
+      <c r="C629" s="6"/>
+    </row>
+    <row r="630" spans="1:3" ht="23">
+      <c r="A630" s="4"/>
+      <c r="B630" s="5"/>
+      <c r="C630" s="6"/>
+    </row>
+    <row r="631" spans="1:3" ht="23">
+      <c r="A631" s="4"/>
+      <c r="B631" s="5"/>
+      <c r="C631" s="6"/>
+    </row>
+    <row r="632" spans="1:3" ht="23">
+      <c r="A632" s="4"/>
+      <c r="B632" s="5"/>
+      <c r="C632" s="6"/>
+    </row>
+    <row r="633" spans="1:3" ht="23">
+      <c r="A633" s="4"/>
+      <c r="B633" s="5"/>
+      <c r="C633" s="6"/>
+    </row>
+    <row r="634" spans="1:3" ht="23">
+      <c r="A634" s="4"/>
+      <c r="B634" s="5"/>
+      <c r="C634" s="6"/>
+    </row>
+    <row r="635" spans="1:3" ht="23">
+      <c r="A635" s="4"/>
+      <c r="B635" s="5"/>
+      <c r="C635" s="6"/>
+    </row>
+    <row r="636" spans="1:3" ht="23">
+      <c r="A636" s="4"/>
+      <c r="B636" s="5"/>
+      <c r="C636" s="6"/>
+    </row>
+    <row r="637" spans="1:3" ht="23">
+      <c r="A637" s="4"/>
+      <c r="B637" s="5"/>
+      <c r="C637" s="6"/>
+    </row>
+    <row r="638" spans="1:3" ht="23">
+      <c r="A638" s="4"/>
+      <c r="B638" s="5"/>
+      <c r="C638" s="6"/>
+    </row>
+    <row r="639" spans="1:3" ht="23">
+      <c r="A639" s="4"/>
+      <c r="B639" s="5"/>
+      <c r="C639" s="6"/>
+    </row>
+    <row r="640" spans="1:3" ht="23">
+      <c r="A640" s="4"/>
+      <c r="B640" s="5"/>
+      <c r="C640" s="6"/>
+    </row>
+    <row r="641" spans="1:3" ht="23">
+      <c r="A641" s="4"/>
+      <c r="B641" s="5"/>
+      <c r="C641" s="6"/>
+    </row>
+    <row r="642" spans="1:3" ht="23">
+      <c r="A642" s="4"/>
+      <c r="B642" s="5"/>
+      <c r="C642" s="6"/>
+    </row>
+    <row r="643" spans="1:3" ht="23">
+      <c r="A643" s="4"/>
+      <c r="B643" s="5"/>
+      <c r="C643" s="6"/>
+    </row>
+    <row r="644" spans="1:3" ht="23">
+      <c r="A644" s="4"/>
+      <c r="B644" s="5"/>
+      <c r="C644" s="6"/>
+    </row>
+    <row r="645" spans="1:3" ht="23">
+      <c r="A645" s="4"/>
+      <c r="B645" s="5"/>
+      <c r="C645" s="6"/>
+    </row>
+    <row r="646" spans="1:3" ht="23">
+      <c r="A646" s="4"/>
+      <c r="B646" s="5"/>
+      <c r="C646" s="6"/>
+    </row>
+    <row r="647" spans="1:3" ht="23">
+      <c r="A647" s="4"/>
+      <c r="B647" s="5"/>
+      <c r="C647" s="6"/>
+    </row>
+    <row r="648" spans="1:3" ht="23">
+      <c r="A648" s="4"/>
+      <c r="B648" s="5"/>
+      <c r="C648" s="6"/>
+    </row>
+    <row r="649" spans="1:3" ht="23">
+      <c r="A649" s="4"/>
+      <c r="B649" s="5"/>
+      <c r="C649" s="6"/>
+    </row>
+    <row r="650" spans="1:3" ht="23">
+      <c r="A650" s="4"/>
+      <c r="B650" s="5"/>
+      <c r="C650" s="6"/>
+    </row>
+    <row r="651" spans="1:3" ht="23">
+      <c r="A651" s="4"/>
+      <c r="B651" s="5"/>
+      <c r="C651" s="6"/>
+    </row>
+    <row r="652" spans="1:3" ht="23">
+      <c r="A652" s="4"/>
+      <c r="B652" s="5"/>
+      <c r="C652" s="6"/>
+    </row>
+    <row r="653" spans="1:3" ht="23">
+      <c r="A653" s="4"/>
+      <c r="B653" s="5"/>
+      <c r="C653" s="6"/>
+    </row>
+    <row r="654" spans="1:3" ht="23">
+      <c r="A654" s="4"/>
+      <c r="B654" s="5"/>
+      <c r="C654" s="6"/>
+    </row>
+    <row r="655" spans="1:3" ht="23">
+      <c r="A655" s="4"/>
+      <c r="B655" s="5"/>
+      <c r="C655" s="6"/>
+    </row>
+    <row r="656" spans="1:3" ht="23">
+      <c r="A656" s="4"/>
+      <c r="B656" s="5"/>
+      <c r="C656" s="6"/>
+    </row>
+    <row r="657" spans="1:3" ht="23">
+      <c r="A657" s="4"/>
+      <c r="B657" s="5"/>
+      <c r="C657" s="6"/>
+    </row>
+    <row r="658" spans="1:3" ht="23">
+      <c r="A658" s="4"/>
+      <c r="B658" s="5"/>
+      <c r="C658" s="6"/>
+    </row>
+    <row r="659" spans="1:3" ht="23">
+      <c r="A659" s="4"/>
+      <c r="B659" s="5"/>
+      <c r="C659" s="6"/>
+    </row>
+    <row r="660" spans="1:3" ht="23">
+      <c r="A660" s="4"/>
+      <c r="B660" s="5"/>
+      <c r="C660" s="6"/>
+    </row>
+    <row r="661" spans="1:3" ht="23">
+      <c r="A661" s="4"/>
+      <c r="B661" s="5"/>
+      <c r="C661" s="6"/>
+    </row>
+    <row r="662" spans="1:3" ht="23">
+      <c r="A662" s="4"/>
+      <c r="B662" s="5"/>
+      <c r="C662" s="6"/>
+    </row>
+    <row r="663" spans="1:3" ht="23">
+      <c r="A663" s="4"/>
+      <c r="B663" s="5"/>
+      <c r="C663" s="6"/>
+    </row>
+    <row r="664" spans="1:3" ht="23">
+      <c r="A664" s="4"/>
+      <c r="B664" s="5"/>
+      <c r="C664" s="6"/>
+    </row>
+    <row r="665" spans="1:3" ht="23">
+      <c r="A665" s="4"/>
+      <c r="B665" s="5"/>
+      <c r="C665" s="6"/>
+    </row>
+    <row r="666" spans="1:3" ht="23">
+      <c r="A666" s="4"/>
+      <c r="B666" s="5"/>
+      <c r="C666" s="6"/>
+    </row>
+    <row r="667" spans="1:3" ht="23">
+      <c r="A667" s="4"/>
+      <c r="B667" s="5"/>
+      <c r="C667" s="6"/>
+    </row>
+    <row r="668" spans="1:3" ht="23">
+      <c r="A668" s="4"/>
+      <c r="B668" s="5"/>
+      <c r="C668" s="6"/>
+    </row>
+    <row r="669" spans="1:3" ht="23">
+      <c r="A669" s="4"/>
+      <c r="B669" s="5"/>
+      <c r="C669" s="6"/>
+    </row>
+    <row r="670" spans="1:3" ht="23">
+      <c r="A670" s="4"/>
+      <c r="B670" s="5"/>
+      <c r="C670" s="6"/>
+    </row>
+    <row r="671" spans="1:3" ht="23">
+      <c r="A671" s="4"/>
+      <c r="B671" s="5"/>
+      <c r="C671" s="6"/>
+    </row>
+    <row r="672" spans="1:3" ht="23">
+      <c r="A672" s="4"/>
+      <c r="B672" s="5"/>
+      <c r="C672" s="6"/>
+    </row>
+    <row r="673" spans="1:3" ht="23">
+      <c r="A673" s="4"/>
+      <c r="B673" s="5"/>
+      <c r="C673" s="6"/>
+    </row>
+    <row r="674" spans="1:3" ht="23">
+      <c r="A674" s="4"/>
+      <c r="B674" s="5"/>
+      <c r="C674" s="6"/>
+    </row>
+    <row r="675" spans="1:3" ht="23">
+      <c r="A675" s="4"/>
+      <c r="B675" s="5"/>
+      <c r="C675" s="6"/>
+    </row>
+    <row r="676" spans="1:3" ht="23">
+      <c r="A676" s="4"/>
+      <c r="B676" s="5"/>
+      <c r="C676" s="6"/>
+    </row>
+    <row r="677" spans="1:3" ht="23">
+      <c r="A677" s="4"/>
+      <c r="B677" s="5"/>
+      <c r="C677" s="6"/>
+    </row>
+    <row r="678" spans="1:3" ht="23">
+      <c r="A678" s="4"/>
+      <c r="B678" s="5"/>
+      <c r="C678" s="6"/>
+    </row>
+    <row r="679" spans="1:3" ht="23">
+      <c r="A679" s="4"/>
+      <c r="B679" s="5"/>
+      <c r="C679" s="6"/>
+    </row>
+    <row r="680" spans="1:3" ht="23">
+      <c r="A680" s="4"/>
+      <c r="B680" s="5"/>
+      <c r="C680" s="6"/>
+    </row>
+    <row r="681" spans="1:3" ht="23">
+      <c r="A681" s="4"/>
+      <c r="B681" s="5"/>
+      <c r="C681" s="6"/>
+    </row>
+    <row r="682" spans="1:3" ht="23">
+      <c r="A682" s="4"/>
+      <c r="B682" s="5"/>
+      <c r="C682" s="6"/>
+    </row>
+    <row r="683" spans="1:3" ht="23">
+      <c r="A683" s="4"/>
+      <c r="B683" s="5"/>
+      <c r="C683" s="6"/>
+    </row>
+    <row r="684" spans="1:3" ht="23">
+      <c r="A684" s="4"/>
+      <c r="B684" s="5"/>
+      <c r="C684" s="6"/>
+    </row>
+    <row r="685" spans="1:3" ht="23">
+      <c r="A685" s="4"/>
+      <c r="B685" s="5"/>
+      <c r="C685" s="6"/>
+    </row>
+    <row r="686" spans="1:3" ht="23">
+      <c r="A686" s="4"/>
+      <c r="B686" s="5"/>
+      <c r="C686" s="6"/>
+    </row>
+    <row r="687" spans="1:3" ht="23">
+      <c r="A687" s="4"/>
+      <c r="B687" s="5"/>
+      <c r="C687" s="6"/>
+    </row>
+    <row r="688" spans="1:3" ht="23">
+      <c r="A688" s="4"/>
+      <c r="B688" s="5"/>
+      <c r="C688" s="6"/>
+    </row>
+    <row r="689" spans="1:3" ht="23">
+      <c r="A689" s="4"/>
+      <c r="B689" s="5"/>
+      <c r="C689" s="6"/>
+    </row>
+    <row r="690" spans="1:3" ht="23">
+      <c r="A690" s="4"/>
+      <c r="B690" s="5"/>
+      <c r="C690" s="6"/>
+    </row>
+    <row r="691" spans="1:3" ht="23">
+      <c r="A691" s="4"/>
+      <c r="B691" s="5"/>
+      <c r="C691" s="6"/>
+    </row>
+    <row r="692" spans="1:3" ht="23">
+      <c r="A692" s="4"/>
+      <c r="B692" s="5"/>
+      <c r="C692" s="6"/>
+    </row>
+    <row r="693" spans="1:3" ht="23">
+      <c r="A693" s="4"/>
+      <c r="B693" s="5"/>
+      <c r="C693" s="6"/>
+    </row>
+    <row r="694" spans="1:3" ht="23">
+      <c r="A694" s="4"/>
+      <c r="B694" s="5"/>
+      <c r="C694" s="6"/>
+    </row>
+    <row r="695" spans="1:3" ht="23">
+      <c r="A695" s="4"/>
+      <c r="B695" s="5"/>
+      <c r="C695" s="6"/>
+    </row>
+    <row r="696" spans="1:3" ht="23">
+      <c r="A696" s="4"/>
+      <c r="B696" s="5"/>
+      <c r="C696" s="6"/>
+    </row>
+    <row r="697" spans="1:3" ht="23">
+      <c r="A697" s="4"/>
+      <c r="B697" s="5"/>
+      <c r="C697" s="6"/>
+    </row>
+    <row r="698" spans="1:3" ht="23">
+      <c r="A698" s="4"/>
+      <c r="B698" s="5"/>
+      <c r="C698" s="6"/>
+    </row>
+    <row r="699" spans="1:3" ht="23">
+      <c r="A699" s="4"/>
+      <c r="B699" s="5"/>
+      <c r="C699" s="6"/>
+    </row>
+    <row r="700" spans="1:3" ht="23">
+      <c r="A700" s="4"/>
+      <c r="B700" s="5"/>
+      <c r="C700" s="6"/>
+    </row>
+    <row r="701" spans="1:3" ht="23">
+      <c r="A701" s="4"/>
+      <c r="B701" s="5"/>
+      <c r="C701" s="6"/>
+    </row>
+    <row r="702" spans="1:3" ht="23">
+      <c r="A702" s="4"/>
+      <c r="B702" s="5"/>
+      <c r="C702" s="6"/>
+    </row>
+    <row r="703" spans="1:3" ht="23">
+      <c r="A703" s="4"/>
+      <c r="B703" s="5"/>
+      <c r="C703" s="6"/>
+    </row>
+    <row r="704" spans="1:3" ht="23">
+      <c r="A704" s="4"/>
+      <c r="B704" s="5"/>
+      <c r="C704" s="6"/>
+    </row>
+    <row r="705" spans="1:3" ht="23">
+      <c r="A705" s="4"/>
+      <c r="B705" s="5"/>
+      <c r="C705" s="6"/>
+    </row>
+    <row r="706" spans="1:3" ht="23">
+      <c r="A706" s="4"/>
+      <c r="B706" s="5"/>
+      <c r="C706" s="6"/>
+    </row>
+    <row r="707" spans="1:3" ht="23">
+      <c r="A707" s="4"/>
+      <c r="B707" s="5"/>
+      <c r="C707" s="6"/>
+    </row>
+    <row r="708" spans="1:3" ht="23">
+      <c r="A708" s="4"/>
+      <c r="B708" s="5"/>
+      <c r="C708" s="6"/>
+    </row>
+    <row r="709" spans="1:3" ht="23">
+      <c r="A709" s="4"/>
+      <c r="B709" s="5"/>
+      <c r="C709" s="6"/>
+    </row>
+    <row r="710" spans="1:3" ht="23">
+      <c r="A710" s="4"/>
+      <c r="B710" s="5"/>
+      <c r="C710" s="6"/>
+    </row>
+    <row r="711" spans="1:3" ht="23">
+      <c r="A711" s="4"/>
+      <c r="B711" s="5"/>
+      <c r="C711" s="6"/>
+    </row>
+    <row r="712" spans="1:3" ht="23">
+      <c r="A712" s="4"/>
+      <c r="B712" s="5"/>
+      <c r="C712" s="6"/>
+    </row>
+    <row r="713" spans="1:3" ht="23">
+      <c r="A713" s="4"/>
+      <c r="B713" s="5"/>
+      <c r="C713" s="6"/>
+    </row>
+    <row r="714" spans="1:3" ht="23">
+      <c r="A714" s="4"/>
+      <c r="B714" s="5"/>
+      <c r="C714" s="6"/>
+    </row>
+    <row r="715" spans="1:3" ht="23">
+      <c r="A715" s="4"/>
+      <c r="B715" s="5"/>
+      <c r="C715" s="6"/>
+    </row>
+    <row r="716" spans="1:3" ht="23">
+      <c r="A716" s="4"/>
+      <c r="B716" s="5"/>
+      <c r="C716" s="6"/>
+    </row>
+    <row r="717" spans="1:3" ht="23">
+      <c r="A717" s="4"/>
+      <c r="B717" s="5"/>
+      <c r="C717" s="6"/>
+    </row>
+    <row r="718" spans="1:3" ht="23">
+      <c r="A718" s="4"/>
+      <c r="B718" s="5"/>
+      <c r="C718" s="6"/>
+    </row>
+    <row r="719" spans="1:3" ht="23">
+      <c r="A719" s="4"/>
+      <c r="B719" s="5"/>
+      <c r="C719" s="6"/>
+    </row>
+    <row r="720" spans="1:3" ht="23">
+      <c r="A720" s="4"/>
+      <c r="B720" s="5"/>
+      <c r="C720" s="6"/>
+    </row>
+    <row r="721" spans="1:3" ht="23">
+      <c r="A721" s="4"/>
+      <c r="B721" s="5"/>
+      <c r="C721" s="6"/>
+    </row>
+    <row r="722" spans="1:3" ht="23">
+      <c r="A722" s="4"/>
+      <c r="B722" s="5"/>
+      <c r="C722" s="6"/>
+    </row>
+    <row r="723" spans="1:3" ht="23">
+      <c r="A723" s="4"/>
+      <c r="B723" s="5"/>
+      <c r="C723" s="6"/>
+    </row>
+    <row r="724" spans="1:3" ht="23">
+      <c r="A724" s="4"/>
+      <c r="B724" s="5"/>
+      <c r="C724" s="6"/>
+    </row>
+    <row r="725" spans="1:3" ht="23">
+      <c r="A725" s="4"/>
+      <c r="B725" s="5"/>
+      <c r="C725" s="6"/>
+    </row>
+    <row r="726" spans="1:3" ht="23">
+      <c r="A726" s="4"/>
+      <c r="B726" s="5"/>
+      <c r="C726" s="6"/>
+    </row>
+    <row r="727" spans="1:3" ht="23">
+      <c r="A727" s="4"/>
+      <c r="B727" s="5"/>
+      <c r="C727" s="6"/>
+    </row>
+    <row r="728" spans="1:3" ht="23">
+      <c r="A728" s="4"/>
+      <c r="B728" s="5"/>
+      <c r="C728" s="6"/>
+    </row>
+    <row r="729" spans="1:3" ht="23">
+      <c r="A729" s="4"/>
+      <c r="B729" s="5"/>
+      <c r="C729" s="6"/>
+    </row>
+    <row r="730" spans="1:3" ht="23">
+      <c r="A730" s="4"/>
+      <c r="B730" s="5"/>
+      <c r="C730" s="6"/>
+    </row>
+    <row r="731" spans="1:3" ht="23">
+      <c r="A731" s="4"/>
+      <c r="B731" s="5"/>
+      <c r="C731" s="6"/>
+    </row>
+    <row r="732" spans="1:3" ht="23">
+      <c r="A732" s="4"/>
+      <c r="B732" s="5"/>
+      <c r="C732" s="6"/>
+    </row>
+    <row r="733" spans="1:3" ht="23">
+      <c r="A733" s="4"/>
+      <c r="B733" s="5"/>
+      <c r="C733" s="6"/>
+    </row>
+    <row r="734" spans="1:3" ht="23">
+      <c r="A734" s="4"/>
+      <c r="B734" s="5"/>
+      <c r="C734" s="6"/>
+    </row>
+    <row r="735" spans="1:3" ht="23">
+      <c r="A735" s="4"/>
+      <c r="B735" s="5"/>
+      <c r="C735" s="6"/>
+    </row>
+    <row r="736" spans="1:3" ht="23">
+      <c r="A736" s="4"/>
+      <c r="B736" s="5"/>
+      <c r="C736" s="6"/>
+    </row>
+    <row r="737" spans="1:3" ht="23">
+      <c r="A737" s="4"/>
+      <c r="B737" s="5"/>
+      <c r="C737" s="6"/>
+    </row>
+    <row r="738" spans="1:3" ht="23">
+      <c r="A738" s="4"/>
+      <c r="B738" s="5"/>
+      <c r="C738" s="6"/>
+    </row>
+    <row r="739" spans="1:3" ht="23">
+      <c r="A739" s="4"/>
+      <c r="B739" s="5"/>
+      <c r="C739" s="6"/>
+    </row>
+    <row r="740" spans="1:3" ht="23">
+      <c r="A740" s="4"/>
+      <c r="B740" s="5"/>
+      <c r="C740" s="6"/>
+    </row>
+    <row r="741" spans="1:3" ht="23">
+      <c r="A741" s="4"/>
+      <c r="B741" s="5"/>
+      <c r="C741" s="6"/>
+    </row>
+    <row r="742" spans="1:3" ht="23">
+      <c r="A742" s="4"/>
+      <c r="B742" s="5"/>
+      <c r="C742" s="6"/>
+    </row>
+    <row r="743" spans="1:3" ht="23">
+      <c r="A743" s="4"/>
+      <c r="B743" s="5"/>
+      <c r="C743" s="6"/>
+    </row>
+    <row r="744" spans="1:3" ht="23">
+      <c r="A744" s="4"/>
+      <c r="B744" s="5"/>
+      <c r="C744" s="6"/>
+    </row>
+    <row r="745" spans="1:3" ht="23">
+      <c r="A745" s="4"/>
+      <c r="B745" s="5"/>
+      <c r="C745" s="6"/>
+    </row>
+    <row r="746" spans="1:3" ht="23">
+      <c r="A746" s="4"/>
+      <c r="B746" s="5"/>
+      <c r="C746" s="6"/>
+    </row>
+    <row r="747" spans="1:3" ht="23">
+      <c r="A747" s="4"/>
+      <c r="B747" s="5"/>
+      <c r="C747" s="6"/>
+    </row>
+    <row r="748" spans="1:3" ht="23">
+      <c r="A748" s="4"/>
+      <c r="B748" s="5"/>
+      <c r="C748" s="6"/>
+    </row>
+    <row r="749" spans="1:3" ht="23">
+      <c r="A749" s="4"/>
+      <c r="B749" s="5"/>
+      <c r="C749" s="6"/>
+    </row>
+    <row r="750" spans="1:3" ht="23">
+      <c r="A750" s="4"/>
+      <c r="B750" s="5"/>
+      <c r="C750" s="6"/>
+    </row>
+    <row r="751" spans="1:3" ht="23">
+      <c r="A751" s="4"/>
+      <c r="B751" s="5"/>
+      <c r="C751" s="6"/>
+    </row>
+    <row r="752" spans="1:3" ht="23">
+      <c r="A752" s="4"/>
+      <c r="B752" s="5"/>
+      <c r="C752" s="6"/>
+    </row>
+    <row r="753" spans="1:3" ht="23">
+      <c r="A753" s="4"/>
+      <c r="B753" s="5"/>
+      <c r="C753" s="6"/>
+    </row>
+    <row r="754" spans="1:3" ht="23">
+      <c r="A754" s="4"/>
+      <c r="B754" s="5"/>
+      <c r="C754" s="6"/>
+    </row>
+    <row r="755" spans="1:3" ht="23">
+      <c r="A755" s="4"/>
+      <c r="B755" s="5"/>
+      <c r="C755" s="6"/>
+    </row>
+    <row r="756" spans="1:3" ht="23">
+      <c r="A756" s="4"/>
+      <c r="B756" s="5"/>
+      <c r="C756" s="6"/>
+    </row>
+    <row r="757" spans="1:3" ht="23">
+      <c r="A757" s="4"/>
+      <c r="B757" s="5"/>
+      <c r="C757" s="6"/>
+    </row>
+    <row r="758" spans="1:3" ht="23">
+      <c r="A758" s="4"/>
+      <c r="B758" s="5"/>
+      <c r="C758" s="6"/>
+    </row>
+    <row r="759" spans="1:3" ht="23">
+      <c r="A759" s="4"/>
+      <c r="B759" s="5"/>
+      <c r="C759" s="6"/>
+    </row>
+    <row r="760" spans="1:3" ht="23">
+      <c r="A760" s="4"/>
+      <c r="B760" s="5"/>
+      <c r="C760" s="6"/>
+    </row>
+    <row r="761" spans="1:3" ht="23">
+      <c r="A761" s="4"/>
+      <c r="B761" s="5"/>
+      <c r="C761" s="6"/>
+    </row>
+    <row r="762" spans="1:3" ht="23">
+      <c r="A762" s="4"/>
+      <c r="B762" s="5"/>
+      <c r="C762" s="6"/>
+    </row>
+    <row r="763" spans="1:3" ht="23">
+      <c r="A763" s="4"/>
+      <c r="B763" s="5"/>
+      <c r="C763" s="6"/>
+    </row>
+    <row r="764" spans="1:3" ht="23">
+      <c r="A764" s="4"/>
+      <c r="B764" s="5"/>
+      <c r="C764" s="6"/>
+    </row>
+    <row r="765" spans="1:3" ht="23">
+      <c r="A765" s="4"/>
+      <c r="B765" s="5"/>
+      <c r="C765" s="6"/>
+    </row>
+    <row r="766" spans="1:3" ht="23">
+      <c r="A766" s="4"/>
+      <c r="B766" s="5"/>
+      <c r="C766" s="6"/>
+    </row>
+    <row r="767" spans="1:3" ht="23">
+      <c r="A767" s="4"/>
+      <c r="B767" s="5"/>
+      <c r="C767" s="6"/>
+    </row>
+    <row r="768" spans="1:3" ht="23">
+      <c r="A768" s="4"/>
+      <c r="B768" s="5"/>
+      <c r="C768" s="6"/>
+    </row>
+    <row r="769" spans="1:3" ht="23">
+      <c r="A769" s="4"/>
+      <c r="B769" s="5"/>
+      <c r="C769" s="6"/>
+    </row>
+    <row r="770" spans="1:3" ht="23">
+      <c r="A770" s="4"/>
+      <c r="B770" s="5"/>
+      <c r="C770" s="6"/>
+    </row>
+    <row r="771" spans="1:3" ht="23">
+      <c r="A771" s="4"/>
+      <c r="B771" s="5"/>
+      <c r="C771" s="6"/>
+    </row>
+    <row r="772" spans="1:3" ht="23">
+      <c r="A772" s="4"/>
+      <c r="B772" s="5"/>
+      <c r="C772" s="6"/>
+    </row>
+    <row r="773" spans="1:3" ht="23">
+      <c r="A773" s="4"/>
+      <c r="B773" s="5"/>
+      <c r="C773" s="6"/>
+    </row>
+    <row r="774" spans="1:3" ht="23">
+      <c r="A774" s="4"/>
+      <c r="B774" s="5"/>
+      <c r="C774" s="6"/>
+    </row>
+    <row r="775" spans="1:3" ht="23">
+      <c r="A775" s="4"/>
+      <c r="B775" s="5"/>
+      <c r="C775" s="6"/>
+    </row>
+    <row r="776" spans="1:3" ht="23">
+      <c r="A776" s="4"/>
+      <c r="B776" s="5"/>
+      <c r="C776" s="6"/>
+    </row>
+    <row r="777" spans="1:3" ht="23">
+      <c r="A777" s="4"/>
+      <c r="B777" s="5"/>
+      <c r="C777" s="6"/>
+    </row>
+    <row r="778" spans="1:3" ht="23">
+      <c r="A778" s="4"/>
+      <c r="B778" s="5"/>
+      <c r="C778" s="6"/>
+    </row>
+    <row r="779" spans="1:3" ht="23">
+      <c r="A779" s="4"/>
+      <c r="B779" s="5"/>
+      <c r="C779" s="6"/>
+    </row>
+    <row r="780" spans="1:3" ht="23">
+      <c r="A780" s="4"/>
+      <c r="B780" s="5"/>
+      <c r="C780" s="6"/>
+    </row>
+    <row r="781" spans="1:3" ht="23">
+      <c r="A781" s="4"/>
+      <c r="B781" s="5"/>
+      <c r="C781" s="6"/>
+    </row>
+    <row r="782" spans="1:3" ht="23">
+      <c r="A782" s="4"/>
+      <c r="B782" s="5"/>
+      <c r="C782" s="6"/>
+    </row>
+    <row r="783" spans="1:3" ht="23">
+      <c r="A783" s="4"/>
+      <c r="B783" s="5"/>
+      <c r="C783" s="6"/>
+    </row>
+    <row r="784" spans="1:3" ht="23">
+      <c r="A784" s="4"/>
+      <c r="B784" s="5"/>
+      <c r="C784" s="6"/>
+    </row>
+    <row r="785" spans="1:3" ht="23">
+      <c r="A785" s="4"/>
+      <c r="B785" s="5"/>
+      <c r="C785" s="6"/>
+    </row>
+    <row r="786" spans="1:3" ht="23">
+      <c r="A786" s="4"/>
+      <c r="B786" s="5"/>
+      <c r="C786" s="6"/>
+    </row>
+    <row r="787" spans="1:3" ht="23">
+      <c r="A787" s="4"/>
+      <c r="B787" s="5"/>
+      <c r="C787" s="6"/>
+    </row>
+    <row r="788" spans="1:3" ht="23">
+      <c r="A788" s="4"/>
+      <c r="B788" s="5"/>
+      <c r="C788" s="6"/>
+    </row>
+    <row r="789" spans="1:3" ht="23">
+      <c r="A789" s="4"/>
+      <c r="B789" s="5"/>
+      <c r="C789" s="6"/>
+    </row>
+    <row r="790" spans="1:3" ht="23">
+      <c r="A790" s="4"/>
+      <c r="B790" s="5"/>
+      <c r="C790" s="6"/>
+    </row>
+    <row r="791" spans="1:3" ht="23">
+      <c r="A791" s="4"/>
+      <c r="B791" s="5"/>
+      <c r="C791" s="6"/>
+    </row>
+    <row r="792" spans="1:3" ht="23">
+      <c r="A792" s="4"/>
+      <c r="B792" s="5"/>
+      <c r="C792" s="6"/>
+    </row>
+    <row r="793" spans="1:3" ht="23">
+      <c r="A793" s="4"/>
+      <c r="B793" s="5"/>
+      <c r="C793" s="6"/>
+    </row>
+    <row r="794" spans="1:3" ht="23">
+      <c r="A794" s="4"/>
+      <c r="B794" s="5"/>
+      <c r="C794" s="6"/>
+    </row>
+    <row r="795" spans="1:3" ht="23">
+      <c r="A795" s="4"/>
+      <c r="B795" s="5"/>
+      <c r="C795" s="6"/>
+    </row>
+    <row r="796" spans="1:3" ht="23">
+      <c r="A796" s="4"/>
+      <c r="B796" s="5"/>
+      <c r="C796" s="6"/>
+    </row>
+    <row r="797" spans="1:3" ht="23">
+      <c r="A797" s="4"/>
+      <c r="B797" s="5"/>
+      <c r="C797" s="6"/>
+    </row>
+    <row r="798" spans="1:3" ht="23">
+      <c r="A798" s="4"/>
+      <c r="B798" s="5"/>
+      <c r="C798" s="6"/>
+    </row>
+    <row r="799" spans="1:3" ht="23">
+      <c r="A799" s="4"/>
+      <c r="B799" s="5"/>
+      <c r="C799" s="6"/>
+    </row>
+    <row r="800" spans="1:3" ht="23">
+      <c r="A800" s="4"/>
+      <c r="B800" s="5"/>
+      <c r="C800" s="6"/>
+    </row>
+    <row r="801" spans="1:3" ht="23">
+      <c r="A801" s="4"/>
+      <c r="B801" s="5"/>
+      <c r="C801" s="6"/>
+    </row>
+    <row r="802" spans="1:3" ht="23">
+      <c r="A802" s="4"/>
+      <c r="B802" s="5"/>
+      <c r="C802" s="6"/>
+    </row>
+    <row r="803" spans="1:3" ht="23">
+      <c r="A803" s="4"/>
+      <c r="B803" s="5"/>
+      <c r="C803" s="6"/>
+    </row>
+    <row r="804" spans="1:3" ht="23">
+      <c r="A804" s="4"/>
+      <c r="B804" s="5"/>
+      <c r="C804" s="6"/>
+    </row>
+    <row r="805" spans="1:3" ht="23">
+      <c r="A805" s="4"/>
+      <c r="B805" s="5"/>
+      <c r="C805" s="6"/>
+    </row>
+    <row r="806" spans="1:3" ht="23">
+      <c r="A806" s="4"/>
+      <c r="B806" s="5"/>
+      <c r="C806" s="6"/>
+    </row>
+    <row r="807" spans="1:3" ht="23">
+      <c r="A807" s="4"/>
+      <c r="B807" s="5"/>
+      <c r="C807" s="6"/>
+    </row>
+    <row r="808" spans="1:3" ht="23">
+      <c r="A808" s="4"/>
+      <c r="B808" s="5"/>
+      <c r="C808" s="6"/>
+    </row>
+    <row r="809" spans="1:3" ht="23">
+      <c r="A809" s="4"/>
+      <c r="B809" s="5"/>
+      <c r="C809" s="6"/>
+    </row>
+    <row r="810" spans="1:3" ht="23">
+      <c r="A810" s="4"/>
+      <c r="B810" s="5"/>
+      <c r="C810" s="6"/>
+    </row>
+    <row r="811" spans="1:3" ht="23">
+      <c r="A811" s="4"/>
+      <c r="B811" s="5"/>
+      <c r="C811" s="6"/>
+    </row>
+    <row r="812" spans="1:3" ht="23">
+      <c r="A812" s="4"/>
+      <c r="B812" s="5"/>
+      <c r="C812" s="6"/>
+    </row>
+    <row r="813" spans="1:3" ht="23">
+      <c r="A813" s="4"/>
+      <c r="B813" s="5"/>
+      <c r="C813" s="6"/>
+    </row>
+    <row r="814" spans="1:3" ht="23">
+      <c r="A814" s="4"/>
+      <c r="B814" s="5"/>
+      <c r="C814" s="6"/>
+    </row>
+    <row r="815" spans="1:3" ht="23">
+      <c r="A815" s="4"/>
+      <c r="B815" s="5"/>
+      <c r="C815" s="6"/>
+    </row>
+    <row r="816" spans="1:3" ht="23">
+      <c r="A816" s="4"/>
+      <c r="B816" s="5"/>
+      <c r="C816" s="6"/>
+    </row>
+    <row r="817" spans="1:3" ht="23">
+      <c r="A817" s="4"/>
+      <c r="B817" s="5"/>
+      <c r="C817" s="6"/>
+    </row>
+    <row r="818" spans="1:3" ht="23">
+      <c r="A818" s="4"/>
+      <c r="B818" s="5"/>
+      <c r="C818" s="6"/>
+    </row>
+    <row r="819" spans="1:3" ht="23">
+      <c r="A819" s="4"/>
+      <c r="B819" s="5"/>
+      <c r="C819" s="6"/>
+    </row>
+    <row r="820" spans="1:3" ht="23">
+      <c r="A820" s="4"/>
+      <c r="B820" s="5"/>
+      <c r="C820" s="6"/>
+    </row>
+    <row r="821" spans="1:3" ht="23">
+      <c r="A821" s="4"/>
+      <c r="B821" s="5"/>
+      <c r="C821" s="6"/>
+    </row>
+    <row r="822" spans="1:3" ht="23">
+      <c r="A822" s="4"/>
+      <c r="B822" s="5"/>
+      <c r="C822" s="6"/>
+    </row>
+    <row r="823" spans="1:3" ht="23">
+      <c r="A823" s="4"/>
+      <c r="B823" s="5"/>
+      <c r="C823" s="6"/>
+    </row>
+    <row r="824" spans="1:3" ht="23">
+      <c r="A824" s="4"/>
+      <c r="B824" s="5"/>
+      <c r="C824" s="6"/>
+    </row>
+    <row r="825" spans="1:3" ht="23">
+      <c r="A825" s="4"/>
+      <c r="B825" s="5"/>
+      <c r="C825" s="6"/>
+    </row>
+    <row r="826" spans="1:3" ht="23">
+      <c r="A826" s="4"/>
+      <c r="B826" s="5"/>
+      <c r="C826" s="6"/>
+    </row>
+    <row r="827" spans="1:3" ht="23">
+      <c r="A827" s="4"/>
+      <c r="B827" s="5"/>
+      <c r="C827" s="6"/>
+    </row>
+    <row r="828" spans="1:3" ht="23">
+      <c r="A828" s="4"/>
+      <c r="B828" s="5"/>
+      <c r="C828" s="6"/>
+    </row>
+    <row r="829" spans="1:3" ht="23">
+      <c r="A829" s="4"/>
+      <c r="B829" s="5"/>
+      <c r="C829" s="6"/>
+    </row>
+    <row r="830" spans="1:3" ht="23">
+      <c r="A830" s="4"/>
+      <c r="B830" s="5"/>
+      <c r="C830" s="6"/>
+    </row>
+    <row r="831" spans="1:3" ht="23">
+      <c r="A831" s="4"/>
+      <c r="B831" s="5"/>
+      <c r="C831" s="6"/>
+    </row>
+    <row r="832" spans="1:3" ht="23">
+      <c r="A832" s="4"/>
+      <c r="B832" s="5"/>
+      <c r="C832" s="6"/>
+    </row>
+    <row r="833" spans="1:3" ht="23">
+      <c r="A833" s="4"/>
+      <c r="B833" s="5"/>
+      <c r="C833" s="6"/>
+    </row>
+    <row r="834" spans="1:3" ht="23">
+      <c r="A834" s="4"/>
+      <c r="B834" s="5"/>
+      <c r="C834" s="6"/>
+    </row>
+    <row r="835" spans="1:3" ht="23">
+      <c r="A835" s="4"/>
+      <c r="B835" s="5"/>
+      <c r="C835" s="6"/>
+    </row>
+    <row r="836" spans="1:3" ht="23">
+      <c r="A836" s="4"/>
+      <c r="B836" s="5"/>
+      <c r="C836" s="6"/>
+    </row>
+    <row r="837" spans="1:3" ht="23">
+      <c r="A837" s="4"/>
+      <c r="B837" s="5"/>
+      <c r="C837" s="6"/>
+    </row>
+    <row r="838" spans="1:3" ht="23">
+      <c r="A838" s="4"/>
+      <c r="B838" s="5"/>
+      <c r="C838" s="6"/>
+    </row>
+    <row r="839" spans="1:3" ht="23">
+      <c r="A839" s="4"/>
+      <c r="B839" s="5"/>
+      <c r="C839" s="6"/>
+    </row>
+    <row r="840" spans="1:3" ht="23">
+      <c r="A840" s="4"/>
+      <c r="B840" s="5"/>
+      <c r="C840" s="6"/>
+    </row>
+    <row r="841" spans="1:3" ht="23">
+      <c r="A841" s="4"/>
+      <c r="B841" s="5"/>
+      <c r="C841" s="6"/>
+    </row>
+    <row r="842" spans="1:3" ht="23">
+      <c r="A842" s="4"/>
+      <c r="B842" s="5"/>
+      <c r="C842" s="6"/>
+    </row>
+    <row r="843" spans="1:3" ht="23">
+      <c r="A843" s="4"/>
+      <c r="B843" s="5"/>
+      <c r="C843" s="6"/>
+    </row>
+    <row r="844" spans="1:3" ht="23">
+      <c r="A844" s="4"/>
+      <c r="B844" s="5"/>
+      <c r="C844" s="6"/>
+    </row>
+    <row r="845" spans="1:3" ht="23">
+      <c r="A845" s="4"/>
+      <c r="B845" s="5"/>
+      <c r="C845" s="6"/>
+    </row>
+    <row r="846" spans="1:3" ht="23">
+      <c r="A846" s="4"/>
+      <c r="B846" s="5"/>
+      <c r="C846" s="6"/>
+    </row>
+    <row r="847" spans="1:3" ht="23">
+      <c r="A847" s="4"/>
+      <c r="B847" s="5"/>
+      <c r="C847" s="6"/>
+    </row>
+    <row r="848" spans="1:3" ht="23">
+      <c r="A848" s="4"/>
+      <c r="B848" s="5"/>
+      <c r="C848" s="6"/>
+    </row>
+    <row r="849" spans="1:3" ht="23">
+      <c r="A849" s="4"/>
+      <c r="B849" s="5"/>
+      <c r="C849" s="6"/>
+    </row>
+    <row r="850" spans="1:3" ht="23">
+      <c r="A850" s="4"/>
+      <c r="B850" s="5"/>
+      <c r="C850" s="6"/>
+    </row>
+    <row r="851" spans="1:3" ht="23">
+      <c r="A851" s="4"/>
+      <c r="B851" s="5"/>
+      <c r="C851" s="6"/>
+    </row>
+    <row r="852" spans="1:3" ht="23">
+      <c r="A852" s="4"/>
+      <c r="B852" s="5"/>
+      <c r="C852" s="6"/>
+    </row>
+    <row r="853" spans="1:3" ht="23">
+      <c r="A853" s="4"/>
+      <c r="B853" s="5"/>
+      <c r="C853" s="6"/>
+    </row>
+    <row r="854" spans="1:3" ht="23">
+      <c r="A854" s="4"/>
+      <c r="B854" s="5"/>
+      <c r="C854" s="6"/>
+    </row>
+    <row r="855" spans="1:3" ht="23">
+      <c r="A855" s="4"/>
+      <c r="B855" s="5"/>
+      <c r="C855" s="6"/>
+    </row>
+    <row r="856" spans="1:3" ht="23">
+      <c r="A856" s="4"/>
+      <c r="B856" s="5"/>
+      <c r="C856" s="6"/>
+    </row>
+    <row r="857" spans="1:3" ht="23">
+      <c r="A857" s="4"/>
+      <c r="B857" s="5"/>
+      <c r="C857" s="6"/>
+    </row>
+    <row r="858" spans="1:3" ht="23">
+      <c r="A858" s="4"/>
+      <c r="B858" s="5"/>
+      <c r="C858" s="6"/>
+    </row>
+    <row r="859" spans="1:3" ht="23">
+      <c r="A859" s="4"/>
+      <c r="B859" s="5"/>
+      <c r="C859" s="6"/>
+    </row>
+    <row r="860" spans="1:3" ht="23">
+      <c r="A860" s="4"/>
+      <c r="B860" s="5"/>
+      <c r="C860" s="6"/>
+    </row>
+    <row r="861" spans="1:3" ht="23">
+      <c r="A861" s="4"/>
+      <c r="B861" s="5"/>
+      <c r="C861" s="6"/>
+    </row>
+    <row r="862" spans="1:3" ht="23">
+      <c r="A862" s="4"/>
+      <c r="B862" s="5"/>
+      <c r="C862" s="6"/>
+    </row>
+    <row r="863" spans="1:3" ht="23">
+      <c r="A863" s="4"/>
+      <c r="B863" s="5"/>
+      <c r="C863" s="6"/>
+    </row>
+    <row r="864" spans="1:3" ht="23">
+      <c r="A864" s="4"/>
+      <c r="B864" s="5"/>
+      <c r="C864" s="6"/>
+    </row>
+    <row r="865" spans="1:3" ht="23">
+      <c r="A865" s="4"/>
+      <c r="B865" s="5"/>
+      <c r="C865" s="6"/>
+    </row>
+    <row r="866" spans="1:3" ht="23">
+      <c r="A866" s="4"/>
+      <c r="B866" s="5"/>
+      <c r="C866" s="6"/>
+    </row>
+    <row r="867" spans="1:3" ht="23">
+      <c r="A867" s="4"/>
+      <c r="B867" s="5"/>
+      <c r="C867" s="6"/>
+    </row>
+    <row r="868" spans="1:3" ht="23">
+      <c r="A868" s="4"/>
+      <c r="B868" s="5"/>
+      <c r="C868" s="6"/>
+    </row>
+    <row r="869" spans="1:3" ht="23">
+      <c r="A869" s="4"/>
+      <c r="B869" s="5"/>
+      <c r="C869" s="6"/>
+    </row>
+    <row r="870" spans="1:3" ht="23">
+      <c r="A870" s="4"/>
+      <c r="B870" s="5"/>
+      <c r="C870" s="6"/>
+    </row>
+    <row r="871" spans="1:3" ht="23">
+      <c r="A871" s="4"/>
+      <c r="B871" s="5"/>
+      <c r="C871" s="6"/>
+    </row>
+    <row r="872" spans="1:3" ht="23">
+      <c r="A872" s="4"/>
+      <c r="B872" s="5"/>
+      <c r="C872" s="6"/>
+    </row>
+    <row r="873" spans="1:3" ht="23">
+      <c r="A873" s="4"/>
+      <c r="B873" s="5"/>
+      <c r="C873" s="6"/>
+    </row>
+    <row r="874" spans="1:3" ht="23">
+      <c r="A874" s="4"/>
+      <c r="B874" s="5"/>
+      <c r="C874" s="6"/>
+    </row>
+    <row r="875" spans="1:3" ht="23">
+      <c r="A875" s="4"/>
+      <c r="B875" s="5"/>
+      <c r="C875" s="6"/>
+    </row>
+    <row r="876" spans="1:3" ht="23">
+      <c r="A876" s="4"/>
+      <c r="B876" s="5"/>
+      <c r="C876" s="6"/>
+    </row>
+    <row r="877" spans="1:3" ht="23">
+      <c r="A877" s="4"/>
+      <c r="B877" s="5"/>
+      <c r="C877" s="6"/>
+    </row>
+    <row r="878" spans="1:3" ht="23">
+      <c r="A878" s="4"/>
+      <c r="B878" s="5"/>
+      <c r="C878" s="6"/>
+    </row>
+    <row r="879" spans="1:3" ht="23">
+      <c r="A879" s="4"/>
+      <c r="B879" s="5"/>
+      <c r="C879" s="6"/>
+    </row>
+    <row r="880" spans="1:3" ht="23">
+      <c r="A880" s="4"/>
+      <c r="B880" s="5"/>
+      <c r="C880" s="6"/>
+    </row>
+    <row r="881" spans="1:3" ht="23">
+      <c r="A881" s="4"/>
+      <c r="B881" s="5"/>
+      <c r="C881" s="6"/>
+    </row>
+    <row r="882" spans="1:3" ht="23">
+      <c r="A882" s="4"/>
+      <c r="B882" s="5"/>
+      <c r="C882" s="6"/>
+    </row>
+    <row r="883" spans="1:3" ht="23">
+      <c r="A883" s="4"/>
+      <c r="B883" s="5"/>
+      <c r="C883" s="6"/>
+    </row>
+    <row r="884" spans="1:3" ht="23">
+      <c r="A884" s="4"/>
+      <c r="B884" s="5"/>
+      <c r="C884" s="6"/>
+    </row>
+    <row r="885" spans="1:3" ht="23">
+      <c r="A885" s="4"/>
+      <c r="B885" s="5"/>
+      <c r="C885" s="6"/>
+    </row>
+    <row r="886" spans="1:3" ht="23">
+      <c r="A886" s="4"/>
+      <c r="B886" s="5"/>
+      <c r="C886" s="6"/>
+    </row>
+    <row r="887" spans="1:3" ht="23">
+      <c r="A887" s="4"/>
+      <c r="B887" s="5"/>
+      <c r="C887" s="6"/>
+    </row>
+    <row r="888" spans="1:3" ht="23">
+      <c r="A888" s="4"/>
+      <c r="B888" s="5"/>
+      <c r="C888" s="6"/>
+    </row>
+    <row r="889" spans="1:3" ht="23">
+      <c r="A889" s="4"/>
+      <c r="B889" s="5"/>
+      <c r="C889" s="6"/>
+    </row>
+    <row r="890" spans="1:3" ht="23">
+      <c r="A890" s="4"/>
+      <c r="B890" s="5"/>
+      <c r="C890" s="6"/>
+    </row>
+    <row r="891" spans="1:3" ht="23">
+      <c r="A891" s="4"/>
+      <c r="B891" s="5"/>
+      <c r="C891" s="6"/>
+    </row>
+    <row r="892" spans="1:3" ht="23">
+      <c r="A892" s="4"/>
+      <c r="B892" s="5"/>
+      <c r="C892" s="6"/>
+    </row>
+    <row r="893" spans="1:3" ht="23">
+      <c r="A893" s="4"/>
+      <c r="B893" s="5"/>
+      <c r="C893" s="6"/>
+    </row>
+    <row r="894" spans="1:3" ht="23">
+      <c r="A894" s="4"/>
+      <c r="B894" s="5"/>
+      <c r="C894" s="6"/>
+    </row>
+    <row r="895" spans="1:3" ht="23">
+      <c r="A895" s="4"/>
+      <c r="B895" s="5"/>
+      <c r="C895" s="6"/>
+    </row>
+    <row r="896" spans="1:3" ht="23">
+      <c r="A896" s="4"/>
+      <c r="B896" s="5"/>
+      <c r="C896" s="6"/>
+    </row>
+    <row r="897" spans="1:3" ht="23">
+      <c r="A897" s="4"/>
+      <c r="B897" s="5"/>
+      <c r="C897" s="6"/>
+    </row>
+    <row r="898" spans="1:3" ht="23">
+      <c r="A898" s="4"/>
+      <c r="B898" s="5"/>
+      <c r="C898" s="6"/>
+    </row>
+    <row r="899" spans="1:3" ht="23">
+      <c r="A899" s="4"/>
+      <c r="B899" s="5"/>
+      <c r="C899" s="6"/>
+    </row>
+    <row r="900" spans="1:3" ht="23">
+      <c r="A900" s="4"/>
+      <c r="B900" s="5"/>
+      <c r="C900" s="6"/>
+    </row>
+    <row r="901" spans="1:3" ht="23">
+      <c r="A901" s="4"/>
+      <c r="B901" s="5"/>
+      <c r="C901" s="6"/>
+    </row>
+    <row r="902" spans="1:3" ht="23">
+      <c r="A902" s="4"/>
+      <c r="B902" s="5"/>
+      <c r="C902" s="6"/>
+    </row>
+    <row r="903" spans="1:3" ht="23">
+      <c r="A903" s="4"/>
+      <c r="B903" s="5"/>
+      <c r="C903" s="6"/>
+    </row>
+    <row r="904" spans="1:3" ht="23">
+      <c r="A904" s="4"/>
+      <c r="B904" s="5"/>
+      <c r="C904" s="6"/>
+    </row>
+    <row r="905" spans="1:3" ht="23">
+      <c r="A905" s="4"/>
+      <c r="B905" s="5"/>
+      <c r="C905" s="6"/>
+    </row>
+    <row r="906" spans="1:3" ht="23">
+      <c r="A906" s="4"/>
+      <c r="B906" s="5"/>
+      <c r="C906" s="6"/>
+    </row>
+    <row r="907" spans="1:3" ht="23">
+      <c r="A907" s="4"/>
+      <c r="B907" s="5"/>
+      <c r="C907" s="6"/>
+    </row>
+    <row r="908" spans="1:3" ht="23">
+      <c r="A908" s="4"/>
+      <c r="B908" s="5"/>
+      <c r="C908" s="6"/>
+    </row>
+    <row r="909" spans="1:3" ht="23">
+      <c r="A909" s="4"/>
+      <c r="B909" s="5"/>
+      <c r="C909" s="6"/>
+    </row>
+    <row r="910" spans="1:3" ht="23">
+      <c r="A910" s="4"/>
+      <c r="B910" s="5"/>
+      <c r="C910" s="6"/>
+    </row>
+    <row r="911" spans="1:3" ht="23">
+      <c r="A911" s="4"/>
+      <c r="B911" s="5"/>
+      <c r="C911" s="6"/>
+    </row>
+    <row r="912" spans="1:3" ht="23">
+      <c r="A912" s="4"/>
+      <c r="B912" s="5"/>
+      <c r="C912" s="6"/>
+    </row>
+    <row r="913" spans="1:3" ht="23">
+      <c r="A913" s="4"/>
+      <c r="B913" s="5"/>
+      <c r="C913" s="6"/>
+    </row>
+    <row r="914" spans="1:3" ht="23">
+      <c r="A914" s="4"/>
+      <c r="B914" s="5"/>
+      <c r="C914" s="6"/>
+    </row>
+    <row r="915" spans="1:3" ht="23">
+      <c r="A915" s="4"/>
+      <c r="B915" s="5"/>
+      <c r="C915" s="6"/>
+    </row>
+    <row r="916" spans="1:3" ht="23">
+      <c r="A916" s="4"/>
+      <c r="B916" s="5"/>
+      <c r="C916" s="6"/>
+    </row>
+    <row r="917" spans="1:3" ht="23">
+      <c r="A917" s="4"/>
+      <c r="B917" s="5"/>
+      <c r="C917" s="6"/>
+    </row>
+    <row r="918" spans="1:3" ht="23">
+      <c r="A918" s="4"/>
+      <c r="B918" s="5"/>
+      <c r="C918" s="6"/>
+    </row>
+    <row r="919" spans="1:3" ht="23">
+      <c r="A919" s="4"/>
+      <c r="B919" s="5"/>
+      <c r="C919" s="6"/>
+    </row>
+    <row r="920" spans="1:3" ht="23">
+      <c r="A920" s="4"/>
+      <c r="B920" s="5"/>
+      <c r="C920" s="6"/>
+    </row>
+    <row r="921" spans="1:3" ht="23">
+      <c r="A921" s="4"/>
+      <c r="B921" s="5"/>
+      <c r="C921" s="6"/>
+    </row>
+    <row r="922" spans="1:3" ht="23">
+      <c r="A922" s="4"/>
+      <c r="B922" s="5"/>
+      <c r="C922" s="6"/>
+    </row>
+    <row r="923" spans="1:3" ht="23">
+      <c r="A923" s="4"/>
+      <c r="B923" s="5"/>
+      <c r="C923" s="6"/>
+    </row>
+    <row r="924" spans="1:3" ht="23">
+      <c r="A924" s="4"/>
+      <c r="B924" s="5"/>
+      <c r="C924" s="6"/>
+    </row>
+    <row r="925" spans="1:3" ht="23">
+      <c r="A925" s="4"/>
+      <c r="B925" s="5"/>
+      <c r="C925" s="6"/>
+    </row>
+    <row r="926" spans="1:3" ht="23">
+      <c r="A926" s="4"/>
+      <c r="B926" s="5"/>
+      <c r="C926" s="6"/>
+    </row>
+    <row r="927" spans="1:3" ht="23">
+      <c r="A927" s="4"/>
+      <c r="B927" s="5"/>
+      <c r="C927" s="6"/>
+    </row>
+    <row r="928" spans="1:3" ht="23">
+      <c r="A928" s="4"/>
+      <c r="B928" s="5"/>
+      <c r="C928" s="6"/>
+    </row>
+    <row r="929" spans="1:3" ht="23">
+      <c r="A929" s="4"/>
+      <c r="B929" s="5"/>
+      <c r="C929" s="6"/>
+    </row>
+    <row r="930" spans="1:3" ht="23">
+      <c r="A930" s="4"/>
+      <c r="B930" s="5"/>
+      <c r="C930" s="6"/>
+    </row>
+    <row r="931" spans="1:3" ht="23">
+      <c r="A931" s="4"/>
+      <c r="B931" s="5"/>
+      <c r="C931" s="6"/>
+    </row>
+    <row r="932" spans="1:3" ht="23">
+      <c r="A932" s="4"/>
+      <c r="B932" s="5"/>
+      <c r="C932" s="6"/>
+    </row>
+    <row r="933" spans="1:3" ht="23">
+      <c r="A933" s="4"/>
+      <c r="B933" s="5"/>
+      <c r="C933" s="6"/>
+    </row>
+    <row r="934" spans="1:3" ht="23">
+      <c r="A934" s="4"/>
+      <c r="B934" s="5"/>
+      <c r="C934" s="6"/>
+    </row>
+    <row r="935" spans="1:3" ht="23">
+      <c r="A935" s="4"/>
+      <c r="B935" s="5"/>
+      <c r="C935" s="6"/>
+    </row>
+    <row r="936" spans="1:3" ht="23">
+      <c r="A936" s="4"/>
+      <c r="B936" s="5"/>
+      <c r="C936" s="6"/>
+    </row>
+    <row r="937" spans="1:3" ht="23">
+      <c r="A937" s="4"/>
+      <c r="B937" s="5"/>
+      <c r="C937" s="6"/>
+    </row>
+    <row r="938" spans="1:3" ht="23">
+      <c r="A938" s="4"/>
+      <c r="B938" s="5"/>
+      <c r="C938" s="6"/>
+    </row>
+    <row r="939" spans="1:3" ht="23">
+      <c r="A939" s="4"/>
+      <c r="B939" s="5"/>
+      <c r="C939" s="6"/>
+    </row>
+    <row r="940" spans="1:3" ht="23">
+      <c r="A940" s="4"/>
+      <c r="B940" s="5"/>
+      <c r="C940" s="6"/>
+    </row>
+    <row r="941" spans="1:3" ht="23">
+      <c r="A941" s="4"/>
+      <c r="B941" s="5"/>
+      <c r="C941" s="6"/>
+    </row>
+    <row r="942" spans="1:3" ht="23">
+      <c r="A942" s="4"/>
+      <c r="B942" s="5"/>
+      <c r="C942" s="6"/>
+    </row>
+    <row r="943" spans="1:3" ht="23">
+      <c r="A943" s="4"/>
+      <c r="B943" s="5"/>
+      <c r="C943" s="6"/>
+    </row>
+    <row r="944" spans="1:3" ht="23">
+      <c r="A944" s="4"/>
+      <c r="B944" s="5"/>
+      <c r="C944" s="6"/>
+    </row>
+    <row r="945" spans="1:3" ht="23">
+      <c r="A945" s="4"/>
+      <c r="B945" s="5"/>
+      <c r="C945" s="6"/>
+    </row>
+    <row r="946" spans="1:3" ht="23">
+      <c r="A946" s="4"/>
+      <c r="B946" s="5"/>
+      <c r="C946" s="6"/>
+    </row>
+    <row r="947" spans="1:3" ht="23">
+      <c r="A947" s="4"/>
+      <c r="B947" s="5"/>
+      <c r="C947" s="6"/>
+    </row>
+    <row r="948" spans="1:3" ht="23">
+      <c r="A948" s="4"/>
+      <c r="B948" s="5"/>
+      <c r="C948" s="6"/>
+    </row>
+    <row r="949" spans="1:3" ht="23">
+      <c r="A949" s="4"/>
+      <c r="B949" s="5"/>
+      <c r="C949" s="6"/>
+    </row>
+    <row r="950" spans="1:3" ht="23">
+      <c r="A950" s="4"/>
+      <c r="B950" s="5"/>
+      <c r="C950" s="6"/>
+    </row>
+    <row r="951" spans="1:3" ht="23">
+      <c r="A951" s="4"/>
+      <c r="B951" s="5"/>
+      <c r="C951" s="6"/>
+    </row>
+    <row r="952" spans="1:3" ht="23">
+      <c r="A952" s="4"/>
+      <c r="B952" s="5"/>
+      <c r="C952" s="6"/>
+    </row>
+    <row r="953" spans="1:3" ht="23">
+      <c r="A953" s="4"/>
+      <c r="B953" s="5"/>
+      <c r="C953" s="6"/>
+    </row>
+    <row r="954" spans="1:3" ht="23">
+      <c r="A954" s="4"/>
+      <c r="B954" s="5"/>
+      <c r="C954" s="6"/>
+    </row>
+    <row r="955" spans="1:3" ht="23">
+      <c r="A955" s="4"/>
+      <c r="B955" s="5"/>
+      <c r="C955" s="6"/>
+    </row>
+    <row r="956" spans="1:3" ht="23">
+      <c r="A956" s="4"/>
+      <c r="B956" s="5"/>
+      <c r="C956" s="6"/>
+    </row>
+    <row r="957" spans="1:3" ht="23">
+      <c r="A957" s="4"/>
+      <c r="B957" s="5"/>
+      <c r="C957" s="6"/>
+    </row>
+    <row r="958" spans="1:3" ht="23">
+      <c r="A958" s="4"/>
+      <c r="B958" s="5"/>
+      <c r="C958" s="6"/>
+    </row>
+    <row r="959" spans="1:3" ht="23">
+      <c r="A959" s="4"/>
+      <c r="B959" s="5"/>
+      <c r="C959" s="6"/>
+    </row>
+    <row r="960" spans="1:3" ht="23">
+      <c r="A960" s="4"/>
+      <c r="B960" s="5"/>
+      <c r="C960" s="6"/>
+    </row>
+    <row r="961" spans="1:3" ht="23">
+      <c r="A961" s="4"/>
+      <c r="B961" s="5"/>
+      <c r="C961" s="6"/>
+    </row>
+    <row r="962" spans="1:3" ht="23">
+      <c r="A962" s="4"/>
+      <c r="B962" s="5"/>
+      <c r="C962" s="6"/>
+    </row>
+    <row r="963" spans="1:3" ht="23">
+      <c r="A963" s="4"/>
+      <c r="B963" s="5"/>
+      <c r="C963" s="6"/>
+    </row>
+    <row r="964" spans="1:3" ht="23">
+      <c r="A964" s="4"/>
+      <c r="B964" s="5"/>
+      <c r="C964" s="6"/>
+    </row>
+    <row r="965" spans="1:3" ht="23">
+      <c r="A965" s="4"/>
+      <c r="B965" s="5"/>
+      <c r="C965" s="6"/>
+    </row>
+    <row r="966" spans="1:3" ht="23">
+      <c r="A966" s="4"/>
+      <c r="B966" s="5"/>
+      <c r="C966" s="6"/>
+    </row>
+    <row r="967" spans="1:3" ht="23">
+      <c r="A967" s="4"/>
+      <c r="B967" s="5"/>
+      <c r="C967" s="6"/>
+    </row>
+    <row r="968" spans="1:3" ht="23">
+      <c r="A968" s="4"/>
+      <c r="B968" s="5"/>
+      <c r="C968" s="6"/>
+    </row>
+    <row r="969" spans="1:3" ht="23">
+      <c r="A969" s="4"/>
+      <c r="B969" s="5"/>
+      <c r="C969" s="6"/>
+    </row>
+    <row r="970" spans="1:3" ht="23">
+      <c r="A970" s="4"/>
+      <c r="B970" s="5"/>
+      <c r="C970" s="6"/>
+    </row>
+    <row r="971" spans="1:3" ht="23">
+      <c r="A971" s="4"/>
+      <c r="B971" s="5"/>
+      <c r="C971" s="6"/>
+    </row>
+    <row r="972" spans="1:3" ht="23">
+      <c r="A972" s="4"/>
+      <c r="B972" s="5"/>
+      <c r="C972" s="6"/>
+    </row>
+    <row r="973" spans="1:3" ht="23">
+      <c r="A973" s="4"/>
+      <c r="B973" s="5"/>
+      <c r="C973" s="6"/>
+    </row>
+    <row r="974" spans="1:3" ht="23">
+      <c r="A974" s="4"/>
+      <c r="B974" s="5"/>
+      <c r="C974" s="6"/>
+    </row>
+    <row r="975" spans="1:3" ht="23">
+      <c r="A975" s="4"/>
+      <c r="B975" s="5"/>
+      <c r="C975" s="6"/>
+    </row>
+    <row r="976" spans="1:3" ht="23">
+      <c r="A976" s="4"/>
+      <c r="B976" s="5"/>
+      <c r="C976" s="6"/>
+    </row>
+    <row r="977" spans="1:3" ht="23">
+      <c r="A977" s="4"/>
+      <c r="B977" s="5"/>
+      <c r="C977" s="6"/>
+    </row>
+    <row r="978" spans="1:3" ht="23">
+      <c r="A978" s="4"/>
+      <c r="B978" s="5"/>
+      <c r="C978" s="6"/>
+    </row>
+    <row r="979" spans="1:3" ht="23">
+      <c r="A979" s="4"/>
+      <c r="B979" s="5"/>
+      <c r="C979" s="6"/>
+    </row>
+    <row r="980" spans="1:3" ht="23">
+      <c r="A980" s="4"/>
+      <c r="B980" s="5"/>
+      <c r="C980" s="6"/>
+    </row>
+    <row r="981" spans="1:3" ht="23">
+      <c r="A981" s="4"/>
+      <c r="B981" s="5"/>
+      <c r="C981" s="6"/>
+    </row>
+    <row r="982" spans="1:3" ht="23">
+      <c r="A982" s="4"/>
+      <c r="B982" s="5"/>
+      <c r="C982" s="6"/>
+    </row>
+    <row r="983" spans="1:3" ht="23">
+      <c r="A983" s="4"/>
+      <c r="B983" s="5"/>
+      <c r="C983" s="6"/>
+    </row>
+    <row r="984" spans="1:3" ht="23">
+      <c r="A984" s="4"/>
+      <c r="B984" s="5"/>
+      <c r="C984" s="6"/>
+    </row>
+    <row r="985" spans="1:3" ht="23">
+      <c r="A985" s="4"/>
+      <c r="B985" s="5"/>
+      <c r="C985" s="6"/>
+    </row>
+    <row r="986" spans="1:3" ht="23">
+      <c r="A986" s="4"/>
+      <c r="B986" s="5"/>
+      <c r="C986" s="6"/>
+    </row>
+    <row r="987" spans="1:3" ht="23">
+      <c r="A987" s="4"/>
+      <c r="B987" s="5"/>
+      <c r="C987" s="6"/>
+    </row>
+    <row r="988" spans="1:3" ht="23">
+      <c r="A988" s="4"/>
+      <c r="B988" s="5"/>
+      <c r="C988" s="6"/>
+    </row>
+    <row r="989" spans="1:3" ht="23">
+      <c r="A989" s="4"/>
+      <c r="B989" s="5"/>
+      <c r="C989" s="6"/>
+    </row>
+    <row r="990" spans="1:3" ht="23">
+      <c r="A990" s="4"/>
+      <c r="B990" s="5"/>
+      <c r="C990" s="6"/>
+    </row>
+    <row r="991" spans="1:3" ht="23">
+      <c r="A991" s="4"/>
+      <c r="B991" s="5"/>
+      <c r="C991" s="6"/>
+    </row>
+    <row r="992" spans="1:3" ht="23">
+      <c r="A992" s="4"/>
+      <c r="B992" s="5"/>
+      <c r="C992" s="6"/>
+    </row>
+    <row r="993" spans="1:3" ht="23">
+      <c r="A993" s="4"/>
+      <c r="B993" s="5"/>
+      <c r="C993" s="6"/>
+    </row>
+    <row r="994" spans="1:3" ht="23">
+      <c r="A994" s="4"/>
+      <c r="B994" s="5"/>
+      <c r="C994" s="6"/>
+    </row>
+    <row r="995" spans="1:3" ht="23">
+      <c r="A995" s="4"/>
+      <c r="B995" s="5"/>
+      <c r="C995" s="6"/>
+    </row>
+    <row r="996" spans="1:3" ht="23">
+      <c r="A996" s="4"/>
+      <c r="B996" s="5"/>
+      <c r="C996" s="6"/>
+    </row>
+    <row r="997" spans="1:3" ht="23">
+      <c r="A997" s="4"/>
+      <c r="B997" s="5"/>
+      <c r="C997" s="6"/>
+    </row>
+    <row r="998" spans="1:3" ht="23">
+      <c r="A998" s="4"/>
+      <c r="B998" s="5"/>
+      <c r="C998" s="6"/>
+    </row>
+    <row r="999" spans="1:3" ht="23">
+      <c r="A999" s="4"/>
+      <c r="B999" s="5"/>
+      <c r="C999" s="6"/>
+    </row>
+    <row r="1000" spans="1:3" ht="23">
+      <c r="A1000" s="4"/>
+      <c r="B1000" s="5"/>
+      <c r="C1000" s="6"/>
+    </row>
+    <row r="1001" spans="1:3" ht="23">
+      <c r="A1001" s="4"/>
+      <c r="B1001" s="5"/>
+      <c r="C1001" s="6"/>
+    </row>
+    <row r="1002" spans="1:3" ht="23">
+      <c r="A1002" s="4"/>
+      <c r="B1002" s="5"/>
+      <c r="C1002" s="6"/>
+    </row>
+    <row r="1003" spans="1:3" ht="23">
+      <c r="A1003" s="4"/>
+      <c r="B1003" s="5"/>
+      <c r="C1003" s="6"/>
+    </row>
+    <row r="1004" spans="1:3" ht="23">
+      <c r="A1004" s="4"/>
+      <c r="B1004" s="5"/>
+      <c r="C1004" s="6"/>
+    </row>
+    <row r="1005" spans="1:3" ht="23">
+      <c r="A1005" s="4"/>
+      <c r="B1005" s="5"/>
+      <c r="C1005" s="6"/>
+    </row>
+    <row r="1006" spans="1:3" ht="23">
+      <c r="A1006" s="4"/>
+      <c r="B1006" s="5"/>
+      <c r="C1006" s="6"/>
+    </row>
+    <row r="1007" spans="1:3" ht="23">
+      <c r="A1007" s="4"/>
+      <c r="B1007" s="5"/>
+      <c r="C1007" s="6"/>
+    </row>
+    <row r="1008" spans="1:3" ht="23">
+      <c r="A1008" s="4"/>
+      <c r="B1008" s="5"/>
+      <c r="C1008" s="6"/>
+    </row>
+    <row r="1009" spans="1:3" ht="23">
+      <c r="A1009" s="4"/>
+      <c r="B1009" s="5"/>
+      <c r="C1009" s="6"/>
+    </row>
+    <row r="1010" spans="1:3" ht="23">
+      <c r="A1010" s="4"/>
+      <c r="B1010" s="5"/>
+      <c r="C1010" s="6"/>
+    </row>
+    <row r="1011" spans="1:3" ht="23">
+      <c r="A1011" s="4"/>
+      <c r="B1011" s="5"/>
+      <c r="C1011" s="6"/>
+    </row>
+    <row r="1012" spans="1:3" ht="23">
+      <c r="A1012" s="4"/>
+      <c r="B1012" s="5"/>
+      <c r="C1012" s="6"/>
+    </row>
+    <row r="1013" spans="1:3" ht="23">
+      <c r="A1013" s="4"/>
+      <c r="B1013" s="5"/>
+      <c r="C1013" s="6"/>
+    </row>
+    <row r="1014" spans="1:3" ht="23">
+      <c r="A1014" s="4"/>
+      <c r="B1014" s="5"/>
+      <c r="C1014" s="6"/>
+    </row>
+    <row r="1015" spans="1:3" ht="23">
+      <c r="A1015" s="4"/>
+      <c r="B1015" s="5"/>
+      <c r="C1015" s="6"/>
+    </row>
+    <row r="1016" spans="1:3" ht="23">
+      <c r="A1016" s="4"/>
+      <c r="B1016" s="5"/>
+      <c r="C1016" s="6"/>
+    </row>
+    <row r="1017" spans="1:3" ht="23">
+      <c r="A1017" s="4"/>
+      <c r="B1017" s="5"/>
+      <c r="C1017" s="6"/>
+    </row>
+    <row r="1018" spans="1:3" ht="23">
+      <c r="A1018" s="4"/>
+      <c r="B1018" s="5"/>
+      <c r="C1018" s="6"/>
+    </row>
+    <row r="1019" spans="1:3" ht="23">
+      <c r="A1019" s="4"/>
+      <c r="B1019" s="5"/>
+      <c r="C1019" s="6"/>
+    </row>
+    <row r="1020" spans="1:3" ht="23">
+      <c r="A1020" s="4"/>
+      <c r="B1020" s="5"/>
+      <c r="C1020" s="6"/>
+    </row>
+    <row r="1021" spans="1:3" ht="23">
+      <c r="A1021" s="4"/>
+      <c r="B1021" s="5"/>
+      <c r="C1021" s="6"/>
+    </row>
+    <row r="1022" spans="1:3" ht="23">
+      <c r="A1022" s="4"/>
+      <c r="B1022" s="5"/>
+      <c r="C1022" s="6"/>
+    </row>
+    <row r="1023" spans="1:3" ht="23">
+      <c r="A1023" s="4"/>
+      <c r="B1023" s="5"/>
+      <c r="C1023" s="6"/>
+    </row>
+    <row r="1024" spans="1:3" ht="23">
+      <c r="A1024" s="4"/>
+      <c r="B1024" s="5"/>
+      <c r="C1024" s="6"/>
+    </row>
+    <row r="1025" spans="1:3" ht="23">
+      <c r="A1025" s="4"/>
+      <c r="B1025" s="5"/>
+      <c r="C1025" s="6"/>
+    </row>
+    <row r="1026" spans="1:3" ht="23">
+      <c r="A1026" s="4"/>
+      <c r="B1026" s="5"/>
+      <c r="C1026" s="6"/>
+    </row>
+    <row r="1027" spans="1:3" ht="23">
+      <c r="A1027" s="4"/>
+      <c r="B1027" s="5"/>
+      <c r="C1027" s="6"/>
+    </row>
+    <row r="1028" spans="1:3" ht="23">
+      <c r="A1028" s="4"/>
+      <c r="B1028" s="5"/>
+      <c r="C1028" s="6"/>
+    </row>
+    <row r="1029" spans="1:3" ht="23">
+      <c r="A1029" s="4"/>
+      <c r="B1029" s="5"/>
+      <c r="C1029" s="6"/>
+    </row>
+    <row r="1030" spans="1:3" ht="23">
+      <c r="A1030" s="4"/>
+      <c r="B1030" s="5"/>
+      <c r="C1030" s="6"/>
+    </row>
+    <row r="1031" spans="1:3" ht="23">
+      <c r="A1031" s="4"/>
+      <c r="B1031" s="5"/>
+      <c r="C1031" s="6"/>
+    </row>
+    <row r="1032" spans="1:3" ht="23">
+      <c r="A1032" s="4"/>
+      <c r="B1032" s="5"/>
+      <c r="C1032" s="6"/>
+    </row>
+    <row r="1033" spans="1:3" ht="23">
+      <c r="A1033" s="4"/>
+      <c r="B1033" s="5"/>
+      <c r="C1033" s="6"/>
+    </row>
+    <row r="1034" spans="1:3" ht="23">
+      <c r="A1034" s="4"/>
+      <c r="B1034" s="5"/>
+      <c r="C1034" s="6"/>
+    </row>
+    <row r="1035" spans="1:3" ht="23">
+      <c r="A1035" s="4"/>
+      <c r="B1035" s="5"/>
+      <c r="C1035" s="6"/>
+    </row>
+    <row r="1036" spans="1:3" ht="23">
+      <c r="A1036" s="4"/>
+      <c r="B1036" s="5"/>
+      <c r="C1036" s="6"/>
+    </row>
+    <row r="1037" spans="1:3" ht="23">
+      <c r="A1037" s="4"/>
+      <c r="B1037" s="5"/>
+      <c r="C1037" s="6"/>
+    </row>
+    <row r="1038" spans="1:3" ht="23">
+      <c r="A1038" s="4"/>
+      <c r="B1038" s="5"/>
+      <c r="C1038" s="6"/>
+    </row>
+    <row r="1039" spans="1:3" ht="23">
+      <c r="A1039" s="4"/>
+      <c r="B1039" s="5"/>
+      <c r="C1039" s="6"/>
+    </row>
+    <row r="1040" spans="1:3" ht="23">
+      <c r="A1040" s="4"/>
+      <c r="B1040" s="5"/>
+      <c r="C1040" s="6"/>
+    </row>
+    <row r="1041" spans="1:3" ht="23">
+      <c r="A1041" s="4"/>
+      <c r="B1041" s="5"/>
+      <c r="C1041" s="6"/>
+    </row>
+    <row r="1042" spans="1:3" ht="23">
+      <c r="A1042" s="4"/>
+      <c r="B1042" s="5"/>
+      <c r="C1042" s="6"/>
+    </row>
+    <row r="1043" spans="1:3" ht="23">
+      <c r="A1043" s="4"/>
+      <c r="B1043" s="5"/>
+      <c r="C1043" s="6"/>
+    </row>
+    <row r="1044" spans="1:3" ht="23">
+      <c r="A1044" s="4"/>
+      <c r="B1044" s="5"/>
+      <c r="C1044" s="6"/>
+    </row>
+    <row r="1045" spans="1:3" ht="23">
+      <c r="A1045" s="4"/>
+      <c r="B1045" s="5"/>
+      <c r="C1045" s="6"/>
+    </row>
+    <row r="1046" spans="1:3" ht="23">
+      <c r="A1046" s="4"/>
+      <c r="B1046" s="5"/>
+      <c r="C1046" s="6"/>
+    </row>
+    <row r="1047" spans="1:3" ht="23">
+      <c r="A1047" s="4"/>
+      <c r="B1047" s="5"/>
+      <c r="C1047" s="6"/>
+    </row>
+    <row r="1048" spans="1:3" ht="23">
+      <c r="A1048" s="4"/>
+      <c r="B1048" s="5"/>
+      <c r="C1048" s="6"/>
+    </row>
+    <row r="1049" spans="1:3" ht="23">
+      <c r="A1049" s="4"/>
+      <c r="B1049" s="5"/>
+      <c r="C1049" s="6"/>
+    </row>
+    <row r="1050" spans="1:3" ht="23">
+      <c r="A1050" s="4"/>
+      <c r="B1050" s="5"/>
+      <c r="C1050" s="6"/>
+    </row>
+    <row r="1051" spans="1:3" ht="23">
+      <c r="A1051" s="4"/>
+      <c r="B1051" s="5"/>
+      <c r="C1051" s="6"/>
+    </row>
+    <row r="1052" spans="1:3" ht="23">
+      <c r="A1052" s="4"/>
+      <c r="B1052" s="5"/>
+      <c r="C1052" s="6"/>
+    </row>
+    <row r="1053" spans="1:3" ht="23">
+      <c r="A1053" s="4"/>
+      <c r="B1053" s="5"/>
+      <c r="C1053" s="6"/>
+    </row>
+    <row r="1054" spans="1:3" ht="23">
+      <c r="A1054" s="4"/>
+      <c r="B1054" s="5"/>
+      <c r="C1054" s="6"/>
+    </row>
+    <row r="1055" spans="1:3" ht="23">
+      <c r="A1055" s="4"/>
+      <c r="B1055" s="5"/>
+      <c r="C1055" s="6"/>
+    </row>
+    <row r="1056" spans="1:3" ht="23">
+      <c r="A1056" s="4"/>
+      <c r="B1056" s="5"/>
+      <c r="C1056" s="6"/>
+    </row>
+    <row r="1057" spans="1:3" ht="23">
+      <c r="A1057" s="4"/>
+      <c r="B1057" s="5"/>
+      <c r="C1057" s="6"/>
+    </row>
+    <row r="1058" spans="1:3" ht="23">
+      <c r="A1058" s="4"/>
+      <c r="B1058" s="5"/>
+      <c r="C1058" s="6"/>
+    </row>
+    <row r="1059" spans="1:3" ht="23">
+      <c r="A1059" s="4"/>
+      <c r="B1059" s="5"/>
+      <c r="C1059" s="6"/>
+    </row>
+    <row r="1060" spans="1:3" ht="23">
+      <c r="A1060" s="4"/>
+      <c r="B1060" s="5"/>
+      <c r="C1060" s="6"/>
+    </row>
+    <row r="1061" spans="1:3" ht="23">
+      <c r="A1061" s="4"/>
+      <c r="B1061" s="5"/>
+      <c r="C1061" s="6"/>
+    </row>
+    <row r="1062" spans="1:3" ht="23">
+      <c r="A1062" s="4"/>
+      <c r="B1062" s="5"/>
+      <c r="C1062" s="6"/>
+    </row>
+    <row r="1063" spans="1:3" ht="23">
+      <c r="A1063" s="4"/>
+      <c r="B1063" s="5"/>
+      <c r="C1063" s="6"/>
+    </row>
+    <row r="1064" spans="1:3" ht="23">
+      <c r="A1064" s="4"/>
+      <c r="B1064" s="5"/>
+      <c r="C1064" s="6"/>
+    </row>
+    <row r="1065" spans="1:3" ht="23">
+      <c r="A1065" s="4"/>
+      <c r="B1065" s="5"/>
+      <c r="C1065" s="6"/>
+    </row>
+    <row r="1066" spans="1:3" ht="23">
+      <c r="A1066" s="4"/>
+      <c r="B1066" s="5"/>
+      <c r="C1066" s="6"/>
+    </row>
+    <row r="1067" spans="1:3" ht="23">
+      <c r="A1067" s="4"/>
+      <c r="B1067" s="5"/>
+      <c r="C1067" s="6"/>
+    </row>
+    <row r="1068" spans="1:3" ht="23">
+      <c r="A1068" s="4"/>
+      <c r="B1068" s="5"/>
+      <c r="C1068" s="6"/>
+    </row>
+    <row r="1069" spans="1:3" ht="23">
+      <c r="A1069" s="4"/>
+      <c r="B1069" s="5"/>
+      <c r="C1069" s="6"/>
+    </row>
+    <row r="1070" spans="1:3" ht="23">
+      <c r="A1070" s="4"/>
+      <c r="B1070" s="5"/>
+      <c r="C1070" s="6"/>
+    </row>
+    <row r="1071" spans="1:3" ht="23">
+      <c r="A1071" s="4"/>
+      <c r="B1071" s="5"/>
+      <c r="C1071" s="6"/>
+    </row>
+    <row r="1072" spans="1:3" ht="23">
+      <c r="A1072" s="4"/>
+      <c r="B1072" s="5"/>
+      <c r="C1072" s="6"/>
+    </row>
+    <row r="1073" spans="1:3" ht="23">
+      <c r="A1073" s="4"/>
+      <c r="B1073" s="5"/>
+      <c r="C1073" s="6"/>
+    </row>
+    <row r="1074" spans="1:3" ht="23">
+      <c r="A1074" s="4"/>
+      <c r="B1074" s="5"/>
+      <c r="C1074" s="6"/>
+    </row>
+    <row r="1075" spans="1:3" ht="23">
+      <c r="A1075" s="4"/>
+      <c r="B1075" s="5"/>
+      <c r="C1075" s="6"/>
+    </row>
+    <row r="1076" spans="1:3" ht="23">
+      <c r="A1076" s="4"/>
+      <c r="B1076" s="5"/>
+      <c r="C1076" s="6"/>
+    </row>
+    <row r="1077" spans="1:3" ht="23">
+      <c r="A1077" s="4"/>
+      <c r="B1077" s="5"/>
+      <c r="C1077" s="6"/>
+    </row>
+    <row r="1078" spans="1:3" ht="23">
+      <c r="A1078" s="4"/>
+      <c r="B1078" s="5"/>
+      <c r="C1078" s="6"/>
+    </row>
+    <row r="1079" spans="1:3" ht="23">
+      <c r="A1079" s="4"/>
+      <c r="B1079" s="5"/>
+      <c r="C1079" s="6"/>
+    </row>
+    <row r="1080" spans="1:3" ht="23">
+      <c r="A1080" s="4"/>
+      <c r="B1080" s="5"/>
+      <c r="C1080" s="6"/>
+    </row>
+    <row r="1081" spans="1:3" ht="23">
+      <c r="A1081" s="4"/>
+      <c r="B1081" s="5"/>
+      <c r="C1081" s="6"/>
+    </row>
+    <row r="1082" spans="1:3" ht="23">
+      <c r="A1082" s="4"/>
+      <c r="B1082" s="5"/>
+      <c r="C1082" s="6"/>
+    </row>
+    <row r="1083" spans="1:3" ht="23">
+      <c r="A1083" s="4"/>
+      <c r="B1083" s="5"/>
+      <c r="C1083" s="6"/>
+    </row>
+    <row r="1084" spans="1:3" ht="23">
+      <c r="A1084" s="4"/>
+      <c r="B1084" s="5"/>
+      <c r="C1084" s="6"/>
+    </row>
+    <row r="1085" spans="1:3" ht="23">
+      <c r="A1085" s="4"/>
+      <c r="B1085" s="5"/>
+      <c r="C1085" s="6"/>
+    </row>
+    <row r="1086" spans="1:3" ht="23">
+      <c r="A1086" s="4"/>
+      <c r="B1086" s="5"/>
+      <c r="C1086" s="6"/>
+    </row>
+    <row r="1087" spans="1:3" ht="23">
+      <c r="A1087" s="4"/>
+      <c r="B1087" s="5"/>
+      <c r="C1087" s="6"/>
+    </row>
+    <row r="1088" spans="1:3" ht="23">
+      <c r="A1088" s="4"/>
+      <c r="B1088" s="5"/>
+      <c r="C1088" s="6"/>
+    </row>
+    <row r="1089" spans="1:3" ht="23">
+      <c r="A1089" s="4"/>
+      <c r="B1089" s="5"/>
+      <c r="C1089" s="6"/>
+    </row>
+    <row r="1090" spans="1:3" ht="23">
+      <c r="A1090" s="4"/>
+      <c r="B1090" s="5"/>
+      <c r="C1090" s="6"/>
+    </row>
+    <row r="1091" spans="1:3" ht="23">
+      <c r="A1091" s="4"/>
+      <c r="B1091" s="5"/>
+      <c r="C1091" s="6"/>
+    </row>
+    <row r="1092" spans="1:3" ht="23">
+      <c r="A1092" s="4"/>
+      <c r="B1092" s="5"/>
+      <c r="C1092" s="6"/>
+    </row>
+    <row r="1093" spans="1:3" ht="23">
+      <c r="A1093" s="4"/>
+      <c r="B1093" s="5"/>
+      <c r="C1093" s="6"/>
+    </row>
+    <row r="1094" spans="1:3" ht="23">
+      <c r="A1094" s="4"/>
+      <c r="B1094" s="5"/>
+      <c r="C1094" s="6"/>
+    </row>
+    <row r="1095" spans="1:3" ht="23">
+      <c r="A1095" s="4"/>
+      <c r="B1095" s="5"/>
+      <c r="C1095" s="6"/>
+    </row>
+    <row r="1096" spans="1:3" ht="23">
+      <c r="A1096" s="4"/>
+      <c r="B1096" s="5"/>
+      <c r="C1096" s="6"/>
+    </row>
+    <row r="1097" spans="1:3" ht="23">
+      <c r="A1097" s="4"/>
+      <c r="B1097" s="5"/>
+      <c r="C1097" s="6"/>
+    </row>
+    <row r="1098" spans="1:3" ht="23">
+      <c r="A1098" s="4"/>
+      <c r="B1098" s="5"/>
+      <c r="C1098" s="6"/>
+    </row>
+    <row r="1099" spans="1:3" ht="23">
+      <c r="A1099" s="4"/>
+      <c r="B1099" s="5"/>
+      <c r="C1099" s="6"/>
+    </row>
+    <row r="1100" spans="1:3" ht="23">
+      <c r="A1100" s="4"/>
+      <c r="B1100" s="5"/>
+      <c r="C1100" s="6"/>
+    </row>
+    <row r="1101" spans="1:3" ht="23">
+      <c r="A1101" s="4"/>
+      <c r="B1101" s="5"/>
+      <c r="C1101" s="6"/>
+    </row>
+    <row r="1102" spans="1:3" ht="23">
+      <c r="A1102" s="4"/>
+      <c r="B1102" s="5"/>
+      <c r="C1102" s="6"/>
+    </row>
+    <row r="1103" spans="1:3" ht="23">
+      <c r="A1103" s="4"/>
+      <c r="B1103" s="5"/>
+      <c r="C1103" s="6"/>
+    </row>
+    <row r="1104" spans="1:3" ht="23">
+      <c r="A1104" s="4"/>
+      <c r="B1104" s="5"/>
+      <c r="C1104" s="6"/>
+    </row>
+    <row r="1105" spans="1:3" ht="23">
+      <c r="A1105" s="4"/>
+      <c r="B1105" s="5"/>
+      <c r="C1105" s="6"/>
+    </row>
+    <row r="1106" spans="1:3" ht="23">
+      <c r="A1106" s="4"/>
+      <c r="B1106" s="5"/>
+      <c r="C1106" s="6"/>
+    </row>
+    <row r="1107" spans="1:3" ht="23">
+      <c r="A1107" s="4"/>
+      <c r="B1107" s="5"/>
+      <c r="C1107" s="6"/>
+    </row>
+    <row r="1108" spans="1:3" ht="23">
+      <c r="A1108" s="4"/>
+      <c r="B1108" s="5"/>
+      <c r="C1108" s="6"/>
+    </row>
+    <row r="1109" spans="1:3" ht="23">
+      <c r="A1109" s="4"/>
+      <c r="B1109" s="5"/>
+      <c r="C1109" s="6"/>
+    </row>
+    <row r="1110" spans="1:3" ht="23">
+      <c r="A1110" s="4"/>
+      <c r="B1110" s="5"/>
+      <c r="C1110" s="6"/>
+    </row>
+    <row r="1111" spans="1:3" ht="23">
+      <c r="A1111" s="4"/>
+      <c r="B1111" s="5"/>
+      <c r="C1111" s="6"/>
+    </row>
+    <row r="1112" spans="1:3" ht="23">
+      <c r="A1112" s="4"/>
+      <c r="B1112" s="5"/>
+      <c r="C1112" s="6"/>
+    </row>
+    <row r="1113" spans="1:3" ht="23">
+      <c r="A1113" s="4"/>
+      <c r="B1113" s="5"/>
+      <c r="C1113" s="6"/>
+    </row>
+    <row r="1114" spans="1:3" ht="23">
+      <c r="A1114" s="4"/>
+      <c r="B1114" s="5"/>
+      <c r="C1114" s="6"/>
+    </row>
+    <row r="1115" spans="1:3" ht="23">
+      <c r="A1115" s="4"/>
+      <c r="B1115" s="5"/>
+      <c r="C1115" s="6"/>
+    </row>
+    <row r="1116" spans="1:3" ht="23">
+      <c r="A1116" s="4"/>
+      <c r="B1116" s="5"/>
+      <c r="C1116" s="6"/>
+    </row>
+    <row r="1117" spans="1:3" ht="23">
+      <c r="A1117" s="4"/>
+      <c r="B1117" s="5"/>
+      <c r="C1117" s="6"/>
+    </row>
+    <row r="1118" spans="1:3" ht="23">
+      <c r="A1118" s="4"/>
+      <c r="B1118" s="5"/>
+      <c r="C1118" s="6"/>
+    </row>
+    <row r="1119" spans="1:3" ht="23">
+      <c r="A1119" s="4"/>
+      <c r="B1119" s="5"/>
+      <c r="C1119" s="6"/>
+    </row>
+    <row r="1120" spans="1:3" ht="23">
+      <c r="A1120" s="4"/>
+      <c r="B1120" s="5"/>
+      <c r="C1120" s="6"/>
+    </row>
+    <row r="1121" spans="1:3" ht="23">
+      <c r="A1121" s="4"/>
+      <c r="B1121" s="5"/>
+      <c r="C1121" s="6"/>
+    </row>
+    <row r="1122" spans="1:3" ht="23">
+      <c r="A1122" s="4"/>
+      <c r="B1122" s="5"/>
+      <c r="C1122" s="6"/>
+    </row>
+    <row r="1123" spans="1:3" ht="23">
+      <c r="A1123" s="4"/>
+      <c r="B1123" s="5"/>
+      <c r="C1123" s="6"/>
+    </row>
+    <row r="1124" spans="1:3" ht="23">
+      <c r="A1124" s="4"/>
+      <c r="B1124" s="5"/>
+      <c r="C1124" s="6"/>
+    </row>
+    <row r="1125" spans="1:3" ht="23">
+      <c r="A1125" s="4"/>
+      <c r="B1125" s="5"/>
+      <c r="C1125" s="6"/>
+    </row>
+    <row r="1126" spans="1:3" ht="23">
+      <c r="A1126" s="4"/>
+      <c r="B1126" s="5"/>
+      <c r="C1126" s="6"/>
+    </row>
+    <row r="1127" spans="1:3" ht="23">
+      <c r="A1127" s="4"/>
+      <c r="B1127" s="5"/>
+      <c r="C1127" s="6"/>
+    </row>
+    <row r="1128" spans="1:3" ht="23">
+      <c r="A1128" s="4"/>
+      <c r="B1128" s="5"/>
+      <c r="C1128" s="6"/>
+    </row>
+    <row r="1129" spans="1:3" ht="23">
+      <c r="A1129" s="4"/>
+      <c r="B1129" s="5"/>
+      <c r="C1129" s="6"/>
+    </row>
+    <row r="1130" spans="1:3" ht="23">
+      <c r="A1130" s="4"/>
+      <c r="B1130" s="5"/>
+      <c r="C1130" s="6"/>
+    </row>
+    <row r="1131" spans="1:3" ht="23">
+      <c r="A1131" s="4"/>
+      <c r="B1131" s="5"/>
+      <c r="C1131" s="6"/>
+    </row>
+    <row r="1132" spans="1:3" ht="23">
+      <c r="A1132" s="4"/>
+      <c r="B1132" s="5"/>
+      <c r="C1132" s="6"/>
+    </row>
+    <row r="1133" spans="1:3" ht="23">
+      <c r="A1133" s="4"/>
+      <c r="B1133" s="5"/>
+      <c r="C1133" s="6"/>
+    </row>
+    <row r="1134" spans="1:3" ht="23">
+      <c r="A1134" s="4"/>
+      <c r="B1134" s="5"/>
+      <c r="C1134" s="6"/>
+    </row>
+    <row r="1135" spans="1:3" ht="23">
+      <c r="A1135" s="4"/>
+      <c r="B1135" s="5"/>
+      <c r="C1135" s="6"/>
+    </row>
+    <row r="1136" spans="1:3" ht="23">
+      <c r="A1136" s="4"/>
+      <c r="B1136" s="5"/>
+      <c r="C1136" s="6"/>
+    </row>
+    <row r="1137" spans="1:3" ht="23">
+      <c r="A1137" s="4"/>
+      <c r="B1137" s="5"/>
+      <c r="C1137" s="6"/>
+    </row>
+    <row r="1138" spans="1:3" ht="23">
+      <c r="A1138" s="4"/>
+      <c r="B1138" s="5"/>
+      <c r="C1138" s="6"/>
+    </row>
+    <row r="1139" spans="1:3" ht="23">
+      <c r="A1139" s="4"/>
+      <c r="B1139" s="5"/>
+      <c r="C1139" s="6"/>
+    </row>
+    <row r="1140" spans="1:3" ht="23">
+      <c r="A1140" s="4"/>
+      <c r="B1140" s="5"/>
+      <c r="C1140" s="6"/>
+    </row>
+    <row r="1141" spans="1:3" ht="23">
+      <c r="A1141" s="4"/>
+      <c r="B1141" s="5"/>
+      <c r="C1141" s="6"/>
+    </row>
+    <row r="1142" spans="1:3" ht="23">
+      <c r="A1142" s="4"/>
+      <c r="B1142" s="5"/>
+      <c r="C1142" s="6"/>
+    </row>
+    <row r="1143" spans="1:3" ht="23">
+      <c r="A1143" s="4"/>
+      <c r="B1143" s="5"/>
+      <c r="C1143" s="6"/>
+    </row>
+    <row r="1144" spans="1:3" ht="23">
+      <c r="A1144" s="4"/>
+      <c r="B1144" s="5"/>
+      <c r="C1144" s="6"/>
+    </row>
+    <row r="1145" spans="1:3" ht="23">
+      <c r="A1145" s="4"/>
+      <c r="B1145" s="5"/>
+      <c r="C1145" s="6"/>
+    </row>
+    <row r="1146" spans="1:3" ht="23">
+      <c r="A1146" s="4"/>
+      <c r="B1146" s="5"/>
+      <c r="C1146" s="6"/>
+    </row>
+    <row r="1147" spans="1:3" ht="23">
+      <c r="A1147" s="4"/>
+      <c r="B1147" s="5"/>
+      <c r="C1147" s="6"/>
+    </row>
+    <row r="1148" spans="1:3" ht="23">
+      <c r="A1148" s="4"/>
+      <c r="B1148" s="5"/>
+      <c r="C1148" s="6"/>
+    </row>
+    <row r="1149" spans="1:3" ht="23">
+      <c r="A1149" s="4"/>
+      <c r="B1149" s="5"/>
+      <c r="C1149" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11525,29 +14780,59 @@
       </c>
     </row>
     <row r="501" spans="1:3" ht="40" customHeight="1">
-      <c r="A501" s="4"/>
-      <c r="B501" s="5"/>
-      <c r="C501" s="5"/>
+      <c r="A501" s="4">
+        <v>46195</v>
+      </c>
+      <c r="B501" s="5">
+        <v>56.435632456249742</v>
+      </c>
+      <c r="C501" s="5">
+        <v>50.658026935398546</v>
+      </c>
     </row>
     <row r="502" spans="1:3" ht="40" customHeight="1">
-      <c r="A502" s="4"/>
-      <c r="B502" s="5"/>
-      <c r="C502" s="5"/>
+      <c r="A502" s="4">
+        <v>46196</v>
+      </c>
+      <c r="B502" s="5">
+        <v>58.129537801840478</v>
+      </c>
+      <c r="C502" s="5">
+        <v>49.272708945289914</v>
+      </c>
     </row>
     <row r="503" spans="1:3" ht="40" customHeight="1">
-      <c r="A503" s="4"/>
-      <c r="B503" s="5"/>
-      <c r="C503" s="5"/>
+      <c r="A503" s="4">
+        <v>46197</v>
+      </c>
+      <c r="B503" s="5">
+        <v>58.151509845031249</v>
+      </c>
+      <c r="C503" s="5">
+        <v>49.151627267642155</v>
+      </c>
     </row>
     <row r="504" spans="1:3" ht="40" customHeight="1">
-      <c r="A504" s="4"/>
-      <c r="B504" s="5"/>
-      <c r="C504" s="5"/>
+      <c r="A504" s="4">
+        <v>46198</v>
+      </c>
+      <c r="B504" s="5">
+        <v>58.342938446347183</v>
+      </c>
+      <c r="C504" s="5">
+        <v>49.080928525491558</v>
+      </c>
     </row>
     <row r="505" spans="1:3" ht="40" customHeight="1">
-      <c r="A505" s="4"/>
-      <c r="B505" s="5"/>
-      <c r="C505" s="5"/>
+      <c r="A505" s="4">
+        <v>46199</v>
+      </c>
+      <c r="B505" s="5">
+        <v>56.954339573931222</v>
+      </c>
+      <c r="C505" s="5">
+        <v>48.790877731924027</v>
+      </c>
     </row>
     <row r="506" spans="1:3" ht="40" customHeight="1">
       <c r="A506" s="4"/>
